--- a/1.xlsx
+++ b/1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$14</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="174">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -87,10 +87,13 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2603/0015</t>
-  </si>
-  <si>
-    <t>132KV_132 KV ASHTA IC CKT-1</t>
+    <t>MR2603/0024</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>132KV_132 KV ASHTA I/C CKT-2</t>
   </si>
   <si>
     <t>400KV_ASHTA4</t>
@@ -99,34 +102,40 @@
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>CONDUCTOR UPGRADATION WORK</t>
+    <t>conductor upgradation work HTLS</t>
   </si>
   <si>
     <t>04-03-2026 08:00:00</t>
   </si>
   <si>
-    <t>NITIN RESHWAL</t>
+    <t>05-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Nitin Reshwal</t>
   </si>
   <si>
     <t>9425804890</t>
   </si>
   <si>
-    <t>MR2603/0024</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>132KV_132 KV ASHTA I/C CKT-2</t>
-  </si>
-  <si>
-    <t>conductor upgradation work HTLS</t>
-  </si>
-  <si>
-    <t>05-03-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Nitin Reshwal</t>
+    <t>MR2603/0025</t>
+  </si>
+  <si>
+    <t>220KV_220 KV MAIN BUS -2</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>B PHASE JHA &amp;CLAMP 220 JABALPUR CKT -2</t>
+  </si>
+  <si>
+    <t>05-03-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>TOSHAN SINGH</t>
+  </si>
+  <si>
+    <t>9752605559</t>
   </si>
   <si>
     <t>Continuous</t>
@@ -183,6 +192,96 @@
     <t>9575074321</t>
   </si>
   <si>
+    <t>MR2603/0028</t>
+  </si>
+  <si>
+    <t>132KV_132 KV CHAMBAL - ELECTRONIC  COMPLEX LINE</t>
+  </si>
+  <si>
+    <t>132KV_INDORE CHAMBAL</t>
+  </si>
+  <si>
+    <t>BIRD GAURD INSTALLATION WORK AND OTHER MAINTANANCE</t>
+  </si>
+  <si>
+    <t>05-03-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>05-03-2026 17:30:00</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>9425801598</t>
+  </si>
+  <si>
+    <t>MR2603/0007</t>
+  </si>
+  <si>
+    <t>400KV_315 MVA ICT-3</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance.</t>
+  </si>
+  <si>
+    <t>06-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>ATUL PARADKAR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2602/0573</t>
+  </si>
+  <si>
+    <t>400KV_400kV 500MVA  ICT (CGL)</t>
+  </si>
+  <si>
+    <t>400KV_MANDSOUR4</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>400kV  500MVA  ICT (CGL) 400kV Center Break Iso.</t>
+  </si>
+  <si>
+    <t>06-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>CP Dhakad</t>
+  </si>
+  <si>
+    <t>7587951067</t>
+  </si>
+  <si>
+    <t>MR2603/0034</t>
+  </si>
+  <si>
+    <t>220KV_220 KV MUNGALIYA CHHAP -BHOPAL</t>
+  </si>
+  <si>
+    <t>220KV_MUGALIYACHAAP</t>
+  </si>
+  <si>
+    <t>MAINTANACE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>05-03-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>ANIL ACHARKATE  (AE)</t>
+  </si>
+  <si>
+    <t>7587951086</t>
+  </si>
+  <si>
     <t>MR2602/0478</t>
   </si>
   <si>
@@ -252,6 +351,24 @@
     <t>9789870318</t>
   </si>
   <si>
+    <t>MR2603/0011</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR-JULWANIA LINE (LINE# 3) ALONG WITH ONE OF THE BUS AND BUS COUPLER</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>09-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>NITINDEEP TAMRAKAR</t>
+  </si>
+  <si>
+    <t>7898703187</t>
+  </si>
+  <si>
     <t>MR2602/0587</t>
   </si>
   <si>
@@ -282,6 +399,36 @@
     <t>400KV_400 KV SSTPH-Pithampur ckt 2</t>
   </si>
   <si>
+    <t>MR2603/0008</t>
+  </si>
+  <si>
+    <t>132KV_132kv Rewa -Inter Connector ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_REWA</t>
+  </si>
+  <si>
+    <t>Modification/Shifting work of line</t>
+  </si>
+  <si>
+    <t>05-03-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Kumar Chaurasia</t>
+  </si>
+  <si>
+    <t>9425805081</t>
+  </si>
+  <si>
+    <t>MR2603/0029</t>
+  </si>
+  <si>
+    <t>132KV_132KV SOUTHZONE â¿¿ SATYASAI   LINE</t>
+  </si>
+  <si>
+    <t>132KV_SATYA SAI</t>
+  </si>
+  <si>
     <t>MR2602/0162</t>
   </si>
   <si>
@@ -291,9 +438,6 @@
     <t>220KV_SHUJALPUR</t>
   </si>
   <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
     <t>for bay Shifting       work for Add. 200 MVA</t>
   </si>
   <si>
@@ -306,55 +450,110 @@
     <t>9425802283</t>
   </si>
   <si>
+    <t>MR2603/0026</t>
+  </si>
+  <si>
+    <t>400KV_315MVA X-MER-Ist</t>
+  </si>
+  <si>
+    <t>400KV_UJJAIN4</t>
+  </si>
+  <si>
+    <t>pre monsoon maint.&amp; testing work</t>
+  </si>
+  <si>
+    <t>santosh chavrasia</t>
+  </si>
+  <si>
+    <t>9425804677</t>
+  </si>
+  <si>
     <t>sub ld</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>as per system requirement</t>
+  </si>
+  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>as per system availability</t>
-  </si>
-  <si>
-    <t>220KV-ITARSI-MP-ITARSI-2</t>
+    <t>ok, through sub ld, 220kv Daloda-Mandsaur ckt 1, 2 to be opened for laod management if required</t>
+  </si>
+  <si>
+    <t>ok, all the elements to be in service through main bus 1</t>
+  </si>
+  <si>
+    <t>ok, load drop scheme shall be implemented on 132kv Rewa -Inter Connector ckt-I to save the network in case of any tripping, EI aproval required while final charging</t>
+  </si>
+  <si>
+    <t>400KV/220KV SATNA-ICT-2</t>
+  </si>
+  <si>
+    <t>400KV-INDORE-UJJAIN-1</t>
+  </si>
+  <si>
+    <t>220KV-MORENA-SABALGARH-1</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-2</t>
+  </si>
+  <si>
+    <t>400KV/220KV</t>
+  </si>
+  <si>
+    <t>05-Mar-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
   </si>
   <si>
     <t>POWERGRID_WR2</t>
   </si>
   <si>
-    <t>For rectification of Wave trap jumper and AMP works.</t>
-  </si>
-  <si>
-    <t>400KV-INDORE-UJJAIN-1</t>
-  </si>
-  <si>
     <t>MP_SLDC</t>
   </si>
   <si>
+    <t xml:space="preserve">AMP Work, Dia to be kept open at both sides.
+</t>
+  </si>
+  <si>
+    <t>AMP Work, Dia to be kept open at both sides.</t>
+  </si>
+  <si>
     <t>FOR REPLACEMENT OF DAMAGED OPGW OF 400KV UJJAIN-INDORE HATUNIYA -1 BETWEEN LOCATION NO 101-99,95-93,86-89 AND 26-29</t>
   </si>
   <si>
-    <t>220KV-KHANDWA-CHHANERA-1</t>
-  </si>
-  <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
-  </si>
-  <si>
     <t> FOR RE-SAGGING WORK  IN  LOCATION 379-388, 388-397, 397-406, 406-418 &amp; 432-441, due to found low ground clearance</t>
   </si>
   <si>
-    <t>220KV-ANNUPUR-KOTMIKALA-2</t>
-  </si>
-  <si>
-    <t>shall be given in low load period</t>
-  </si>
-  <si>
-    <t>defered by site</t>
+    <t>deferred , as loading is high</t>
+  </si>
+  <si>
+    <t>deferred by site</t>
   </si>
   <si>
     <t>real time</t>
@@ -368,7 +567,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -398,20 +597,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,8 +615,20 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -484,11 +688,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -514,6 +768,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -522,10 +779,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -891,45 +1179,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="48.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="64.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="64.85546875" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="11" max="11" width="23.28515625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="30.5703125" customWidth="1"/>
+    <col min="13" max="13" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -979,7 +1267,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -997,138 +1285,138 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46083.672881944447</v>
+        <v>46084.5390162037</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="6">
-        <v>46085.75</v>
+        <v>23</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46084.5390162037</v>
+        <v>46085.391909722224</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="F6" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A13" si="0">A6+1</f>
+        <f t="shared" ref="A7:A28" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>46050.577592592592</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1137,450 +1425,876 @@
         <v>46082.494803240741</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46078.609456018516</v>
+        <v>46085.565428240741</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46082.600104166668</v>
+        <v>46083.529814814814</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>58</v>
+        <v>34</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46080.462106481478</v>
+        <v>46080.659583333334</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="J11" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46081.76353009259</v>
+        <v>46085.604085648149</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>31</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
+        <v>46078.609456018516</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46082.600104166668</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46080.462106481478</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46083.663414351853</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46081.76353009259</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
         <v>46081.765081018515</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46083.590208333335</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="22">
+        <v>46085.567546296297</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="23">
+        <v>46064.690474537034</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="23">
+        <v>46085.412129629629</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="I22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="J22" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="M22" s="18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21">
+        <v>291456</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="M23" s="24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <f>A13+1</f>
-        <v>10</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46064.690474537034</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="6">
-        <v>46085.375</v>
-      </c>
-      <c r="J15" s="6">
-        <v>46085.75</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="6">
-        <v>46085.291666666664</v>
-      </c>
-      <c r="J16" s="6">
-        <v>46085.791666666664</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="6" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21">
+        <v>291712</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" s="24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21">
+        <v>291163</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="21">
+        <v>400</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J25" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="M25" s="24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="J17" s="6">
-        <v>46085.75</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="6">
-        <v>46085.75</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="6">
-        <v>46085.75</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="4"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21">
+        <v>291201</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F26" s="21">
+        <v>220</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J26" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" s="24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21">
+        <v>292936</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" s="21">
+        <v>220</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="M27" s="24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21">
+        <v>292956</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" s="21">
+        <v>220</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="M28" s="24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1588,7 +2302,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -3359,7 +3359,9 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B49" s="11"/>
+      <c r="B49" s="11">
+        <v>46090</v>
+      </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10"/>
       <c r="E49" s="12" t="s">
@@ -3388,7 +3390,9 @@
       <c r="A50" s="10">
         <v>46</v>
       </c>
-      <c r="B50" s="11"/>
+      <c r="B50" s="11">
+        <v>46090</v>
+      </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10"/>
       <c r="E50" s="12" t="s">
@@ -3417,7 +3421,9 @@
       <c r="A51" s="10">
         <v>47</v>
       </c>
-      <c r="B51" s="11"/>
+      <c r="B51" s="11">
+        <v>46090</v>
+      </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
       <c r="E51" s="12" t="s">
@@ -3446,7 +3452,9 @@
       <c r="A52" s="10">
         <v>48</v>
       </c>
-      <c r="B52" s="11"/>
+      <c r="B52" s="11">
+        <v>46090</v>
+      </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
       <c r="E52" s="12" t="s">
@@ -3475,7 +3483,9 @@
       <c r="A53" s="10">
         <v>49</v>
       </c>
-      <c r="B53" s="11"/>
+      <c r="B53" s="11">
+        <v>46090</v>
+      </c>
       <c r="C53" s="10"/>
       <c r="D53" s="10"/>
       <c r="E53" s="12" t="s">
@@ -3504,7 +3514,9 @@
       <c r="A54" s="10">
         <v>50</v>
       </c>
-      <c r="B54" s="11"/>
+      <c r="B54" s="11">
+        <v>46090</v>
+      </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
       <c r="E54" s="12" t="s">

--- a/1.xlsx
+++ b/1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="317">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -883,9 +883,6 @@
   </si>
   <si>
     <t>9425805295</t>
-  </si>
-  <si>
-    <t>approval pending from WRLDC, Pl check latest status in WRLDC RC1</t>
   </si>
   <si>
     <t xml:space="preserve">132/33KV NEW  50 MVA  BBL X-MER </t>
@@ -1105,11 +1102,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1121,9 +1113,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1148,6 +1137,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1484,43 +1481,43 @@
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="51.140625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" style="12" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="64.85546875" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="40.5703125" style="16" customWidth="1"/>
+    <col min="13" max="13" width="40.5703125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>46091</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="6"/>
+      <c r="E2" s="3"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1528,22 +1525,22 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1551,1993 +1548,1993 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="6"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="8" t="s">
+      <c r="L4" s="16"/>
+      <c r="M4" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>46090.514780092592</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="6">
         <f>A5+1</f>
         <v>2</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="7">
         <v>46090.671041666668</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="6">
         <f t="shared" ref="A7:A49" si="0">A6+1</f>
         <v>3</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="7">
         <v>46090.569722222222</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="7">
         <v>46090.551759259259</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="7">
         <v>46090.489166666666</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="7">
         <v>46090.624224537038</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="7">
         <v>46088.512824074074</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="7">
         <v>46050.577592592592</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="7">
         <v>46088.577800925923</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="12" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="7">
         <v>46082.494803240741</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="8" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="7">
         <v>46087.397719907407</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="I15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="12" t="s">
+      <c r="M15" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="7">
         <v>46090.493807870371</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="6">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="7">
         <v>46090.454004629632</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="12" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="7">
         <v>46090.606736111113</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="7">
         <v>46090.54824074074</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="12" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="J19" s="13" t="s">
+      <c r="J19" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="7">
         <v>46090.560046296298</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="12" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="M20" s="12" t="s">
+      <c r="M20" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="6">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="7">
         <v>46090.480509259258</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="12" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J21" s="13" t="s">
+      <c r="J21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="14" t="s">
+      <c r="K21" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="7">
         <v>46087.634074074071</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="I22" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="J22" s="13" t="s">
+      <c r="J22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="14" t="s">
+      <c r="K22" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="6">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="7">
         <v>46090.532546296294</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="12" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="13" t="s">
+      <c r="J23" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K23" s="14" t="s">
+      <c r="K23" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="6">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="7">
         <v>46087.547071759262</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="12" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="6">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="7">
         <v>46090.532800925925</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="12" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="14" t="s">
+      <c r="K25" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="M25" s="12" t="s">
+      <c r="M25" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="6">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="7">
         <v>46078.609456018516</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="K26" s="14" t="s">
+      <c r="K26" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="M26" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="6">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="7">
         <v>46082.600104166668</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="I27" s="13" t="s">
+      <c r="I27" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J27" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="M27" s="12" t="s">
+      <c r="M27" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="7">
         <v>46083.676921296297</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J28" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="K28" s="14" t="s">
+      <c r="K28" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="L28" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="M28" s="12" t="s">
+      <c r="M28" s="8" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="7">
         <v>46090.560532407406</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="12" t="s">
+      <c r="D29" s="6"/>
+      <c r="E29" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="K29" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="M29" s="12" t="s">
+      <c r="M29" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="7">
         <v>46080.462106481478</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I30" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="K30" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="M30" s="12" t="s">
+      <c r="M30" s="8" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="6">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="7">
         <v>46090.462731481479</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="12" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="I31" s="13" t="s">
+      <c r="I31" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="J31" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="K31" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="M31" s="12" t="s">
+      <c r="M31" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="6">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="7">
         <v>46090.645555555559</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="12" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="I32" s="13" t="s">
+      <c r="I32" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="K32" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="M32" s="12" t="s">
+      <c r="M32" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="A33" s="6">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="7">
         <v>46081.76353009259</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="I33" s="13" t="s">
+      <c r="I33" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J33" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="K33" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="M33" s="12" t="s">
+      <c r="M33" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="7">
         <v>46081.765081018515</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J34" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K34" s="14" t="s">
+      <c r="K34" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="L34" s="15" t="s">
+      <c r="L34" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="M34" s="12" t="s">
+      <c r="M34" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+      <c r="A35" s="6">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="7">
         <v>46090.651898148149</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="12" t="s">
+      <c r="D35" s="6"/>
+      <c r="E35" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K35" s="14" t="s">
+      <c r="K35" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="L35" s="15" t="s">
+      <c r="L35" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="M35" s="12" t="s">
+      <c r="M35" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="6">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="7">
         <v>46083.590208333335</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J36" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K36" s="14" t="s">
+      <c r="K36" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="L36" s="15" t="s">
+      <c r="L36" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="M36" s="12" t="s">
+      <c r="M36" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
+      <c r="A37" s="6">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="7">
         <v>46090.456296296295</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="12" t="s">
+      <c r="D37" s="6"/>
+      <c r="E37" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J37" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="K37" s="14" t="s">
+      <c r="K37" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="L37" s="15" t="s">
+      <c r="L37" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="M37" s="12" t="s">
+      <c r="M37" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+      <c r="A38" s="6">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="7">
         <v>46090.547083333331</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="12" t="s">
+      <c r="D38" s="6"/>
+      <c r="E38" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K38" s="14" t="s">
+      <c r="K38" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="L38" s="15" t="s">
+      <c r="L38" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="M38" s="12" t="s">
+      <c r="M38" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
+      <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="7">
         <v>46064.690474537034</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J39" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K39" s="14" t="s">
+      <c r="K39" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="L39" s="15" t="s">
+      <c r="L39" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="M39" s="12" t="s">
+      <c r="M39" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+      <c r="A40" s="6">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="7">
         <v>46085.884606481479</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="I40" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J40" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="K40" s="14" t="s">
+      <c r="K40" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="L40" s="15" t="s">
+      <c r="L40" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="M40" s="12" t="s">
+      <c r="M40" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
+      <c r="A41" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="7">
         <v>46090.517951388887</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="12" t="s">
+      <c r="D41" s="6"/>
+      <c r="E41" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="I41" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="J41" s="13" t="s">
+      <c r="J41" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="K41" s="14" t="s">
+      <c r="K41" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="L41" s="15" t="s">
+      <c r="L41" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="M41" s="12" t="s">
+      <c r="M41" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
+      <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="7">
         <v>46090.515729166669</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="12" t="s">
+      <c r="D42" s="6"/>
+      <c r="E42" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="I42" s="13" t="s">
+      <c r="I42" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J42" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K42" s="14" t="s">
+      <c r="K42" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="L42" s="15" t="s">
+      <c r="L42" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="M42" s="12" t="s">
+      <c r="M42" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+      <c r="A43" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="7">
         <v>46090.612824074073</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="12" t="s">
+      <c r="D43" s="6"/>
+      <c r="E43" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="I43" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J43" s="13" t="s">
+      <c r="J43" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="K43" s="14" t="s">
+      <c r="K43" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="L43" s="15" t="s">
+      <c r="L43" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="M43" s="12" t="s">
+      <c r="M43" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10">
+      <c r="A44" s="6">
         <v>40</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="7">
         <v>46087.55232638889</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I44" s="13" t="s">
+      <c r="I44" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="J44" s="13" t="s">
+      <c r="J44" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="K44" s="14" t="s">
+      <c r="K44" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="L44" s="15" t="s">
+      <c r="L44" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="M44" s="12" t="s">
+      <c r="M44" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="8" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B45" s="11">
+      <c r="F45" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>42</v>
+      </c>
+      <c r="B46" s="7">
         <v>46090</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="I45" s="13" t="s">
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="L47" s="11"/>
+      <c r="M47" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>44</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="L48" s="11"/>
+      <c r="M48" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="K49" s="10"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>46</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="K50" s="10"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46090</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="J51" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="J45" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="K45" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="L45" s="15"/>
-      <c r="M45" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
-        <v>42</v>
-      </c>
-      <c r="B46" s="11">
+      <c r="K51" s="10"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>48</v>
+      </c>
+      <c r="B52" s="7">
         <v>46090</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="L46" s="15"/>
-      <c r="M46" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" s="11">
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="K52" s="10"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>49</v>
+      </c>
+      <c r="B53" s="7">
         <v>46090</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="K47" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="L47" s="15"/>
-      <c r="M47" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
-        <v>44</v>
-      </c>
-      <c r="B48" s="11">
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="K53" s="10"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>50</v>
+      </c>
+      <c r="B54" s="7">
         <v>46090</v>
       </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="K48" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="L48" s="15"/>
-      <c r="M48" s="12" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="G49" s="10"/>
-      <c r="H49" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="I49" s="13" t="s">
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="J54" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="J49" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="K49" s="14"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
-        <v>46</v>
-      </c>
-      <c r="B50" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
-        <v>47</v>
-      </c>
-      <c r="B51" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="K51" s="14"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
-        <v>48</v>
-      </c>
-      <c r="B52" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="G52" s="10"/>
-      <c r="H52" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
-        <v>49</v>
-      </c>
-      <c r="B53" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="G53" s="10"/>
-      <c r="H53" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
-        <v>50</v>
-      </c>
-      <c r="B54" s="11">
-        <v>46090</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="G54" s="10"/>
-      <c r="H54" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="J54" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="K54" s="14"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="12" t="s">
+      <c r="K54" s="10"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="8" t="s">
         <v>68</v>
       </c>
     </row>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$27</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="337">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -87,61 +87,247 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2603/0283</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Main Bus</t>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>132KV_132KV Alot-Taal Line</t>
+  </si>
+  <si>
+    <t>132KV_ALOT</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>Overhead crossing work</t>
+  </si>
+  <si>
+    <t>16-03-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>18-03-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>Kamal Solanki</t>
+  </si>
+  <si>
+    <t>9425805262</t>
+  </si>
+  <si>
+    <t>MR2603/0288</t>
+  </si>
+  <si>
+    <t>MR2603/0298</t>
+  </si>
+  <si>
+    <t>132KV_160mva BBL X-MER</t>
+  </si>
+  <si>
+    <t>220KV_ANUPPUR</t>
+  </si>
+  <si>
+    <t>HOT POINT ATTENDING WORK 132KV SIDE</t>
+  </si>
+  <si>
+    <t>16-03-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>16-03-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>SUNIL KUMAR BHALAVI</t>
+  </si>
+  <si>
+    <t>9425804704</t>
+  </si>
+  <si>
+    <t>MR2603/0301</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 40 MVA BBL XMER</t>
+  </si>
+  <si>
+    <t>132KV_BARMAN</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance work</t>
+  </si>
+  <si>
+    <t>16-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Er. Khagesh Choure</t>
+  </si>
+  <si>
+    <t>9425801357</t>
+  </si>
+  <si>
+    <t>MR2603/0058</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>400KV_500 MVA Transformer-No-1</t>
+  </si>
+  <si>
+    <t>400KV_BHOPAL4</t>
+  </si>
+  <si>
+    <t>For pre-monsoon Maint. &amp; Testing work</t>
+  </si>
+  <si>
+    <t>16-03-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>17-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>R.K. Gayaki</t>
+  </si>
+  <si>
+    <t>9407528876</t>
+  </si>
+  <si>
+    <t>MR2603/0303</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL-I (XMER-II)</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>PREMONSOON MAINTENANCE &amp; TESTING WORK</t>
+  </si>
+  <si>
+    <t>ER.LALIT SINGH</t>
+  </si>
+  <si>
+    <t>9425806845</t>
+  </si>
+  <si>
+    <t>MR2603/0299</t>
+  </si>
+  <si>
+    <t>220KV_220 KV JABALPUR CKT-2</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>PRE MONSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>TOSHAN SINGH</t>
+  </si>
+  <si>
+    <t>9752605559</t>
+  </si>
+  <si>
+    <t>MR2603/0304</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Half Main Bus (200 MVA I/C section)</t>
   </si>
   <si>
     <t>220KV_CHATARPUR</t>
   </si>
   <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
-    <t>for mainbus section span jumper isolating work</t>
-  </si>
-  <si>
-    <t>15-03-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>15-03-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Brajendra Soni</t>
+    <t>for single zebra bus converted to double zebra</t>
+  </si>
+  <si>
+    <t>16-03-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>Brajendra soni</t>
   </si>
   <si>
     <t>9131327770</t>
   </si>
   <si>
-    <t>MR2603/0216</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Chhindwara Amarwara</t>
-  </si>
-  <si>
-    <t>220KV_CHHINDWARA</t>
-  </si>
-  <si>
-    <t>Conductor Re-sagging work</t>
-  </si>
-  <si>
-    <t>13-03-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>15-03-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>A.M.Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>Continuous</t>
+    <t>MR2603/0274</t>
+  </si>
+  <si>
+    <t>400KV_400 kV Chhegaon - Julwaniya Ckt 2nd</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>For Jumper Cone Tightening &amp; Other Line Maintenanc</t>
+  </si>
+  <si>
+    <t>16-03-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>16-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>M.K.More</t>
+  </si>
+  <si>
+    <t>9425805258</t>
+  </si>
+  <si>
+    <t>MR2603/0280</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER</t>
+  </si>
+  <si>
+    <t>220KV_GORABAZAR</t>
+  </si>
+  <si>
+    <t>PRE MONSSON MAINTEANCE WORK</t>
+  </si>
+  <si>
+    <t>R S BAIS</t>
+  </si>
+  <si>
+    <t>9425163265</t>
+  </si>
+  <si>
+    <t>MR2603/0297</t>
+  </si>
+  <si>
+    <t>132KV_40 mva x-mer -IInd (make - BHEL)</t>
+  </si>
+  <si>
+    <t>220KV_GUNA</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance work.</t>
+  </si>
+  <si>
+    <t>16-03-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>Sagar Singh Dhakad</t>
+  </si>
+  <si>
+    <t>9589205697</t>
+  </si>
+  <si>
+    <t>MR2603/0295</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 63 MVA X-mer no.III,make  BBL</t>
+  </si>
+  <si>
+    <t>132KV_HARDA</t>
+  </si>
+  <si>
+    <t>Premonsoon Maintanance &amp; testing work</t>
+  </si>
+  <si>
+    <t>Sh.J.D.Khoria</t>
+  </si>
+  <si>
+    <t>9425804975</t>
   </si>
   <si>
     <t>132KV_HATTA</t>
@@ -168,33 +354,87 @@
     <t>M.M. Baig</t>
   </si>
   <si>
-    <t>MR2603/0004</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#04</t>
+    <t>MR2603/0282</t>
+  </si>
+  <si>
+    <t>400KV_UNIT#08</t>
   </si>
   <si>
     <t>400KV_INDIRASAGAR</t>
   </si>
   <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE OF THE SAID UNIT</t>
-  </si>
-  <si>
-    <t>01-03-2026 10:30:00</t>
-  </si>
-  <si>
-    <t>15-03-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SHRI SANJAY PATEL</t>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>16-03-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>31-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
   </si>
   <si>
     <t>9575074321</t>
   </si>
   <si>
+    <t>MR2603/0293</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA TRANSFORMER 2 MAKE BBL</t>
+  </si>
+  <si>
+    <t>220KV_INDORE-NZ</t>
+  </si>
+  <si>
+    <t>PRE MANSOON MAINTENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>16-03-2026 16:30:00</t>
+  </si>
+  <si>
+    <t>CHANDRAKANT KAUSHAL</t>
+  </si>
+  <si>
+    <t>9425801530</t>
+  </si>
+  <si>
+    <t>MR2603/0191</t>
+  </si>
+  <si>
+    <t>315MVA_400/220KV_BHEL_X'mer_4</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>For Transformer painting work .</t>
+  </si>
+  <si>
+    <t>ATUL PARADKAR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2603/0270</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Itarsi-Hoshangabad II</t>
+  </si>
+  <si>
+    <t>220KV_ITARSI</t>
+  </si>
+  <si>
+    <t>VD Provided,JC Tightening and other maint. work</t>
+  </si>
+  <si>
+    <t>Ashutosh Rai</t>
+  </si>
+  <si>
+    <t>9425806902</t>
+  </si>
+  <si>
     <t>MR2603/0248</t>
   </si>
   <si>
@@ -225,196 +465,247 @@
     <t>220KV_220 kV Jabalpur- Narsinghpur ckt-I</t>
   </si>
   <si>
-    <t>MR2603/0167</t>
-  </si>
-  <si>
-    <t>132KV_KHURAI</t>
-  </si>
-  <si>
-    <t>for OPGW Fiber Installation work</t>
-  </si>
-  <si>
-    <t>15-03-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>Dilip Singh Walkey</t>
-  </si>
-  <si>
-    <t>9425804578</t>
-  </si>
-  <si>
-    <t>MR2603/0269</t>
-  </si>
-  <si>
-    <t>220KV_100 MVA  XMER T&amp;R MAKE</t>
-  </si>
-  <si>
-    <t>220KV_MANDIDEEP</t>
-  </si>
-  <si>
-    <t>Pre monsoon .Testing and Painting work.</t>
+    <t>MR2603/0246</t>
+  </si>
+  <si>
+    <t>132KV_132KV Mandsaur Interconnector circuit IInd</t>
+  </si>
+  <si>
+    <t>132KV_MANDSOUR</t>
+  </si>
+  <si>
+    <t>Replace ACSR Conductor to HTLS Conductor</t>
+  </si>
+  <si>
+    <t>14-03-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>19-03-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2603/0259</t>
+  </si>
+  <si>
+    <t>315MVA_400/220KV_CGL_Xmer_2</t>
+  </si>
+  <si>
+    <t>400KV_MANDSOUR4</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>pre monsoon maintenance &amp; testing work</t>
+  </si>
+  <si>
+    <t>SH. CHANDRA PRAKASH DHAKAD</t>
+  </si>
+  <si>
+    <t>9907804919</t>
+  </si>
+  <si>
+    <t>MR2602/0484</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Narsinghpur-Interconnector Line Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_NARSINGHPUR</t>
+  </si>
+  <si>
+    <t>Uprating the capacity of 132 KV Transmission Lines</t>
+  </si>
+  <si>
+    <t>12-03-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>31-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
+  </si>
+  <si>
+    <t>MR2603/0253</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Narsinghpur-Interconnector Line Ckt-I</t>
+  </si>
+  <si>
+    <t>14-03-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>17-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>MR2603/0275</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 160MVA NGEF X-Mer-I</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>Pre-Monsoon Maintenance &amp; Testing work</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
+  </si>
+  <si>
+    <t>MR2603/0249</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Interconnector Circuit IInd</t>
+  </si>
+  <si>
+    <t>132KV_NEEMUCH1</t>
+  </si>
+  <si>
+    <t>Replace ACSR Conductor To HTLS Conductor</t>
+  </si>
+  <si>
+    <t>MR2603/0230</t>
+  </si>
+  <si>
+    <t>220KV_Generating Unit No.08</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR</t>
+  </si>
+  <si>
+    <t>Annual maintenance</t>
+  </si>
+  <si>
+    <t>30-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Sh. M. S. Karunakar</t>
+  </si>
+  <si>
+    <t>7898703187</t>
+  </si>
+  <si>
+    <t>MR2603/0284</t>
+  </si>
+  <si>
+    <t>132KV_132 KV KATNI PANAGAR MANSAKRA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>MODI.SHIF.WORK</t>
   </si>
   <si>
     <t>15-03-2026 09:00:00</t>
   </si>
   <si>
-    <t>A.K. VERMA</t>
-  </si>
-  <si>
-    <t>9425801324</t>
-  </si>
-  <si>
-    <t>MR2603/0246</t>
-  </si>
-  <si>
-    <t>132KV_132KV Mandsaur Interconnector circuit IInd</t>
-  </si>
-  <si>
-    <t>132KV_MANDSOUR</t>
-  </si>
-  <si>
-    <t>Replace ACSR Conductor to HTLS Conductor</t>
-  </si>
-  <si>
-    <t>14-03-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>19-03-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2602/0484</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Narsinghpur-Interconnector Line Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_NARSINGHPUR</t>
-  </si>
-  <si>
-    <t>Uprating the capacity of 132 KV Transmission Lines</t>
-  </si>
-  <si>
-    <t>12-03-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>31-03-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Ashish Kumar</t>
-  </si>
-  <si>
-    <t>9425805935</t>
-  </si>
-  <si>
-    <t>MR2603/0253</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Narsinghpur-Interconnector Line Ckt-I</t>
-  </si>
-  <si>
-    <t>14-03-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>17-03-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>MR2603/0249</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Interconnector Circuit IInd</t>
-  </si>
-  <si>
-    <t>132KV_NEEMUCH1</t>
-  </si>
-  <si>
-    <t>Replace ACSR Conductor To HTLS Conductor</t>
-  </si>
-  <si>
-    <t>MR2602/0561</t>
-  </si>
-  <si>
-    <t>220KV_Generating Unit # 07</t>
-  </si>
-  <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
-    <t>Annual maintenance</t>
-  </si>
-  <si>
-    <t>02-03-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>M S Karunakar</t>
-  </si>
-  <si>
-    <t>9789870318</t>
-  </si>
-  <si>
-    <t>MR2603/0284</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>MODI.SHIF.WORK</t>
-  </si>
-  <si>
-    <t>16-03-2026 18:00:00</t>
-  </si>
-  <si>
     <t>MANOJ KUMAR TIWARI</t>
   </si>
   <si>
     <t>7389495001</t>
   </si>
   <si>
-    <t>MR2602/0587</t>
-  </si>
-  <si>
-    <t>400KV_400 KV SSTPH-Pithampur ckt 1</t>
+    <t>MR2603/0264</t>
+  </si>
+  <si>
+    <t>400KV_315MVA ICT-2</t>
   </si>
   <si>
     <t>400KV_PITHAMPUR4</t>
   </si>
   <si>
-    <t>Tower Restrengthening work on cross arm.</t>
-  </si>
-  <si>
-    <t>01-03-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Naresh Pandre</t>
-  </si>
-  <si>
-    <t>9425806905</t>
-  </si>
-  <si>
-    <t>MR2602/0588</t>
-  </si>
-  <si>
-    <t>400KV_400 KV SSTPH-Pithampur ckt 2</t>
-  </si>
-  <si>
-    <t>MR2603/0008</t>
-  </si>
-  <si>
-    <t>132KV_132kv Rewa -Inter Connector ckt-II</t>
+    <t>SH RAJUDAS BAIRAGI</t>
+  </si>
+  <si>
+    <t>9425801532</t>
+  </si>
+  <si>
+    <t>MR2603/0251</t>
+  </si>
+  <si>
+    <t>400KV_400 kV SSTPH- Pithampur Ckt-IV</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Anil Alawa</t>
+  </si>
+  <si>
+    <t>9691647063</t>
+  </si>
+  <si>
+    <t>MR2603/0300</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_IMP_X'mer_1</t>
+  </si>
+  <si>
+    <t>132KV_RATLAM1</t>
+  </si>
+  <si>
+    <t>For pre-monsoon maintenance &amp; testing work.</t>
+  </si>
+  <si>
+    <t>NIKHIL DUNGE</t>
+  </si>
+  <si>
+    <t>9425801487</t>
+  </si>
+  <si>
+    <t>MR2603/0309</t>
+  </si>
+  <si>
+    <t>132KV_40MVA XMER 2nd BBL</t>
   </si>
   <si>
     <t>220KV_REWA</t>
   </si>
   <si>
-    <t>Modification/Shifting work of line</t>
-  </si>
-  <si>
-    <t>05-03-2026 08:00:00</t>
+    <t>PMM</t>
+  </si>
+  <si>
+    <t>Kanishka Singh</t>
+  </si>
+  <si>
+    <t>9425804656</t>
+  </si>
+  <si>
+    <t>MR2603/0310</t>
+  </si>
+  <si>
+    <t>132KV_132kv Silpara ckt-1</t>
+  </si>
+  <si>
+    <t>For panel replacement</t>
+  </si>
+  <si>
+    <t>kanishka Singh</t>
+  </si>
+  <si>
+    <t>MR2603/0227</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Rewa Interconnector Ckt-I line</t>
+  </si>
+  <si>
+    <t>tower Erection &amp; Stringing work</t>
+  </si>
+  <si>
+    <t>13-03-2026 10:00:00</t>
   </si>
   <si>
     <t>Mr. Ajay Kumar Chaurasia</t>
@@ -423,25 +714,43 @@
     <t>9425805081</t>
   </si>
   <si>
-    <t>MR2603/0227</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Rewa Interconnector Ckt-I line</t>
-  </si>
-  <si>
-    <t>tower Erection &amp; Stringing work</t>
-  </si>
-  <si>
-    <t>13-03-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>17-03-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>MR2603/0281</t>
-  </si>
-  <si>
-    <t>400KV_400KV Sarni-ISP line</t>
+    <t>MR2603/0311</t>
+  </si>
+  <si>
+    <t>220KV_220KV Satna(MPPTCL)-Katni ckt</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>Dubble Fitting work</t>
+  </si>
+  <si>
+    <t>R.K</t>
+  </si>
+  <si>
+    <t>9425805161</t>
+  </si>
+  <si>
+    <t>MR2603/0312</t>
+  </si>
+  <si>
+    <t>220KV_Satna(PGCIL)-Ajaygarh 220 KV Line</t>
+  </si>
+  <si>
+    <t>Wiring work of Lo No. 1R/0 to 2/0</t>
+  </si>
+  <si>
+    <t>Dharmendra Dwivedi</t>
+  </si>
+  <si>
+    <t>9425805311</t>
+  </si>
+  <si>
+    <t>MR2601/0478</t>
+  </si>
+  <si>
+    <t>400KV_400KV/220KV ICT</t>
   </si>
   <si>
     <t>400KV_SATPURA TPS</t>
@@ -450,52 +759,139 @@
     <t>DCRM TESTING ,GEN.CHECK,MAINTAINANCE OF BAY</t>
   </si>
   <si>
-    <t>D.P.MISHRA</t>
-  </si>
-  <si>
-    <t>9425611132</t>
-  </si>
-  <si>
-    <t>MR2602/0162</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Shujalpur -Bhopal Ckt- I st</t>
-  </si>
-  <si>
-    <t>220KV_SHUJALPUR</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>for bay Shifting       work for Add. 200 MVA</t>
-  </si>
-  <si>
-    <t>15-02-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>Shri Bhupendra Rane</t>
-  </si>
-  <si>
-    <t>9425802283</t>
-  </si>
-  <si>
-    <t>MR2603/0279</t>
-  </si>
-  <si>
-    <t>132KV_132KV JBP-VFJ CKT 1&amp;2 ,40MVA BBL NO.-1&amp;2</t>
+    <t>YASHWANT WARATHE</t>
+  </si>
+  <si>
+    <t>9425611046</t>
+  </si>
+  <si>
+    <t>MR2603/0232</t>
+  </si>
+  <si>
+    <t>220KV_BAY NO 08 BRS-AMK FEEDER</t>
+  </si>
+  <si>
+    <t>400KV_SGTPS</t>
+  </si>
+  <si>
+    <t>OVERHAULING WORK OF CIRCUIT BKR.</t>
+  </si>
+  <si>
+    <t>19-03-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>S BANERJEE</t>
+  </si>
+  <si>
+    <t>9424352880</t>
+  </si>
+  <si>
+    <t>MR2603/0198</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_BBL_Xmer</t>
+  </si>
+  <si>
+    <t>132KV_SHAHPURA</t>
+  </si>
+  <si>
+    <t>pre monsoon maintenance work</t>
+  </si>
+  <si>
+    <t>H L koshta</t>
+  </si>
+  <si>
+    <t>7587951105</t>
+  </si>
+  <si>
+    <t>MR2603/0306</t>
+  </si>
+  <si>
+    <t>220KV_220KV SIDHI-BARGAWAN(TBCB) CKT-II</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Disc Replacement work</t>
+  </si>
+  <si>
+    <t>G.L SAHU</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Singaji to Chhegaon ckt-1</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI TPS</t>
+  </si>
+  <si>
+    <t>Preventive maintenance</t>
+  </si>
+  <si>
+    <t>Yogesh Chouhan</t>
+  </si>
+  <si>
+    <t>7999328631</t>
+  </si>
+  <si>
+    <t>MR2603/0272</t>
+  </si>
+  <si>
+    <t>MR2603/0036</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI-TPS-II-PITHAMPUR4_Ckt_3</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI-TPS-II</t>
+  </si>
+  <si>
+    <t>AOH</t>
+  </si>
+  <si>
+    <t>16-03-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>17-03-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>SARAD TIWARI</t>
+  </si>
+  <si>
+    <t>9981811428</t>
+  </si>
+  <si>
+    <t>MR2603/0296</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA 3rd cgl-make Transformer</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>For nifps installation work</t>
+  </si>
+  <si>
+    <t>Pushpendra Kumar soni</t>
+  </si>
+  <si>
+    <t>9425806398</t>
+  </si>
+  <si>
+    <t>MR2603/0294</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL X-MER NO.-2</t>
   </si>
   <si>
     <t>132KV_VFJ</t>
   </si>
   <si>
-    <t>132KV Main BUS for Connecting all three Phase Jum</t>
-  </si>
-  <si>
-    <t>15-03-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>15-03-2026 11:00:00</t>
+    <t>PRE MONSOON MAINTENANCE</t>
   </si>
   <si>
     <t>AMIT KUMAR DAHIYA</t>
@@ -504,43 +900,88 @@
     <t>9425806926</t>
   </si>
   <si>
+    <t>MR2603/0285</t>
+  </si>
+  <si>
+    <t>132KV_132kV Vidisha Sanchi Rly. Tr.-II</t>
+  </si>
+  <si>
+    <t>220KV_VIDISHA</t>
+  </si>
+  <si>
+    <t>For modification/shiting work of line.</t>
+  </si>
+  <si>
+    <t>16-03-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Rajkumar Bhusare</t>
+  </si>
+  <si>
+    <t>9425820042</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
     <t>as per system requirement</t>
   </si>
   <si>
-    <t>sub ld</t>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>2 days continous s/d required for painting work?</t>
+  </si>
+  <si>
+    <t>ok, through sub ld</t>
   </si>
   <si>
     <t>deferred due to s/d on ckt 2</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>ok, loading on 132kv Ajaygarh-Lavkushnagar ckt to be monitored, if required load to be managed from discom end</t>
-  </si>
-  <si>
-    <t>deferred due to s/d on 132 KV Main Bus at Chattarpur</t>
-  </si>
-  <si>
-    <t>ok, timely restoration is required</t>
-  </si>
-  <si>
-    <t>ok, through sub ld, o&amp;m to be informed</t>
-  </si>
-  <si>
-    <t>132KV_132 KV PANAGAR MANSAKRA LINE</t>
-  </si>
-  <si>
-    <t>ok, T&amp;C and O&amp;M to be informed for any emergency during the s/d period, EI charging approval required while charging the line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ok, s/d shall be given after 11hrs, loading on 220kv Sukha-Narsinghpur ckt 1, 2 tobe monitored, if it increases then 220kv Narsinghpur-Pipariya ckt and 132kv Pondar-Bankhedi ckt to be opened, EI charging approval required while normalisation </t>
-  </si>
-  <si>
-    <t>132KV_132 KV Khurai-Khimlasa ckt 1&amp;2</t>
+    <t>deferred , discom not consented for 16th</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 400KV_SINGHAJI-TPS-II-PITHAMPUR4_Ckt_4</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on chattarpur bus section, shall be given only if chattarpur outage not availed</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on chattarpur/tikamgarh</t>
+  </si>
+  <si>
+    <t>ok, shall be given after 11hrs, EI approval required while charging</t>
+  </si>
+  <si>
+    <t>Allowed for 3 days only, due to multiple outages planned in nearby area, s/d must be revived in 3 days</t>
+  </si>
+  <si>
+    <t>ok, through sub ld, if required 220kv Mandsaur-Daloda ckt 1, 2 to be opened for load management</t>
+  </si>
+  <si>
+    <t>400KV-BHOPAL-MP-DAMOH-1</t>
+  </si>
+  <si>
+    <t>400KV-BHOPAL-MP-DAMOH-2</t>
+  </si>
+  <si>
+    <t>JABALPUR - 400KV - BUS 1</t>
+  </si>
+  <si>
+    <t>400KV/220KV GWALIOR-ICT-1</t>
+  </si>
+  <si>
+    <t>400KV/220KV SATNA-ICT-2</t>
+  </si>
+  <si>
+    <t>220KV-AJAYGARH-SATNA-1</t>
   </si>
   <si>
     <t>400KV-SSP-RAJGARH-1</t>
@@ -549,16 +990,61 @@
     <t>400KV-SSP-RAJGARH-2</t>
   </si>
   <si>
+    <t>POWERGRID-WR2 (PGCIL)</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>NCA,POWERGRID-WR2 (PGCIL),SSP (SSNL),MADHYA PRADESH,GUJARAT</t>
+  </si>
+  <si>
+    <t>s/d required for making LILO of 400kv Bhopal -Damoh ckt 2 at Sagar MP ss</t>
+  </si>
+  <si>
+    <t>Bus AMP Tightening work</t>
+  </si>
+  <si>
+    <t>AMP works,  Dia to be kept open at both sides</t>
+  </si>
+  <si>
+    <t>"AMP Work, Dia to be kept open at both sides. "</t>
+  </si>
+  <si>
+    <t>FOR WIRING FROM LOCATION No. 1R/0 to 2/0.</t>
+  </si>
+  <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
     <t>A/R OFF IS REQUIRED FOR OUTAGE ON 400KV-SSP-RAJGARH-1</t>
   </si>
   <si>
+    <t>ok, FTC formalities to be completed before charging</t>
+  </si>
+  <si>
+    <t>deferred due to s/d of 220 kV Jabalpur- Narsinghpur ckt-I &amp; II</t>
+  </si>
+  <si>
+    <t>deferred due to high loading conditions</t>
+  </si>
+  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>NCA,POWERGRID-WR2 (PGCIL),SSP (SSNL),MADHYA PRADESH,GUJARAT</t>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>17:59</t>
   </si>
 </sst>
 </file>
@@ -569,7 +1055,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -582,25 +1068,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -609,7 +1091,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -624,6 +1106,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -757,16 +1245,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1130,24 +1635,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M55"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="49" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="64.85546875" customWidth="1"/>
-    <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="9" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="52.7109375" customWidth="1"/>
-    <col min="14" max="14" width="46.85546875" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="10" t="s">
         <v>0</v>
@@ -1164,12 +1668,12 @@
       <c r="L1" s="11"/>
       <c r="M1" s="12"/>
     </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1183,7 +1687,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1206,7 +1710,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="42" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1245,18 +1749,20 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="36.75" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46095.537141203706</v>
+        <v>46095.682129629633</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1281,23 +1787,21 @@
         <v>25</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="36.75" customHeight="1">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46093.615613425929</v>
+        <v>46096.489537037036</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1323,330 +1827,320 @@
         <v>34</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36.75" customHeight="1">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A25" si="0">A6+1</f>
+        <f t="shared" ref="A7:A46" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46050.577592592592</v>
+        <v>46096.55190972222</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="L7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="M7" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46087.612569444442</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46082.494803240741</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="L8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="M8" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46096.555868055555</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46094.560972222222</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="M9" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46096.49732638889</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="F10" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46094.559374999997</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="36.75" customHeight="1">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46091.715081018519</v>
+        <v>46096.564618055556</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>63</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="K11" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="36.75" customHeight="1">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46095.475682870368</v>
+        <v>46095.494062500002</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="36.75" customHeight="1">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46094.558831018519</v>
+        <v>46095.521527777775</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="36.75" customHeight="1">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46078.625555555554</v>
+        <v>46096.467245370368</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>35</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>90</v>
@@ -1655,67 +2149,65 @@
         <v>91</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="36.75" customHeight="1">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46094.586064814815</v>
+        <v>46096.433009259257</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>93</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="36.75" customHeight="1">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46094.562615740739</v>
+        <v>46050.577592592592</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>98</v>
@@ -1724,449 +2216,1539 @@
         <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="M16" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="36.75" customHeight="1">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46080.462106481478</v>
+        <v>46095.523935185185</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="36.75" customHeight="1">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46095.57240740741</v>
+        <v>46095.743668981479</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>165</v>
+        <v>114</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="36.75" customHeight="1">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46081.76353009259</v>
+        <v>46092.655995370369</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>114</v>
+        <v>43</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="M19" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="36.75" customHeight="1">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46081.765081018515</v>
+        <v>46095.483298611114</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>35</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="36.75" customHeight="1">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46083.590208333335</v>
+        <v>46094.560972222222</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="36.75" customHeight="1">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46093.673634259256</v>
+        <v>46094.559374999997</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="36.75" customHeight="1">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46095.522303240738</v>
+        <v>46094.558831018519</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="9" t="s">
-        <v>135</v>
+        <v>143</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="M23" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46094.6094212963</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="7" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>20</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46064.690474537034</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="L24" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="M24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46078.625555555554</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46095.519895833335</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K25" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46094.586064814815</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46095.499050925922</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A28" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46094.562615740739</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A29" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46093.757233796299</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A30" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46095.57240740741</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46094.64739583333</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A32" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46094.574652777781</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46096.54173611111</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46096.589722222219</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A35" s="4">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46096.605393518519</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A36" s="4">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46093.673634259256</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A37" s="4">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46096.628182870372</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A38" s="4">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46096.672129629631</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A39" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>46051.833240740743</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="44.25" customHeight="1">
+      <c r="A40" s="4">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46094.407442129632</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A41" s="4">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="5">
+        <v>46092.865416666667</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A42" s="4">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46096.571759259263</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A43" s="4">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" s="5">
+        <v>46095.488703703704</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A44" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="5">
+        <v>46085.892094907409</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="L25" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>22</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46095.519895833335</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="17" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46095.519895833335</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="17" t="s">
-        <v>173</v>
+      <c r="H44" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A45" s="4">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="5">
+        <v>46096.444918981484</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A46" s="4">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46096.399537037039</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A47" s="4">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5">
+        <v>46095.627118055556</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="M47" s="14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A48" s="4">
+        <v>44</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46096.399537037039</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="G48" s="17"/>
+      <c r="H48" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="K48" s="18"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A49" s="4">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5">
+        <v>46096.399537037039</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="G49" s="17"/>
+      <c r="H49" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="K49" s="18"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="20" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A50" s="4">
+        <v>46</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="G50" s="17"/>
+      <c r="H50" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="K50" s="18"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A51" s="4">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="G51" s="17"/>
+      <c r="H51" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="K51" s="18"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="21" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A52" s="4">
+        <v>48</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="G52" s="17"/>
+      <c r="H52" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J52" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="K52" s="18"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A53" s="4">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="G53" s="17"/>
+      <c r="H53" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J53" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="K53" s="18"/>
+      <c r="L53" s="19"/>
+      <c r="M53" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="72" customHeight="1">
+      <c r="A54" s="4">
+        <v>50</v>
+      </c>
+      <c r="B54" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="G54" s="17"/>
+      <c r="H54" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="K54" s="18"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A55" s="4">
+        <v>51</v>
+      </c>
+      <c r="B55" s="5">
+        <v>46096</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="G55" s="17"/>
+      <c r="H55" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="K55" s="18"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="22" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,14 +15,25 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$19</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="361">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -106,58 +117,208 @@
     <t>9425805262</t>
   </si>
   <si>
-    <t>MR2603/0418</t>
-  </si>
-  <si>
-    <t>132KV_132Kv Main Bus</t>
-  </si>
-  <si>
-    <t>132KV_DONGRITAL</t>
+    <t>MR2603/0446</t>
+  </si>
+  <si>
+    <t>400KV_315  X-MER NO.1 MAKE CGL</t>
+  </si>
+  <si>
+    <t>400KV_ASHTA4</t>
+  </si>
+  <si>
+    <t>pre mansoon maintenance work</t>
+  </si>
+  <si>
+    <t>23-03-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>23-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>jitendra lohana</t>
+  </si>
+  <si>
+    <t>9425804978</t>
+  </si>
+  <si>
+    <t>MR2603/0420</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA _II BHEL</t>
+  </si>
+  <si>
+    <t>220KV_BADOD</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>Pre monsoon &amp; xmer testing work</t>
+  </si>
+  <si>
+    <t>ER YK RATHORE</t>
+  </si>
+  <si>
+    <t>9425804968</t>
+  </si>
+  <si>
+    <t>MR2603/0250</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>132KV_Unit no. 1 &amp; Unit no. 2 &amp; Bus Coupler</t>
+  </si>
+  <si>
+    <t>132KV_BARGI</t>
   </si>
   <si>
     <t>OCCM-MP</t>
   </si>
   <si>
-    <t>132Kv PT R&amp;Y phase oil leakage arresting work.</t>
-  </si>
-  <si>
-    <t>22-03-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>22-03-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>SABHAPATI PRAJAPATI</t>
-  </si>
-  <si>
-    <t>9039634660</t>
-  </si>
-  <si>
-    <t>MR2603/0462</t>
-  </si>
-  <si>
-    <t>132KV_132 KV 63 MVA XMER BBL -1</t>
-  </si>
-  <si>
-    <t>132KV_GADARWARA</t>
-  </si>
-  <si>
-    <t>For 132/33 KV 63 MVA BBL XMER  pre monsoon mainten</t>
-  </si>
-  <si>
-    <t>22-03-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>22-03-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mukesh Augrwall</t>
-  </si>
-  <si>
-    <t>7987152911</t>
-  </si>
-  <si>
-    <t>Continuous</t>
+    <t>C&amp;R Panel replacement</t>
+  </si>
+  <si>
+    <t>27-03-2026 21:00:00</t>
+  </si>
+  <si>
+    <t>Mohd Shahid</t>
+  </si>
+  <si>
+    <t>8770060307</t>
+  </si>
+  <si>
+    <t>132KV_BETUL1</t>
+  </si>
+  <si>
+    <t>line maint. work</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>MR2603/0486</t>
+  </si>
+  <si>
+    <t>132KV_Betul Tr. Ckt-2</t>
+  </si>
+  <si>
+    <t>23-03-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>220KV_160MVA BHEL TRANSFORMER</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>PREMANSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>23-03-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>LALIT SINGH</t>
+  </si>
+  <si>
+    <t>9425806845</t>
+  </si>
+  <si>
+    <t>MR2603/0491</t>
+  </si>
+  <si>
+    <t>MR2603/0305</t>
+  </si>
+  <si>
+    <t>220KV_220KV MAIN BUS-I</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>OVER HEAD STRINGING OVER THE  BUS</t>
+  </si>
+  <si>
+    <t>24-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>ANIL MAHOR</t>
+  </si>
+  <si>
+    <t>9425805149</t>
+  </si>
+  <si>
+    <t>MR2603/0481</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA 132/33 KV ABB X-MER</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>Pre Monsoon maintenance And Testing   work.</t>
+  </si>
+  <si>
+    <t>M.K.Choubey</t>
+  </si>
+  <si>
+    <t>9425801424</t>
+  </si>
+  <si>
+    <t>MR2603/0467</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER-I,BHEL &amp; 220 KV B/C</t>
+  </si>
+  <si>
+    <t>220KV_DATIA</t>
+  </si>
+  <si>
+    <t>Premoon soon maintenance &amp; testing work</t>
+  </si>
+  <si>
+    <t>23-03-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Atul Shakya</t>
+  </si>
+  <si>
+    <t>9425806928</t>
+  </si>
+  <si>
+    <t>MR2603/0480</t>
+  </si>
+  <si>
+    <t>160MVA_220/132KV_BHEL_X'mer_1</t>
+  </si>
+  <si>
+    <t>220KV_GWALIOR-II</t>
+  </si>
+  <si>
+    <t>PRE MONSOON MAINTENANCE &amp; TESTING WORK</t>
+  </si>
+  <si>
+    <t>R.C. ARORA</t>
+  </si>
+  <si>
+    <t>9425805108</t>
+  </si>
+  <si>
+    <t>MR2603/0482</t>
+  </si>
+  <si>
+    <t>220KV_220KV BUS COUPLER</t>
+  </si>
+  <si>
+    <t>SAFETY PURPOSE</t>
+  </si>
+  <si>
+    <t>R.C.ARORA</t>
   </si>
   <si>
     <t>132KV_HATTA</t>
@@ -193,9 +354,6 @@
     <t>400KV_INDIRASAGAR</t>
   </si>
   <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
     <t>ANNUAL MAINTENANCE</t>
   </si>
   <si>
@@ -211,6 +369,24 @@
     <t>9575074321</t>
   </si>
   <si>
+    <t>MR2603/0415</t>
+  </si>
+  <si>
+    <t>400KV_315 MVA 400/220 KV ICT- IV (Make-Emco)</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>for Transformer painting work.</t>
+  </si>
+  <si>
+    <t>Er.Atul paradkar</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
     <t>220KV_220 kV Jabalpur- Narsinghpur ckt-II</t>
   </si>
   <si>
@@ -241,6 +417,108 @@
     <t>220KV_220 kV Jabalpur- Narsinghpur ckt-I</t>
   </si>
   <si>
+    <t>220KV_160 mva -II</t>
+  </si>
+  <si>
+    <t>220KV_JAORA</t>
+  </si>
+  <si>
+    <t>PREE MANSOON MAINTANCE WORK</t>
+  </si>
+  <si>
+    <t>23-03-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>RAKESH BADGOTYA</t>
+  </si>
+  <si>
+    <t>7587951143</t>
+  </si>
+  <si>
+    <t>MR2603/0469</t>
+  </si>
+  <si>
+    <t>MR2603/0489</t>
+  </si>
+  <si>
+    <t>132KV_40MVA TRANSFORMER-II NGEF</t>
+  </si>
+  <si>
+    <t>132KV_JHABUA</t>
+  </si>
+  <si>
+    <t>PRE MONSOON MAINTENACE</t>
+  </si>
+  <si>
+    <t>23-03-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>VARSINGH MOHANIYA</t>
+  </si>
+  <si>
+    <t>9425803496</t>
+  </si>
+  <si>
+    <t>400KV_400KV JP BINA -MP BINA LINE</t>
+  </si>
+  <si>
+    <t>400KV_JP BINA</t>
+  </si>
+  <si>
+    <t>PRIVENTIVE MAINTANCE</t>
+  </si>
+  <si>
+    <t>23-03-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>31-03-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>Krishna SinghThakur</t>
+  </si>
+  <si>
+    <t>7987976012</t>
+  </si>
+  <si>
+    <t>MR2602/0134</t>
+  </si>
+  <si>
+    <t>MR2603/0495</t>
+  </si>
+  <si>
+    <t>132KV_40MVA BBL X-MER</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>For Pre-Monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>SK chaturvedi</t>
+  </si>
+  <si>
+    <t>9425806938</t>
+  </si>
+  <si>
+    <t>220KV_220/132 kv 160 MVA BHEL-I</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>pre monsoon maintenance</t>
+  </si>
+  <si>
+    <t>P.datey</t>
+  </si>
+  <si>
+    <t>9425805110</t>
+  </si>
+  <si>
+    <t>MR2603/0461</t>
+  </si>
+  <si>
     <t>MR2603/0316</t>
   </si>
   <si>
@@ -262,6 +540,42 @@
     <t>9407070182</t>
   </si>
   <si>
+    <t>MR2603/0470</t>
+  </si>
+  <si>
+    <t>220KV_MANDSOUR4-NIPANIYA_Ckt_1</t>
+  </si>
+  <si>
+    <t>400KV_MANDSOUR4</t>
+  </si>
+  <si>
+    <t>Pree Monsoon Maintenance &amp; Testing work</t>
+  </si>
+  <si>
+    <t>C.P dhakad</t>
+  </si>
+  <si>
+    <t>7587951067</t>
+  </si>
+  <si>
+    <t>MR2603/0479</t>
+  </si>
+  <si>
+    <t>220KV_NALKHEDA RAJGARH CKT 1</t>
+  </si>
+  <si>
+    <t>220KV_NALKHEDA</t>
+  </si>
+  <si>
+    <t>LINE MAINTENANCE</t>
+  </si>
+  <si>
+    <t>K SACHINDRA</t>
+  </si>
+  <si>
+    <t>7415651054</t>
+  </si>
+  <si>
     <t>132KV_132 KV Narsinghpur-Interconnector Line Ckt-II</t>
   </si>
   <si>
@@ -286,15 +600,45 @@
     <t>18-03-2026 08:00:00</t>
   </si>
   <si>
+    <t>MR2603/0422</t>
+  </si>
+  <si>
+    <t>220KV_220/132 kv 160 MVA BHEL X-MER NO-1</t>
+  </si>
+  <si>
+    <t>PRE MOONSOON MAINRENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>DINESH KUSHWAHA</t>
+  </si>
+  <si>
+    <t>9425182413</t>
+  </si>
+  <si>
+    <t>MR2603/0022</t>
+  </si>
+  <si>
+    <t>220KV_MAIN BUS-A ALONG WITH BUS COUPLER</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR</t>
+  </si>
+  <si>
+    <t>25-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>NITINDEEP TAMRAKAR</t>
+  </si>
+  <si>
+    <t>7898703187</t>
+  </si>
+  <si>
     <t>MR2603/0230</t>
   </si>
   <si>
     <t>220KV_Generating Unit No.08</t>
   </si>
   <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
     <t>Annual maintenance</t>
   </si>
   <si>
@@ -307,7 +651,115 @@
     <t>Sh. M. S. Karunakar</t>
   </si>
   <si>
-    <t>7898703187</t>
+    <t>MR2603/0483</t>
+  </si>
+  <si>
+    <t>220KV_Pandhurna Betul PGCIL</t>
+  </si>
+  <si>
+    <t>220KV_PANDHURNA</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>Re-sagging work &amp; other line maint. work</t>
+  </si>
+  <si>
+    <t>28-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>MR2603/0443</t>
+  </si>
+  <si>
+    <t>220KV_220kv Pandhurna-Betul</t>
+  </si>
+  <si>
+    <t>conductor Re-Sagging &amp; other line maintanance</t>
+  </si>
+  <si>
+    <t>A.M Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 50 MVA X-MER BBL</t>
+  </si>
+  <si>
+    <t>132KV_PATAN</t>
+  </si>
+  <si>
+    <t>PRE MANSOON MAINTINANCE WORK</t>
+  </si>
+  <si>
+    <t>23-03-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>V.P. SHARMA</t>
+  </si>
+  <si>
+    <t>8770147285</t>
+  </si>
+  <si>
+    <t>MR2603/0474</t>
+  </si>
+  <si>
+    <t>MR2603/0488</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL X-MER 1</t>
+  </si>
+  <si>
+    <t>132KV_PAWAI</t>
+  </si>
+  <si>
+    <t>Pree mansoon maintenance work</t>
+  </si>
+  <si>
+    <t>RN UPADHYAY</t>
+  </si>
+  <si>
+    <t>9425802349</t>
+  </si>
+  <si>
+    <t>MR2603/0441</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Pipariya-Bareli II line</t>
+  </si>
+  <si>
+    <t>220KV_PIPARIYA</t>
+  </si>
+  <si>
+    <t>VD Provided,Conductor Repair and other line work</t>
+  </si>
+  <si>
+    <t>Ashutosh Rai</t>
+  </si>
+  <si>
+    <t>9425806902</t>
+  </si>
+  <si>
+    <t>MR2603/0464</t>
+  </si>
+  <si>
+    <t>220KV_220kV Pithampur I/C ckt-1 line</t>
+  </si>
+  <si>
+    <t>220KV_PITHAMPUR (SEC-III)</t>
+  </si>
+  <si>
+    <t>Modification/Shifting work stringing of conductors</t>
+  </si>
+  <si>
+    <t>24-03-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>RAJENDRA KANOJE</t>
+  </si>
+  <si>
+    <t>9425801348</t>
   </si>
   <si>
     <t>MR2603/0314</t>
@@ -334,6 +786,54 @@
     <t>400KV_400KV SSTPH Pithampur ckt 1</t>
   </si>
   <si>
+    <t>MR2603/0496</t>
+  </si>
+  <si>
+    <t>132KV_132 KV SILPARA GEN CKT 1ST</t>
+  </si>
+  <si>
+    <t>220KV_REWA</t>
+  </si>
+  <si>
+    <t>PANEL REPLACEMENT OF 123KV SILPARA GEN CKT 1ST</t>
+  </si>
+  <si>
+    <t>ER. KANISHK SINGH</t>
+  </si>
+  <si>
+    <t>9425804656</t>
+  </si>
+  <si>
+    <t>MR2603/0484</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 40 MVA IMP X-MER</t>
+  </si>
+  <si>
+    <t>132KV_REWA-II (SAGRA)</t>
+  </si>
+  <si>
+    <t>PRE MANSOON MAINTINENCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>MR2603/0456</t>
+  </si>
+  <si>
+    <t>220KV_220kv Sabalgarh Morena Ckt</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
     <t>MR2603/0439</t>
   </si>
   <si>
@@ -358,49 +858,199 @@
     <t>220KV_220  kv Satna (MPPTCL)  â¿¿  Katni line</t>
   </si>
   <si>
-    <t>MR2603/0445</t>
-  </si>
-  <si>
-    <t>132KV_132kV Vidisha-Sanchi Rly. Tr.-II</t>
-  </si>
-  <si>
-    <t>220KV_VIDISHA</t>
-  </si>
-  <si>
-    <t>For modification/shifting work of line.</t>
-  </si>
-  <si>
-    <t>21-03-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>22-03-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Rajkumar Bhusare</t>
-  </si>
-  <si>
-    <t>9425820042</t>
+    <t>MR2603/0478</t>
+  </si>
+  <si>
+    <t>132KV_132 KV SEONI -AMARWADA LINE</t>
+  </si>
+  <si>
+    <t>220KV_SEONI</t>
+  </si>
+  <si>
+    <t>RYB PHASE CT REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>Arshad Qureshi</t>
+  </si>
+  <si>
+    <t>7000771014</t>
+  </si>
+  <si>
+    <t>220KV_BAY NO 02 BRS-PALI I/c 1</t>
+  </si>
+  <si>
+    <t>400KV_SGTPS</t>
+  </si>
+  <si>
+    <t>For O/hauling of C.Bkr &amp; hot point attending</t>
+  </si>
+  <si>
+    <t>s banerjee</t>
+  </si>
+  <si>
+    <t>9424352880</t>
+  </si>
+  <si>
+    <t>MR2603/0411</t>
+  </si>
+  <si>
+    <t>MR2603/0435</t>
+  </si>
+  <si>
+    <t>220KV_PGCIL CKT- 2nd</t>
+  </si>
+  <si>
+    <t>220KV_SHUJALPUR</t>
+  </si>
+  <si>
+    <t>DUE TO MAIN BUS S/D FOR NEW 200 MVA JUMPER WORK</t>
+  </si>
+  <si>
+    <t>23-03-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>NITIN NARAYAN VERMA</t>
+  </si>
+  <si>
+    <t>7587951076</t>
+  </si>
+  <si>
+    <t>MR2603/0436</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER-1st BHEL</t>
+  </si>
+  <si>
+    <t>MR2603/0434</t>
+  </si>
+  <si>
+    <t>220KV_PGCIL CKT- 1st</t>
+  </si>
+  <si>
+    <t>NITIN NARAYAAN VERMA</t>
+  </si>
+  <si>
+    <t>MR2603/0438</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER-3rd CGL</t>
+  </si>
+  <si>
+    <t>MR2603/0437</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER-2nd BHEL</t>
+  </si>
+  <si>
+    <t>MR2603/0440</t>
+  </si>
+  <si>
+    <t>220KV_MAIN BUS</t>
+  </si>
+  <si>
+    <t>MR2603/0487</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA Transformer -2nd BHEL make</t>
+  </si>
+  <si>
+    <t>400KV_UJJAIN4</t>
+  </si>
+  <si>
+    <t>Pre-Monsoon bay Maintenance &amp; transformer testing</t>
+  </si>
+  <si>
+    <t>Mr. Santosh Chavrasia</t>
+  </si>
+  <si>
+    <t>9425804677</t>
+  </si>
+  <si>
+    <t>MR2603/0463</t>
+  </si>
+  <si>
+    <t>132KV_40 mva x-mer Bhel</t>
+  </si>
+  <si>
+    <t>132KV_VINOBA BHAVE</t>
+  </si>
+  <si>
+    <t>pre monsoon mainteannce work</t>
+  </si>
+  <si>
+    <t>23-03-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>R S Bais</t>
+  </si>
+  <si>
+    <t>9425163265</t>
   </si>
   <si>
     <t>sub ld</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>unit s/d shall be given as per system availability</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
     <t>as per system availability</t>
   </si>
   <si>
-    <t>ok, shall be given after 11 hrs</t>
-  </si>
-  <si>
     <t>deferred</t>
   </si>
   <si>
-    <t>ok,  permitted from 12 hrs to 15hrs only (as per railway consent)</t>
-  </si>
-  <si>
-    <t>o&amp;m consent required</t>
+    <t>ok, through sub ld, 220kv Pandhurna-Kalmeshwar to be in service</t>
+  </si>
+  <si>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>deferred, scheduled for 24th</t>
+  </si>
+  <si>
+    <t>real time, in view of multiple outages near narsinghpur</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on x-mer at Datia and mahalgaon</t>
+  </si>
+  <si>
+    <t>ok, through sub ld, EI approval required while charging</t>
+  </si>
+  <si>
+    <t>220KV-REWA-REWA-MP-2</t>
+  </si>
+  <si>
+    <t>400KV/220KV GWALIOR-ICT-3</t>
+  </si>
+  <si>
+    <t>220KV-ITARSI-BUDNI-2</t>
+  </si>
+  <si>
+    <t>400KV/220KV JABALPUR-ICT-3</t>
+  </si>
+  <si>
+    <t>400KV-BHOPAL-MP-BINA-MP-1</t>
+  </si>
+  <si>
+    <t>220KV-DAMOH-DAMOH-MP-3</t>
+  </si>
+  <si>
+    <t>220KV-BETUL-PANDURNA-1</t>
+  </si>
+  <si>
+    <t>220KV-SEONI-PG-CHINDWARA-1</t>
+  </si>
+  <si>
+    <t>220KV-REWA-REWA-MP-1</t>
   </si>
   <si>
     <t>400KV-SSP-RAJGARH-2</t>
@@ -409,25 +1059,64 @@
     <t>400KV-SSP-RAJGARH-1</t>
   </si>
   <si>
+    <t>POWERGRID_WR2</t>
+  </si>
+  <si>
     <t>MP_SLDC</t>
   </si>
   <si>
+    <t>Line terminal equipment AMP Work</t>
+  </si>
+  <si>
+    <t>AMP works, Dia to be kept open at both sides</t>
+  </si>
+  <si>
+    <t>Mechanical Interlock issue in 211-89C and AMP works</t>
+  </si>
+  <si>
+    <t>AMP Work of ICT &amp; terminal equipment.Dia to be kept open at both sides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR 400KV BUS BAR SCHEME COMMISIONING WORK AT BHOPAL 400KV S/S </t>
+  </si>
+  <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR CONDUCTOR RE-SAGGING WORK FROM LOC. 178 TO 194) &amp; LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS </t>
+  </si>
+  <si>
     <t>A/R OFF IS REQUIRED FOR OUTAGE ON 400KV-SSP-RAJGARH-2</t>
   </si>
   <si>
+    <t>A/R OFF IS REQUIRED FOR OUTAGE ON 400KV-SSP-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
     <t>08:00</t>
   </si>
   <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
     <t>17:59</t>
   </si>
   <si>
     <t>real time</t>
   </si>
   <si>
-    <t>ok, line to be inservice</t>
+    <t>WR</t>
   </si>
 </sst>
 </file>
@@ -438,7 +1127,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -451,25 +1140,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -487,18 +1172,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -608,90 +1292,80 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1057,800 +1731,2642 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M68"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6"/>
-    <col min="2" max="2" width="11.140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11" style="6" customWidth="1"/>
-    <col min="5" max="5" width="49" style="6" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="64.85546875" style="6" customWidth="1"/>
-    <col min="9" max="10" width="19.5703125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12" style="6" customWidth="1"/>
-    <col min="13" max="13" width="56.42578125" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="43.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="42.42578125" customWidth="1"/>
+    <col min="9" max="10" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="13"/>
+    </row>
+    <row r="2" spans="1:13" ht="42" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>46103</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="2">
+        <v>46104</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" ht="42" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" ht="42" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="2" t="s">
+      <c r="L4" s="13"/>
+      <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+    <row r="5" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="5">
         <v>46095.684398148151</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="M5" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A6" s="4">
+        <f>A5+1</f>
         <v>2</v>
       </c>
-      <c r="B6" s="10">
-        <v>46099.622974537036</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="5">
+        <v>46102.432604166665</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="L6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="M6" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A7" s="4">
+        <f t="shared" ref="A7:A68" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46099.717789351853</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46094.565659722219</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46103.553414351853</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46103.593518518515</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46096.568865740737</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46103.5159375</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46103.385925925926</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46103.512349537035</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46103.516875000001</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46050.577592592592</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46095.523935185185</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46099.58016203704</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46094.560972222222</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10">
-        <v>46102.604444444441</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="J19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46094.559374999997</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46103.437349537038</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46103.575162037036</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A23" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46063.508946759262</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46103.656921296293</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46102.531493055554</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46097.470451388886</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46103.466064814813</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A28" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46103.498599537037</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A29" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46094.592499999999</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A30" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46099.758287037039</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46083.708483796298</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A32" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46093.757233796299</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46103.529293981483</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46101.598657407405</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A35" s="4">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46103.47996527778</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A36" s="4">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46103.572557870371</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A37" s="4">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46101.578726851854</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A38" s="4">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46102.713182870371</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A39" s="4">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>46096.847037037034</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A40" s="4">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="s">
+      <c r="B40" s="5">
+        <v>46096.845358796294</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A41" s="4">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="B41" s="5">
+        <v>46103.74322916667</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A42" s="4">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="B42" s="5">
+        <v>46103.52988425926</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G42" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H42" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A43" s="4">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="B43" s="5">
+        <v>46102.491805555554</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A44" s="4">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="B44" s="5">
+        <v>46101.497349537036</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A45" s="4">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="B45" s="5">
+        <v>46097.474606481483</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A46" s="4">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="B46" s="5">
+        <v>46103.494849537034</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A47" s="4">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="M7" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
-        <v>4</v>
-      </c>
-      <c r="B8" s="10">
-        <v>46050.577592592592</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B47" s="5">
+        <v>46099.467777777776</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A48" s="4">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46101.489178240743</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A49" s="4">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="5">
+        <v>46101.491342592592</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A50" s="4">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46101.486770833333</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A51" s="4">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="B51" s="5">
+        <v>46101.496122685188</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A52" s="4">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="B52" s="5">
+        <v>46101.494166666664</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H52" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A53" s="16">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="B53" s="17">
+        <v>46101.498171296298</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A54" s="21">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="B54" s="22">
+        <v>46103.570185185185</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="I54" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="K54" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="L54" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="29.25" customHeight="1">
+      <c r="A55" s="21">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="B55" s="22">
+        <v>46102.624027777776</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="I55" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="K55" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="L55" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="30">
+      <c r="A56" s="21">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10">
-        <v>46095.523935185185</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="B56" s="24"/>
+      <c r="C56" s="15">
+        <v>291475</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="E56" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G56" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="I56" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="26" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="30">
+      <c r="A57" s="21">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="B57" s="24"/>
+      <c r="C57" s="15">
+        <v>292379</v>
+      </c>
+      <c r="D57" s="24"/>
+      <c r="E57" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G57" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="26" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="30">
+      <c r="A58" s="21">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="B58" s="24"/>
+      <c r="C58" s="15">
+        <v>295473</v>
+      </c>
+      <c r="D58" s="24"/>
+      <c r="E58" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G58" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="26" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="30">
+      <c r="A59" s="21">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="B59" s="24"/>
+      <c r="C59" s="15">
+        <v>291732</v>
+      </c>
+      <c r="D59" s="24"/>
+      <c r="E59" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="G59" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K59" s="24"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="26" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="30">
+      <c r="A60" s="21">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="B60" s="24"/>
+      <c r="C60" s="15">
+        <v>291193</v>
+      </c>
+      <c r="D60" s="24"/>
+      <c r="E60" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="F60" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G60" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="90">
+      <c r="A61" s="21">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="B61" s="24"/>
+      <c r="C61" s="15">
+        <v>291236</v>
+      </c>
+      <c r="D61" s="24"/>
+      <c r="E61" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G61" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="105">
+      <c r="A62" s="21">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="B62" s="24"/>
+      <c r="C62" s="15">
+        <v>291237</v>
+      </c>
+      <c r="D62" s="24"/>
+      <c r="E62" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="F62" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G62" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K62" s="24"/>
+      <c r="L62" s="24"/>
+      <c r="M62" s="26" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="90">
+      <c r="A63" s="21">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="B63" s="24"/>
+      <c r="C63" s="15">
+        <v>291238</v>
+      </c>
+      <c r="D63" s="24"/>
+      <c r="E63" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G63" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="90">
+      <c r="A64" s="21">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="B64" s="24"/>
+      <c r="C64" s="15">
+        <v>291239</v>
+      </c>
+      <c r="D64" s="24"/>
+      <c r="E64" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="26" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="90">
+      <c r="A65" s="21">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10">
-        <v>46094.560972222222</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="B65" s="24"/>
+      <c r="C65" s="15">
+        <v>296243</v>
+      </c>
+      <c r="D65" s="24"/>
+      <c r="E65" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G65" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="K65" s="24"/>
+      <c r="L65" s="24"/>
+      <c r="M65" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="90">
+      <c r="A66" s="21">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="B66" s="24"/>
+      <c r="C66" s="15">
+        <v>296233</v>
+      </c>
+      <c r="D66" s="24"/>
+      <c r="E66" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G66" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K66" s="24"/>
+      <c r="L66" s="24"/>
+      <c r="M66" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="30">
+      <c r="A67" s="21">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="B67" s="24"/>
+      <c r="C67" s="15">
+        <v>296254</v>
+      </c>
+      <c r="D67" s="24"/>
+      <c r="E67" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G67" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="K67" s="24"/>
+      <c r="L67" s="24"/>
+      <c r="M67" s="26" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="30">
+      <c r="A68" s="21">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>7</v>
-      </c>
-      <c r="B11" s="10">
-        <v>46094.559374999997</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46097.470451388886</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
-        <v>9</v>
-      </c>
-      <c r="B13" s="15">
-        <v>46094.592499999999</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19">
-        <v>10</v>
-      </c>
-      <c r="B14" s="20">
-        <v>46093.757233796299</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>11</v>
-      </c>
-      <c r="B15" s="20">
-        <v>46096.847037037034</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
-        <v>12</v>
-      </c>
-      <c r="B16" s="20">
-        <v>46096.845358796294</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <v>13</v>
-      </c>
-      <c r="B17" s="20">
-        <v>46101.497349537036</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
-        <v>14</v>
-      </c>
-      <c r="B18" s="20">
-        <v>46097.474606481483</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K18" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <v>15</v>
-      </c>
-      <c r="B19" s="20">
-        <v>46101.724907407406</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
-        <v>16</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23">
-        <v>296242</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>17</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23">
-        <v>296253</v>
-      </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="15">
+        <v>296264</v>
+      </c>
+      <c r="D68" s="24"/>
+      <c r="E68" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="G68" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="26" t="s">
+        <v>359</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,20 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="221">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,7 +87,7 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2604/0701</t>
+    <t>MR2605/0032</t>
   </si>
   <si>
     <t>Continuous</t>
@@ -91,250 +102,400 @@
     <t>NON-OCCM-WR</t>
   </si>
   <si>
-    <t>Breaker Control shifting in new ecr building</t>
+    <t>Breaker control shifting in new ecr building</t>
+  </si>
+  <si>
+    <t>02-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>03-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Vijay Kothari</t>
+  </si>
+  <si>
+    <t>9425808910</t>
+  </si>
+  <si>
+    <t>MR2604/0405</t>
+  </si>
+  <si>
+    <t>220KV_160MVA BBL TRANSFORMER</t>
+  </si>
+  <si>
+    <t>220KV_ANUPPUR</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>BELL TANK OIL LEAKAGE ATTENDING WORK</t>
+  </si>
+  <si>
+    <t>17-04-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>06-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SUNIL KUMAR BHALAVI</t>
+  </si>
+  <si>
+    <t>9425804704</t>
+  </si>
+  <si>
+    <t>132KV_BADAMALHERA</t>
+  </si>
+  <si>
+    <t>for pre monsoon maintenence</t>
+  </si>
+  <si>
+    <t>02-05-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>02-05-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Brajendra Soni</t>
+  </si>
+  <si>
+    <t>9131327770</t>
+  </si>
+  <si>
+    <t>MR2605/0018</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL Transformer</t>
+  </si>
+  <si>
+    <t>MR2605/0034</t>
+  </si>
+  <si>
+    <t>132KV_132kv SHAHDOL-DINDORI CKT-II</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>JUMPER CONE TIGHTENING AND OTHER WORK</t>
+  </si>
+  <si>
+    <t>02-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>02-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>JAGDISH PRSAD ASAHTI</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2605/0031</t>
+  </si>
+  <si>
+    <t>220KV_220KV 100 MVA 220/33KV X-MER-1 IMP Make</t>
+  </si>
+  <si>
+    <t>220KV_GUJARKHEDI</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance WORK</t>
+  </si>
+  <si>
+    <t>02-05-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02-05-2026 20:00:00</t>
+  </si>
+  <si>
+    <t>SUNIL PAWAR</t>
+  </si>
+  <si>
+    <t>9425804939</t>
+  </si>
+  <si>
+    <t>MR2605/0005</t>
+  </si>
+  <si>
+    <t>132KV_132KV HATTA - BIJAWAR LINE</t>
+  </si>
+  <si>
+    <t>132KV_HATTA</t>
+  </si>
+  <si>
+    <t>REPLACE ACSR PANTHER CONDUCTOR WITH HTLS CONDUCTOR</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2604/0694</t>
+  </si>
+  <si>
+    <t>400KV_UNIT#07</t>
+  </si>
+  <si>
+    <t>400KV_INDIRASAGAR</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE OF U#07</t>
+  </si>
+  <si>
+    <t>01-05-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>15-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>9575074321</t>
+  </si>
+  <si>
+    <t>MR2604/0676</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Jabalpur-Narsinghpur Line Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>Resagging work at Loc. No. 15-236</t>
+  </si>
+  <si>
+    <t>30-04-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>03-05-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
+  </si>
+  <si>
+    <t>MR2605/0013</t>
+  </si>
+  <si>
+    <t>132KV_132 KV KATNI - I.C. LINE CKT - 2ND</t>
+  </si>
+  <si>
+    <t>132KV_KATNI</t>
+  </si>
+  <si>
+    <t>HTLS CONDUCTOR REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>03-05-2026 02:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2605/0035</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch(220)-Malharagarh(132) Line</t>
+  </si>
+  <si>
+    <t>132KV_MALHARGARH</t>
+  </si>
+  <si>
+    <t>For Line Mailenance work</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2604/0697</t>
+  </si>
+  <si>
+    <t>220KV_Generating Unit No.03</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR</t>
+  </si>
+  <si>
+    <t>Annual maintenance</t>
+  </si>
+  <si>
+    <t>Sh. M. S. Karunakar</t>
+  </si>
+  <si>
+    <t>7898703187</t>
+  </si>
+  <si>
+    <t>MR2605/0030</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Prithvipur-Niwari Ckt. IInd line</t>
+  </si>
+  <si>
+    <t>132KV_PRITHVIPUR</t>
+  </si>
+  <si>
+    <t>Pilot Disc Installation Work in Jumper</t>
+  </si>
+  <si>
+    <t>02-05-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2605/0027</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Satna  â¿¿  Satna IC â¿¿II  Ckt</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>for  ACSR Panther Conductor replacement to HTLS Co</t>
+  </si>
+  <si>
+    <t>02-05-2026 05:00:00</t>
+  </si>
+  <si>
+    <t>15-05-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R.K.Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2604/0699</t>
+  </si>
+  <si>
+    <t>220KV_220  kV Satna (MPPTCL)  â¿¿  Ajaygarh line</t>
+  </si>
+  <si>
+    <t>Double  fitting work</t>
   </si>
   <si>
     <t>01-05-2026 08:00:00</t>
   </si>
   <si>
-    <t>02-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Vijay Kothari</t>
-  </si>
-  <si>
-    <t>9425808910</t>
-  </si>
-  <si>
-    <t>MR2604/0405</t>
-  </si>
-  <si>
-    <t>220KV_160MVA BBL TRANSFORMER</t>
-  </si>
-  <si>
-    <t>220KV_ANUPPUR</t>
-  </si>
-  <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
-    <t>BELL TANK OIL LEAKAGE ATTENDING WORK</t>
-  </si>
-  <si>
-    <t>17-04-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>06-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SUNIL KUMAR BHALAVI</t>
-  </si>
-  <si>
-    <t>9425804704</t>
-  </si>
-  <si>
-    <t>MR2604/0703</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA BBL Transformer</t>
-  </si>
-  <si>
-    <t>132KV_BIJAWAR</t>
-  </si>
-  <si>
-    <t>for pre monsoon maintenence</t>
-  </si>
-  <si>
-    <t>01-05-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>01-05-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Brajendra Soni</t>
-  </si>
-  <si>
-    <t>9131327770</t>
-  </si>
-  <si>
-    <t>MR2604/0696</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Shahdol-Dindori Circuit II</t>
-  </si>
-  <si>
-    <t>132KV_DINDORI</t>
-  </si>
-  <si>
-    <t>For line maintenance work</t>
+    <t>15-05-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0011</t>
+  </si>
+  <si>
+    <t>132KV_132kV Seoni Nainpur Ckt-IInd</t>
+  </si>
+  <si>
+    <t>220KV_SEONI</t>
+  </si>
+  <si>
+    <t>Old OPGW wire removing Work</t>
+  </si>
+  <si>
+    <t>04-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2604/0291</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Shahapura â¿¿  Shrinagar link from Shahapura end on daily basis from 10:00 to 18:00 Hrs to avoid  overload tripping on 33KV Feeders</t>
+  </si>
+  <si>
+    <t>132KV_SHAHPURA</t>
+  </si>
+  <si>
+    <t>proposed to open the 132 KV Shahapura â¿¿  Shrinagar</t>
+  </si>
+  <si>
+    <t>12-04-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>12-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>H.L.KOSHTA</t>
+  </si>
+  <si>
+    <t>7587951105</t>
+  </si>
+  <si>
+    <t>MR2604/0704</t>
+  </si>
+  <si>
+    <t>220KV_90 MVA, 220/11/6.6 KV Station Transformer</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI TPS</t>
+  </si>
+  <si>
+    <t>Oil Seepage</t>
   </si>
   <si>
     <t>01-05-2026 09:00:00</t>
   </si>
   <si>
-    <t>01-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Jagdish Prasad Asati</t>
-  </si>
-  <si>
-    <t>9424445533</t>
-  </si>
-  <si>
-    <t>MR2604/0694</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#07</t>
-  </si>
-  <si>
-    <t>400KV_INDIRASAGAR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE OF U#07</t>
-  </si>
-  <si>
-    <t>01-05-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>15-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>9575074321</t>
-  </si>
-  <si>
-    <t>MR2604/0676</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Jabalpur-Narsinghpur Line Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>Resagging work at Loc. No. 15-236</t>
-  </si>
-  <si>
-    <t>30-04-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>03-05-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Ashish Kumar</t>
-  </si>
-  <si>
-    <t>9425805935</t>
-  </si>
-  <si>
-    <t>MR2604/0058</t>
-  </si>
-  <si>
-    <t>132KV_132KV KATNI IC LINE IIND CKT</t>
-  </si>
-  <si>
-    <t>132KV_KATNI</t>
-  </si>
-  <si>
-    <t>HTLS CONDUCTOR REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>03-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2604/0700</t>
-  </si>
-  <si>
-    <t>400KV_125MVAR BUS REACTOR</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>For Pre-Monsoon Maintenance and testing work</t>
-  </si>
-  <si>
-    <t>SK Chaturvedi</t>
-  </si>
-  <si>
-    <t>9425806938</t>
-  </si>
-  <si>
-    <t>MR2604/0698</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna  â¿¿  Satna IC â¿¿II  line</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>ACSR Panther Conductor replacement to HTLS Conduct</t>
-  </si>
-  <si>
-    <t>15-05-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Mr.R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2604/0699</t>
-  </si>
-  <si>
-    <t>220KV_220  kV Satna (MPPTCL)  â¿¿  Ajaygarh line</t>
-  </si>
-  <si>
-    <t>Double  fitting work</t>
-  </si>
-  <si>
-    <t>15-05-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Mr. R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>MR2604/0291</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Shahapura â¿¿  Shrinagar link from Shahapura end on daily basis from 10:00 to 18:00 Hrs to avoid  overload tripping on 33KV Feeders</t>
-  </si>
-  <si>
-    <t>132KV_SHAHPURA</t>
-  </si>
-  <si>
-    <t>proposed to open the 132 KV Shahapura â¿¿  Shrinagar</t>
-  </si>
-  <si>
-    <t>12-04-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>12-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>H.L.KOSHTA</t>
-  </si>
-  <si>
-    <t>7587951105</t>
-  </si>
-  <si>
-    <t>MR2604/0695</t>
-  </si>
-  <si>
-    <t>220KV_160MVA X-MER NO-I EMCO</t>
+    <t>Yogesh Chouhan</t>
+  </si>
+  <si>
+    <t>7999328631</t>
+  </si>
+  <si>
+    <t>MR2605/0003</t>
+  </si>
+  <si>
+    <t>220KV_INDORE (HATUNIYA PGCIL) - UJJAIN CKT â¿¿ 1</t>
+  </si>
+  <si>
+    <t>220KV_UJJAIN</t>
+  </si>
+  <si>
+    <t>REPLACEMENT OF FLASH OVER DISC INSULATOR STRING.</t>
+  </si>
+  <si>
+    <t>02-05-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>02-05-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2605/0002</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA XMER-II BHEL</t>
   </si>
   <si>
     <t>220KV_VIDISHA</t>
@@ -346,10 +507,7 @@
     <t>PRE-MONSOON MAINTENANCE WORK</t>
   </si>
   <si>
-    <t>01-05-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>K.C. GOSWAMI</t>
+    <t>K.C GOSWAMI</t>
   </si>
   <si>
     <t>9425804976</t>
@@ -379,81 +537,138 @@
     <t>9425805102</t>
   </si>
   <si>
+    <t>MR2605/0033</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_BBL_X'mer_3</t>
+  </si>
+  <si>
+    <t>for CT replacement work</t>
+  </si>
+  <si>
+    <t>RB Singh</t>
+  </si>
+  <si>
+    <t>9907230394</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>NTPC conent required</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 220kv Amarkantak-Gorabazar ckt</t>
+  </si>
+  <si>
     <t>as per system availability</t>
   </si>
   <si>
-    <t>under review</t>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>after load management</t>
+  </si>
+  <si>
+    <t>ok, alternate supply shall be available</t>
+  </si>
+  <si>
+    <t>deferred</t>
+  </si>
+  <si>
+    <t>deferred, not in wr list</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>deferred</t>
-  </si>
-  <si>
-    <t>deferred due to s/d on 132 kV Shahdol-Dindori Circuit II</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 01.05.2026</t>
+    <t>APPROVED OUTAGE LIST FOR DATED 02.05.2026</t>
   </si>
   <si>
     <t>400KV-KORBA-NTPC-BIRSINGPUR-1</t>
   </si>
   <si>
-    <t>POWERGRID-WR1 (PGCIL)</t>
+    <t>02-May-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>Attending S/D nature defect in line, Non auto mode of parallel ckt  is required . Dia to be kept open at both ends.</t>
+  </si>
+  <si>
+    <t>400KV-CHHEGAON-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>Attending S/D nature defect in line, Non auto mode of paralel ckt  is required . Dia to be kept open at both ends.</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-MAIHAR-1</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
+  </si>
+  <si>
+    <t>400KV-SSP-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>DISC INSULATOR STRING REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>220KV-MORENA-SABALGARH-1</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-2</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
+  </si>
+  <si>
+    <t>400KV-SEONI-KIRNAPUR-1</t>
+  </si>
+  <si>
+    <t>Tie LBB Relay retrofitting and testing work @ Seoni S/S</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>400KV-SEONI-PG-SATPURA-1</t>
+  </si>
+  <si>
+    <t>JP-BINA - 400KV - BUS 1</t>
   </si>
   <si>
     <t>01-May-2026</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Attending S/D nature defect in line, Non auto mode of parallel ckt  is required . Dia to be kept open at both ends.</t>
-  </si>
-  <si>
-    <t>220KV-SATNA-MAIHAR-1</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-2</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,NTPC</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
-  </si>
-  <si>
-    <t>shall be taken from 3rd May</t>
-  </si>
-  <si>
-    <t>JP-BINA - 400KV - BUS 1</t>
-  </si>
-  <si>
-    <t>JP BINA</t>
-  </si>
-  <si>
     <t>08-May-2026</t>
   </si>
   <si>
@@ -469,28 +684,16 @@
     <t xml:space="preserve">FOR TOWER STRENGTHNING WORK AT VARIOUS LINE LOCATIONS I.E. CONE TIGHTNING &amp; STRENGTHNING, MISSING PART PROVIDING  </t>
   </si>
   <si>
+    <t>ok, wrldc code to be taken</t>
+  </si>
+  <si>
     <t>400KV-SINGAJI-PITHAMPUR-2</t>
   </si>
   <si>
-    <t>400KV-SSP-RAJGARH-1</t>
-  </si>
-  <si>
-    <t>NCA,POWERGRID-WR2 (PGCIL),SSP (SSNL),MADHYA PRADESH,GUJARAT</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>DISC INSULATOR STRING REPLACEMENT WORK</t>
-  </si>
-  <si>
     <t>400KV-SSP-RAJGARH-2</t>
   </si>
   <si>
     <t>Hot line permit (Non auto mode) for safety purpose .A/R OFF REQUIRED DUE TO OUTAGE OF CKT -1</t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
@@ -501,8 +704,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -539,7 +742,7 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="22"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -573,7 +776,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,7 +901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -724,18 +927,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -745,16 +936,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -771,21 +959,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1150,60 +1341,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="61.42578125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="50.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="51.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="64.85546875" customWidth="1"/>
+    <col min="9" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="24.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="50.140625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="37.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
+      <c r="D2" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="9"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1218,7 +1408,7 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1226,7 +1416,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="9"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1241,7 +1431,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1259,20 +1449,20 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="M4" s="10" t="s">
+      <c r="L4" s="11"/>
+      <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46142.672951388886</v>
+        <v>46143.610578703701</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1280,7 +1470,7 @@
       <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1304,11 +1494,11 @@
       <c r="L5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1322,7 +1512,7 @@
       <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1346,63 +1536,63 @@
       <c r="L6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" ref="A7:A25" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46142.685254629629</v>
+        <v>46143.555173611108</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="L7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46142.555266203701</v>
+        <v>46143.619780092595</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -1426,32 +1616,30 @@
       <c r="L8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46141.703472222223</v>
+        <v>46143.604108796295</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
         <v>53</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>55</v>
@@ -1468,249 +1656,247 @@
       <c r="L9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46141.549629629626</v>
+        <v>46143.524305555555</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46114.694895833331</v>
+        <v>46141.703472222223</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="I11" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="J11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="K11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="6" t="s">
+      <c r="L11" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46142.652870370373</v>
+        <v>46141.549629629626</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="J12" s="6" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46142.628252314818</v>
+        <v>46143.542592592596</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46142.633240740739</v>
+        <v>46143.636377314811</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="11" t="s">
         <v>90</v>
       </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="F14" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46123.698136574072</v>
+        <v>46142.599212962959</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>95</v>
+        <v>18</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>100</v>
@@ -1718,386 +1904,805 @@
       <c r="L15" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46142.463206018518</v>
+        <v>46143.594143518516</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="4" t="s">
         <v>103</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>104</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="J16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="7" t="s">
+      <c r="L16" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="22">
-        <v>46111.697233796294</v>
-      </c>
-      <c r="C17" s="21" t="s">
+      <c r="B17" s="5">
+        <v>46143.576249999998</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="20" t="s">
+      <c r="F17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="G17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="21" t="s">
+      <c r="I17" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="J17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J17" s="23" t="s">
+      <c r="K17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="L17" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L17" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="M17" s="20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+      <c r="M17" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="L18" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M18" s="29" t="s">
+      <c r="B18" s="5">
+        <v>46142.633240740739</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
+      <c r="F18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="28" t="s">
+      <c r="B19" s="5">
+        <v>46143.531504629631</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J19" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="M19" s="29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+      <c r="L19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28" t="s">
+      <c r="B20" s="5">
+        <v>46123.698136574072</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J20" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="M20" s="29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+      <c r="M20" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28" t="s">
+      <c r="B21" s="5">
+        <v>46142.762673611112</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="J21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" s="28" t="s">
+      <c r="L21" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="L21" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M21" s="29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+      <c r="M21" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28" t="s">
+      <c r="B22" s="5">
+        <v>46143.511562500003</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F22" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28" t="s">
+      <c r="F22" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J22" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="L22" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M22" s="29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="26">
+      <c r="I22" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28" t="s">
+      <c r="B23" s="5">
+        <v>46143.468935185185</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M23" s="29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
+      <c r="J23" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="F24" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M24" s="29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+      <c r="B24" s="5">
+        <v>46111.697233796294</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="F25" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="L25" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="M25" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="31" t="s">
-        <v>156</v>
+      <c r="B25" s="17">
+        <v>46143.611678240741</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L29" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L30" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="M30" s="26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="M31" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L32" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M32" s="23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L33" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="L34" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M35" s="25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M36" s="25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="I37" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="K37" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="24" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="D2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,31 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$46</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="330">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -138,6 +127,33 @@
     <t>8989986610</t>
   </si>
   <si>
+    <t>MR2605/0269</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Amarpatan-Jhinna DCSS line</t>
+  </si>
+  <si>
+    <t>132KV_AMARPATAN</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>jumper tightening &amp; other line maintenance work</t>
+  </si>
+  <si>
+    <t>12-05-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>12-05-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Kumar Chaurasia</t>
+  </si>
+  <si>
+    <t>9425805081</t>
+  </si>
+  <si>
     <t>MR2605/0260</t>
   </si>
   <si>
@@ -147,9 +163,6 @@
     <t>132KV_AMARWARA</t>
   </si>
   <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
     <t>conductor re-saging work</t>
   </si>
   <si>
@@ -165,40 +178,112 @@
     <t>7587951136</t>
   </si>
   <si>
-    <t>220KV_220/132 KV 160 MVA BBL X-MER</t>
+    <t>MR2605/0279</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Anuppur-Janakpur Circuit</t>
   </si>
   <si>
     <t>220KV_ANUPPUR</t>
   </si>
   <si>
-    <t>For Air release of Transformer</t>
-  </si>
-  <si>
-    <t>11-05-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>11-05-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Sunil kumar bhalavi</t>
-  </si>
-  <si>
-    <t>9425804704</t>
-  </si>
-  <si>
-    <t>11-05-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>11-05-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>MR2605/0262</t>
-  </si>
-  <si>
-    <t>MR2605/0229</t>
-  </si>
-  <si>
-    <t>315MVA_400/220KV__X'mer_2</t>
+    <t>F/o disc replacement &amp; other line maint.</t>
+  </si>
+  <si>
+    <t>12-05-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Asati</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2605/0153</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bhanpura - Modak Line</t>
+  </si>
+  <si>
+    <t>220KV_BHANPURA</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>12-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Ravindra Kumar Marskole</t>
+  </si>
+  <si>
+    <t>9425814080</t>
+  </si>
+  <si>
+    <t>MR2605/0271</t>
+  </si>
+  <si>
+    <t>50MVA_132/33KV_BHEL_X'mer</t>
+  </si>
+  <si>
+    <t>pre monsooon maintenance</t>
+  </si>
+  <si>
+    <t>12-05-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>12-05-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>LAXMAN SARYAM</t>
+  </si>
+  <si>
+    <t>9425811507</t>
+  </si>
+  <si>
+    <t>MR2605/0292</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Bijawar - Badamalhera Line</t>
+  </si>
+  <si>
+    <t>132KV_BIJAWAR</t>
+  </si>
+  <si>
+    <t>F/O Disc Replacement Work</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2605/0285</t>
+  </si>
+  <si>
+    <t>400KV_315MVA X-MER-III(CGL)</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>Pre  Monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>Mr. P. N. Namdeo</t>
+  </si>
+  <si>
+    <t>7587951092</t>
+  </si>
+  <si>
+    <t>MR2605/0273</t>
+  </si>
+  <si>
+    <t>315MVA_400/220KV_CGL_X'mer_1</t>
   </si>
   <si>
     <t>400KV_CHHEGAON4</t>
@@ -207,214 +292,187 @@
     <t>Pre mansoon maintenance work</t>
   </si>
   <si>
+    <t>12-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Shri Ganesh Mansare</t>
+  </si>
+  <si>
+    <t>9425802441</t>
+  </si>
+  <si>
+    <t>MR2605/0213</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Chichli-Pipariya Ckt</t>
+  </si>
+  <si>
+    <t>220KV_CHICHLI</t>
+  </si>
+  <si>
+    <t>Resagging work at Loc. No. 400- 418,418-436</t>
+  </si>
+  <si>
+    <t>09-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>17-05-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
+  </si>
+  <si>
+    <t>MR2605/0235</t>
+  </si>
+  <si>
+    <t>132KV_50 mva xmer BBL</t>
+  </si>
+  <si>
+    <t>132KV_DEORI</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>P D GOUTAM</t>
+  </si>
+  <si>
+    <t>9425808329</t>
+  </si>
+  <si>
+    <t>MR2605/0236</t>
+  </si>
+  <si>
+    <t>132KV_132KV GOURJHAMAR - DEORI (REDIAL) LINE</t>
+  </si>
+  <si>
+    <t>MR2605/0274</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 50MVA BBL TRANSFORMER</t>
+  </si>
+  <si>
+    <t>132KV_DEOSAR</t>
+  </si>
+  <si>
+    <t>FOR PRE MANSOON MAINTENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>RAMESH KUMAR SHAHU</t>
+  </si>
+  <si>
+    <t>8109414234</t>
+  </si>
+  <si>
+    <t>MR2605/0281</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 63 MVA BBL XMER</t>
+  </si>
+  <si>
+    <t>132KV_GADARWARA</t>
+  </si>
+  <si>
+    <t>FOR PAINTING WORK</t>
+  </si>
+  <si>
+    <t>12-05-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>MUKESH AGRAWAL</t>
+  </si>
+  <si>
+    <t>9425805687</t>
+  </si>
+  <si>
+    <t>MR2605/0284</t>
+  </si>
+  <si>
+    <t>132KV_132 KV GADARWARA-OGPL</t>
+  </si>
+  <si>
+    <t>12-05-2026 12:30:00</t>
+  </si>
+  <si>
+    <t>MR2605/0277</t>
+  </si>
+  <si>
+    <t>132KV_132KV GOURJHAMER - DEORI LINE</t>
+  </si>
+  <si>
+    <t>132KV_GOURJHAMAR</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>PANKAJ YADAV</t>
+  </si>
+  <si>
+    <t>MR2604/0694</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>400KV_UNIT#07</t>
+  </si>
+  <si>
+    <t>400KV_INDIRASAGAR</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE OF U#07</t>
+  </si>
+  <si>
+    <t>01-05-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>9575074321</t>
+  </si>
+  <si>
+    <t>MR2605/0248</t>
+  </si>
+  <si>
+    <t>400KV_400KV BUS II</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>Shri Sanjay Patel</t>
+  </si>
+  <si>
+    <t>957504321</t>
+  </si>
+  <si>
+    <t>132KV_132 KV KATNI - I.C. LINE CKT - 1ST</t>
+  </si>
+  <si>
+    <t>132KV_KATNI</t>
+  </si>
+  <si>
+    <t>HTLS CONDUCTOR REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2605/0025</t>
+  </si>
+  <si>
     <t>11-05-2026 18:00:00</t>
   </si>
   <si>
-    <t>Shri Ganesh Mansare</t>
-  </si>
-  <si>
-    <t>9425802441</t>
-  </si>
-  <si>
-    <t>MR2605/0213</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Chichli-Pipariya Ckt</t>
-  </si>
-  <si>
-    <t>220KV_CHICHLI</t>
-  </si>
-  <si>
-    <t>Resagging work at Loc. No. 400- 418,418-436</t>
-  </si>
-  <si>
-    <t>09-05-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>17-05-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Ashish Kumar</t>
-  </si>
-  <si>
-    <t>9425805935</t>
-  </si>
-  <si>
-    <t>MR2605/0250</t>
-  </si>
-  <si>
-    <t>132KV_132KV  Damoh Tejgarh ckt</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>B-Phase CT Replacement work</t>
-  </si>
-  <si>
-    <t>11-05-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>11-05-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>M.K.Choubey</t>
-  </si>
-  <si>
-    <t>9425801424</t>
-  </si>
-  <si>
-    <t>MR2605/0249</t>
-  </si>
-  <si>
-    <t>132KV_132/33KV 40MVA T&amp;R X-MER</t>
-  </si>
-  <si>
-    <t>132KV_DEOSAR</t>
-  </si>
-  <si>
-    <t>FOR PRE MANSOON MAINETANCE WORK</t>
-  </si>
-  <si>
-    <t>RAMESH KUMAR SHAHU</t>
-  </si>
-  <si>
-    <t>8109414234</t>
-  </si>
-  <si>
-    <t>MR2605/0253</t>
-  </si>
-  <si>
-    <t>132KV_132 KV GADARWARA-BARMAN LINE</t>
-  </si>
-  <si>
-    <t>132KV_GADARWARA</t>
-  </si>
-  <si>
-    <t>FOR PAINTING WORK</t>
-  </si>
-  <si>
-    <t>11-05-2026 05:30:00</t>
-  </si>
-  <si>
-    <t>11-05-2026 06:30:00</t>
-  </si>
-  <si>
-    <t>MUKESH AGRAWAL</t>
-  </si>
-  <si>
-    <t>9425805687</t>
-  </si>
-  <si>
-    <t>MR2605/0255</t>
-  </si>
-  <si>
-    <t>132KV_132 KV GADARWARA-PONDAR LINE</t>
-  </si>
-  <si>
-    <t>11-05-2026 07:30:00</t>
-  </si>
-  <si>
-    <t>MR2605/0258</t>
-  </si>
-  <si>
-    <t>132KV_132 KV GADARWARA-BLA CKT-2</t>
-  </si>
-  <si>
-    <t>11-05-2026 16:30:00</t>
-  </si>
-  <si>
-    <t>MR2605/0257</t>
-  </si>
-  <si>
-    <t>132KV_132 KV GADARWARA-BLA CKT -1</t>
-  </si>
-  <si>
-    <t>11-05-2026 16:15:00</t>
-  </si>
-  <si>
-    <t>MR2605/0261</t>
-  </si>
-  <si>
-    <t>220KV_220/132/33KV 160MVA XMER BHEL</t>
-  </si>
-  <si>
-    <t>220KV_GUDGAON2</t>
-  </si>
-  <si>
-    <t>PMM &amp; Testing work.</t>
-  </si>
-  <si>
-    <t>Sanjay Pawar</t>
-  </si>
-  <si>
-    <t>9425802293</t>
-  </si>
-  <si>
-    <t>MR2605/0254</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA XMER (220/132/33KV)</t>
-  </si>
-  <si>
-    <t>220KV_HOSHANGABAD</t>
-  </si>
-  <si>
-    <t>PRE MONSOON MAINTENANCE $ TESTING WORK</t>
-  </si>
-  <si>
-    <t>V.P.DWIVEDI</t>
-  </si>
-  <si>
-    <t>9425804799</t>
-  </si>
-  <si>
-    <t>MR2604/0694</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#07</t>
-  </si>
-  <si>
-    <t>400KV_INDIRASAGAR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE OF U#07</t>
-  </si>
-  <si>
-    <t>01-05-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>9575074321</t>
-  </si>
-  <si>
-    <t>132KV_132 KV KATNI - I.C. LINE CKT - 1ST</t>
-  </si>
-  <si>
-    <t>132KV_KATNI</t>
-  </si>
-  <si>
-    <t>HTLS CONDUCTOR REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2605/0024</t>
-  </si>
-  <si>
-    <t>10-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>11-05-2026 02:00:00</t>
+    <t>12-05-2026 02:00:00</t>
   </si>
   <si>
     <t>MR2605/0155</t>
@@ -432,112 +490,25 @@
     <t>08-05-2026 09:00:00</t>
   </si>
   <si>
-    <t>MR2605/0225</t>
-  </si>
-  <si>
-    <t>132KV_132KV KOTMA - ANUPPUR CKT -I</t>
-  </si>
-  <si>
-    <t>132KV_KOTMA</t>
-  </si>
-  <si>
-    <t>132KV CB OVERHAULING WORK</t>
-  </si>
-  <si>
-    <t>RAM NARESH SINGH GOND</t>
-  </si>
-  <si>
-    <t>9425801257</t>
-  </si>
-  <si>
-    <t>MR2605/0224</t>
-  </si>
-  <si>
-    <t>132KV_40MVA 132/33KV BHEL X-MER</t>
-  </si>
-  <si>
-    <t>SAFETY PURPOSE ON 132KV CB OVERHAULING WORK</t>
-  </si>
-  <si>
-    <t>MR2605/0245</t>
-  </si>
-  <si>
-    <t>132KV_63MVA TRANSFORMER-I BBL</t>
-  </si>
-  <si>
-    <t>132KV_MANAWAR</t>
-  </si>
-  <si>
-    <t>Pre monsoon maintenance work.</t>
-  </si>
-  <si>
-    <t>KAILASH MOURYA</t>
-  </si>
-  <si>
-    <t>9752348190</t>
-  </si>
-  <si>
-    <t>MR2605/0256</t>
-  </si>
-  <si>
-    <t>220KV_220KV Circuit Breaker of IVT-4</t>
-  </si>
-  <si>
-    <t>400KV_NAGDA4</t>
-  </si>
-  <si>
-    <t>For control cable replacement work of 220KV CB</t>
-  </si>
-  <si>
-    <t>Ram Sharan Yadav</t>
-  </si>
-  <si>
-    <t>9425805101</t>
-  </si>
-  <si>
-    <t>MR2605/0247</t>
-  </si>
-  <si>
-    <t>132KV_132/33 kv of 50 mva X-mer make TAL</t>
-  </si>
-  <si>
-    <t>132KV_NAGOD</t>
-  </si>
-  <si>
-    <t>For pre mansoon maintenance work for</t>
-  </si>
-  <si>
-    <t>Pushkar kushwaha</t>
-  </si>
-  <si>
-    <t>9425813990</t>
-  </si>
-  <si>
-    <t>MR2605/0241</t>
-  </si>
-  <si>
-    <t>132KV_40MVA BBL X-mer-1</t>
-  </si>
-  <si>
-    <t>220KV_NEPANAGAR</t>
-  </si>
-  <si>
-    <t>Transformer Painting Work</t>
-  </si>
-  <si>
-    <t>Mr.M.K.Pawar</t>
-  </si>
-  <si>
-    <t>9425805191</t>
-  </si>
-  <si>
-    <t>MR2605/0242</t>
-  </si>
-  <si>
-    <t>220KV_220/132KV 160MVA TRANSFORMER -II(BHEL)</t>
-  </si>
-  <si>
-    <t>M.K.PAWAR</t>
+    <t>MR2605/0283</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Tons-Kotar Ckt.-1 line</t>
+  </si>
+  <si>
+    <t>220KV_KOTAR</t>
+  </si>
+  <si>
+    <t>double fitting work.</t>
+  </si>
+  <si>
+    <t>15-05-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R K Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
   </si>
   <si>
     <t>MR2604/0697</t>
@@ -561,19 +532,16 @@
     <t>7898703187</t>
   </si>
   <si>
-    <t>MR2605/0266</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Panagar Patan</t>
+    <t>MR2605/0272</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Panagar- Patan</t>
   </si>
   <si>
     <t>220KV_PANAGAR</t>
   </si>
   <si>
-    <t>installation of new earth wire at loc. No. 27R, 28</t>
-  </si>
-  <si>
-    <t>11-05-2026 19:00:00</t>
+    <t>Installation of new earth wire at loc. No. 27R, 28</t>
   </si>
   <si>
     <t>Jitendra Tiwari</t>
@@ -582,6 +550,24 @@
     <t>9425805298</t>
   </si>
   <si>
+    <t>MR2605/0280</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA TELK X-MER</t>
+  </si>
+  <si>
+    <t>132KV_PANNA</t>
+  </si>
+  <si>
+    <t>Pree mansoon maintenance &amp; testing work</t>
+  </si>
+  <si>
+    <t>RN UPADHYAY</t>
+  </si>
+  <si>
+    <t>9425802349</t>
+  </si>
+  <si>
     <t>MR2605/0039</t>
   </si>
   <si>
@@ -609,22 +595,22 @@
     <t>400KV_400KV SSTPH Pithampur ckt 2 line</t>
   </si>
   <si>
-    <t>132KV_40 MVA XMER BHEL</t>
-  </si>
-  <si>
-    <t>220KV_SARNI</t>
-  </si>
-  <si>
-    <t>for Oil Leakage attending Top air realease valve O</t>
-  </si>
-  <si>
-    <t>Er. Anup Kumar Dange</t>
-  </si>
-  <si>
-    <t>9425814073</t>
-  </si>
-  <si>
-    <t>MR2605/0238</t>
+    <t>MR2605/0288</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ratlam Badnawar Ckt- 1st</t>
+  </si>
+  <si>
+    <t>220KV_RATLAM</t>
+  </si>
+  <si>
+    <t>for line maintenance work.</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
   </si>
   <si>
     <t>MR2605/0027</t>
@@ -648,9 +634,6 @@
     <t>Mr. R.K.Prajapati</t>
   </si>
   <si>
-    <t>9407070182</t>
-  </si>
-  <si>
     <t>MR2604/0699</t>
   </si>
   <si>
@@ -678,6 +661,60 @@
     <t>17-05-2026 14:00:00</t>
   </si>
   <si>
+    <t>MR2605/0282</t>
+  </si>
+  <si>
+    <t>400KV_SARNI SEONI PGCIL LINE</t>
+  </si>
+  <si>
+    <t>400KV_SATPURA TPS</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA XMER-1 CGL</t>
+  </si>
+  <si>
+    <t>220KV_SEONI</t>
+  </si>
+  <si>
+    <t>Pre monsoon maintenance</t>
+  </si>
+  <si>
+    <t>Arshad Qureshi</t>
+  </si>
+  <si>
+    <t>7000771014</t>
+  </si>
+  <si>
+    <t>MR2605/0287</t>
+  </si>
+  <si>
+    <t>MR2605/0270</t>
+  </si>
+  <si>
+    <t>400KV_400 kV Seoni-Sarni line</t>
+  </si>
+  <si>
+    <t>765KV_SEONI-PG</t>
+  </si>
+  <si>
+    <t>Spacer Provide work</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
     <t>MR2605/0183</t>
   </si>
   <si>
@@ -723,16 +760,22 @@
     <t>7587951105</t>
   </si>
   <si>
-    <t>MR2605/0209</t>
-  </si>
-  <si>
-    <t>132KV_40 mva bbl x mer</t>
-  </si>
-  <si>
-    <t>hot point</t>
-  </si>
-  <si>
-    <t>H.L.koshta</t>
+    <t>MR2605/0276</t>
+  </si>
+  <si>
+    <t>220KV_220KV SIDHI-BARGAWAN CKT-II</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Jumper cone tightening work</t>
+  </si>
+  <si>
+    <t>G.L SAHU</t>
+  </si>
+  <si>
+    <t>9425805102</t>
   </si>
   <si>
     <t>MR2605/0240</t>
@@ -756,19 +799,22 @@
     <t>9425804939</t>
   </si>
   <si>
-    <t>MR2605/0252</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA bbl -make transformer</t>
+    <t>MR2605/0278</t>
+  </si>
+  <si>
+    <t>132KV_50 MVA Tal-make Transformer</t>
   </si>
   <si>
     <t>220KV_TIKAMGARH</t>
   </si>
   <si>
-    <t>Pre-mansoon maintenance</t>
-  </si>
-  <si>
-    <t>11-05-2026 16:00:00</t>
+    <t>Pre mansoon maintenance and testing</t>
+  </si>
+  <si>
+    <t>12-05-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>12-05-2026 14:00:00</t>
   </si>
   <si>
     <t>Pushpendra kumar soni</t>
@@ -801,48 +847,6 @@
     <t>9425804677</t>
   </si>
   <si>
-    <t>MR2605/0227</t>
-  </si>
-  <si>
-    <t>40MVA_132/33KV_BBL_Xmer_2</t>
-  </si>
-  <si>
-    <t>132KV_UMRETH</t>
-  </si>
-  <si>
-    <t>Pre Monsoon Maintenance and Testing work</t>
-  </si>
-  <si>
-    <t>Er. Dinesh Pawar</t>
-  </si>
-  <si>
-    <t>7587951131</t>
-  </si>
-  <si>
-    <t>MR2605/0244</t>
-  </si>
-  <si>
-    <t>132KV_132KV JABALPUR- VINOBA BHAVE LINE SECTION</t>
-  </si>
-  <si>
-    <t>132KV_VINOBA BHAVE</t>
-  </si>
-  <si>
-    <t>OLD STRUCTURES DISMANTLING WORK</t>
-  </si>
-  <si>
-    <t>CHETAN YADAV</t>
-  </si>
-  <si>
-    <t>9425805282</t>
-  </si>
-  <si>
-    <t>MR2605/0246</t>
-  </si>
-  <si>
-    <t>132KV_132KV VINOBA BHAVE- VFJ LINE SECTION</t>
-  </si>
-  <si>
     <t>MR2603/0710</t>
   </si>
   <si>
@@ -864,115 +868,148 @@
     <t>G.L Sahu</t>
   </si>
   <si>
-    <t>9425805102</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>ok, 132kv Pondar-Bankhedi ckt to be opened for load management</t>
+  </si>
+  <si>
+    <t>as per system availability</t>
+  </si>
+  <si>
+    <t>real time as per load management</t>
+  </si>
+  <si>
+    <t>deferred</t>
+  </si>
+  <si>
+    <t>work done</t>
+  </si>
+  <si>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>deferred due to multiple s/d in maihar area</t>
+  </si>
+  <si>
     <t>o&amp;m consent required</t>
   </si>
   <si>
-    <t>real time, through sub ld</t>
-  </si>
-  <si>
-    <t>as per system availability</t>
-  </si>
-  <si>
-    <t>ok, as per load management</t>
-  </si>
-  <si>
-    <t>deferred</t>
-  </si>
-  <si>
-    <t>sub ld</t>
+    <t>OGPL consent required</t>
+  </si>
+  <si>
+    <t>under review</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 12.05.2026</t>
+  </si>
+  <si>
+    <t>400KV-SEONI-PG-SATPURA-1</t>
+  </si>
+  <si>
+    <t>Line Circuits</t>
+  </si>
+  <si>
+    <t>POWERGRID-WR1 (PGCIL)</t>
+  </si>
+  <si>
+    <t>12-May-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>MP_SLDC</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>All other lines at Seoni/Stapura to be in service with AR enabled.WR1 to be informed. Load to be managed by SLDC MP.</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-GWALIOR-II-1</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>ok, other 220 kV lines at Gwalior/ Gwalior II to be in service.</t>
   </si>
   <si>
     <t>real time</t>
   </si>
   <si>
-    <t>deferred due to s/d on 132KV  Damoh Tejgarh ckt</t>
-  </si>
-  <si>
-    <t>work done</t>
-  </si>
-  <si>
-    <t>BLA consent required</t>
-  </si>
-  <si>
-    <t>s/d shall be given after normalisation of 132 KV GADARWARA-PONDAR LINE, 132kv Pondar-Bankhedi ckt to be opened for load management</t>
-  </si>
-  <si>
-    <t>ICT 4 to be in service through TBC, through sub ld</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 11.05.2026</t>
-  </si>
-  <si>
-    <t>400KV/220KV DAMOH-ICT-3</t>
-  </si>
-  <si>
-    <t>11-May-2026</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>AMP WORKS, Dia to be kept open at both sides.</t>
-  </si>
-  <si>
-    <t>220KV-KHANDWA-CHHEGAON-2</t>
+    <t>220KV-BHANPURA-MODAK-1</t>
+  </si>
+  <si>
+    <t>POWERGRID-NR,NLDC,MADHYA PRADESH</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t xml:space="preserve">AMP WORK </t>
-  </si>
-  <si>
-    <t>400KV-SSP-RAJGARH-1</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>DISC INSULATOR STRING REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>400KV-INDORE-UJJAIN-2</t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>400KV-CHHEGAON-KHANDWA-1</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-MALANPUR-2</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-MAHALGAON-1</t>
-  </si>
-  <si>
-    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+    <t>Ok, Load to be managed by SLDC MP. NLDC consent is required.</t>
   </si>
   <si>
     <t>132KV-VSTPS-WAIDHAN-2</t>
   </si>
   <si>
+    <t>MADHYA PRADESH,NTPC</t>
+  </si>
+  <si>
     <t>16:59</t>
   </si>
   <si>
     <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ckt-1 will be in service. load to be managed by SLDC MP. NTPC to be informed. </t>
+  </si>
+  <si>
+    <t>TIE BAY OF 220KV-SATNA-MP-SATNA-2 AND 400KV/220KV SATNA-ICT-1 @SATNA - 220KV at SATNA - 220KV</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>POWERGRID-WR2 (PGCIL)</t>
+  </si>
+  <si>
+    <t>13-May-2026</t>
+  </si>
+  <si>
+    <t>18:59</t>
+  </si>
+  <si>
+    <t>Continous</t>
+  </si>
+  <si>
+    <t>bay s/d required for accomodating 220kv Satna PG-Satna MP ckt 3 after bay shifting work</t>
+  </si>
+  <si>
+    <t>Ok, Load to be managed by SLDC MP. FTC procedure to be followed.</t>
+  </si>
+  <si>
+    <t>MAIN BAY OF 220KV-SATNA-MP-SATNA-2 AND SATNA - 220KV - BUS 2 @SATNA - 220KV at SATNA - 220KV</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
@@ -983,10 +1020,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1017,20 +1054,13 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1058,7 +1088,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1180,11 +1210,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1210,6 +1239,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1219,15 +1260,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1250,18 +1298,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 6" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1622,58 +1669,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="46.5703125" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="5" max="5" width="49.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="48" customWidth="1"/>
     <col min="9" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="48.5703125" customWidth="1"/>
+    <col min="13" max="13" width="50.28515625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1688,7 +1735,7 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1696,7 +1743,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1711,7 +1758,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1729,15 +1776,15 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="15"/>
+      <c r="M4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1750,7 +1797,7 @@
       <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="11" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1774,11 +1821,11 @@
       <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1792,7 +1839,7 @@
       <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1816,25 +1863,23 @@
       <c r="L6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A54" si="0">A6+1</f>
+        <f t="shared" ref="A7:A51" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46152.634641203702</v>
+        <v>46153.45107638889</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1858,671 +1903,673 @@
       <c r="L7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46152.644988425927</v>
+        <v>46152.634641203702</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="F8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="M8" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46153.579224537039</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46151.491631944446</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="6" t="s">
+      <c r="L9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="M9" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46148.447141203702</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46150.563472222224</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="J10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46153.455682870372</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="D11" s="4"/>
+      <c r="E11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46152.561689814815</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="L11" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="M11" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46153.696585648147</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="F12" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46152.524039351854</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>78</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46153.625474537039</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K12" s="7" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="F13" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46152.591874999998</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46153.509444444448</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46152.59479166667</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46150.563472222224</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" s="5">
-        <v>46152.603819444441</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46152.601585648146</v>
+        <v>46151.617118055554</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>97</v>
+      <c r="E16" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46152.639687499999</v>
+        <v>46151.619513888887</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>100</v>
+      <c r="E17" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46152.594074074077</v>
+        <v>46153.514861111114</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>106</v>
+      <c r="E18" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46141.703472222223</v>
+        <v>46153.591273148151</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46153.60496527778</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46143.572025462963</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46153.546122685184</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46148.479027777779</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46150.654560185183</v>
+        <v>46141.703472222223</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="I22" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" s="4" t="s">
+      <c r="J22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" s="7" t="s">
+      <c r="L22" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="M22" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46152.518854166665</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46150.65011574074</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="I23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="L23" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46152.484699074077</v>
+        <v>46143.573263888888</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>142</v>
       </c>
       <c r="F24" s="4" t="s">
@@ -2535,10 +2582,10 @@
         <v>144</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>145</v>
@@ -2546,1190 +2593,1375 @@
       <c r="L24" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46152.597187500003</v>
+        <v>46148.479027777779</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>46</v>
+        <v>154</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46152.489074074074</v>
+        <v>46153.600486111114</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="5">
-        <v>46152.443333333336</v>
+        <v>46142.599212962959</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" s="5">
-        <v>46152.446562500001</v>
+        <v>46153.496307870373</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="4" t="s">
-        <v>166</v>
+      <c r="E28" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" s="5">
-        <v>46142.599212962959</v>
+        <v>46153.586041666669</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>172</v>
+        <v>39</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B30" s="5">
-        <v>46152.71197916667</v>
+        <v>46144.322141203702</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>39</v>
+        <v>185</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B31" s="5">
-        <v>46144.322141203702</v>
+        <v>46144.323842592596</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H31" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K31" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="L31" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" s="5">
-        <v>46144.323842592596</v>
+        <v>46153.656782407408</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="4" t="s">
         <v>190</v>
       </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="11" t="s">
+        <v>191</v>
+      </c>
       <c r="F32" s="4" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>186</v>
+        <v>55</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B33" s="5">
-        <v>46152.374513888892</v>
+        <v>46143.576249999998</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4" t="s">
-        <v>191</v>
+      <c r="D33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B34" s="5">
-        <v>46143.576249999998</v>
+        <v>46142.633240740739</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>199</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K34" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>203</v>
-      </c>
       <c r="L34" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B35" s="5">
-        <v>46142.633240740739</v>
+        <v>46148.618541666663</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>206</v>
+      <c r="E35" s="11" t="s">
+        <v>209</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B36" s="5">
-        <v>46148.618541666663</v>
+        <v>46153.597743055558</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>37</v>
+        <v>215</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>212</v>
+        <v>89</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>213</v>
+        <v>31</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B37" s="5">
-        <v>46149.457337962966</v>
+        <v>46153.633645833332</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>218</v>
+        <v>89</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>219</v>
+        <v>40</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B38" s="5">
-        <v>46123.698136574072</v>
+        <v>46153.451203703706</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="11" t="s">
+        <v>226</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M38" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B39" s="5">
-        <v>46150.467083333337</v>
+        <v>46149.457337962966</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4" t="s">
         <v>230</v>
       </c>
+      <c r="D39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>231</v>
+      </c>
       <c r="F39" s="4" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>72</v>
+        <v>234</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B40" s="5">
-        <v>46152.436851851853</v>
+        <v>46123.698136574072</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>234</v>
+        <v>17</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>31</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B41" s="5">
-        <v>46152.580648148149</v>
+        <v>46153.529699074075</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="4" t="s">
-        <v>241</v>
+      <c r="E41" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B42" s="5">
-        <v>46141.551655092589</v>
+        <v>46152.436851851853</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>248</v>
+        <v>130</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>252</v>
+        <v>31</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B43" s="5">
-        <v>46150.697627314818</v>
+        <v>46153.569062499999</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="4" t="s">
-        <v>256</v>
+      <c r="E43" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>72</v>
+        <v>262</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="M43" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="5">
+        <v>46141.551655092589</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="24">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="25">
+        <v>46111.697233796294</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H45" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="I45" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="J45" s="26" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B44" s="5">
-        <v>46152.483668981484</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="L44" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B45" s="5">
-        <v>46152.486909722225</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="I45" s="6" t="s">
+      <c r="K45" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="L45" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="M45" s="23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="I46" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J46" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="K46" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="L46" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="M46" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="24">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="I47" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J47" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="K47" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="L47" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="M47" s="31" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="I48" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="L48" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="M48" s="31" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="24">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="I49" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J49" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="K49" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="L49" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="M49" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="I50" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J50" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="K50" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="L50" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="M50" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="24">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="J45" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="L45" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" s="18">
-        <v>46111.697233796294</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="D46" s="17" t="s">
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="I51" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="J51" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="K51" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="L51" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="M51" s="31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="33" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="32"/>
+    </row>
+    <row r="61" spans="1:16" ht="240" x14ac:dyDescent="0.25">
+      <c r="B61" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" s="20">
+        <v>400</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="I61" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="J61" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="K46" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="L46" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="M46" s="17" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="23" t="s">
+      <c r="K61" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L61" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M61" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="N61" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="O61" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="P61" s="22"/>
+    </row>
+    <row r="62" spans="1:16" ht="135" x14ac:dyDescent="0.25">
+      <c r="B62" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="I47" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J47" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="K47" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L47" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="M47" s="24" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="17">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="23" t="s">
+      <c r="D62" s="20">
+        <v>220</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G62" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="I48" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J48" s="23" t="s">
+      <c r="H62" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K48" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L48" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="23" t="s">
+      <c r="I62" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L62" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M62" s="20" t="s">
+        <v>308</v>
+      </c>
+      <c r="N62" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="O62" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="P62" s="22"/>
+    </row>
+    <row r="63" spans="1:16" ht="150" x14ac:dyDescent="0.25">
+      <c r="B63" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D63" s="20">
+        <v>220</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="23" t="s">
+      <c r="J63" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L63" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="I49" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J49" s="23" t="s">
+      <c r="M63" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="N63" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="O63" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="P63" s="22"/>
+    </row>
+    <row r="64" spans="1:16" ht="195" x14ac:dyDescent="0.25">
+      <c r="B64" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D64" s="20">
+        <v>132</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="I64" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="K49" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L49" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="M49" s="26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A50" s="17">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J50" s="23" t="s">
+      <c r="L64" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M64" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="N64" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="O64" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="P64" s="22"/>
+    </row>
+    <row r="65" spans="2:16" ht="195" x14ac:dyDescent="0.25">
+      <c r="B65" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" s="20">
+        <v>220</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="F65" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K50" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L50" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="M50" s="26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="I51" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J51" s="23" t="s">
+      <c r="G65" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L65" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M65" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="N65" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="O65" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="P65" s="22"/>
+    </row>
+    <row r="66" spans="2:16" ht="195" x14ac:dyDescent="0.25">
+      <c r="B66" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="D66" s="20">
+        <v>220</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="F66" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="K51" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L51" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="M51" s="26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="I52" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J52" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="K52" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L52" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="M52" s="26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="I53" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J53" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="K53" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L53" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="M53" s="26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="J54" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="K54" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="L54" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="M54" s="26" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A55" s="22"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="22"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="25" t="s">
+      <c r="G66" s="20" t="s">
         <v>313</v>
       </c>
+      <c r="H66" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="I66" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="J66" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="L66" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="M66" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="N66" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="O66" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="P66" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="E2:M2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1479,8 +1479,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
     <col min="2" max="2" width="10.42578125" style="5" customWidth="1"/>
@@ -1498,7 +1501,7 @@
     <col min="14" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -1515,7 +1518,7 @@
       <c r="L1" s="7"/>
       <c r="M1" s="8"/>
     </row>
-    <row r="2" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1534,7 +1537,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1557,7 +1560,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1677,7 +1680,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f t="shared" ref="A7:A42" si="0">A6+1</f>
         <v>3</v>
@@ -1719,7 +1722,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1759,7 +1762,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1801,7 +1804,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1841,7 +1844,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1881,7 +1884,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1923,7 +1926,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1963,7 +1966,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2005,7 +2008,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2047,7 +2050,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2089,7 +2092,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2129,7 +2132,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2171,7 +2174,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2211,7 +2214,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2253,7 +2256,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2293,7 +2296,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2333,7 +2336,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2375,7 +2378,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2415,7 +2418,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2457,7 +2460,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2499,7 +2502,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2541,7 +2544,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2583,7 +2586,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2625,7 +2628,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2665,7 +2668,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2707,7 +2710,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2747,7 +2750,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2787,7 +2790,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2829,7 +2832,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2871,7 +2874,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2911,7 +2914,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2951,7 +2954,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2991,7 +2994,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3031,7 +3034,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3071,7 +3074,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3111,7 +3114,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3151,7 +3154,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="29"/>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -3171,8 +3174,8 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$42</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="232">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,6 +76,33 @@
     <t>REMARK</t>
   </si>
   <si>
+    <t>MR2605/0671</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220KV Anuppur No.1</t>
+  </si>
+  <si>
+    <t>220KV_AMARKANTAK</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>28-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>29-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Vijay Kothari</t>
+  </si>
+  <si>
+    <t>9425808910</t>
+  </si>
+  <si>
     <t>MR2605/0367</t>
   </si>
   <si>
@@ -106,30 +133,6 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2605/0653</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA X-MER-II MAKE-BBL</t>
-  </si>
-  <si>
-    <t>220KV_BETUL</t>
-  </si>
-  <si>
-    <t>Pre-monsoon Maintenance work</t>
-  </si>
-  <si>
-    <t>27-05-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>27-05-2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Er. Vishal Malviya</t>
-  </si>
-  <si>
-    <t>9425804955</t>
-  </si>
-  <si>
     <t>MR2605/0506</t>
   </si>
   <si>
@@ -154,12 +157,30 @@
     <t>9425820042</t>
   </si>
   <si>
+    <t>MR2605/0298</t>
+  </si>
+  <si>
+    <t>400KV_400 KV ITARSI CKT-2(OCCM APPROVED0</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>400 KV  BUS-BAR OUT FOR C.T. SHIFTING WORK</t>
+  </si>
+  <si>
+    <t>28-05-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>R.K.GAYKI</t>
+  </si>
+  <si>
+    <t>9407528876</t>
+  </si>
+  <si>
     <t>MR2605/0301</t>
   </si>
   <si>
-    <t>Continuous</t>
-  </si>
-  <si>
     <t>400KV_Bus-Bar</t>
   </si>
   <si>
@@ -175,28 +196,22 @@
     <t>RK Gayaki</t>
   </si>
   <si>
-    <t>9407528876</t>
-  </si>
-  <si>
-    <t>MR2605/0644</t>
-  </si>
-  <si>
-    <t>400KV_50MVAR Bhopal-1 LIne Reactor(BHEL)</t>
+    <t>MR2605/0660</t>
+  </si>
+  <si>
+    <t>400KV_50 MVAR LINE REACTOR -2 BHOPAL</t>
   </si>
   <si>
     <t>400KV_BINA4</t>
   </si>
   <si>
-    <t>Pre Monsoon Maintenance Work.</t>
-  </si>
-  <si>
-    <t>27-05-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>27-05-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Mr. P.N.Namdeo</t>
+    <t>PRE MANSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>28-05-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>P. N. NAMDEO</t>
   </si>
   <si>
     <t>7587951092</t>
@@ -244,30 +259,6 @@
     <t>MR2605/0332</t>
   </si>
   <si>
-    <t>MR2605/0650</t>
-  </si>
-  <si>
-    <t>132KV_50MVA X-MER-II MAKE TAL</t>
-  </si>
-  <si>
-    <t>132KV_BISNOOR</t>
-  </si>
-  <si>
-    <t>GAS COLLECTING DEVICE COMMISSIONNING</t>
-  </si>
-  <si>
-    <t>27-05-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>27-05-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>ER SANJAY KUMAR PAWAR</t>
-  </si>
-  <si>
-    <t>9425802293</t>
-  </si>
-  <si>
     <t>MR2605/0639</t>
   </si>
   <si>
@@ -283,58 +274,31 @@
     <t>27-05-2026 07:00:00</t>
   </si>
   <si>
-    <t>29-05-2026 18:00:00</t>
-  </si>
-  <si>
     <t>A.M.Shende</t>
   </si>
   <si>
     <t>7587951136</t>
   </si>
   <si>
-    <t>MR2605/0646</t>
-  </si>
-  <si>
-    <t>132KV_50 MVA BBL Transformer</t>
+    <t>MR2605/0663</t>
+  </si>
+  <si>
+    <t>132KV_132kV Dindori Gorakhpur Line</t>
   </si>
   <si>
     <t>132KV_DINDORI</t>
   </si>
   <si>
-    <t>Pre- Monsoon maintenance and testing work</t>
-  </si>
-  <si>
-    <t>27-05-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>27-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Vikram Singh</t>
-  </si>
-  <si>
-    <t>8319555199</t>
-  </si>
-  <si>
-    <t>MR2605/0654</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA BBL 220/132 KV</t>
-  </si>
-  <si>
-    <t>220KV_HOSHANGABAD</t>
-  </si>
-  <si>
-    <t>PRE MANSOON MAINTENANCE &amp; TESTING WORK</t>
-  </si>
-  <si>
-    <t>27-05-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>V.P.DWIVEDI</t>
-  </si>
-  <si>
-    <t>9425804799</t>
+    <t>Jumper Cone Tightening &amp; Other Maint. Work</t>
+  </si>
+  <si>
+    <t>28-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
   </si>
   <si>
     <t>MR2605/0649</t>
@@ -346,9 +310,6 @@
     <t>400KV_INDIRASAGAR</t>
   </si>
   <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
     <t>ANNUAL MAINTENANCE &amp; CHANGE OF SF 6 CIRCUIT BREAKE</t>
   </si>
   <si>
@@ -400,16 +361,61 @@
     <t>MR2605/0612</t>
   </si>
   <si>
-    <t>MR2605/0652</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Narsinghpur-Karakbel Line Ckt-II</t>
-  </si>
-  <si>
-    <t>132KV_KARAKBEL</t>
-  </si>
-  <si>
-    <t>Pre - Monsoon Maintenance work.</t>
+    <t>MR2605/0667</t>
+  </si>
+  <si>
+    <t>400KV_500 MVA-400KV/220KV/33KV-T&amp;R-X-Mer-III</t>
+  </si>
+  <si>
+    <t>400KV_JULWANIYA4</t>
+  </si>
+  <si>
+    <t>for Pre monsoon maintenance &amp; Testing work.</t>
+  </si>
+  <si>
+    <t>400Kv S/s Julwaniya</t>
+  </si>
+  <si>
+    <t>8319599488</t>
+  </si>
+  <si>
+    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_KOTAR</t>
+  </si>
+  <si>
+    <t>For double fitting work</t>
+  </si>
+  <si>
+    <t>26-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>10-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R.K.Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2605/0635</t>
+  </si>
+  <si>
+    <t>MR2605/0607</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Narsinghpur-Chichli Line</t>
+  </si>
+  <si>
+    <t>220KV_NARSINGHPUR</t>
+  </si>
+  <si>
+    <t>Resagging work at Loc. No. 251-267, 312-326. .</t>
+  </si>
+  <si>
+    <t>02-06-2026 19:00:00</t>
   </si>
   <si>
     <t>Ashish Kumar</t>
@@ -418,135 +424,6 @@
     <t>9425805935</t>
   </si>
   <si>
-    <t>MR2605/0477</t>
-  </si>
-  <si>
-    <t>132KV_SHUTDOWN ON 40MVA APEX X-MER AT 132KV S/S KATNI</t>
-  </si>
-  <si>
-    <t>132KV_KATNI</t>
-  </si>
-  <si>
-    <t>Bell tank oil leakage attending work</t>
-  </si>
-  <si>
-    <t>20-05-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>YOGESH PATEL</t>
-  </si>
-  <si>
-    <t>9425808211</t>
-  </si>
-  <si>
-    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_KOTAR</t>
-  </si>
-  <si>
-    <t>For double fitting work</t>
-  </si>
-  <si>
-    <t>26-05-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>10-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mr. R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2605/0635</t>
-  </si>
-  <si>
-    <t>MR2605/0647</t>
-  </si>
-  <si>
-    <t>220KV_160MVA X-MER IMP</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>FOR PRE MANSOON MAINT. &amp; TESTING WORK.</t>
-  </si>
-  <si>
-    <t>ARUN KUMAR KOL</t>
-  </si>
-  <si>
-    <t>8319677721</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA X-mer-II (Make- ABB)</t>
-  </si>
-  <si>
-    <t>220KV_KUKSHI</t>
-  </si>
-  <si>
-    <t>For Pre Monsoon Maintenance work.</t>
-  </si>
-  <si>
-    <t>Er. Manoj Randa</t>
-  </si>
-  <si>
-    <t>9425820034</t>
-  </si>
-  <si>
-    <t>MR2605/0657</t>
-  </si>
-  <si>
-    <t>MR2605/0655</t>
-  </si>
-  <si>
-    <t>132KV_132kV Malanpur - Banmore ckt-I</t>
-  </si>
-  <si>
-    <t>220KV_MALANPUR</t>
-  </si>
-  <si>
-    <t>Line Maintenance work</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2605/0533</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Narsinghpur-Pipariya Line</t>
-  </si>
-  <si>
-    <t>220KV_NARSINGHPUR</t>
-  </si>
-  <si>
-    <t>Resagging work at Loc. No. . 251-267 &amp; 312-326.</t>
-  </si>
-  <si>
-    <t>22-05-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>27-05-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MR2605/0607</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Narsinghpur-Chichli Line</t>
-  </si>
-  <si>
-    <t>Resagging work at Loc. No. 251-267, 312-326. .</t>
-  </si>
-  <si>
-    <t>02-06-2026 19:00:00</t>
-  </si>
-  <si>
     <t>MR2605/0396</t>
   </si>
   <si>
@@ -568,10 +445,43 @@
     <t>7898703187</t>
   </si>
   <si>
-    <t>MR2605/0418</t>
-  </si>
-  <si>
-    <t>400KV_400 KV SSTPH-Pithampur ckt 1 line</t>
+    <t>MR2605/0670</t>
+  </si>
+  <si>
+    <t>220KV_220KV Panagar Birsinghpur</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>Disc F/o Change at loc. 108 Top Ph</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2605/0668</t>
+  </si>
+  <si>
+    <t>220KV_220 KV PITHAMPUR(SEC-3 )- DHAR LINE</t>
+  </si>
+  <si>
+    <t>220KV_PITHAMPUR (SEC-III)</t>
+  </si>
+  <si>
+    <t>Pre monsoon maint.and testing work</t>
+  </si>
+  <si>
+    <t>28-05-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>RAJU DAS BAIRAGI</t>
+  </si>
+  <si>
+    <t>9425801532</t>
   </si>
   <si>
     <t>400KV_PITHAMPUR4</t>
@@ -595,24 +505,6 @@
     <t>400KV_400 KV SSTPH-Pithampur ckt 2 line</t>
   </si>
   <si>
-    <t>MR2605/0648</t>
-  </si>
-  <si>
-    <t>220KV_200MVA XMER T&amp;R</t>
-  </si>
-  <si>
-    <t>220KV_REWA</t>
-  </si>
-  <si>
-    <t>Hot point attending work</t>
-  </si>
-  <si>
-    <t>Kanishka Singh</t>
-  </si>
-  <si>
-    <t>9425804656</t>
-  </si>
-  <si>
     <t>MR2605/0604</t>
   </si>
   <si>
@@ -634,36 +526,39 @@
     <t>Mr.R.K.Prajapati</t>
   </si>
   <si>
-    <t>MR2605/0645</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Nainpur Ckt-IInd</t>
-  </si>
-  <si>
-    <t>220KV_SEONI</t>
-  </si>
-  <si>
-    <t>PG Clamp Removing work</t>
-  </si>
-  <si>
-    <t>27-05-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>MR2605/0651</t>
-  </si>
-  <si>
-    <t>132KV_132/33 KV 40 MVA BBL X-MER</t>
-  </si>
-  <si>
-    <t>132KV_SIDHI1</t>
+    <t>132KV_132 KV SEHORE RLY TRAC. CKT-2</t>
+  </si>
+  <si>
+    <t>132KV_SEHORE</t>
+  </si>
+  <si>
+    <t>LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>NITIN RESHWAL</t>
+  </si>
+  <si>
+    <t>9425804890</t>
+  </si>
+  <si>
+    <t>MR2605/0664</t>
+  </si>
+  <si>
+    <t>MR2605/0666</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV IMP X-MER</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
   </si>
   <si>
     <t>PRE MONSOON MAINTENANCE AND TESTING WORK</t>
   </si>
   <si>
+    <t>28-05-2026 09:00:00</t>
+  </si>
+  <si>
     <t>Shri Vishal Bhaladhare</t>
   </si>
   <si>
@@ -724,97 +619,106 @@
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok, alternate station supply shall be available</t>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>as per system availability</t>
+  </si>
+  <si>
+    <t>work done</t>
+  </si>
+  <si>
+    <t>as per real time load management</t>
   </si>
   <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok</t>
+    <t>ok, after load management</t>
+  </si>
+  <si>
+    <t>control cable shifting work from old cable route to New ECR cable rout</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>ok, timely completion strictly required</t>
+  </si>
+  <si>
+    <t>400KV-BHOPAL-MP-ITARSI-2</t>
+  </si>
+  <si>
+    <t>400KV-SEONI-KIRNAPUR-1</t>
+  </si>
+  <si>
+    <t>220KV-MORENA-MEHGAON-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-1</t>
+  </si>
+  <si>
+    <t>220KV-REWA-SINDHI-MP-2</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-1</t>
+  </si>
+  <si>
+    <t>NHPTL-TESTING-@-NHPTL - 400KV at BINA-NHPTL - 400KV</t>
+  </si>
+  <si>
+    <t>SHUTDOWN TAKEN FOR 400 KV BUS BAR COMMISIONING WORK AT 400KV S/S BHOPAL</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
+  </si>
+  <si>
+    <t>SC TESTING</t>
   </si>
   <si>
     <t>real time</t>
   </si>
   <si>
-    <t>as per system availability</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>work done</t>
-  </si>
-  <si>
-    <t>ok, after real time load management</t>
-  </si>
-  <si>
-    <t>ok, after real time load management, o&amp;m shall be informed for any emergency during the s/d period</t>
-  </si>
-  <si>
-    <t>ok, line to be in service through TBC, Electrical Inspector approval required while charging for Breaker change</t>
-  </si>
-  <si>
-    <t>220KV GUNA - SHIVPURI CIRCUIT-1</t>
-  </si>
-  <si>
-    <t>FOR STRINGING WORK , REMOVAL OF INLINE ERS &amp; NBFC ARRANGEMENT</t>
-  </si>
-  <si>
-    <t>220KV GUNA - SHIVPURI CIRCUIT-2</t>
-  </si>
-  <si>
-    <t>RTAMC WR2</t>
-  </si>
-  <si>
-    <t>ok, through sub ld, EI CHARGING APPROVAL REQUIRED FOR SHIFTING OF LINE ON MAIN TOWERS</t>
-  </si>
-  <si>
-    <t>220KV SHIVPURI- SABHLGARH LINE-1&amp;2</t>
-  </si>
-  <si>
-    <t>AE TLM SHIVPURI</t>
-  </si>
-  <si>
-    <t>SAFE CONDUCTOR LIFTING AND RECTIFICATION WORK</t>
-  </si>
-  <si>
-    <t>132KV BALAGHAT- WARASEONI FEEDER</t>
-  </si>
-  <si>
-    <t>AE 132KV BALAGHAT/ WARASEONI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPR RELAY TESTING </t>
-  </si>
-  <si>
-    <t>ok, line to be in service through TBC</t>
-  </si>
-  <si>
-    <t>220KV-DAMOH-SAGAR-2</t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-1</t>
+    <t>ok, every instructions of WRLDC  to be passed to JP BINA and MP BINA</t>
   </si>
   <si>
     <t>MADHYA PRADESH</t>
   </si>
   <si>
+    <t>MADHYA PRADESH,POWERGRID-WR1 (PGCIL)</t>
+  </si>
+  <si>
     <t>MADHYA PRADESH,NTPC</t>
   </si>
   <si>
-    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
-  </si>
-  <si>
-    <t>OK,  Ckt-1 to be in service. No other element shall be effected. Wr2 to be informed. Load to be managed by SLDC MP in case of contingency.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OK, Ckt-2 to be in service. NTPC to be informed.</t>
-  </si>
-  <si>
-    <t>S/I, JABALPUR</t>
+    <t>NHPTL</t>
+  </si>
+  <si>
+    <t>S/I JABALPUR</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>17:59</t>
   </si>
 </sst>
 </file>
@@ -825,7 +729,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -838,24 +742,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -874,7 +775,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -892,8 +793,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -972,7 +879,44 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -980,7 +924,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -999,11 +945,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1041,6 +996,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1049,29 +1010,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1079,7 +1019,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1445,45 +1412,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="44.5703125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" style="12" customWidth="1"/>
     <col min="6" max="6" width="29.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="46.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="48.140625" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="68.28515625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1495,7 +1462,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="9"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1518,7 +1485,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="9"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1551,20 +1518,20 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="M4" s="10" t="s">
+      <c r="L4" s="17"/>
+      <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46156.701944444445</v>
+        <v>46169.67292824074</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1582,36 +1549,38 @@
         <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46168.623194444444</v>
+        <v>46156.701944444445</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1619,100 +1588,100 @@
         <v>29</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A34" si="0">A6+1</f>
+        <f t="shared" ref="A7:A28" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>46162.508391203701</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46154.485196759262</v>
+        <v>46153.801666666666</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>49</v>
@@ -1720,175 +1689,177 @@
       <c r="L8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46168.442511574074</v>
+        <v>46154.485196759262</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="11" t="s">
         <v>52</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="L9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46167.77621527778</v>
+        <v>46169.468877314815</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46155.566747685189</v>
+        <v>46167.77621527778</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="J11" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="K11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="L11" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46168.586550925924</v>
+        <v>46155.566747685189</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="11" t="s">
+      <c r="G12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="I12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="J12" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1897,646 +1868,646 @@
         <v>46167.715428240743</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="11" t="s">
+      <c r="I13" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="J13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="L13" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46168.53702546296</v>
+        <v>46169.520960648151</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="L14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46168.652951388889</v>
+        <v>46168.553599537037</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E15" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46168.553599537037</v>
+        <v>46157.561793981484</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="L16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46157.561793981484</v>
+        <v>46166.450868055559</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>106</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="I17" s="6" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46166.450868055559</v>
+        <v>46169.596909722219</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="13" t="s">
+        <v>113</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46168.599791666667</v>
+        <v>46167.661944444444</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E19" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46161.498749999999</v>
+        <v>46165.693564814814</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="11" t="s">
+      <c r="L20" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46167.661944444444</v>
+        <v>46157.664976851855</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46168.539942129632</v>
+        <v>46169.622349537036</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46168.691400462965</v>
+        <v>46169.615972222222</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46168.687071759261</v>
+        <v>46158.790833333333</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E24" s="11" t="s">
         <v>159</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46163.56931712963</v>
+        <v>46165.579976851855</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="11" t="s">
+      <c r="J25" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="K25" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="L25" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46165.693564814814</v>
+        <v>46169.551423611112</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="11" t="s">
+      <c r="L26" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="5">
-        <v>46157.664976851855</v>
+        <v>46169.561481481483</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="11" t="s">
+      <c r="F27" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="J27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="L27" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="L27" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" s="5">
-        <v>46158.789317129631</v>
+        <v>46160.781122685185</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="11" t="s">
+      <c r="F28" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="J28" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>186</v>
@@ -2544,509 +2515,293 @@
       <c r="L28" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="M28" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" s="5">
-        <v>46158.790833333333</v>
+        <v>46141.551655092589</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>189</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <f t="shared" si="0"/>
+        <v>191</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="L29" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="M29" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="23">
         <v>26</v>
       </c>
-      <c r="B30" s="5">
-        <v>46168.544108796297</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <f t="shared" si="0"/>
+      <c r="B30" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G30" s="23"/>
+      <c r="H30" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K30" s="26"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="23">
         <v>27</v>
       </c>
-      <c r="B31" s="5">
-        <v>46165.579976851855</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="B31" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K31" s="26"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="23">
+        <v>28</v>
+      </c>
+      <c r="B32" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G32" s="23"/>
+      <c r="H32" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="K32" s="26"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="23">
+        <v>29</v>
+      </c>
+      <c r="B33" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G33" s="23"/>
+      <c r="H33" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="J33" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K33" s="26"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="23">
+        <v>30</v>
+      </c>
+      <c r="B34" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="G34" s="23"/>
+      <c r="H34" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="K34" s="26"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="23">
+        <v>31</v>
+      </c>
+      <c r="B35" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="G35" s="23"/>
+      <c r="H35" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="K35" s="26"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" s="5">
-        <v>46168.469328703701</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" s="5">
-        <v>46168.596030092594</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K33" s="7" t="s">
+    </row>
+    <row r="36" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="23">
+        <v>32</v>
+      </c>
+      <c r="B36" s="24">
+        <v>46169</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="L33" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" s="5">
-        <v>46160.781122685185</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="F36" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="23"/>
+      <c r="H36" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="I34" s="6" t="s">
+      <c r="I36" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="K36" s="26"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
-        <v>31</v>
-      </c>
-      <c r="B35" s="5">
-        <v>46141.551655092589</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="11" t="s">
+    </row>
+    <row r="37" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
-        <v>32</v>
-      </c>
-      <c r="B36" s="5">
-        <v>46168</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J36" s="6">
-        <v>46170.833333333336</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="L36" s="8"/>
-      <c r="M36" s="17" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>33</v>
-      </c>
-      <c r="B37" s="5">
-        <v>46168</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="I37" s="6">
-        <v>46169.625</v>
-      </c>
-      <c r="J37" s="6">
-        <v>46169.708333333336</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
-        <v>34</v>
-      </c>
-      <c r="B38" s="5">
-        <v>46168</v>
-      </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="I38" s="6">
-        <v>46169.416666666664</v>
-      </c>
-      <c r="J38" s="6">
-        <v>46169.75</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
-        <v>35</v>
-      </c>
-      <c r="B39" s="5">
-        <v>46168</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="I39" s="6">
-        <v>46169.458333333336</v>
-      </c>
-      <c r="J39" s="6">
-        <v>46169.708333333336</v>
-      </c>
-      <c r="K39" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
-        <v>36</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="I40" s="6">
-        <v>46169.375</v>
-      </c>
-      <c r="J40" s="6">
-        <v>46169.75</v>
-      </c>
-      <c r="K40" s="7"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="21" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="H41" s="20" t="s">
-        <v>260</v>
-      </c>
-      <c r="I41" s="6">
-        <v>46169.375</v>
-      </c>
-      <c r="J41" s="6">
-        <v>46169.708333333336</v>
-      </c>
-      <c r="K41" s="7"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="21" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="L42" s="25"/>
-      <c r="M42" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="A37:K37"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,20 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$37</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="270">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -133,6 +144,60 @@
     <t>9424445533</t>
   </si>
   <si>
+    <t>MR2605/0690</t>
+  </si>
+  <si>
+    <t>220KV_220 KV PITHAMPUR-BARNAGAR CKT</t>
+  </si>
+  <si>
+    <t>220KV_BADNAGAR</t>
+  </si>
+  <si>
+    <t>CT Tan delta &amp; IR test work</t>
+  </si>
+  <si>
+    <t>29-05-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>29-05-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>RAVI PANDEY</t>
+  </si>
+  <si>
+    <t>9425805296</t>
+  </si>
+  <si>
+    <t>MR2605/0689</t>
+  </si>
+  <si>
+    <t>220KV_INDORE4-BADNAGAR_Ckt</t>
+  </si>
+  <si>
+    <t>29-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0676</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA X Mer Make BBL</t>
+  </si>
+  <si>
+    <t>132KV_BETUL1</t>
+  </si>
+  <si>
+    <t>Pre mansoon maintance</t>
+  </si>
+  <si>
+    <t>29-05-2026 05:00:00</t>
+  </si>
+  <si>
+    <t>VISHAL MALVI</t>
+  </si>
+  <si>
+    <t>9425804955</t>
+  </si>
+  <si>
     <t>MR2605/0506</t>
   </si>
   <si>
@@ -196,25 +261,31 @@
     <t>RK Gayaki</t>
   </si>
   <si>
-    <t>MR2605/0660</t>
-  </si>
-  <si>
-    <t>400KV_50 MVAR LINE REACTOR -2 BHOPAL</t>
-  </si>
-  <si>
-    <t>400KV_BINA4</t>
-  </si>
-  <si>
-    <t>PRE MANSOON MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>28-05-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>P. N. NAMDEO</t>
-  </si>
-  <si>
-    <t>7587951092</t>
+    <t>MR2605/0679</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Birsinghpur -Naurozabad Traction Circuit I</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>For line clearance maintain work</t>
+  </si>
+  <si>
+    <t>29-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0680</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Birsinghpur TPH - Birsinghpur IC No. 04</t>
+  </si>
+  <si>
+    <t>For safe work during shutdown</t>
+  </si>
+  <si>
+    <t>MR2605/0643</t>
   </si>
   <si>
     <t>220KV_11/220KV Substation and its auxiliaries</t>
@@ -238,9 +309,6 @@
     <t>8989156186</t>
   </si>
   <si>
-    <t>MR2605/0642</t>
-  </si>
-  <si>
     <t>11KV_1X20 mw HYDEL UNIT</t>
   </si>
   <si>
@@ -259,6 +327,27 @@
     <t>MR2605/0332</t>
   </si>
   <si>
+    <t>MR2605/0685</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Chhegaon - Khandwa Ckt 1st</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
+  </si>
+  <si>
+    <t>For Jumper Tightening &amp; Other Line Maintenance wor</t>
+  </si>
+  <si>
+    <t>29-05-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>M.K.More</t>
+  </si>
+  <si>
+    <t>9425805258</t>
+  </si>
+  <si>
     <t>MR2605/0639</t>
   </si>
   <si>
@@ -280,129 +369,159 @@
     <t>7587951136</t>
   </si>
   <si>
-    <t>MR2605/0663</t>
-  </si>
-  <si>
-    <t>132KV_132kV Dindori Gorakhpur Line</t>
-  </si>
-  <si>
-    <t>132KV_DINDORI</t>
+    <t>MR2605/0688</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Narsinghpur-Gadarwara Line</t>
+  </si>
+  <si>
+    <t>132KV_GADARWARA</t>
+  </si>
+  <si>
+    <t>Pre - Monsoon Maintenance work.</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
+  </si>
+  <si>
+    <t>MR2605/0649</t>
+  </si>
+  <si>
+    <t>400KV_400 KV ISP-INDORE I</t>
+  </si>
+  <si>
+    <t>400KV_INDIRASAGAR</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE &amp; CHANGE OF SF 6 CIRCUIT BREAKE</t>
+  </si>
+  <si>
+    <t>29-05-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>9575074321</t>
+  </si>
+  <si>
+    <t>MR2605/0380</t>
+  </si>
+  <si>
+    <t>400KV_UNIT#06</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>16-05-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>31-05-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SHRI SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>220KV_220KV JETPURA ASHTA-I CKT</t>
+  </si>
+  <si>
+    <t>220KV_INDORE-II (JETPURA)</t>
+  </si>
+  <si>
+    <t>220KV Ashta - I Feeder overhauling of C.B.</t>
+  </si>
+  <si>
+    <t>25-05-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>DEPPAK GUPTA</t>
+  </si>
+  <si>
+    <t>9425803845</t>
+  </si>
+  <si>
+    <t>MR2605/0612</t>
+  </si>
+  <si>
+    <t>MR2605/0677</t>
+  </si>
+  <si>
+    <t>400KV_INDORE-NAGDA LINE.</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>REPLACEMENT OF SUSPENSION DISC INSULATOR STRING</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_KOTAR</t>
+  </si>
+  <si>
+    <t>For double fitting work</t>
+  </si>
+  <si>
+    <t>26-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>10-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R.K.Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2605/0635</t>
+  </si>
+  <si>
+    <t>MR2605/0686</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER AREVA</t>
+  </si>
+  <si>
+    <t>FOR PRE MANSOON MAINT. &amp; TESTING WORK.</t>
+  </si>
+  <si>
+    <t>ARUN KUMAR KOL</t>
+  </si>
+  <si>
+    <t>8319677721</t>
+  </si>
+  <si>
+    <t>MR2605/0678</t>
+  </si>
+  <si>
+    <t>132KV_132kV Nainpur Baihar Line</t>
+  </si>
+  <si>
+    <t>132KV_NAINPUR</t>
   </si>
   <si>
     <t>Jumper Cone Tightening &amp; Other Maint. Work</t>
   </si>
   <si>
-    <t>28-05-2026 18:00:00</t>
-  </si>
-  <si>
     <t>S.K. BHALADHARE</t>
   </si>
   <si>
     <t>9425807264</t>
   </si>
   <si>
-    <t>MR2605/0649</t>
-  </si>
-  <si>
-    <t>400KV_400 KV ISP-INDORE I</t>
-  </si>
-  <si>
-    <t>400KV_INDIRASAGAR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE &amp; CHANGE OF SF 6 CIRCUIT BREAKE</t>
-  </si>
-  <si>
-    <t>29-05-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>9575074321</t>
-  </si>
-  <si>
-    <t>MR2605/0380</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#06</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE</t>
-  </si>
-  <si>
-    <t>16-05-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>31-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SHRI SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>220KV_220KV JETPURA ASHTA-I CKT</t>
-  </si>
-  <si>
-    <t>220KV_INDORE-II (JETPURA)</t>
-  </si>
-  <si>
-    <t>220KV Ashta - I Feeder overhauling of C.B.</t>
-  </si>
-  <si>
-    <t>25-05-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>DEPPAK GUPTA</t>
-  </si>
-  <si>
-    <t>9425803845</t>
-  </si>
-  <si>
-    <t>MR2605/0612</t>
-  </si>
-  <si>
-    <t>MR2605/0667</t>
-  </si>
-  <si>
-    <t>400KV_500 MVA-400KV/220KV/33KV-T&amp;R-X-Mer-III</t>
-  </si>
-  <si>
-    <t>400KV_JULWANIYA4</t>
-  </si>
-  <si>
-    <t>for Pre monsoon maintenance &amp; Testing work.</t>
-  </si>
-  <si>
-    <t>400Kv S/s Julwaniya</t>
-  </si>
-  <si>
-    <t>8319599488</t>
-  </si>
-  <si>
-    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_KOTAR</t>
-  </si>
-  <si>
-    <t>For double fitting work</t>
-  </si>
-  <si>
-    <t>26-05-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>10-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mr. R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2605/0635</t>
-  </si>
-  <si>
     <t>MR2605/0607</t>
   </si>
   <si>
@@ -418,12 +537,6 @@
     <t>02-06-2026 19:00:00</t>
   </si>
   <si>
-    <t>Ashish Kumar</t>
-  </si>
-  <si>
-    <t>9425805935</t>
-  </si>
-  <si>
     <t>MR2605/0396</t>
   </si>
   <si>
@@ -445,43 +558,10 @@
     <t>7898703187</t>
   </si>
   <si>
-    <t>MR2605/0670</t>
-  </si>
-  <si>
-    <t>220KV_220KV Panagar Birsinghpur</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>Disc F/o Change at loc. 108 Top Ph</t>
-  </si>
-  <si>
-    <t>Jitendra Tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2605/0668</t>
-  </si>
-  <si>
-    <t>220KV_220 KV PITHAMPUR(SEC-3 )- DHAR LINE</t>
-  </si>
-  <si>
-    <t>220KV_PITHAMPUR (SEC-III)</t>
-  </si>
-  <si>
-    <t>Pre monsoon maint.and testing work</t>
-  </si>
-  <si>
-    <t>28-05-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>RAJU DAS BAIRAGI</t>
-  </si>
-  <si>
-    <t>9425801532</t>
+    <t>MR2605/0418</t>
+  </si>
+  <si>
+    <t>400KV_400 KV SSTPH-Pithampur ckt 1 line</t>
   </si>
   <si>
     <t>400KV_PITHAMPUR4</t>
@@ -505,6 +585,33 @@
     <t>400KV_400 KV SSTPH-Pithampur ckt 2 line</t>
   </si>
   <si>
+    <t>MR2605/0683</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ratlam-Nagra Ckt -II both end</t>
+  </si>
+  <si>
+    <t>220KV_RATLAM</t>
+  </si>
+  <si>
+    <t>Pre-monsoon maintenance work.</t>
+  </si>
+  <si>
+    <t>Nikhil Dunge</t>
+  </si>
+  <si>
+    <t>9425801487</t>
+  </si>
+  <si>
+    <t>MR2605/0684</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bus coupler</t>
+  </si>
+  <si>
+    <t>Safety purpose for Aux bus isolator maintenance.</t>
+  </si>
+  <si>
     <t>MR2605/0604</t>
   </si>
   <si>
@@ -526,45 +633,78 @@
     <t>Mr.R.K.Prajapati</t>
   </si>
   <si>
-    <t>132KV_132 KV SEHORE RLY TRAC. CKT-2</t>
-  </si>
-  <si>
-    <t>132KV_SEHORE</t>
-  </si>
-  <si>
-    <t>LINE MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>NITIN RESHWAL</t>
-  </si>
-  <si>
-    <t>9425804890</t>
-  </si>
-  <si>
-    <t>MR2605/0664</t>
-  </si>
-  <si>
-    <t>MR2605/0666</t>
-  </si>
-  <si>
-    <t>220KV_220/132KV IMP X-MER</t>
+    <t>MR2605/0672</t>
+  </si>
+  <si>
+    <t>220KV_220kv Shivpuri Sei Sunshine Ckt -1</t>
+  </si>
+  <si>
+    <t>220KV_SHIVPURI</t>
+  </si>
+  <si>
+    <t>for Relay testing in PSS and GSS end</t>
+  </si>
+  <si>
+    <t>29-05-2026 23:59:00</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2605/0682</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_B.H.E.L._X'mer_1</t>
   </si>
   <si>
     <t>220KV_SIDHI</t>
   </si>
   <si>
-    <t>PRE MONSOON MAINTENANCE AND TESTING WORK</t>
-  </si>
-  <si>
-    <t>28-05-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Shri Vishal Bhaladhare</t>
+    <t>PRE MANSOON MAINTENCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>VISHAL BALADHARE</t>
   </si>
   <si>
     <t>9425804690</t>
   </si>
   <si>
+    <t>MR2605/0687</t>
+  </si>
+  <si>
+    <t>220KV_220kV Tikamgarh-Damoh (PGCIL) Line</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>Flash Over disc replacement</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2605/0681</t>
+  </si>
+  <si>
+    <t>220KV_220KV DAMOH - TIKAMGARH PGCIL LINE</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
     <t>MR2605/0471</t>
   </si>
   <si>
@@ -604,9 +744,6 @@
     <t>04-05-2026 12:00:00</t>
   </si>
   <si>
-    <t>29-05-2026 13:00:00</t>
-  </si>
-  <si>
     <t>shri Santosh chavarasia</t>
   </si>
   <si>
@@ -619,106 +756,94 @@
     <t>ok, through sub ld</t>
   </si>
   <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
     <t>as per system availability</t>
   </si>
   <si>
     <t>work done</t>
   </si>
   <si>
-    <t>as per real time load management</t>
-  </si>
-  <si>
-    <t>sub ld</t>
-  </si>
-  <si>
-    <t>ok, after load management</t>
-  </si>
-  <si>
-    <t>control cable shifting work from old cable route to New ECR cable rout</t>
+    <t>sun shine consent required</t>
   </si>
   <si>
     <t>o&amp;m consent required</t>
   </si>
   <si>
-    <t>ok, timely completion strictly required</t>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 220KV DAMOH - TIKAMGARH PGCIL LINE</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 29.05.2026</t>
+  </si>
+  <si>
+    <t>NHPTL-TESTING-@-NHPTL - 400KV at BINA-NHPTL - 400KV</t>
+  </si>
+  <si>
+    <t>29-May-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:59</t>
+  </si>
+  <si>
+    <t>SC TESTING</t>
+  </si>
+  <si>
+    <t>ok, all the instructions to be passed to JP BINA and MP BINA</t>
+  </si>
+  <si>
+    <t>220KV-DAMOH-TIKAMGAD-1</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-2</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-2</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-1</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
   </si>
   <si>
     <t>400KV-BHOPAL-MP-ITARSI-2</t>
   </si>
   <si>
-    <t>400KV-SEONI-KIRNAPUR-1</t>
-  </si>
-  <si>
-    <t>220KV-MORENA-MEHGAON-1</t>
-  </si>
-  <si>
-    <t>220KV-KHANDWA-CHHANERA-1</t>
-  </si>
-  <si>
-    <t>220KV-REWA-SINDHI-MP-2</t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-1</t>
-  </si>
-  <si>
-    <t>NHPTL-TESTING-@-NHPTL - 400KV at BINA-NHPTL - 400KV</t>
+    <t>28-May-2026</t>
   </si>
   <si>
     <t>SHUTDOWN TAKEN FOR 400 KV BUS BAR COMMISIONING WORK AT 400KV S/S BHOPAL</t>
   </si>
   <si>
-    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
-  </si>
-  <si>
-    <t>SC TESTING</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>ok, every instructions of WRLDC  to be passed to JP BINA and MP BINA</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,POWERGRID-WR1 (PGCIL)</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,NTPC</t>
-  </si>
-  <si>
-    <t>NHPTL</t>
-  </si>
-  <si>
-    <t>S/I JABALPUR</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
-    <t>17:59</t>
+    <t>S/I SLDC JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -726,10 +851,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -763,13 +888,22 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="24"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -789,7 +923,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +934,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -910,55 +1044,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -984,30 +1074,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1019,34 +1106,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1412,55 +1483,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="47.5703125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="52.5703125" customWidth="1"/>
     <col min="6" max="6" width="29.140625" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="48.140625" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="45.85546875" customWidth="1"/>
+    <col min="13" max="13" width="61.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="17"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="D2" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="15"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
@@ -1477,7 +1550,7 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1500,7 +1573,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1518,15 +1591,15 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="17"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1539,7 +1612,7 @@
       <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1548,9 +1621,7 @@
       <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>204</v>
-      </c>
+      <c r="H5" s="4"/>
       <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
@@ -1563,11 +1634,11 @@
       <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1581,7 +1652,7 @@
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1606,31 +1677,29 @@
         <v>35</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A28" si="0">A6+1</f>
+        <f t="shared" ref="A7:A45" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46162.508391203701</v>
+        <v>46170.671550925923</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>39</v>
@@ -1648,1157 +1717,1552 @@
         <v>43</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46153.801666666666</v>
+        <v>46170.659328703703</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46170.456782407404</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
+      <c r="F9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46154.485196759262</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="M9" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46162.508391203701</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="F10" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46169.468877314815</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46153.801666666666</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46167.77621527778</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="L11" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="M11" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46154.485196759262</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46155.566747685189</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>72</v>
+      <c r="E12" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="L12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46170.473437499997</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46167.715428240743</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>79</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46169.520960648151</v>
+        <v>46170.473564814813</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D14" s="4"/>
-      <c r="E14" s="11" t="s">
-        <v>86</v>
+      <c r="E14" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46168.553599537037</v>
+        <v>46167.77648148148</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>93</v>
+      <c r="E15" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="M15" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46157.561793981484</v>
+        <v>46155.566747685189</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46170.576921296299</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="I17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="K17" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="L17" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="M17" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46167.715428240743</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46166.450868055559</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46170.649259259262</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46169.596909722219</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="13" t="s">
+      <c r="F19" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46167.661944444444</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46168.553599537037</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="K20" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="L20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="M20" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46157.561793981484</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46165.693564814814</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46157.664976851855</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>134</v>
+      <c r="E21" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46166.450868055559</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <f t="shared" si="0"/>
+      <c r="D22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="5">
-        <v>46169.622349537036</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="11" t="s">
-        <v>141</v>
+      <c r="E22" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46170.463819444441</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46167.661944444444</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K22" s="7" t="s">
+      <c r="F24" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46169.615972222222</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46158.790833333333</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46170.578599537039</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="L25" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24" s="7" t="s">
+      <c r="M25" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46170.471932870372</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46165.579976851855</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46169.551423611112</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="F26" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="5">
-        <v>46169.561481481483</v>
+        <v>46165.693564814814</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="11" t="s">
-        <v>174</v>
+        <v>162</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>177</v>
+        <v>32</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.781122685185</v>
+        <v>46157.664976851855</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>181</v>
+      <c r="E28" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" s="5">
-        <v>46141.551655092589</v>
+        <v>46158.789317129631</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>189</v>
+      <c r="E29" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46158.790833333333</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46170.572164351855</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46170.574363425927</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46165.579976851855</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="J29" s="19" t="s">
+      <c r="D33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="F33" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="G33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="M29" s="22" t="s">
+      <c r="I33" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46169.694085648145</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46170.539687500001</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46170.589560185188</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46170.488159722219</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46160.781122685185</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23">
-        <v>26</v>
-      </c>
-      <c r="B30" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="I30" s="25" t="s">
+      <c r="E38" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="J30" s="25" t="s">
+      <c r="G38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="26" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23">
-        <v>27</v>
-      </c>
-      <c r="B31" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="23"/>
-      <c r="H31" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I31" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23">
-        <v>28</v>
-      </c>
-      <c r="B32" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G32" s="23"/>
-      <c r="H32" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I32" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="J32" s="25" t="s">
+      <c r="K38" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23">
-        <v>29</v>
-      </c>
-      <c r="B33" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I33" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="J33" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23">
+      <c r="L38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="17">
+        <v>46141.551655092589</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="G39" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B34" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="I34" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23">
-        <v>31</v>
-      </c>
-      <c r="B35" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="I35" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="J35" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="26" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23">
-        <v>32</v>
-      </c>
-      <c r="B36" s="24">
-        <v>46169</v>
-      </c>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="I36" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="26" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="31" t="s">
-        <v>224</v>
-      </c>
+      <c r="H39" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I40" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J40" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K40" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L40" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="M40" s="25" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J41" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K41" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L41" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M41" s="26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J42" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L42" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M42" s="26" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A43" s="16">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J43" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L43" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M43" s="26" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="J44" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="K44" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L44" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="M44" s="26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="16">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="J45" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="K45" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="L45" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="D2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,14 +15,25 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$18</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="281">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -106,6 +117,30 @@
     <t>9424445533</t>
   </si>
   <si>
+    <t>MR2605/0742</t>
+  </si>
+  <si>
+    <t>220KV_50 MVA X-mer make BBL</t>
+  </si>
+  <si>
+    <t>400KV_ASHTA4</t>
+  </si>
+  <si>
+    <t>Attending DC leakage wokt 220 kv cb side</t>
+  </si>
+  <si>
+    <t>01-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>01-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Akram khan</t>
+  </si>
+  <si>
+    <t>9425804695</t>
+  </si>
+  <si>
     <t>MR2605/0720</t>
   </si>
   <si>
@@ -154,6 +189,54 @@
     <t>9407528876</t>
   </si>
   <si>
+    <t>MR2605/0732</t>
+  </si>
+  <si>
+    <t>400KV_50 MVAR Bhopal-2 Line Reactor</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>Premansoon maintenance &amp; Testing work</t>
+  </si>
+  <si>
+    <t>01-06-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>01-06-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>P N NAMDEO</t>
+  </si>
+  <si>
+    <t>7587951092</t>
+  </si>
+  <si>
+    <t>MR2605/0734</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Birsinghpur-Naurozabad Traction Circuit II</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>For Jumper cone tightening &amp; other line maintananc</t>
+  </si>
+  <si>
+    <t>01-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>01-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0735</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Birsinghpur-Birsinghpur TPH IC 03</t>
+  </si>
+  <si>
     <t>11KV_1X20 mw HYDEL UNIT</t>
   </si>
   <si>
@@ -178,10 +261,46 @@
     <t>MR2605/0332</t>
   </si>
   <si>
-    <t>MR2605/0380</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#06</t>
+    <t>MR2605/0719</t>
+  </si>
+  <si>
+    <t>132KV_132 Damoh -Damoh Ckt.-2</t>
+  </si>
+  <si>
+    <t>132KV_DAMOH1</t>
+  </si>
+  <si>
+    <t>Replacemant of line Isolator</t>
+  </si>
+  <si>
+    <t>B K Sahu</t>
+  </si>
+  <si>
+    <t>9425801433</t>
+  </si>
+  <si>
+    <t>MR2605/0740</t>
+  </si>
+  <si>
+    <t>220KV_220 kv gorabazar-amarkantak line</t>
+  </si>
+  <si>
+    <t>220KV_GORABAZAR</t>
+  </si>
+  <si>
+    <t>main 2 dpr relay installation &amp; cable replacement</t>
+  </si>
+  <si>
+    <t>Shri chetan yadav</t>
+  </si>
+  <si>
+    <t>9425805282</t>
+  </si>
+  <si>
+    <t>MR2605/0727</t>
+  </si>
+  <si>
+    <t>400KV_U#05</t>
   </si>
   <si>
     <t>400KV_INDIRASAGAR</t>
@@ -193,19 +312,133 @@
     <t>ANNUAL MAINTENANCE</t>
   </si>
   <si>
-    <t>16-05-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>31-05-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SHRI SANJAY PATEL</t>
+    <t>01-06-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>15-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
   </si>
   <si>
     <t>9575074321</t>
   </si>
   <si>
-    <t>MR2605/0636</t>
+    <t>MR2605/0707</t>
+  </si>
+  <si>
+    <t>132KV_132KV Jabalpur-Shahpura DP Line</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>Stringing of JBP-Shahpura Line</t>
+  </si>
+  <si>
+    <t>01-06-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Rajesh Tiwari</t>
+  </si>
+  <si>
+    <t>7898239595</t>
+  </si>
+  <si>
+    <t>MR2605/0706</t>
+  </si>
+  <si>
+    <t>220KV_220kv Jabalpur-Narsinghpur CKT-II</t>
+  </si>
+  <si>
+    <t>Stringing of 132KV Sahpura-JBP line</t>
+  </si>
+  <si>
+    <t>20-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0718</t>
+  </si>
+  <si>
+    <t>220KV_220KV 160MVA X MER NO-II (BBL)</t>
+  </si>
+  <si>
+    <t>220KV_JULWANIYA</t>
+  </si>
+  <si>
+    <t>Pre Monsson Mainteanance work</t>
+  </si>
+  <si>
+    <t>01-06-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>01-06-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Executive  Engineer</t>
+  </si>
+  <si>
+    <t>9425806931</t>
+  </si>
+  <si>
+    <t>MR2605/0721</t>
+  </si>
+  <si>
+    <t>132KV_132 KV KATNI - KAYMORE LINE CKT - 1st &amp; 2nd</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>Re-sagging  of  Conductor and  other line maintena</t>
+  </si>
+  <si>
+    <t>10-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2605/0736</t>
+  </si>
+  <si>
+    <t>400KV_400KV DAMOH - KATNI LINE</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2605/0743</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_ECE_X'mer_1</t>
+  </si>
+  <si>
+    <t>132KV_KATRA</t>
+  </si>
+  <si>
+    <t>For hot point attending work</t>
+  </si>
+  <si>
+    <t>01-06-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>Mr. Kaniska Singh</t>
+  </si>
+  <si>
+    <t>9425804656</t>
   </si>
   <si>
     <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
@@ -229,6 +462,27 @@
     <t>9407070182</t>
   </si>
   <si>
+    <t>MR2605/0635</t>
+  </si>
+  <si>
+    <t>MR2605/0729</t>
+  </si>
+  <si>
+    <t>220KV_220kv Malanpur Auraiya lin e</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>Old insulator replacement work &amp; Line maintainance</t>
+  </si>
+  <si>
+    <t>Baidyanath Bhattacyarya</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
     <t>220KV_220KV Nagda-Ujjain Ckt-I Line</t>
   </si>
   <si>
@@ -247,6 +501,15 @@
     <t>9425806905</t>
   </si>
   <si>
+    <t>MR2605/0739</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ujjain Nagda ckt-2 line</t>
+  </si>
+  <si>
+    <t>Re sagging work</t>
+  </si>
+  <si>
     <t>MR2605/0722</t>
   </si>
   <si>
@@ -274,25 +537,127 @@
     <t>9425805935</t>
   </si>
   <si>
-    <t>MR2605/0418</t>
-  </si>
-  <si>
-    <t>400KV_400 KV SSTPH-Pithampur ckt 1 line</t>
+    <t>MR2605/0728</t>
+  </si>
+  <si>
+    <t>220KV_50MVAR REACTOR T&amp;R</t>
+  </si>
+  <si>
+    <t>220KV_PANDHURNA</t>
+  </si>
+  <si>
+    <t>Premansoon Maintenance work</t>
+  </si>
+  <si>
+    <t>S.R. Shende</t>
+  </si>
+  <si>
+    <t>9425811447</t>
+  </si>
+  <si>
+    <t>MR2605/0379</t>
+  </si>
+  <si>
+    <t>220KV_PANDHURNA BETUL PGCIL</t>
+  </si>
+  <si>
+    <t>RESAGGING WORK BETWEEN LOC. NO. 178-194</t>
+  </si>
+  <si>
+    <t>06-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>MR2605/0733</t>
+  </si>
+  <si>
+    <t>220KV_RAJGARH-PG-PITHAMPUR (SEC-III)_Ckt</t>
+  </si>
+  <si>
+    <t>220KV_PITHAMPUR (SEC-III)</t>
+  </si>
+  <si>
+    <t>RYB PH LA REPLACMENT AND BAY MAINT.WORK</t>
+  </si>
+  <si>
+    <t>RAJU DAS BAIRAGI</t>
+  </si>
+  <si>
+    <t>9425801532</t>
+  </si>
+  <si>
+    <t>MR2605/0709</t>
+  </si>
+  <si>
+    <t>220KV_220KV Super Corridor-1</t>
   </si>
   <si>
     <t>400KV_PITHAMPUR4</t>
   </si>
   <si>
-    <t>Tower Restrengthening work on cross arm.</t>
-  </si>
-  <si>
-    <t>17-05-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>MR2605/0419</t>
-  </si>
-  <si>
-    <t>400KV_400 KV SSTPH-Pithampur ckt 2 line</t>
+    <t>For Pre-monsoon maintenance &amp; Testing work</t>
+  </si>
+  <si>
+    <t>Rajudas Bairagi</t>
+  </si>
+  <si>
+    <t>MR2605/0708</t>
+  </si>
+  <si>
+    <t>220KV_220KV Pithampur-Depalpur line</t>
+  </si>
+  <si>
+    <t>01-06-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0737</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ratlam - Badnawar-II</t>
+  </si>
+  <si>
+    <t>220KV_RATLAM</t>
+  </si>
+  <si>
+    <t>Premonsoon maintenance work</t>
+  </si>
+  <si>
+    <t>NIKHIL DUNGE</t>
+  </si>
+  <si>
+    <t>9425801487</t>
+  </si>
+  <si>
+    <t>MR2605/0738</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bus coupler</t>
+  </si>
+  <si>
+    <t>Safety purpose for Aux bus isolator maint. work.</t>
+  </si>
+  <si>
+    <t>MR2605/0731</t>
+  </si>
+  <si>
+    <t>220KV_160mva xmer Areva</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For premansoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
   </si>
   <si>
     <t>MR2605/0726</t>
@@ -301,52 +666,85 @@
     <t>220KV_220  kv Satna (MPPTCL)  â¿¿  Kotar  line</t>
   </si>
   <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
     <t>For double  fitting work</t>
   </si>
   <si>
     <t>09-06-2026 19:00:00</t>
   </si>
   <si>
-    <t>MR2605/0673</t>
-  </si>
-  <si>
-    <t>220KV_220kv Shivpuri Sei Sunshine Ckt -1</t>
+    <t>MR2605/0741</t>
+  </si>
+  <si>
+    <t>220KV_220 KV SHIVPURI SEI SUN SHINE CKT IST &amp; IIND</t>
   </si>
   <si>
     <t>220KV_SHIVPURI</t>
   </si>
   <si>
+    <t>ON REQUEST OF SUN SHINEN FOR MCT/MPT TESTING WORK</t>
+  </si>
+  <si>
+    <t>01-06-2026 23:59:00</t>
+  </si>
+  <si>
+    <t>ER. SURAJ PAWAR</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2605/0675</t>
+  </si>
+  <si>
+    <t>220KV_220kv Shivpuri Sei Sunshine Ckt -2</t>
+  </si>
+  <si>
     <t>for Relay testing in PSS and GSS end</t>
   </si>
   <si>
-    <t>31-05-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>31-05-2026 23:59:00</t>
-  </si>
-  <si>
     <t>Suraj Pawar</t>
   </si>
   <si>
-    <t>9425814079</t>
-  </si>
-  <si>
-    <t>MR2605/0725</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Sukha-Narsinghpur Line Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_SUKHA</t>
-  </si>
-  <si>
-    <t>Pre - Monsoon Maintenance work.</t>
-  </si>
-  <si>
-    <t>31-05-2026 10:00:00</t>
+    <t>MR2605/0730</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA X-Mer no.2 make TELK</t>
+  </si>
+  <si>
+    <t>132KV_SULTANPUR</t>
+  </si>
+  <si>
+    <t>for OLTC Tank OIL  Filtration &amp; Replacement work</t>
+  </si>
+  <si>
+    <t>B.L.Lakhore</t>
+  </si>
+  <si>
+    <t>7587951074</t>
+  </si>
+  <si>
+    <t>MR2605/0472</t>
+  </si>
+  <si>
+    <t>132KV_220kv _Unit No 1</t>
+  </si>
+  <si>
+    <t>220KV_TONS</t>
+  </si>
+  <si>
+    <t>Replacement of hydraulic power pack with new one</t>
+  </si>
+  <si>
+    <t>01-06-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>05-07-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>Mr CL KIRADE</t>
+  </si>
+  <si>
+    <t>9301373521</t>
   </si>
   <si>
     <t>MR2605/0471</t>
@@ -355,67 +753,130 @@
     <t>132KV_220kv_Unit #3</t>
   </si>
   <si>
-    <t>220KV_TONS</t>
-  </si>
-  <si>
-    <t>Replacement of hydraulic power pack with new one</t>
-  </si>
-  <si>
     <t>27-05-2026 00:00:00</t>
   </si>
   <si>
-    <t>01-06-2026 00:00:00</t>
-  </si>
-  <si>
     <t>Mr C L KIRADE</t>
   </si>
   <si>
-    <t>9301373521</t>
-  </si>
-  <si>
     <t>deferred</t>
   </si>
   <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
     <t>as per system availability</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>work done</t>
-  </si>
-  <si>
-    <t>deferred from site</t>
-  </si>
-  <si>
-    <t>sunshine consent required</t>
-  </si>
-  <si>
-    <t>ok, 132kv Shahpura-Shrinagar ckt to be opened for load management</t>
-  </si>
-  <si>
-    <t>??::???::::</t>
-  </si>
-  <si>
-    <t>:&gt;17:48::&gt;</t>
+    <t>deferred, not in WR list</t>
+  </si>
+  <si>
+    <t>element not clear</t>
+  </si>
+  <si>
+    <t>ok, through sub ld, sub ld shall monitor loading of depalpur</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>deferred by site</t>
+  </si>
+  <si>
+    <t>sun shine consent required</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 220kv Satna PG-Maihar ckt</t>
+  </si>
+  <si>
+    <t>400KV-DAMOH-KATNI-1</t>
+  </si>
+  <si>
+    <t>400KV-BADNAWAR-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>400KV/220KV ITARSI-ICT-1</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-MAIHAR-1</t>
   </si>
   <si>
     <t>132KV-VSTPS-WAIDHAN-1</t>
   </si>
   <si>
+    <t>220KV-SEONI-PG-CHINDWARA-2</t>
+  </si>
+  <si>
+    <t>POWERGRID_WR2</t>
+  </si>
+  <si>
     <t>MP_SLDC</t>
   </si>
   <si>
-    <t>FOR REPLACEMENT OF CONDUCTOR WITH HTLS CONDUCTOR</t>
+    <t>POWERGRID_WR1</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>16:59</t>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>AMP work of 400KV Katni #1 Line Reactor</t>
+  </si>
+  <si>
+    <t>For attending hotspot in Isolator, Dia to be kept open at both ends.</t>
+  </si>
+  <si>
+    <t>For Air cell discharge checking and AMP works, Dia to be kept open at both sides.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>For AMP work @ Seoni SS</t>
+  </si>
+  <si>
+    <t>WR</t>
   </si>
 </sst>
 </file>
@@ -439,25 +900,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -466,7 +923,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,17 +932,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -534,6 +986,19 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -561,6 +1026,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -575,44 +1051,68 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,46 +1477,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="40.140625" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="44.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.5703125" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="64.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="5"/>
+    <col min="2" max="2" width="11.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11" style="5" customWidth="1"/>
+    <col min="5" max="5" width="52.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="29" style="5" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="46.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12" style="5" customWidth="1"/>
+    <col min="13" max="13" width="52.7109375" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>46173</v>
+      <c r="B2" s="6">
+        <v>46174</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1031,16 +1533,16 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1"/>
@@ -1054,653 +1556,1747 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="7" t="s">
+      <c r="L4" s="4"/>
+      <c r="M4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+    <row r="5" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <v>46156.701944444445</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <f>A5+1</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46173.623379629629</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <f t="shared" ref="A7:A47" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46172.580011574071</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46154.485196759262</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46173.543344907404</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46173.556828703702</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46173.559930555559</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46155.566747685189</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46172.542766203704</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46173.602986111109</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46172.729803240742</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46171.786412037036</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46171.784594907411</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46172.48269675926</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46172.591562499998</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46172.580011574071</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="F19" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46173.565300925926</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46173.668275462966</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="9">
+        <v>46167.661944444444</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46173.45994212963</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="9">
+        <v>46173.600844907407</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46172.596203703702</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="9">
+        <v>46165.693564814814</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="9">
+        <v>46173.267222222225</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="9">
+        <v>46157.552314814813</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46173.556527777779</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46172.378298611111</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="B31" s="9">
+        <v>46172.376840277779</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46173.589502314811</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46173.590925925928</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46173.51017361111</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46172.680532407408</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="10" t="s">
+      <c r="E35" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G35" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="H35" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="B36" s="9">
+        <v>46173.615717592591</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="B37" s="9">
+        <v>46169.700381944444</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="M6" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46154.485196759262</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B38" s="14">
+        <v>46173.502662037034</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="B39" s="19">
+        <v>46160.785312499997</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="B40" s="19">
+        <v>46160.781122685185</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="B41" s="21"/>
+      <c r="C41" s="22">
+        <v>309323</v>
+      </c>
+      <c r="D41" s="21"/>
+      <c r="E41" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H41" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="I41" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="J41" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="B42" s="21"/>
+      <c r="C42" s="22">
+        <v>309419</v>
+      </c>
+      <c r="D42" s="21"/>
+      <c r="E42" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="I42" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="J42" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="B43" s="21"/>
+      <c r="C43" s="22">
+        <v>309931</v>
+      </c>
+      <c r="D43" s="21"/>
+      <c r="E43" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="B44" s="21"/>
+      <c r="C44" s="22">
+        <v>310246</v>
+      </c>
+      <c r="D44" s="21"/>
+      <c r="E44" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H44" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="B45" s="21"/>
+      <c r="C45" s="22">
+        <v>310247</v>
+      </c>
+      <c r="D45" s="21"/>
+      <c r="E45" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="J45" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46155.566747685189</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="22">
+        <v>310352</v>
+      </c>
+      <c r="D46" s="21"/>
+      <c r="E46" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H46" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="J46" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11">
-        <v>46157.561793981484</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11">
-        <v>46167.662141203706</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11">
-        <v>46172.596203703702</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11">
-        <v>46165.693564814814</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>9</v>
-      </c>
-      <c r="B13" s="11">
-        <v>46158.789317129631</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>10</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46158.790833333333</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>11</v>
-      </c>
-      <c r="B15" s="11">
-        <v>46172.680532407408</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>12</v>
-      </c>
-      <c r="B16" s="11">
-        <v>46169.695844907408</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:38" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11">
-        <v>46172.640740740739</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:38" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
-        <v>14</v>
-      </c>
-      <c r="B18" s="11">
-        <v>46160.781122685185</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:38" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>15</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14">
-        <v>303149</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="AL20" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="AK21" t="s">
-        <v>125</v>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22">
+        <v>308196</v>
+      </c>
+      <c r="D47" s="21"/>
+      <c r="E47" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="J47" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="23" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -772,9 +772,6 @@
     <t>deferred due to high SSTPS generation</t>
   </si>
   <si>
-    <t>ok, through sub ld, approved from 8-16 only</t>
-  </si>
-  <si>
     <t>ok, timely normalisation is required</t>
   </si>
   <si>
@@ -857,6 +854,9 @@
   </si>
   <si>
     <t xml:space="preserve">REAL TIME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deferred , DUE TO RELAIBILTY ISSUE , PGCIL MAY EXPLOR OTHER OPTION FOR AVAILING THE SHUTDOWN </t>
   </si>
 </sst>
 </file>
@@ -867,7 +867,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -905,6 +905,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1075,7 +1082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1152,34 +1159,37 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1555,15 +1565,15 @@
     <col min="2" max="2" width="11.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" style="4" customWidth="1"/>
     <col min="4" max="4" width="8" style="4" customWidth="1"/>
-    <col min="5" max="5" width="51.5703125" style="32" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="51.5703125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" style="33" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="32" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="33" customWidth="1"/>
     <col min="9" max="9" width="12" style="4" customWidth="1"/>
     <col min="10" max="10" width="11.7109375" style="4" customWidth="1"/>
     <col min="11" max="11" width="11.140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="6.140625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="44.28515625" style="32" customWidth="1"/>
+    <col min="13" max="13" width="44.28515625" style="33" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
@@ -1593,15 +1603,15 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="26"/>
+      <c r="H2" s="27"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="26"/>
+      <c r="M2" s="27"/>
     </row>
     <row r="3" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1616,15 +1626,15 @@
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="26"/>
+      <c r="H3" s="27"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="26"/>
+      <c r="M3" s="27"/>
     </row>
     <row r="4" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1639,16 +1649,16 @@
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="28" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="28" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1661,7 +1671,7 @@
         <v>15</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="28" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1678,16 +1688,16 @@
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="28" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="28" t="s">
         <v>246</v>
       </c>
       <c r="I5" s="17" t="s">
@@ -1702,7 +1712,7 @@
       <c r="L5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="28" t="s">
         <v>247</v>
       </c>
     </row>
@@ -1718,16 +1728,16 @@
         <v>26</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="28" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="28" t="s">
         <v>29</v>
       </c>
       <c r="I6" s="17" t="s">
@@ -1742,8 +1752,8 @@
       <c r="L6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="27" t="s">
-        <v>250</v>
+      <c r="M6" s="28" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1758,16 +1768,16 @@
         <v>34</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="28" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="28" t="s">
         <v>36</v>
       </c>
       <c r="I7" s="17" t="s">
@@ -1782,7 +1792,7 @@
       <c r="L7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="28" t="s">
         <v>239</v>
       </c>
     </row>
@@ -1800,16 +1810,16 @@
       <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="28" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="28" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="17" t="s">
@@ -1824,7 +1834,7 @@
       <c r="L8" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="28" t="s">
         <v>235</v>
       </c>
     </row>
@@ -1842,16 +1852,16 @@
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="28" t="s">
         <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="28" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="17" t="s">
@@ -1866,7 +1876,7 @@
       <c r="L9" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="28" t="s">
         <v>235</v>
       </c>
     </row>
@@ -1884,16 +1894,16 @@
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>55</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="28" t="s">
         <v>56</v>
       </c>
       <c r="I10" s="17" t="s">
@@ -1908,7 +1918,7 @@
       <c r="L10" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="28" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1924,16 +1934,16 @@
         <v>62</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="28" t="s">
         <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="27" t="s">
+      <c r="H11" s="28" t="s">
         <v>65</v>
       </c>
       <c r="I11" s="17" t="s">
@@ -1948,7 +1958,7 @@
       <c r="L11" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="28" t="s">
         <v>236</v>
       </c>
     </row>
@@ -1966,16 +1976,16 @@
       <c r="D12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="28" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="28" t="s">
         <v>72</v>
       </c>
       <c r="I12" s="17" t="s">
@@ -1990,7 +2000,7 @@
       <c r="L12" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="28" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2006,16 +2016,16 @@
         <v>77</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="28" t="s">
         <v>79</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="H13" s="28" t="s">
         <v>80</v>
       </c>
       <c r="I13" s="17" t="s">
@@ -2030,7 +2040,7 @@
       <c r="L13" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="M13" s="28" t="s">
         <v>238</v>
       </c>
     </row>
@@ -2046,16 +2056,16 @@
         <v>85</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="28" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="H14" s="28" t="s">
         <v>88</v>
       </c>
       <c r="I14" s="17" t="s">
@@ -2070,7 +2080,7 @@
       <c r="L14" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="27" t="s">
+      <c r="M14" s="28" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2088,16 +2098,16 @@
       <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="28" t="s">
         <v>87</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="28" t="s">
         <v>94</v>
       </c>
       <c r="I15" s="17" t="s">
@@ -2112,7 +2122,7 @@
       <c r="L15" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="M15" s="27" t="s">
+      <c r="M15" s="28" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2128,16 +2138,16 @@
         <v>106</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="28" t="s">
         <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="28" t="s">
         <v>102</v>
       </c>
       <c r="I16" s="17" t="s">
@@ -2152,7 +2162,7 @@
       <c r="L16" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="27" t="s">
+      <c r="M16" s="28" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2170,16 +2180,16 @@
       <c r="D17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="28" t="s">
         <v>109</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="27" t="s">
+      <c r="H17" s="28" t="s">
         <v>110</v>
       </c>
       <c r="I17" s="17" t="s">
@@ -2194,7 +2204,7 @@
       <c r="L17" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="28" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2210,16 +2220,16 @@
         <v>114</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="28" t="s">
         <v>116</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="27" t="s">
+      <c r="H18" s="28" t="s">
         <v>117</v>
       </c>
       <c r="I18" s="17" t="s">
@@ -2234,7 +2244,7 @@
       <c r="L18" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="M18" s="27" t="s">
+      <c r="M18" s="28" t="s">
         <v>245</v>
       </c>
     </row>
@@ -2252,16 +2262,16 @@
       <c r="D19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="28" t="s">
         <v>121</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="27" t="s">
+      <c r="H19" s="28" t="s">
         <v>122</v>
       </c>
       <c r="I19" s="17" t="s">
@@ -2276,7 +2286,7 @@
       <c r="L19" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="M19" s="27" t="s">
+      <c r="M19" s="28" t="s">
         <v>243</v>
       </c>
     </row>
@@ -2292,16 +2302,16 @@
         <v>128</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="28" t="s">
         <v>130</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H20" s="27" t="s">
+      <c r="H20" s="28" t="s">
         <v>132</v>
       </c>
       <c r="I20" s="17" t="s">
@@ -2316,7 +2326,7 @@
       <c r="L20" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="M20" s="27" t="s">
+      <c r="M20" s="28" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2332,16 +2342,16 @@
         <v>135</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="28" t="s">
         <v>137</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="H21" s="28" t="s">
         <v>138</v>
       </c>
       <c r="I21" s="17" t="s">
@@ -2356,7 +2366,7 @@
       <c r="L21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="M21" s="27" t="s">
+      <c r="M21" s="28" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2374,16 +2384,16 @@
       <c r="D22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="28" t="s">
         <v>143</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="28" t="s">
         <v>144</v>
       </c>
       <c r="I22" s="17" t="s">
@@ -2398,8 +2408,8 @@
       <c r="L22" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="M22" s="27" t="s">
-        <v>249</v>
+      <c r="M22" s="26" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2416,16 +2426,16 @@
       <c r="D23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="F23" s="28" t="s">
         <v>143</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H23" s="27" t="s">
+      <c r="H23" s="28" t="s">
         <v>151</v>
       </c>
       <c r="I23" s="17" t="s">
@@ -2440,8 +2450,8 @@
       <c r="L23" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="M23" s="27" t="s">
-        <v>249</v>
+      <c r="M23" s="26" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2458,16 +2468,16 @@
       <c r="D24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="28" t="s">
         <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="27" t="s">
+      <c r="H24" s="28" t="s">
         <v>156</v>
       </c>
       <c r="I24" s="17" t="s">
@@ -2482,7 +2492,7 @@
       <c r="L24" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="M24" s="27" t="s">
+      <c r="M24" s="28" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2500,16 +2510,16 @@
       <c r="D25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="28" t="s">
         <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="27" t="s">
+      <c r="H25" s="28" t="s">
         <v>163</v>
       </c>
       <c r="I25" s="17" t="s">
@@ -2524,7 +2534,7 @@
       <c r="L25" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="M25" s="27" t="s">
+      <c r="M25" s="28" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2540,16 +2550,16 @@
         <v>168</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="28" t="s">
         <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="27" t="s">
+      <c r="H26" s="28" t="s">
         <v>171</v>
       </c>
       <c r="I26" s="17" t="s">
@@ -2564,7 +2574,7 @@
       <c r="L26" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="M26" s="27" t="s">
+      <c r="M26" s="28" t="s">
         <v>241</v>
       </c>
     </row>
@@ -2580,16 +2590,16 @@
         <v>174</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="28" t="s">
         <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H27" s="27" t="s">
+      <c r="H27" s="28" t="s">
         <v>176</v>
       </c>
       <c r="I27" s="17" t="s">
@@ -2604,7 +2614,7 @@
       <c r="L27" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="M27" s="27" t="s">
+      <c r="M27" s="28" t="s">
         <v>241</v>
       </c>
     </row>
@@ -2620,16 +2630,16 @@
         <v>179</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="28" t="s">
         <v>181</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="28" t="s">
         <v>182</v>
       </c>
       <c r="I28" s="17" t="s">
@@ -2644,7 +2654,7 @@
       <c r="L28" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="M28" s="27" t="s">
+      <c r="M28" s="28" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2660,16 +2670,16 @@
         <v>185</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="28" t="s">
         <v>187</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="27" t="s">
+      <c r="H29" s="28" t="s">
         <v>188</v>
       </c>
       <c r="I29" s="17" t="s">
@@ -2684,7 +2694,7 @@
       <c r="L29" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="M29" s="27" t="s">
+      <c r="M29" s="28" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2702,16 +2712,16 @@
       <c r="D30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="28" t="s">
         <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="27" t="s">
+      <c r="H30" s="28" t="s">
         <v>194</v>
       </c>
       <c r="I30" s="17" t="s">
@@ -2726,7 +2736,7 @@
       <c r="L30" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="M30" s="27" t="s">
+      <c r="M30" s="28" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2742,16 +2752,16 @@
         <v>197</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="28" t="s">
         <v>199</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="H31" s="28" t="s">
         <v>200</v>
       </c>
       <c r="I31" s="17" t="s">
@@ -2766,7 +2776,7 @@
       <c r="L31" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="M31" s="27" t="s">
+      <c r="M31" s="28" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2782,16 +2792,16 @@
         <v>203</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="28" t="s">
         <v>205</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H32" s="27" t="s">
+      <c r="H32" s="28" t="s">
         <v>206</v>
       </c>
       <c r="I32" s="17" t="s">
@@ -2806,7 +2816,7 @@
       <c r="L32" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="M32" s="27" t="s">
+      <c r="M32" s="28" t="s">
         <v>244</v>
       </c>
     </row>
@@ -2822,16 +2832,16 @@
         <v>210</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="28" t="s">
         <v>212</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="27" t="s">
+      <c r="H33" s="28" t="s">
         <v>213</v>
       </c>
       <c r="I33" s="17" t="s">
@@ -2846,7 +2856,7 @@
       <c r="L33" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="M33" s="27" t="s">
+      <c r="M33" s="28" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2864,16 +2874,16 @@
       <c r="D34" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="28" t="s">
         <v>218</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="H34" s="28" t="s">
         <v>219</v>
       </c>
       <c r="I34" s="17" t="s">
@@ -2888,7 +2898,7 @@
       <c r="L34" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="M34" s="27" t="s">
+      <c r="M34" s="28" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2904,16 +2914,16 @@
         <v>224</v>
       </c>
       <c r="D35" s="6"/>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="29" t="s">
         <v>226</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="29" t="s">
         <v>227</v>
       </c>
       <c r="I35" s="21" t="s">
@@ -2928,7 +2938,7 @@
       <c r="L35" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="M35" s="28" t="s">
+      <c r="M35" s="29" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2944,16 +2954,16 @@
         <v>230</v>
       </c>
       <c r="D36" s="7"/>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="30" t="s">
         <v>226</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H36" s="29" t="s">
+      <c r="H36" s="30" t="s">
         <v>232</v>
       </c>
       <c r="I36" s="25" t="s">
@@ -2968,7 +2978,7 @@
       <c r="L36" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="M36" s="29" t="s">
+      <c r="M36" s="30" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2982,32 +2992,32 @@
         <v>311686</v>
       </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="F37" s="30">
+      <c r="E37" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="F37" s="31">
         <v>220</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H37" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
+      </c>
+      <c r="H37" s="31" t="s">
+        <v>259</v>
       </c>
       <c r="I37" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="K37" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="L37" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="K37" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="M37" s="33" t="s">
-        <v>275</v>
+      <c r="M37" s="34" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3020,32 +3030,32 @@
         <v>309799</v>
       </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="F38" s="30">
+      <c r="E38" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="F38" s="31">
         <v>400</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="H38" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>260</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J38" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="L38" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="K38" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="M38" s="33" t="s">
-        <v>275</v>
+      <c r="M38" s="34" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3058,32 +3068,32 @@
         <v>309935</v>
       </c>
       <c r="D39" s="8"/>
-      <c r="E39" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="F39" s="30">
+      <c r="E39" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="F39" s="31">
         <v>220</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="H39" s="34" t="s">
-        <v>262</v>
+        <v>258</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>261</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J39" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="L39" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="K39" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="M39" s="33" t="s">
-        <v>276</v>
+      <c r="M39" s="34" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3096,32 +3106,32 @@
         <v>310257</v>
       </c>
       <c r="D40" s="8"/>
-      <c r="E40" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="F40" s="30">
+      <c r="E40" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="F40" s="31">
         <v>220</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H40" s="34" t="s">
-        <v>263</v>
+        <v>257</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>262</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="M40" s="33" t="s">
-        <v>277</v>
+        <v>272</v>
+      </c>
+      <c r="M40" s="34" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3134,32 +3144,32 @@
         <v>310258</v>
       </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="F41" s="30">
+      <c r="E41" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" s="31">
         <v>220</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>264</v>
+        <v>257</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>263</v>
       </c>
       <c r="I41" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J41" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="J41" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="K41" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L41" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="M41" s="33" t="s">
-        <v>276</v>
+        <v>273</v>
+      </c>
+      <c r="M41" s="34" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="87" customHeight="1" x14ac:dyDescent="0.25">
@@ -3172,32 +3182,32 @@
         <v>310355</v>
       </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="F42" s="30">
+      <c r="E42" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="F42" s="31">
         <v>132</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H42" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="J42" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="K42" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="M42" s="33" t="s">
-        <v>276</v>
+        <v>272</v>
+      </c>
+      <c r="M42" s="34" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3210,32 +3220,32 @@
         <v>310256</v>
       </c>
       <c r="D43" s="8"/>
-      <c r="E43" s="30" t="s">
+      <c r="E43" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="F43" s="31">
+        <v>220</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="F43" s="30">
-        <v>220</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H43" s="34" t="s">
-        <v>264</v>
+      <c r="H43" s="35" t="s">
+        <v>263</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K43" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="M43" s="33" t="s">
-        <v>275</v>
+        <v>272</v>
+      </c>
+      <c r="M43" s="34" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3243,180 +3253,180 @@
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
       <c r="G44" s="8"/>
-      <c r="H44" s="31"/>
+      <c r="H44" s="32"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
-      <c r="M44" s="31"/>
+      <c r="M44" s="32"/>
     </row>
     <row r="45" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
       <c r="G45" s="8"/>
-      <c r="H45" s="31"/>
+      <c r="H45" s="32"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
-      <c r="M45" s="31"/>
+      <c r="M45" s="32"/>
     </row>
     <row r="46" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
       <c r="G46" s="8"/>
-      <c r="H46" s="31"/>
+      <c r="H46" s="32"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
-      <c r="M46" s="31"/>
+      <c r="M46" s="32"/>
     </row>
     <row r="47" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
       <c r="G47" s="8"/>
-      <c r="H47" s="31"/>
+      <c r="H47" s="32"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
-      <c r="M47" s="31"/>
+      <c r="M47" s="32"/>
     </row>
     <row r="48" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
       <c r="G48" s="8"/>
-      <c r="H48" s="31"/>
+      <c r="H48" s="32"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
-      <c r="M48" s="31"/>
+      <c r="M48" s="32"/>
     </row>
     <row r="49" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
       <c r="G49" s="8"/>
-      <c r="H49" s="31"/>
+      <c r="H49" s="32"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
-      <c r="M49" s="31"/>
+      <c r="M49" s="32"/>
     </row>
     <row r="50" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
       <c r="G50" s="8"/>
-      <c r="H50" s="31"/>
+      <c r="H50" s="32"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
-      <c r="M50" s="31"/>
+      <c r="M50" s="32"/>
     </row>
     <row r="51" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
       <c r="G51" s="8"/>
-      <c r="H51" s="31"/>
+      <c r="H51" s="32"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
-      <c r="M51" s="31"/>
+      <c r="M51" s="32"/>
     </row>
     <row r="52" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
       <c r="G52" s="8"/>
-      <c r="H52" s="31"/>
+      <c r="H52" s="32"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
-      <c r="M52" s="31"/>
+      <c r="M52" s="32"/>
     </row>
     <row r="53" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
       <c r="G53" s="8"/>
-      <c r="H53" s="31"/>
+      <c r="H53" s="32"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
-      <c r="M53" s="31"/>
+      <c r="M53" s="32"/>
     </row>
     <row r="54" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
       <c r="G54" s="8"/>
-      <c r="H54" s="31"/>
+      <c r="H54" s="32"/>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
-      <c r="M54" s="31"/>
+      <c r="M54" s="32"/>
     </row>
     <row r="55" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
       <c r="G55" s="8"/>
-      <c r="H55" s="31"/>
+      <c r="H55" s="32"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
-      <c r="M55" s="31"/>
+      <c r="M55" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,25 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$25</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$36</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="259">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -117,22 +106,22 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2606/0127</t>
-  </si>
-  <si>
-    <t>220KV_220kV Bhopal-Interconnector Ckt I</t>
+    <t>MR2606/0096</t>
+  </si>
+  <si>
+    <t>220KV_220kV Bhopal-Mandideep line</t>
   </si>
   <si>
     <t>400KV_BHOPAL4</t>
   </si>
   <si>
-    <t>Stringing of broken OPGW</t>
-  </si>
-  <si>
-    <t>07-06-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>07-06-2026 18:00:00</t>
+    <t>Disc insulator replacement work</t>
+  </si>
+  <si>
+    <t>05-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>10-06-2026 18:00:00</t>
   </si>
   <si>
     <t>Ankit Mehrolya</t>
@@ -141,21 +130,6 @@
     <t>9425804506</t>
   </si>
   <si>
-    <t>MR2606/0096</t>
-  </si>
-  <si>
-    <t>220KV_220kV Bhopal-Mandideep line</t>
-  </si>
-  <si>
-    <t>Disc insulator replacement work</t>
-  </si>
-  <si>
-    <t>05-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>10-06-2026 18:00:00</t>
-  </si>
-  <si>
     <t>MR2605/0301</t>
   </si>
   <si>
@@ -180,211 +154,526 @@
     <t>9407528876</t>
   </si>
   <si>
-    <t>MR2606/0136</t>
-  </si>
-  <si>
-    <t>400KV_NEW 315 MVA Transformer no. -04</t>
-  </si>
-  <si>
-    <t>400KV_BINA4</t>
-  </si>
-  <si>
-    <t>for trapped air removed</t>
-  </si>
-  <si>
-    <t>P.N. NAMDEO</t>
-  </si>
-  <si>
-    <t>7587951092</t>
-  </si>
-  <si>
-    <t>MR2606/0107</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Datia(220 KV) Dabra</t>
-  </si>
-  <si>
-    <t>220KV_DATIA</t>
-  </si>
-  <si>
-    <t>765 KV power line crossing work</t>
+    <t>MR2606/0123</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Chhegaon - Nepa Line</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>For Flash over disc replacement &amp; Line Maint.Work</t>
+  </si>
+  <si>
+    <t>08-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>08-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>M.K.More</t>
+  </si>
+  <si>
+    <t>9425805258</t>
+  </si>
+  <si>
+    <t>MR2606/0122</t>
+  </si>
+  <si>
+    <t>132KV_132kV Dindori Gorakhpur Line</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>Jumper Cone Tightening &amp; Other Maint. Work</t>
+  </si>
+  <si>
+    <t>08-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2606/0142</t>
+  </si>
+  <si>
+    <t>220KV_160MVA X-MER MAKE BHEL</t>
+  </si>
+  <si>
+    <t>220KV_GUDGAON2</t>
+  </si>
+  <si>
+    <t>oil leakage attending work</t>
+  </si>
+  <si>
+    <t>ER SANJAY KUMAR PAWAR</t>
+  </si>
+  <si>
+    <t>9425802293</t>
+  </si>
+  <si>
+    <t>MR2605/0727</t>
+  </si>
+  <si>
+    <t>400KV_U#05</t>
+  </si>
+  <si>
+    <t>400KV_INDIRASAGAR</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>01-06-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>15-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>9575074321</t>
+  </si>
+  <si>
+    <t>MR2606/0147</t>
+  </si>
+  <si>
+    <t>132KV_132KV Jabalpur VFJ Ckt 1</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>After Resagging Work Removal Conductor Roller  at</t>
+  </si>
+  <si>
+    <t>08-06-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2606/0146</t>
+  </si>
+  <si>
+    <t>132KV_132KV Jabalpur Vinoba Bhave Line</t>
+  </si>
+  <si>
+    <t>08-06-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>08-06-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>20-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Rajesh Tiwari</t>
+  </si>
+  <si>
+    <t>7898239595</t>
+  </si>
+  <si>
+    <t>MR2605/0706</t>
+  </si>
+  <si>
+    <t>220KV_220kv Jabalpur-Narsinghpur CKT-II</t>
+  </si>
+  <si>
+    <t>Stringing of 132KV Sahpura-JBP line</t>
+  </si>
+  <si>
+    <t>01-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>MR2606/0120</t>
+  </si>
+  <si>
+    <t>132KV_132 kv katni - kaymore line ckt - 2nd</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>Re-sagging  of Conductor and other line maint.</t>
   </si>
   <si>
     <t>06-06-2026 09:00:00</t>
   </si>
   <si>
-    <t>07-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Satish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>9425806916</t>
-  </si>
-  <si>
-    <t>MR2605/0727</t>
-  </si>
-  <si>
-    <t>400KV_U#05</t>
-  </si>
-  <si>
-    <t>400KV_INDIRASAGAR</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE</t>
-  </si>
-  <si>
-    <t>01-06-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>15-06-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>9575074321</t>
-  </si>
-  <si>
-    <t>MR2606/0028</t>
-  </si>
-  <si>
-    <t>220KV_220KV Jabalpur-Narsingpur CKT-II</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>erection &amp; stringing work of 132 Jabalpur-Shahpura</t>
-  </si>
-  <si>
-    <t>03-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>20-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Rajesh Tiwari</t>
-  </si>
-  <si>
-    <t>7898239595</t>
-  </si>
-  <si>
-    <t>MR2606/0090</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Jabalpur- VFJ -I</t>
-  </si>
-  <si>
-    <t>Conductor Shifting on ERS  to New erected tower</t>
+    <t>Manoj Kumar Tiwari</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2606/0129</t>
+  </si>
+  <si>
+    <t>400KV_400kV Kirnapur Bhilai Line</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Suspension Calmp Tightening &amp; Other Maint. Work</t>
+  </si>
+  <si>
+    <t>12-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_KOTAR</t>
+  </si>
+  <si>
+    <t>For double fitting work</t>
+  </si>
+  <si>
+    <t>26-05-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>10-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R.K.Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2605/0635</t>
+  </si>
+  <si>
+    <t>MR2606/0134</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA 132/33KV BBL X-MER</t>
+  </si>
+  <si>
+    <t>132KV_KOTMA</t>
+  </si>
+  <si>
+    <t>OLTC OIL REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>08-06-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>RAM NARESH SINGH GOND</t>
+  </si>
+  <si>
+    <t>9425801257</t>
+  </si>
+  <si>
+    <t>MR2606/0143</t>
+  </si>
+  <si>
+    <t>400KV_400kV  500MVA  ICT (CGL)</t>
+  </si>
+  <si>
+    <t>400KV_MANDSOUR4</t>
+  </si>
+  <si>
+    <t>400kV B- Phase Centre break Isolator Jha (Male-Fem</t>
+  </si>
+  <si>
+    <t>C P Dhakad</t>
+  </si>
+  <si>
+    <t>7587951067</t>
+  </si>
+  <si>
+    <t>132KV_MANERI</t>
+  </si>
+  <si>
+    <t>CHETAN YADAV</t>
+  </si>
+  <si>
+    <t>9425805282</t>
+  </si>
+  <si>
+    <t>MR2606/0156</t>
+  </si>
+  <si>
+    <t>132KV_40MVA X-MER BBL</t>
+  </si>
+  <si>
+    <t>PAIMTING &amp; ASSOCIATED WORK</t>
+  </si>
+  <si>
+    <t>MR2606/0152</t>
+  </si>
+  <si>
+    <t>132KV_MANGLIYA-RAUKHEDI LINE.</t>
+  </si>
+  <si>
+    <t>132KV_MANGLIA</t>
+  </si>
+  <si>
+    <t>BROKEN  DISC INSULATOR STRING REPLACEMENT WORK.</t>
+  </si>
+  <si>
+    <t>08-06-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2606/0155</t>
+  </si>
+  <si>
+    <t>220KV_220KV Mehgaon Auriya line</t>
+  </si>
+  <si>
+    <t>220KV_MEHGAON</t>
+  </si>
+  <si>
+    <t>Old Insulator replacement work &amp;</t>
+  </si>
+  <si>
+    <t>08-06-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>Baidyanath Kumar</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
+    <t>MR2606/0002</t>
+  </si>
+  <si>
+    <t>220KV_220 KV-GENERATING UNIT # 5</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR</t>
+  </si>
+  <si>
+    <t>Annual maintenance f Generating Unit # 5</t>
+  </si>
+  <si>
+    <t>01-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Sharma</t>
+  </si>
+  <si>
+    <t>7389491599</t>
+  </si>
+  <si>
+    <t>MR2605/0716</t>
+  </si>
+  <si>
+    <t>400KV_400KV Pithampur-Badnawar Ckt-II</t>
+  </si>
+  <si>
+    <t>400KV_PITHAMPUR4</t>
+  </si>
+  <si>
+    <t>Pre Monsoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>Rajudas bairagi</t>
+  </si>
+  <si>
+    <t>9425801532</t>
+  </si>
+  <si>
+    <t>MR2606/0151</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ratlam-Nagra-II ckt.</t>
+  </si>
+  <si>
+    <t>220KV_RATLAM</t>
+  </si>
+  <si>
+    <t>) Overhaulling work of Sf6 Circuit Breaker of 220K</t>
+  </si>
+  <si>
+    <t>Nikhil Dunge</t>
+  </si>
+  <si>
+    <t>9425801487</t>
+  </si>
+  <si>
+    <t>MR2606/0153</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bus coupler</t>
+  </si>
+  <si>
+    <t>Safety purpose for Aux bus isolator maintenance wo</t>
+  </si>
+  <si>
+    <t>NIKHIL DUNGE</t>
+  </si>
+  <si>
+    <t>MR2606/0150</t>
+  </si>
+  <si>
+    <t>132KV_MSP(DEWAS)â¿¿RAUKHEDI LINE</t>
+  </si>
+  <si>
+    <t>132KV_RAUKHEDI</t>
+  </si>
+  <si>
+    <t>220KV_50 MVA XMER BBL 220/33 KV</t>
+  </si>
+  <si>
+    <t>400KV_SAGAR</t>
+  </si>
+  <si>
+    <t>NIFPS VALVE CHANGED &amp; TESTING WORK.</t>
+  </si>
+  <si>
+    <t>Shri Srajan Sisodiya .</t>
+  </si>
+  <si>
+    <t>7879960164</t>
+  </si>
+  <si>
+    <t>MR2606/0140</t>
+  </si>
+  <si>
+    <t>MR2606/0126</t>
+  </si>
+  <si>
+    <t>132KV_JETPURA-SANWER LINE.</t>
+  </si>
+  <si>
+    <t>132KV_SANWER</t>
+  </si>
+  <si>
+    <t>JUMPER CONE  TIGHTING &amp; OTHER MAINTENANCE WORK.</t>
+  </si>
+  <si>
+    <t>MR2606/0125</t>
+  </si>
+  <si>
+    <t>220KV_220  kV Satna (MPPTCL)  â¿¿  Ajaygarh line</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For double  fitting work</t>
   </si>
   <si>
     <t>07-06-2026 08:00:00</t>
   </si>
   <si>
-    <t>Jitendra Tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2606/0120</t>
-  </si>
-  <si>
-    <t>132KV_132 kv katni - kaymore line ckt - 2nd</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>Re-sagging  of Conductor and other line maint.</t>
-  </si>
-  <si>
-    <t>Manoj Kumar Tiwari</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>220KV_220 KV  Kotar - Tons Ckt-II</t>
-  </si>
-  <si>
-    <t>220KV_KOTAR</t>
-  </si>
-  <si>
-    <t>For double fitting work</t>
-  </si>
-  <si>
-    <t>26-05-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>10-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mr. R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2605/0635</t>
-  </si>
-  <si>
-    <t>MR2606/0133</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA 132/33KV BHEL X-MER</t>
-  </si>
-  <si>
-    <t>132KV_KOTMA</t>
-  </si>
-  <si>
-    <t>OLTC OIL REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>07-06-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>RAM NARESH SINGH GOND</t>
-  </si>
-  <si>
-    <t>9425801257</t>
-  </si>
-  <si>
-    <t>MR2606/0137</t>
-  </si>
-  <si>
-    <t>220KV_220KV Mehgaon Auraiya line</t>
-  </si>
-  <si>
-    <t>220KV_MEHGAON</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Insulator replacement work &amp; other maintenance wor</t>
-  </si>
-  <si>
-    <t>07-06-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>Baidyanath Kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
-  </si>
-  <si>
-    <t>MR2606/0131</t>
-  </si>
-  <si>
-    <t>220KV_220KV UJJAIN NAGDA CKT 2</t>
-  </si>
-  <si>
-    <t>400KV_NAGDA4</t>
+    <t>09-06-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>MR2606/0141</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Satna  â¿¿  Satna IC â¿¿II  line</t>
+  </si>
+  <si>
+    <t>07-06-2026 05:00:00</t>
+  </si>
+  <si>
+    <t>12-06-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>MR2605/0726</t>
+  </si>
+  <si>
+    <t>220KV_220  kv Satna (MPPTCL)  â¿¿  Kotar  line</t>
+  </si>
+  <si>
+    <t>31-05-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>MR2606/0154</t>
+  </si>
+  <si>
+    <t>132KV_132kV Seoni Pench Ckt II</t>
+  </si>
+  <si>
+    <t>132KV_SEONI1</t>
+  </si>
+  <si>
+    <t>Line maintenance work</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2606/0124</t>
+  </si>
+  <si>
+    <t>400KV_400KV Singaji to Chhegaon Ckt-01</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI TPS</t>
+  </si>
+  <si>
+    <t>Preventive maintenance of isolators &amp; ckt breakers</t>
+  </si>
+  <si>
+    <t>Yogesh Chouhan</t>
+  </si>
+  <si>
+    <t>7999328631</t>
+  </si>
+  <si>
+    <t>MR2605/0472</t>
+  </si>
+  <si>
+    <t>132KV_220kv _Unit No 1</t>
+  </si>
+  <si>
+    <t>220KV_TONS</t>
+  </si>
+  <si>
+    <t>Replacement of hydraulic power pack with new one</t>
+  </si>
+  <si>
+    <t>01-06-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>05-07-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>Mr CL KIRADE</t>
+  </si>
+  <si>
+    <t>9301373521</t>
+  </si>
+  <si>
+    <t>MR2606/0157</t>
+  </si>
+  <si>
+    <t>220KV_220KV UJJAIN NAGDA CKT 1</t>
+  </si>
+  <si>
+    <t>400KV_UJJAIN4</t>
   </si>
   <si>
     <t>RE SAGGING WORK</t>
@@ -396,163 +685,79 @@
     <t>9425805295</t>
   </si>
   <si>
-    <t>MR2606/0027</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
-  </si>
-  <si>
-    <t>220KV_NEEMUCH</t>
-  </si>
-  <si>
-    <t>765KV Power Line Crossing Work</t>
-  </si>
-  <si>
-    <t>03-06-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>07-06-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2606/0026</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur circuit Ist</t>
-  </si>
-  <si>
-    <t>765KV Power line crossing work</t>
-  </si>
-  <si>
-    <t>Gaurav  Goyal</t>
-  </si>
-  <si>
-    <t>MR2606/0002</t>
-  </si>
-  <si>
-    <t>220KV_220 KV-GENERATING UNIT # 5</t>
-  </si>
-  <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
-    <t>Annual maintenance f Generating Unit # 5</t>
-  </si>
-  <si>
-    <t>01-06-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Sharma</t>
-  </si>
-  <si>
-    <t>7389491599</t>
-  </si>
-  <si>
-    <t>MR2606/0125</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>For double  fitting work</t>
-  </si>
-  <si>
-    <t>09-06-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MR2605/0726</t>
-  </si>
-  <si>
-    <t>31-05-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>MR2605/0472</t>
-  </si>
-  <si>
-    <t>132KV_220kv _Unit No 1</t>
-  </si>
-  <si>
-    <t>220KV_TONS</t>
-  </si>
-  <si>
-    <t>Replacement of hydraulic power pack with new one</t>
-  </si>
-  <si>
-    <t>01-06-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>05-07-2026 00:00:00</t>
-  </si>
-  <si>
-    <t>Mr CL KIRADE</t>
-  </si>
-  <si>
-    <t>9301373521</t>
-  </si>
-  <si>
-    <t>MR2606/0135</t>
-  </si>
-  <si>
-    <t>220KV_160MVA X-MER-3 BHEL</t>
-  </si>
-  <si>
-    <t>220KV_VIDISHA</t>
-  </si>
-  <si>
-    <t>FOR AIR RELEASE WORK</t>
-  </si>
-  <si>
-    <t>07-06-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>SHRI A A QURESHI</t>
-  </si>
-  <si>
-    <t>9425804318</t>
-  </si>
-  <si>
     <t>deferred</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>deferred due to s/d on 220kV Bhopal-Interconnector Ckt I</t>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>as per system availability</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>deferred by site</t>
+  </si>
+  <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>as per system availability</t>
-  </si>
-  <si>
-    <t>ok, Charging approval will be required during charging the line</t>
-  </si>
-  <si>
-    <t>deferred by site</t>
-  </si>
-  <si>
-    <t>o&amp;m consnet required</t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>220KV_220  kV Satna (MPPTCL)  -Ajaygarh line</t>
-  </si>
-  <si>
-    <t>220KV_220  kv Satna (MPPTCL)  -Kotar  line</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 07.06.2026</t>
+    <t>ok, allowed between 8-14hrs only</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 400kV Kirnapur Bhilai Line</t>
+  </si>
+  <si>
+    <t>real time, if possible try to schedule it after 18hrs</t>
+  </si>
+  <si>
+    <t>ok, charging approval of Electrical Inspector required while charging both lines</t>
+  </si>
+  <si>
+    <t>ok, charging approval of Electrical Inspector required while charging</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 08.06.2026</t>
+  </si>
+  <si>
+    <t>400KV/220KV JABALPUR-ICT-2</t>
+  </si>
+  <si>
+    <t>POWERGRID-WR2 (PGCIL)</t>
+  </si>
+  <si>
+    <t>08-Jun-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09-Jun-2026</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>400KV-KIRNAPUR-BHILAI-1</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH,CHATTISGARH</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR INSTALLATION OF VIBRATION DAMPER (VD) AT VARIOUS LOCATION  </t>
   </si>
   <si>
     <t>220KV-MEHGAON-AURIYA-1</t>
@@ -561,40 +766,37 @@
     <t>NLDC,MADHYA PRADESH</t>
   </si>
   <si>
-    <t>07-Jun-2026</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
   </si>
   <si>
+    <t>220KV-MORENA-MORENA-MP-1</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
     <t>220KV-SATNA-MAIHAR-1</t>
   </si>
   <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
     <t>08:00</t>
   </si>
   <si>
     <t>19:00</t>
   </si>
   <si>
-    <t>work completed</t>
+    <t>220KV-INDORE-INDORE NORTH ZONE-1</t>
+  </si>
+  <si>
+    <t>SHUTDOWN REQUIRED FOR REPLACEMENT OF DIFECTIVE DISC INSULATORS IN INDUSTIRAL AREA</t>
   </si>
   <si>
     <t>132KV-VSTPS-WAIDHAN-1</t>
   </si>
   <si>
     <t>MADHYA PRADESH,NTPC</t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
@@ -608,7 +810,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -643,21 +845,13 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -677,7 +871,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -802,7 +996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -860,6 +1054,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -867,7 +1064,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1233,20 +1430,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="43" customWidth="1"/>
+    <col min="5" max="5" width="47.140625" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" customWidth="1"/>
+    <col min="8" max="8" width="47.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="41.140625" customWidth="1"/>
+    <col min="13" max="13" width="46.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
@@ -1271,20 +1468,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="14"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="13" t="s">
+        <v>232</v>
+      </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
       <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1349,7 +1546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1387,21 +1584,23 @@
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46179.529340277775</v>
+        <v>46177.595046296294</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
@@ -1427,25 +1626,25 @@
         <v>34</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A28" si="0">A6+1</f>
+        <f t="shared" ref="A7:A43" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46177.595046296294</v>
+        <v>46154.485196759262</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>29</v>
@@ -1454,149 +1653,145 @@
         <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46154.485196759262</v>
+        <v>46179.480717592596</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46179.690092592595</v>
+        <v>46179.478321759256</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46178.524976851855</v>
+        <v>46180.395474537036</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1605,194 +1800,192 @@
         <v>46172.729803240742</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46175.55263888889</v>
+        <v>46180.528402777774</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46177.576956018522</v>
+        <v>46180.526643518519</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>82</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46178.685173611113</v>
+        <v>46171.784594907411</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46167.661944444444</v>
+        <v>46178.685173611113</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>96</v>
@@ -1801,178 +1994,180 @@
         <v>97</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46179.664363425924</v>
+        <v>46179.582986111112</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>102</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>103</v>
       </c>
       <c r="K16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46167.661944444444</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="F17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46179.694409722222</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
+      <c r="I17" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="J17" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="K17" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="L17" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="M17" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46179.687222222223</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46179.653402777774</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="7" t="s">
+      <c r="L18" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="M18" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46180.459826388891</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46175.522037037037</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="L19" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="J19" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="M19" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46175.519976851851</v>
+        <v>46180.638206018521</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>128</v>
@@ -1984,7 +2179,7 @@
         <v>129</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>21</v>
@@ -1993,368 +2188,931 @@
         <v>130</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>127</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46174.30568287037</v>
+        <v>46180.561863425923</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="J21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J21" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="M21" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46180.62</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46179.522175925929</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>140</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>141</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46172.680532407408</v>
+        <v>46174.30568287037</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.785312499997</v>
+        <v>46172.397696759261</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>41</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M24" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46180.559861111113</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46180.561874999999</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <f t="shared" si="0"/>
+      <c r="F26" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="17">
-        <v>46179.687881944446</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" s="16" t="s">
+      <c r="H26" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46180.556226851855</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46179.705243055556</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46179.524085648147</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46179.522175925929</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="18" t="s">
+      <c r="L30" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46179.773912037039</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46172.680532407408</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46180.562037037038</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46179.518518518518</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="J25" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="L25" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="G27" s="21"/>
-      <c r="H27" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="M27" s="23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <f t="shared" si="0"/>
+      <c r="B35" s="5">
+        <v>46160.785312499997</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" s="17">
+        <v>46180.646631944444</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="21"/>
-      <c r="H28" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="M28" s="23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
+      <c r="K36" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="21">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="G37" s="22"/>
+      <c r="H37" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J37" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K37" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="L37" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="M37" s="24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="21">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L38" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="M38" s="24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="21">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="22"/>
+      <c r="H39" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="M39" s="24" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A40" s="21">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G40" s="22"/>
+      <c r="H40" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="K40" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L40" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="M40" s="24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="21">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G41" s="22"/>
+      <c r="H41" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J41" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K41" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="M41" s="24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="21">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="G42" s="22"/>
+      <c r="H42" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="M42" s="24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A43" s="21">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="22"/>
+      <c r="H43" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K43" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="M43" s="24" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="25" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="D2:L2"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$43</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$48</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="286">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,7 +76,7 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2606/0462</t>
+    <t>MR2606/0470</t>
   </si>
   <si>
     <t>132KV_132 KV ASHTA SEHORE LINE</t>
@@ -88,537 +88,615 @@
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>LINE MAINTENANCE WORK</t>
+    <t>LINE MAINTENANE WORK</t>
+  </si>
+  <si>
+    <t>25-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>25-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>NITIN RESHWAL</t>
+  </si>
+  <si>
+    <t>9425804890</t>
+  </si>
+  <si>
+    <t>MR2606/0434</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_BADNAWAR KANWAN  BOTH CKT HOTLINE PERMIT</t>
+  </si>
+  <si>
+    <t>400KV_BADNAWAR</t>
+  </si>
+  <si>
+    <t>HOTLINE ONLINE PERMIT FOR OPGW STRINGING ,</t>
+  </si>
+  <si>
+    <t>23-06-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>15-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>K SACHINDRA</t>
+  </si>
+  <si>
+    <t>9425805295</t>
+  </si>
+  <si>
+    <t>MR2606/0477</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220KV BUS TIE</t>
+  </si>
+  <si>
+    <t>220KV_BAIRAGARH</t>
+  </si>
+  <si>
+    <t>OVER HAULING OF CB</t>
+  </si>
+  <si>
+    <t>25-06-2026 09:29:00</t>
+  </si>
+  <si>
+    <t>01-07-2026 17:30:00</t>
+  </si>
+  <si>
+    <t>AMBARISH SHRIPAD JOSHI</t>
+  </si>
+  <si>
+    <t>7587951085</t>
+  </si>
+  <si>
+    <t>MR2606/0493</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bus 1</t>
+  </si>
+  <si>
+    <t>220KV_BHOPAL</t>
+  </si>
+  <si>
+    <t>To attend hot point</t>
+  </si>
+  <si>
+    <t>25-06-2026 07:30:00</t>
+  </si>
+  <si>
+    <t>25-06-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>A K Jain</t>
+  </si>
+  <si>
+    <t>9425806899</t>
+  </si>
+  <si>
+    <t>MR2606/0492</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Bus Tie Bay</t>
+  </si>
+  <si>
+    <t>To attend hot point due to damaged conductor</t>
+  </si>
+  <si>
+    <t>MR2605/0301</t>
+  </si>
+  <si>
+    <t>400KV_Bus-Bar</t>
+  </si>
+  <si>
+    <t>400KV_BHOPAL4</t>
+  </si>
+  <si>
+    <t>For Commissioning of New 400kV Bus-Bar Panel</t>
+  </si>
+  <si>
+    <t>13-05-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>30-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>RK Gayaki</t>
+  </si>
+  <si>
+    <t>9407528876</t>
+  </si>
+  <si>
+    <t>MR2606/0494</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bus 2 with bus Tie</t>
+  </si>
+  <si>
+    <t>To attend hot point due to damaged dropper conduct</t>
+  </si>
+  <si>
+    <t>25-06-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>25-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>MR2606/0479</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bina -IC-II</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>F/o disc insulater replacement at old loc no 13T</t>
+  </si>
+  <si>
+    <t>25-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Dilip Singh Walkey</t>
+  </si>
+  <si>
+    <t>9425804578</t>
+  </si>
+  <si>
+    <t>MR2606/0484</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Chhindwara-Amarwara</t>
+  </si>
+  <si>
+    <t>220KV_CHHINDWARA</t>
+  </si>
+  <si>
+    <t>F/o replacement &amp; Jumper tightening work</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2606/0473</t>
+  </si>
+  <si>
+    <t>220KV_220KV traction-2 Feeder</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>Bay Maintenance work</t>
+  </si>
+  <si>
+    <t>25-06-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>M.K.Choubey</t>
+  </si>
+  <si>
+    <t>9425801424</t>
+  </si>
+  <si>
+    <t>MR2606/0486</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Indore Bay C.B.</t>
+  </si>
+  <si>
+    <t>220KV_DEWAS</t>
+  </si>
+  <si>
+    <t>Hot point attand</t>
+  </si>
+  <si>
+    <t>A.K.Joshi</t>
+  </si>
+  <si>
+    <t>9425801305</t>
+  </si>
+  <si>
+    <t>MR2606/0472</t>
+  </si>
+  <si>
+    <t>132KV_132kV Dindori Gorakhpur Line</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>Jumper Cone Tightening &amp; Other Maint. Work</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2606/0482</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Gwalior-II - Hastinapur Both Ckt.</t>
+  </si>
+  <si>
+    <t>132KV_HASTINAPUR</t>
+  </si>
+  <si>
+    <t>OPGW stringing work of above line</t>
+  </si>
+  <si>
+    <t>25-06-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Er. Ranjeet Kumar</t>
+  </si>
+  <si>
+    <t>9425805309</t>
+  </si>
+  <si>
+    <t>MR2606/0476</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Hoshangabad-Mandideep</t>
+  </si>
+  <si>
+    <t>220KV_HOSHANGABAD</t>
+  </si>
+  <si>
+    <t>Resagging work loc.no. 1-7 &amp; 81-88R</t>
+  </si>
+  <si>
+    <t>27-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Ashutosh Rai</t>
+  </si>
+  <si>
+    <t>9425806902</t>
+  </si>
+  <si>
+    <t>MR2606/0292</t>
+  </si>
+  <si>
+    <t>400KV_UNIT#03</t>
+  </si>
+  <si>
+    <t>400KV_INDIRASAGAR</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>ANNUAL MAINTENANCE</t>
+  </si>
+  <si>
+    <t>16-06-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>SANJAY PATEL</t>
+  </si>
+  <si>
+    <t>9575074321</t>
+  </si>
+  <si>
+    <t>MR2606/0435</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Jabalpur- Tejgarh</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>Modification/shifting at loc. 62- 63</t>
+  </si>
+  <si>
+    <t>23-06-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>29-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2606/0490</t>
+  </si>
+  <si>
+    <t>132KV_132 KV JBP- MADHOTAL NO. 02</t>
+  </si>
+  <si>
+    <t>PRE MONSOON MAINTENENACE &amp; TESTING WOEK.</t>
+  </si>
+  <si>
+    <t>D.N. PODDAR</t>
+  </si>
+  <si>
+    <t>9425805034</t>
+  </si>
+  <si>
+    <t>MR2606/0491</t>
+  </si>
+  <si>
+    <t>400KV_400/132/33KV 100MVA X-MER -II MAKE BHEL</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>PRE-MONSOON MAINT. WORK</t>
+  </si>
+  <si>
+    <t>SANDEEP DAMAHE</t>
+  </si>
+  <si>
+    <t>9425805009</t>
+  </si>
+  <si>
+    <t>MR2606/0478</t>
+  </si>
+  <si>
+    <t>220KV_220KV Malanpur Auraiya line</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Insulator replacement work</t>
+  </si>
+  <si>
+    <t>25-06-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>Baidyanath kumar</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
+    <t>MR2606/0474</t>
+  </si>
+  <si>
+    <t>132KV_40MVA BBL-I X-MER &amp; 40 MVA BBL-II X-MER</t>
+  </si>
+  <si>
+    <t>132KV_MANGAWAN</t>
+  </si>
+  <si>
+    <t>MAINTINANCE OF 33KV MAIN BUS</t>
+  </si>
+  <si>
+    <t>25-06-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>KANISHKA SINGH</t>
+  </si>
+  <si>
+    <t>9425804656</t>
+  </si>
+  <si>
+    <t>MR2606/0488</t>
+  </si>
+  <si>
+    <t>132KV_132KV MORWA-BARGAWAN (TBCB) CKT-I</t>
+  </si>
+  <si>
+    <t>132KV_MORWA</t>
+  </si>
+  <si>
+    <t>FLASH OVER DISC REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>G.L SAHU</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2606/0487</t>
+  </si>
+  <si>
+    <t>400KV_ISP - NAGDA LINE.</t>
+  </si>
+  <si>
+    <t>400KV_NAGDA4</t>
+  </si>
+  <si>
+    <t>FOR BROKEN  DISC INSULATOR STRING REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2606/0475</t>
+  </si>
+  <si>
+    <t>220KV_220 Kv Nimrani Julwaniya Line</t>
+  </si>
+  <si>
+    <t>220KV_NIMRANI</t>
+  </si>
+  <si>
+    <t>For CT Tan Delta Measurement work</t>
+  </si>
+  <si>
+    <t>25-06-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>Shri Pradip Patidar</t>
+  </si>
+  <si>
+    <t>9425801217</t>
+  </si>
+  <si>
+    <t>MR2606/0372</t>
+  </si>
+  <si>
+    <t>220KV_Unit # 6</t>
+  </si>
+  <si>
+    <t>220KV_OMKARESHWAR</t>
+  </si>
+  <si>
+    <t>Annual maintenance</t>
+  </si>
+  <si>
+    <t>19-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>Bhanu pratap Pal</t>
+  </si>
+  <si>
+    <t>7898703187</t>
+  </si>
+  <si>
+    <t>MR2606/0485</t>
+  </si>
+  <si>
+    <t>220KV_Main BUS-A with BUS coupler</t>
+  </si>
+  <si>
+    <t>Annual Maintenance Bus A Isolator &amp; CB of U#6</t>
+  </si>
+  <si>
+    <t>PANKAJ SHARMA</t>
+  </si>
+  <si>
+    <t>MR2606/0480</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL X-MER II</t>
+  </si>
+  <si>
+    <t>132KV_PAWAI</t>
+  </si>
+  <si>
+    <t>Sefty reason for 132 KV B/C 3No. CT REPLACEMENT</t>
+  </si>
+  <si>
+    <t>RN UPADHYAY</t>
+  </si>
+  <si>
+    <t>9425802349</t>
+  </si>
+  <si>
+    <t>MR2606/0471</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 160MVA BHEL X-Mer-I</t>
+  </si>
+  <si>
+    <t>220KV_RATANGARH</t>
+  </si>
+  <si>
+    <t>Minor DC leakage attending work</t>
+  </si>
+  <si>
+    <t>25-06-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
+  </si>
+  <si>
+    <t>MR2606/0439</t>
+  </si>
+  <si>
+    <t>132KV_132KV Sabalgarh Sheopur Ckt-2 Tap To Khandar</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2606/0481</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 160MVA IMP X-MER</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>NIFPS INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>SHRI VISHAL BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425804690</t>
+  </si>
+  <si>
+    <t>MR2606/0489</t>
+  </si>
+  <si>
+    <t>132KV_HANDIYA-SULTANPUR_Ckt</t>
+  </si>
+  <si>
+    <t>132KV_SULTANPUR</t>
+  </si>
+  <si>
+    <t>132 KV main Bus to Existin 132KV Main Bus fly over</t>
+  </si>
+  <si>
+    <t>25-06-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>25-06-2026 15:30:00</t>
+  </si>
+  <si>
+    <t>B.L.Lakhore</t>
+  </si>
+  <si>
+    <t>7587951074</t>
+  </si>
+  <si>
+    <t>MR2606/0469</t>
+  </si>
+  <si>
+    <t>220KV_220kv chhatrapur circuit-breaker</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>For overhauling of 220kv chhatarpur breaker</t>
   </si>
   <si>
     <t>24-06-2026 10:00:00</t>
   </si>
   <si>
-    <t>24-06-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>NITIN RESHWAL</t>
-  </si>
-  <si>
-    <t>9425804890</t>
-  </si>
-  <si>
-    <t>MR2606/0434</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_BADNAWAR KANWAN  BOTH CKT HOTLINE PERMIT</t>
-  </si>
-  <si>
-    <t>400KV_BADNAWAR</t>
-  </si>
-  <si>
-    <t>HOTLINE ONLINE PERMIT FOR OPGW STRINGING ,</t>
-  </si>
-  <si>
-    <t>23-06-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>15-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>K SACHINDRA</t>
-  </si>
-  <si>
-    <t>9425805295</t>
-  </si>
-  <si>
-    <t>MR2606/0348</t>
-  </si>
-  <si>
-    <t>132KV_132kV Balaghat Baihar Line</t>
-  </si>
-  <si>
-    <t>132KV_BALAGHAT</t>
-  </si>
-  <si>
-    <t>Conductor Vibration Damper Provide Work &amp; Other Li</t>
-  </si>
-  <si>
-    <t>19-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2606/0461</t>
-  </si>
-  <si>
-    <t>132KV_132kV Bhonra Kapasi Ckt. IInd</t>
-  </si>
-  <si>
-    <t>132KV_BHONRA</t>
-  </si>
-  <si>
-    <t>For line maintenance work</t>
-  </si>
-  <si>
-    <t>Akhilesh Singh</t>
-  </si>
-  <si>
-    <t>8586865656</t>
-  </si>
-  <si>
-    <t>MR2605/0301</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>400KV_Bus-Bar</t>
-  </si>
-  <si>
-    <t>400KV_BHOPAL4</t>
-  </si>
-  <si>
-    <t>For Commissioning of New 400kV Bus-Bar Panel</t>
-  </si>
-  <si>
-    <t>13-05-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>30-06-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>RK Gayaki</t>
-  </si>
-  <si>
-    <t>9407528876</t>
-  </si>
-  <si>
-    <t>MR2606/0378</t>
-  </si>
-  <si>
-    <t>220KV_220kV Shivpuri Ckt Circuit Brekar Only</t>
-  </si>
-  <si>
-    <t>400KV_BINA4</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Circuit Brekar overhauling</t>
-  </si>
-  <si>
-    <t>20-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Mr. P.N. Namdeo</t>
-  </si>
-  <si>
-    <t>7587951092</t>
-  </si>
-  <si>
-    <t>MR2606/0450</t>
-  </si>
-  <si>
-    <t>220KV_160 MVAX-MER-I,BHEL</t>
-  </si>
-  <si>
-    <t>220KV_DATIA</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>CTR Engineer NIFPS Inspection work</t>
-  </si>
-  <si>
-    <t>24-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>24-06-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>Mukesh Verma</t>
-  </si>
-  <si>
-    <t>7587951058</t>
-  </si>
-  <si>
-    <t>MR2606/0438</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Gadarwara B.L.A. ckt-II</t>
-  </si>
-  <si>
-    <t>132KV_GADARWARA</t>
-  </si>
-  <si>
-    <t>Pre Monsoon Maintenance work</t>
-  </si>
-  <si>
-    <t>24-06-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Ashish Kumar</t>
-  </si>
-  <si>
-    <t>9425805935</t>
-  </si>
-  <si>
-    <t>MR2606/0458</t>
-  </si>
-  <si>
-    <t>220KV_160MVA X-Mer BHEL</t>
-  </si>
-  <si>
-    <t>220KV_GORABAZAR</t>
-  </si>
-  <si>
-    <t>Body Protection Cable Replacement work</t>
-  </si>
-  <si>
-    <t>Ashok Binghade</t>
-  </si>
-  <si>
-    <t>7587951135</t>
-  </si>
-  <si>
-    <t>MR2606/0464</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA X-MER Ist (BHEL)</t>
-  </si>
-  <si>
-    <t>220KV_GUNA</t>
-  </si>
-  <si>
-    <t>FOR TRANSFORMER PAINTING WORK</t>
-  </si>
-  <si>
-    <t>SH. SAGAR SINGH DHAKAD</t>
-  </si>
-  <si>
-    <t>9589205697</t>
-  </si>
-  <si>
-    <t>MR2606/0421</t>
-  </si>
-  <si>
-    <t>132KV_132 KV HOSHANGABAD-MANDIDEEP</t>
-  </si>
-  <si>
-    <t>220KV_HOSHANGABAD</t>
-  </si>
-  <si>
-    <t>RESAGGING WORK B/W LOC.NO. 1-7 &amp;</t>
-  </si>
-  <si>
-    <t>22-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>ASHUTOSH RAI</t>
-  </si>
-  <si>
-    <t>9425806902</t>
-  </si>
-  <si>
-    <t>MR2606/0292</t>
-  </si>
-  <si>
-    <t>400KV_UNIT#03</t>
-  </si>
-  <si>
-    <t>400KV_INDIRASAGAR</t>
-  </si>
-  <si>
-    <t>ANNUAL MAINTENANCE</t>
-  </si>
-  <si>
-    <t>16-06-2026 06:00:00</t>
-  </si>
-  <si>
-    <t>SANJAY PATEL</t>
-  </si>
-  <si>
-    <t>9575074321</t>
-  </si>
-  <si>
-    <t>MR2606/0452</t>
-  </si>
-  <si>
-    <t>132KV_JETPURA-UJJAIN LINE.</t>
-  </si>
-  <si>
-    <t>220KV_INDORE-II (JETPURA)</t>
-  </si>
-  <si>
-    <t>FOR JUMPER CONE TIGHTING AND OTHER MAINTENANCE WOR</t>
-  </si>
-  <si>
-    <t>RAVINDRA PATIL</t>
-  </si>
-  <si>
-    <t>8305612190</t>
-  </si>
-  <si>
-    <t>MR2606/0451</t>
-  </si>
-  <si>
-    <t>132KV_N/Z(INDORE) - JETPURA LINE.</t>
-  </si>
-  <si>
-    <t>220KV_INDORE-NZ</t>
-  </si>
-  <si>
-    <t>REPLACEMENT OF BROKEN  DISC INSULATOR STRING</t>
-  </si>
-  <si>
-    <t>24-06-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>MR2606/0468</t>
-  </si>
-  <si>
-    <t>132KV_132KV JBP - Bargi (Chanderi)</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>PREE MONSOON MAINTENANEC</t>
-  </si>
-  <si>
-    <t>D.N. Poddar</t>
-  </si>
-  <si>
-    <t>9425805034</t>
-  </si>
-  <si>
-    <t>MR2606/0435</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Jabalpur- Tejgarh</t>
-  </si>
-  <si>
-    <t>Modification/shifting at loc. 62- 63</t>
-  </si>
-  <si>
-    <t>23-06-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>29-06-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Jitendra Tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2606/0457</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA Transformer-II make BHEL</t>
-  </si>
-  <si>
-    <t>220KV_JAORA</t>
-  </si>
-  <si>
-    <t>132 KV CT cable repairing work.</t>
-  </si>
-  <si>
-    <t>Er. Rakesh kumar Badgotiya</t>
-  </si>
-  <si>
-    <t>8305447051</t>
-  </si>
-  <si>
-    <t>MR2606/0454</t>
-  </si>
-  <si>
-    <t>132KV_20MVA GEC Xmer</t>
-  </si>
-  <si>
-    <t>132KV_KATRA</t>
-  </si>
-  <si>
-    <t>33kv 50MVA Bph main bus jumper hot point attending</t>
-  </si>
-  <si>
-    <t>24-06-2026 10:30:00</t>
-  </si>
-  <si>
-    <t>Kanishka Singh</t>
-  </si>
-  <si>
-    <t>9425804656</t>
-  </si>
-  <si>
-    <t>MR2606/0453</t>
-  </si>
-  <si>
-    <t>132KV_50MVA XMER</t>
-  </si>
-  <si>
-    <t>33KV Bph main jumper hot point attending work</t>
-  </si>
-  <si>
-    <t>kanishka Singh</t>
-  </si>
-  <si>
-    <t>MR2606/0460</t>
-  </si>
-  <si>
-    <t>220KV_220KV Mehgaon Auraiya line</t>
-  </si>
-  <si>
-    <t>220KV_MEHGAON</t>
-  </si>
-  <si>
-    <t>Insulator replacement work &amp; other maintenance wor</t>
-  </si>
-  <si>
-    <t>24-06-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>Baidyanath kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
-  </si>
-  <si>
-    <t>MR2606/0372</t>
-  </si>
-  <si>
-    <t>220KV_Unit # 6</t>
-  </si>
-  <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
-    <t>Annual maintenance</t>
-  </si>
-  <si>
-    <t>19-06-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Bhanu pratap Pal</t>
-  </si>
-  <si>
-    <t>7898703187</t>
-  </si>
-  <si>
-    <t>MR2606/0449</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Pichhore Basai Tr- I &amp; II</t>
-  </si>
-  <si>
-    <t>220KV_PICHHORE</t>
-  </si>
-  <si>
-    <t>Broken earth wire re-stringing work</t>
-  </si>
-  <si>
-    <t>24-06-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Satish Kumar Bhagat</t>
-  </si>
-  <si>
-    <t>9425806916</t>
-  </si>
-  <si>
-    <t>MR2606/0463</t>
-  </si>
-  <si>
-    <t>63MVA_132/33KV_VIJAY ELCTRICAL_X'mer</t>
-  </si>
-  <si>
-    <t>132KV_RAJMILAN</t>
-  </si>
-  <si>
-    <t>03No I/c CT &amp; 01No 132kV Bph CT replacement work</t>
-  </si>
-  <si>
-    <t>R.B. Singh</t>
-  </si>
-  <si>
-    <t>9907230394</t>
-  </si>
-  <si>
-    <t>MR2606/0401</t>
-  </si>
-  <si>
-    <t>220KV_220 kv Satna â¿¿ Rewa line.</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>Conductor Re-sagging work at loc no 104-114 of 220</t>
-  </si>
-  <si>
-    <t>21-06-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>R.K. Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2606/0465</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Pench Ckt-IInd</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>Tighening of J/C, A/H, V/D and emergency T/C</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2606/0466</t>
-  </si>
-  <si>
-    <t>220KV_220kV Sidhi Bargawan Ckt - II</t>
-  </si>
-  <si>
-    <t>220KV_SIDHI</t>
-  </si>
-  <si>
-    <t>F/o Disc Replacement</t>
-  </si>
-  <si>
-    <t>G.L Sahu</t>
-  </si>
-  <si>
-    <t>9425805102</t>
-  </si>
-  <si>
-    <t>MR2606/0469</t>
-  </si>
-  <si>
-    <t>220KV_220kv chhatrapur circuit-breaker</t>
-  </si>
-  <si>
-    <t>220KV_TIKAMGARH</t>
-  </si>
-  <si>
-    <t>For overhauling of 220kv chhatarpur breaker</t>
-  </si>
-  <si>
     <t>30-06-2026 17:00:00</t>
   </si>
   <si>
@@ -628,6 +706,15 @@
     <t>9425806398</t>
   </si>
   <si>
+    <t>MR2606/0483</t>
+  </si>
+  <si>
+    <t>220KV_220kv Tikamgarh-chhatarpur line</t>
+  </si>
+  <si>
+    <t>For overhauling work of 220kv chhatarpur cb</t>
+  </si>
+  <si>
     <t>MR2605/0472</t>
   </si>
   <si>
@@ -667,9 +754,6 @@
     <t>23-06-2026 11:00:00</t>
   </si>
   <si>
-    <t>25-06-2026 17:00:00</t>
-  </si>
-  <si>
     <t>SANTOSH CHAVRASIA</t>
   </si>
   <si>
@@ -679,61 +763,79 @@
     <t>sub ld</t>
   </si>
   <si>
-    <t>COMMUNICATION CONSENT REQUIRED</t>
+    <t>OK THROUGH SUB LD</t>
+  </si>
+  <si>
+    <t>DEFERRED - WRPC CONSENT REUIRED</t>
+  </si>
+  <si>
+    <t>DEFERRED-COMMUNICATION CONSENT REQUIRED</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
+    <t xml:space="preserve">OK </t>
+  </si>
+  <si>
     <t>SUB LD</t>
   </si>
   <si>
-    <t>DEFERRED</t>
+    <t>AS PER SYSTEM REQUIREMENT</t>
   </si>
   <si>
     <t>CONTINUE</t>
   </si>
   <si>
-    <t>OK THROUGH SUB LD</t>
-  </si>
-  <si>
-    <t>OK, IF REQUIRED 132KV MANERI-MANDLA CKT TO BE OPENED</t>
-  </si>
-  <si>
-    <t>AS PER SYSTEM REQUIREMENT</t>
-  </si>
-  <si>
-    <t>OK, PRIOR TO CHARGING UNDERTAKING TO BE PROVIDED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK </t>
-  </si>
-  <si>
-    <t>AS PER SYSTEM REUIREMENT</t>
+    <t>CONTINUE, LINE TO BE IN SERVICE</t>
+  </si>
+  <si>
+    <t>DEFERRED DUE TO SD ON SATNA - CHHATARPUR CKT</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-AJAYGARH-SATNA-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-1</t>
+  </si>
+  <si>
+    <t>132KV-SHEOPUR-KHANDAR-1</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-1</t>
+  </si>
+  <si>
+    <t>400KV-SAGAR-BINA-1</t>
   </si>
   <si>
     <t>400KV-BALCO (MRSDS)-BIRSINGPUR-1</t>
   </si>
   <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-AJAYGARH-SATNA-1</t>
-  </si>
-  <si>
-    <t>220KV-KHANDWA-CHHEGAON-2</t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-1</t>
-  </si>
-  <si>
-    <t>400KV-SAGAR-BINA-1</t>
-  </si>
-  <si>
     <t>400KV-KORBA-NTPC-BIRSINGPUR-1</t>
   </si>
   <si>
-    <t>Hot Spot attending wave trap connector &amp; LBB Relay Replacement work at Birsinghpur.Dia to be kept open at both ends.</t>
+    <t>NLDC,MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>POWERGRID-NR,MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH,NTPC</t>
+  </si>
+  <si>
+    <t>POWERGRID-WR2 (PGCIL)</t>
+  </si>
+  <si>
+    <t>BALCO,POWERGRID-WR1 (PGCIL)</t>
+  </si>
+  <si>
+    <t>POWERGRID-WR1 (PGCIL)</t>
   </si>
   <si>
     <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
@@ -748,18 +850,12 @@
     <t>Non auto mode reuired for identifying faulty insulator before mansoon</t>
   </si>
   <si>
-    <t>OK LINE TO BE IN SERVICE</t>
+    <t>09:00</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -769,37 +865,22 @@
     <t>18:00</t>
   </si>
   <si>
-    <t>BALCO,POWERGRID-WR1 (PGCIL)</t>
-  </si>
-  <si>
-    <t>NLDC,MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,NTPC</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR2 (PGCIL)</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR1 (PGCIL)</t>
-  </si>
-  <si>
-    <t>220KV TIKAMGARH</t>
-  </si>
-  <si>
-    <t>CB OVERHAULING WORK</t>
-  </si>
-  <si>
-    <t>AE S/S TKM</t>
-  </si>
-  <si>
-    <t>220KV MAIN CB   CHHATARPUR BAY</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.24.06.26</t>
+    <t>ok through sub ld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok </t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>ok line to be in service</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.25.06.26</t>
+  </si>
+  <si>
+    <t>S/I SLDC JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -882,7 +963,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -961,15 +1042,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -983,6 +1055,24 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1013,23 +1103,39 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1073,12 +1179,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1088,38 +1188,50 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1468,21 +1580,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="11.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" style="2" customWidth="1"/>
-    <col min="9" max="10" width="11.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.28515625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -1508,23 +1621,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="3">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="30"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="23"/>
+    </row>
+    <row r="3" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1537,17 +1650,17 @@
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="26"/>
+    </row>
+    <row r="4" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1591,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <v>46196.590902777774</v>
+        <v>46197.422314814816</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>17</v>
@@ -1622,7 +1735,7 @@
         <v>25</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1663,7 +1776,7 @@
         <v>34</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1671,40 +1784,40 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <v>46191.51152777778</v>
+        <v>46197.567430555559</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1712,38 +1825,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <v>46196.581122685187</v>
+        <v>46197.684837962966</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1751,81 +1864,79 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <v>46154.485196759262</v>
+        <v>46197.681574074071</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <v>46192.538518518515</v>
+        <v>46154.485196759262</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="G10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="I10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="J10" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="K10" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="L10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="M10" s="5" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1833,38 +1944,38 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <v>46196.468807870369</v>
+        <v>46197.692465277774</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="J11" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="K11" s="8" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1872,38 +1983,38 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <v>46195.623460648145</v>
+        <v>46197.572465277779</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1911,23 +2022,23 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <v>46196.568240740744</v>
+        <v>46197.603703703702</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>22</v>
@@ -1936,52 +2047,52 @@
         <v>23</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="51" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <v>46196.61209490741</v>
+        <v>46197.479479166665</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -1989,40 +2100,38 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <v>46194.689386574071</v>
+        <v>46197.621134259258</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>27</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2030,79 +2139,77 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <v>46188.440798611111</v>
+        <v>46197.466458333336</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="51" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <v>46196.533773148149</v>
+        <v>46197.59983796296</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2110,77 +2217,81 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <v>46196.505949074075</v>
+        <v>46197.54478009259</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="E18" s="5" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <v>46196.657280092593</v>
+        <v>46188.440798611111</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
+      <c r="I19" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="J19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="L19" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="M19" s="5" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2191,37 +2302,37 @@
         <v>46195.618981481479</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="J20" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="K20" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="L20" s="9" t="s">
-        <v>130</v>
-      </c>
       <c r="M20" s="5" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2229,38 +2340,38 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <v>46196.567800925928</v>
+        <v>46197.673113425924</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2268,142 +2379,146 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <v>46196.561273148145</v>
+        <v>46197.675370370373</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="L22" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="M22" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <v>46196.556620370371</v>
+        <v>46197.570972222224</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="J23" s="7" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>147</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="24" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <v>46196.573263888888</v>
+        <v>46197.482199074075</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="M24" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="25" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <v>46191.762696759259</v>
+        <v>46197.629004629627</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>160</v>
@@ -2412,15 +2527,15 @@
         <v>161</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <v>46196.394803240742</v>
+        <v>46197.628750000003</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>162</v>
@@ -2442,16 +2557,16 @@
         <v>22</v>
       </c>
       <c r="J26" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="L26" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="L26" s="9" t="s">
-        <v>168</v>
-      </c>
       <c r="M26" s="5" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2459,29 +2574,29 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <v>46196.603043981479</v>
+        <v>46197.514409722222</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="I27" s="7" t="s">
-        <v>70</v>
-      </c>
       <c r="J27" s="7" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>173</v>
@@ -2490,21 +2605,21 @@
         <v>174</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <v>46193.489675925928</v>
+        <v>46191.762696759259</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>175</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>176</v>
@@ -2513,7 +2628,7 @@
         <v>177</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>178</v>
@@ -2522,7 +2637,7 @@
         <v>179</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>180</v>
@@ -2531,7 +2646,7 @@
         <v>181</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2539,38 +2654,40 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <v>46196.622847222221</v>
+        <v>46197.608148148145</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="E29" s="5" t="s">
         <v>183</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
@@ -2578,464 +2695,628 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <v>46196.625706018516</v>
+        <v>46197.577627314815</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="L30" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>193</v>
-      </c>
       <c r="M30" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <v>46196.680393518516</v>
+        <v>46197.459409722222</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="G31" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="I31" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="J31" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="L31" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>200</v>
-      </c>
       <c r="M31" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <v>46160.785312499997</v>
+        <v>46195.626018518517</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="I32" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="5" t="s">
+      <c r="L32" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="M32" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <v>46195.604699074072</v>
+        <v>46197.588541666664</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6">
+        <v>46197.639143518521</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="F34" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="G34" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="I34" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="L33" s="15" t="s">
+      <c r="J34" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="K34" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6">
+        <v>46196.680393518516</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="17">
-        <v>30</v>
-      </c>
-      <c r="B34" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="19" t="s">
+      <c r="I35" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6">
+        <v>46197.602592592593</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>33</v>
+      </c>
+      <c r="B37" s="6">
+        <v>46160.785312499997</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6">
+        <v>46195.604699074072</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>35</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="G39" s="15"/>
+      <c r="H39" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="K39" s="18"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="20" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>36</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="L34" s="21"/>
-      <c r="M34" s="22" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A35" s="17">
-        <v>31</v>
-      </c>
-      <c r="B35" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J35" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
-      <c r="M35" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A36" s="17">
-        <v>32</v>
-      </c>
-      <c r="B36" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="F36" s="19" t="s">
+      <c r="F40" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="G40" s="15"/>
+      <c r="H40" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="K40" s="18"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>37</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="G41" s="15"/>
+      <c r="H41" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="K41" s="18"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>38</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="G42" s="15"/>
+      <c r="H42" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" s="18"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="20" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>39</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="K43" s="18"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>40</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="K44" s="18"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="G36" s="17"/>
-      <c r="H36" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="22" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A37" s="17">
-        <v>33</v>
-      </c>
-      <c r="B37" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="22" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A38" s="17">
-        <v>34</v>
-      </c>
-      <c r="B38" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="G38" s="17"/>
-      <c r="H38" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="K38" s="23"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="25" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="165" x14ac:dyDescent="0.25">
-      <c r="A39" s="17">
-        <v>35</v>
-      </c>
-      <c r="B39" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="G39" s="17"/>
-      <c r="H39" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="K39" s="26"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A40" s="17">
-        <v>36</v>
-      </c>
-      <c r="B40" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="G40" s="17"/>
-      <c r="H40" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="K40" s="26"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A41" s="17">
-        <v>37</v>
-      </c>
-      <c r="B41" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="G41" s="17"/>
-      <c r="H41" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="K41" s="26"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="22" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A42" s="17">
-        <v>38</v>
-      </c>
-      <c r="B42" s="18">
-        <v>46196</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="K42" s="26"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="22" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="5"/>
+    </row>
+    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>41</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="G45" s="15"/>
+      <c r="H45" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="K45" s="18"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>42</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="G46" s="15"/>
+      <c r="H46" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="K46" s="18"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="20" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="29"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A47:M48"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:M2"/>
+    <mergeCell ref="E2:M3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,25 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$27</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="214">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -192,6 +181,78 @@
     <t>9407528876</t>
   </si>
   <si>
+    <t>MR2606/0525</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Birsinghpur-Shahdol Circuit II</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>F/o disc string replacement &amp; other line maintanan</t>
+  </si>
+  <si>
+    <t>29-06-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>29-06-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Asati</t>
+  </si>
+  <si>
+    <t>9524445533</t>
+  </si>
+  <si>
+    <t>MR2606/0522</t>
+  </si>
+  <si>
+    <t>132KV_132kv chhindwara-saori ckt-2</t>
+  </si>
+  <si>
+    <t>220KV_CHHINDWARA</t>
+  </si>
+  <si>
+    <t>polythine  contaminations removing&amp; other line mat</t>
+  </si>
+  <si>
+    <t>29-06-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>29-06-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>A.M Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2606/0527</t>
+  </si>
+  <si>
+    <t>132KV_132KV Handia -Harda Ckt -2</t>
+  </si>
+  <si>
+    <t>220KV_HANDIYA</t>
+  </si>
+  <si>
+    <t>B Phase CT Hot Point Attending Work</t>
+  </si>
+  <si>
+    <t>29-06-2026 12:30:00</t>
+  </si>
+  <si>
+    <t>29-06-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>Khemraj Kumar Dongre</t>
+  </si>
+  <si>
+    <t>9424430754</t>
+  </si>
+  <si>
     <t>MR2606/0292</t>
   </si>
   <si>
@@ -216,6 +277,21 @@
     <t>9575074321</t>
   </si>
   <si>
+    <t>MR2606/0499</t>
+  </si>
+  <si>
+    <t>400KV_400 KV ISP- NAGDA LINE</t>
+  </si>
+  <si>
+    <t>29-06-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>Vinay Mishra</t>
+  </si>
+  <si>
+    <t>9425693890</t>
+  </si>
+  <si>
     <t>MR2606/0435</t>
   </si>
   <si>
@@ -231,15 +307,54 @@
     <t>23-06-2026 08:00:00</t>
   </si>
   <si>
-    <t>29-06-2026 18:00:00</t>
-  </si>
-  <si>
     <t>Jitendra Tiwari</t>
   </si>
   <si>
     <t>9425805298</t>
   </si>
   <si>
+    <t>MR2606/0524</t>
+  </si>
+  <si>
+    <t>220KV_220  kv Satna (MPPTCL)  â¿¿  Kotar  line</t>
+  </si>
+  <si>
+    <t>220KV_KOTAR</t>
+  </si>
+  <si>
+    <t>Conductor Clipping work at loc No. 130 of  220  kv</t>
+  </si>
+  <si>
+    <t>29-06-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>R.K. Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2606/0530</t>
+  </si>
+  <si>
+    <t>220KV_220kV Malanpur-Auraiya Line</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Baidyanath Kumar</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
     <t>MR2606/0372</t>
   </si>
   <si>
@@ -297,6 +412,57 @@
     <t>9425806902</t>
   </si>
   <si>
+    <t>MR2606/0521</t>
+  </si>
+  <si>
+    <t>132KV_132KV SAGAR - INTERCONNECTOR IIND LINE</t>
+  </si>
+  <si>
+    <t>400KV_SAGAR</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2606/0518</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Chhindwara Saori Ckt-I</t>
+  </si>
+  <si>
+    <t>132KV_SAORI</t>
+  </si>
+  <si>
+    <t>Flash over disc replacement</t>
+  </si>
+  <si>
+    <t>29-06-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>29-06-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
+    <t>MR2606/0528</t>
+  </si>
+  <si>
+    <t>220KV_220  kv Satna Rewa  line</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>Conductor Re-sagging work at loc No. 104 - 114</t>
+  </si>
+  <si>
     <t>MR2606/0469</t>
   </si>
   <si>
@@ -345,6 +511,21 @@
     <t>9301373521</t>
   </si>
   <si>
+    <t>MR2606/0529</t>
+  </si>
+  <si>
+    <t>220KV_220KV UJJAIN TAJPUR IC 3 , 4 SIMULTENOUSLY</t>
+  </si>
+  <si>
+    <t>220KV_UJJAIN</t>
+  </si>
+  <si>
+    <t>JUMPER CONE TIGHETING</t>
+  </si>
+  <si>
+    <t>29-06-2026 11:00:00</t>
+  </si>
+  <si>
     <t>MR2606/0508</t>
   </si>
   <si>
@@ -390,30 +571,42 @@
     <t>9425806926</t>
   </si>
   <si>
+    <t>OK LINE TO BE IN SERVICE</t>
+  </si>
+  <si>
+    <t>DEFERRED</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>SUB LD</t>
+  </si>
+  <si>
+    <t>AS PER SYSTEM REQUIREMENT</t>
+  </si>
+  <si>
     <t>OK THROUGH SUB LD</t>
   </si>
   <si>
-    <t>DEFERRED</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>AS PER SYSTEM REQUIREMENT</t>
-  </si>
-  <si>
     <t>CONTINUE</t>
   </si>
   <si>
-    <t>OK, O&amp;M TO BE INTIMATED.</t>
-  </si>
-  <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
+    <t>OK AFTER RESTORATION OF CKT -1</t>
+  </si>
+  <si>
+    <t>CONTINUE , LINE TO BE IN SERVIE THROUGH TBC</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
   </si>
   <si>
     <t>220KV-AJAYGARH-SATNA-1</t>
   </si>
   <si>
+    <t>220KV-KHANDWA-CHHANERA-2</t>
+  </si>
+  <si>
     <t>132KV-VSTPS-WAIDHAN-2</t>
   </si>
   <si>
@@ -423,13 +616,28 @@
     <t>400KV-BHOPAL-MP-ITARSI-2</t>
   </si>
   <si>
-    <t>400KV-SAGAR-BINA-1</t>
-  </si>
-  <si>
-    <t>MP_SLDC</t>
-  </si>
-  <si>
-    <t>POWERGRID_WR2</t>
+    <t>29-Jun-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>26-Jun-2026</t>
+  </si>
+  <si>
+    <t>30-Jun-2026</t>
   </si>
   <si>
     <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
@@ -441,31 +649,22 @@
     <t>For the formation of LILO and re-routing of the 400 kV Bhopal-Itarsi (PGCIL) line to make way for construction activities at proposed 400 kV S/s Mandideep</t>
   </si>
   <si>
-    <t>For Erection and Stringing Work in 400 kV Bina Sagar C1 line under WRD Diversion Work.</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>ok through sub ld</t>
+    <t>OK THROUGH SUB LS</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>continue, EI &amp; PTTC APPROVAL REQUIRED PRIOR TO CHARGING. FTC procedure to be followed.</t>
+    <t>ok, EI aproval to be submitted prior to charging and FTC formalities to be completed</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.29.06.26</t>
+  </si>
+  <si>
+    <t>S/I SLDC MPPTCL JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -476,7 +675,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -510,10 +709,50 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -530,12 +769,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -595,70 +834,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -687,40 +873,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1088,72 +1283,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="2"/>
     <col min="2" max="2" width="11.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="48.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="37" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="35.7109375" style="2" customWidth="1"/>
+    <col min="9" max="10" width="11.42578125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="33.42578125" style="2" customWidth="1"/>
     <col min="14" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="12"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>46201</v>
+      <c r="B2" s="19">
+        <v>46202</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="D2" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="25"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="1"/>
@@ -1166,768 +1362,1268 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:13" s="12" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="4" t="s">
+      <c r="L4" s="22"/>
+      <c r="M4" s="20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+    <row r="5" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46195.607777777775</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
+        <v>46197.567430555559</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46200.478171296294</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46154.485196759262</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46201.560972222222</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46201.469444444447</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>16</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46201.61478009259</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>2</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46188.440798611111</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46198.531400462962</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46195.618981481479</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>6</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46201.486145833333</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>5</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46201.69568287037</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>8</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46191.762696759259</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46197.608148148145</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46198.58866898148</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46201.45994212963</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46200.49082175926</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>26</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46201.621064814812</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>7</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46196.680393518516</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
-        <v>46195.607777777775</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B24" s="5">
+        <v>46160.785312499997</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="B25" s="5">
+        <v>46201.641331018516</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="H25" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6">
-        <v>46197.567430555559</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="M25" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46198.686157407406</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="5" t="s">
+      <c r="E26" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6">
-        <v>46200.478171296294</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="H26" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>12</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="H27" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46154.485196759262</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46188.440798611111</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46195.618981481479</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46191.762696759259</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <v>46197.608148148145</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6">
-        <v>46198.58866898148</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
-        <v>10</v>
-      </c>
-      <c r="B14" s="15">
-        <v>46196.680393518516</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <v>11</v>
-      </c>
-      <c r="B15" s="20">
-        <v>46160.785312499997</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="K15" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="19">
-        <v>12</v>
-      </c>
-      <c r="B16" s="20">
-        <v>46198.686157407406</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <v>13</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="J27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14">
         <v>46198.591157407405</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="K17" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="19">
-        <v>14</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="23">
-        <v>310342</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <v>15</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23">
-        <v>310343</v>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
-        <v>16</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23">
-        <v>310379</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="19">
-        <v>17</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23">
-        <v>314776</v>
-      </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="19">
-        <v>18</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23">
-        <v>314777</v>
-      </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="19">
-        <v>19</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23">
-        <v>309392</v>
-      </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="24" t="s">
-        <v>122</v>
-      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="13"/>
+      <c r="B30" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="18" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14">
+        <v>46198.591157407405</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="26" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="4"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="4"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="D2:L2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$26</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="170">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,45 +76,21 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>132KV_132 kV Main Bus</t>
-  </si>
-  <si>
-    <t>220KV_BADNAGAR</t>
+    <t>MR2606/0434</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_BADNAWAR KANWAN  BOTH CKT HOTLINE PERMIT</t>
+  </si>
+  <si>
+    <t>400KV_BADNAWAR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>For attending hot point in R phase jaw of bus sect</t>
-  </si>
-  <si>
-    <t>07-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>07-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>Ravi Pandey</t>
-  </si>
-  <si>
-    <t>9425805296</t>
-  </si>
-  <si>
-    <t>MR2607/0079</t>
-  </si>
-  <si>
-    <t>MR2606/0434</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_BADNAWAR KANWAN  BOTH CKT HOTLINE PERMIT</t>
-  </si>
-  <si>
-    <t>400KV_BADNAWAR</t>
-  </si>
-  <si>
     <t>HOTLINE ONLINE PERMIT FOR OPGW STRINGING ,</t>
   </si>
   <si>
@@ -214,6 +190,54 @@
     <t>10-07-2026 16:00:00</t>
   </si>
   <si>
+    <t>MR2607/0096</t>
+  </si>
+  <si>
+    <t>220KV_160MVA X-MER (BBL)</t>
+  </si>
+  <si>
+    <t>220KV_BARWAHA</t>
+  </si>
+  <si>
+    <t>Bus bar wiring</t>
+  </si>
+  <si>
+    <t>08-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>08-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er. Imran beg</t>
+  </si>
+  <si>
+    <t>9425805200</t>
+  </si>
+  <si>
+    <t>MR2607/0089</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina Chanderi</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>Flash over disc replacement work and other line ma</t>
+  </si>
+  <si>
+    <t>08-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>08-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Satish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>9425806916</t>
+  </si>
+  <si>
     <t>MR2606/0526</t>
   </si>
   <si>
@@ -238,16 +262,19 @@
     <t>9406713326</t>
   </si>
   <si>
-    <t>MR2607/0071</t>
-  </si>
-  <si>
-    <t>220KV_220/132 160 MVA TRANSFORMER IMP</t>
-  </si>
-  <si>
-    <t>For incoming side R phase CT Clamp hot point atten</t>
-  </si>
-  <si>
-    <t>07-07-2026 15:00:00</t>
+    <t>MR2607/0091</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA IMP Transformer</t>
+  </si>
+  <si>
+    <t>for attending hot point at incooming R PH CT</t>
+  </si>
+  <si>
+    <t>08-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>08-07-2026 15:00:00</t>
   </si>
   <si>
     <t>Brajendra Soni</t>
@@ -256,43 +283,61 @@
     <t>9131327770</t>
   </si>
   <si>
-    <t>MR2607/0076</t>
-  </si>
-  <si>
-    <t>220KV_(Change over to Bus coupler) of 220KV Tikamgarh Breaker</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>DPR Relay Testing work.</t>
-  </si>
-  <si>
-    <t>07-07-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>07-07-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>M.K.Choubey</t>
-  </si>
-  <si>
-    <t>9425801424</t>
-  </si>
-  <si>
-    <t>MR2607/0075</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Gorabazar- Amarkantak</t>
-  </si>
-  <si>
-    <t>220KV_GORABAZAR</t>
-  </si>
-  <si>
-    <t>Melted Jumper cone repair at loc. 9 Top Ph</t>
-  </si>
-  <si>
-    <t>07-07-2026 18:00:00</t>
+    <t>MR2607/0093</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Shahdol-Dindori Circuit II</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>F/o disc stringing replacement &amp; other line maint.</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Asati</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2607/0087</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA -I</t>
+  </si>
+  <si>
+    <t>220KV_JAORA</t>
+  </si>
+  <si>
+    <t>DC Leakege Attainding work</t>
+  </si>
+  <si>
+    <t>08-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>RAKESH BADGOTYA</t>
+  </si>
+  <si>
+    <t>7587951143</t>
+  </si>
+  <si>
+    <t>MR2607/0097</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Jabalpur - Tejgarh (Tap Patan) at present 132 kV Patan Tejgarh</t>
+  </si>
+  <si>
+    <t>132KV_PATAN</t>
+  </si>
+  <si>
+    <t>Jumper connect on Tapping system at loc no 98 RYB</t>
+  </si>
+  <si>
+    <t>08-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>08-07-2026 19:00:00</t>
   </si>
   <si>
     <t>Jitendra Tiwari</t>
@@ -301,196 +346,100 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>MR2607/0067</t>
-  </si>
-  <si>
-    <t>132KV_132KV BETUL-GUDGAON 1ST CKT</t>
-  </si>
-  <si>
-    <t>220KV_GUDGAON2</t>
-  </si>
-  <si>
-    <t>B-PH CT OIL LEAKAGE ATTENDING WORK</t>
-  </si>
-  <si>
-    <t>ER SANJAY KUMAR PAWAR</t>
-  </si>
-  <si>
-    <t>9425802293</t>
-  </si>
-  <si>
-    <t>MR2607/0069</t>
-  </si>
-  <si>
-    <t>220KV_220KV Itarsi-Sarni No.-3 Feeder</t>
-  </si>
-  <si>
-    <t>220KV_ITARSI</t>
-  </si>
-  <si>
-    <t>02No CT R&amp;Y- Phase replacment work.</t>
-  </si>
-  <si>
-    <t>J.D.Khoria</t>
-  </si>
-  <si>
-    <t>9425804975</t>
-  </si>
-  <si>
-    <t>MR2607/0049</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Jabalpur- Tejgarh (Tap Patan)</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>Modification/shifting at loc. 62- 63</t>
-  </si>
-  <si>
-    <t>05-07-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0084</t>
-  </si>
-  <si>
-    <t>132KV_20 MVA bbl-make Transformer</t>
-  </si>
-  <si>
-    <t>132KV_JATARA</t>
-  </si>
-  <si>
-    <t>Safety purpose during shutdown on 33kv main-bus</t>
-  </si>
-  <si>
-    <t>07-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Pushpendra Kumar soni</t>
-  </si>
-  <si>
-    <t>9425806398</t>
-  </si>
-  <si>
-    <t>MR2607/0082</t>
-  </si>
-  <si>
-    <t>132KV_63mva bbl-make transformer</t>
-  </si>
-  <si>
-    <t>Safety purpose during 33kv Main-bus shutdown</t>
-  </si>
-  <si>
-    <t>MR2607/0065</t>
-  </si>
-  <si>
-    <t>220KV_220KV Mehgaon Auraiya line</t>
-  </si>
-  <si>
-    <t>220KV_MEHGAON</t>
+    <t>MR2607/0068</t>
+  </si>
+  <si>
+    <t>220KV_220KV PITHAMPUR IC CKT-1 LINE</t>
+  </si>
+  <si>
+    <t>400KV_PITHAMPUR4</t>
+  </si>
+  <si>
+    <t>replacement single insulator fitting with Doubl</t>
+  </si>
+  <si>
+    <t>07-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>RAJENDRA KANOJE</t>
+  </si>
+  <si>
+    <t>9425801348</t>
+  </si>
+  <si>
+    <t>MR2607/0090</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Rewa-Sidhi DCDS line</t>
+  </si>
+  <si>
+    <t>220KV_REWA</t>
+  </si>
+  <si>
+    <t>flashover disc insulator string replacement</t>
+  </si>
+  <si>
+    <t>Mr. Ajay Kumar Chaurasia</t>
+  </si>
+  <si>
+    <t>9425805081</t>
+  </si>
+  <si>
+    <t>132KV_132kv PT -2</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
   </si>
   <si>
     <t>OCCM-MP</t>
   </si>
   <si>
-    <t>Insulator Replacement &amp; Earthwire stringing work</t>
-  </si>
-  <si>
-    <t>07-07-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>Baidyanath Kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
-  </si>
-  <si>
-    <t>MR2607/0074</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Jabalpur - Tejgarh (Tap Patan) at present 132 kV Patan Tejgarh</t>
-  </si>
-  <si>
-    <t>132KV_PATAN</t>
-  </si>
-  <si>
-    <t>Jumper connect on Tapping system at loc no 98 RYB</t>
-  </si>
-  <si>
-    <t>07-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0068</t>
-  </si>
-  <si>
-    <t>220KV_220KV PITHAMPUR IC CKT-1 LINE</t>
-  </si>
-  <si>
-    <t>400KV_PITHAMPUR4</t>
-  </si>
-  <si>
-    <t>replacement single insulator fitting with Doubl</t>
-  </si>
-  <si>
-    <t>11-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>RAJENDRA KANOJE</t>
-  </si>
-  <si>
-    <t>9425801348</t>
-  </si>
-  <si>
-    <t>MR2607/0077</t>
-  </si>
-  <si>
-    <t>132KV_132KV RAJMILAN-JANAKPUR CKT</t>
-  </si>
-  <si>
-    <t>132KV_RAJMILAN</t>
-  </si>
-  <si>
-    <t>FLASH OVER DISC REPLACEMENT</t>
-  </si>
-  <si>
-    <t>G.L SAHU</t>
-  </si>
-  <si>
-    <t>9425805102</t>
-  </si>
-  <si>
-    <t>MR2607/0072</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna â¿¿ Nagod ckt â¿¿Ist line.</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>line maintenance work of 132 kv Satna â¿¿ Nagod ckt</t>
-  </si>
-  <si>
-    <t>R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2607/0073</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA BHEL X-mer  - Ist</t>
+    <t>For PT separation work</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2607/0094</t>
+  </si>
+  <si>
+    <t>MR2607/0086</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_BBL_Xmer</t>
+  </si>
+  <si>
+    <t>132KV_SHAHPURA</t>
+  </si>
+  <si>
+    <t>Penal replacement &amp; oil leakage attending work</t>
+  </si>
+  <si>
+    <t>08-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>H L koshta</t>
+  </si>
+  <si>
+    <t>9893281195</t>
+  </si>
+  <si>
+    <t>MR2607/0092</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-mer -II</t>
   </si>
   <si>
     <t>220KV_SHAJAPUR</t>
   </si>
   <si>
-    <t>for replacement of fire survival cable of NIFPS</t>
-  </si>
-  <si>
-    <t>07-07-2026 10:00:00</t>
+    <t>for Replacement of fire survival cable</t>
   </si>
   <si>
     <t>Nitin Verma</t>
@@ -499,103 +448,91 @@
     <t>9981559007</t>
   </si>
   <si>
-    <t>MR2607/0085</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Sirmaur-Atraila ckt.-I line</t>
-  </si>
-  <si>
-    <t>220KV_SIRMOUR</t>
-  </si>
-  <si>
-    <t>For various line maintenance work.</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Kumar Chaurasia</t>
-  </si>
-  <si>
-    <t>9425805081</t>
-  </si>
-  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>ok, line to be in service through TBC</t>
+    <t>ok, through sub ld</t>
   </si>
   <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>ok, charging approval of Electrical Inspector will be required for charging of line on new tower (if any)</t>
-  </si>
-  <si>
-    <t>real time, as per loading conditions</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 07.07.2026</t>
-  </si>
-  <si>
-    <t>400KV-CHHEGAON-KHANDWA-1</t>
-  </si>
-  <si>
-    <t>07-Jul-2026</t>
+    <t>deferred due to s/d on 132kV Baihar Mandla Line</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>ok, EI approval will be required if charging on new/modified towers</t>
+  </si>
+  <si>
+    <t>220KV-MEHGAON-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-SEONI-MP-SEONI-PG-1</t>
+  </si>
+  <si>
+    <t>220KV-MORENA-MORENA-MP-1</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-KOTAR-1</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-MALANPUR-2</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-MP-SATNA-3</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-MAIHAR-1</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>FOR STRINGING AND JUMPERING  WORK FOR CHARGING OF NEWLY CONSTRUCTED 220 KV SATNA (PG)-SATNA (IC-4) AND 220 KV SATNA (PG) - MAIHAR-II LINE DUE TO MULTI CKT TOWER</t>
+  </si>
+  <si>
+    <t>FOR STRINGING AND JUMPERING  WORK FOR CHARGING OF NEWLY CONSTRUCTED 220 KV SATNA (PG)-SATNA (IC-4) AND 220 KV SATNA (PG) - MAIHAR-II LINE, DUE TO MULTI CKT TOWER. ALSO MAIN BUS JUMPERING WORK AT MAIHAR END</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF EXISTING CONDUCTOR WITH HTLS TYPE CONDUCTOR</t>
+  </si>
+  <si>
+    <t>09:00</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
+    <t>17:00</t>
+  </si>
+  <si>
     <t>18:00</t>
   </si>
   <si>
-    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
-  </si>
-  <si>
-    <t>220KV-SATNA-MP-SATNA-1</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-1</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF EXISTING CONDUCTOR WITH HTLS TYPE CONDUCTOR</t>
-  </si>
-  <si>
-    <t>400KV/220KV JABALPUR-ICT-2</t>
-  </si>
-  <si>
-    <t>06-Jul-2026</t>
-  </si>
-  <si>
-    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
-  </si>
-  <si>
-    <t>S/I SLDC JABALPUR</t>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>MP_SLDC</t>
+  </si>
+  <si>
+    <t>OCCM WR</t>
   </si>
 </sst>
 </file>
@@ -606,7 +543,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -640,28 +577,13 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,13 +597,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -800,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -837,9 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -849,18 +762,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -879,12 +780,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1252,57 +1162,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="60.5703125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="54.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="57.85546875" customWidth="1"/>
     <col min="9" max="9" width="19.5703125" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" customWidth="1"/>
     <col min="11" max="11" width="24.28515625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="44.7109375" style="12" customWidth="1"/>
+    <col min="13" max="13" width="49.85546875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="16"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="9"/>
@@ -1361,66 +1269,68 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="15"/>
       <c r="M4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46209.651747685188</v>
+        <v>46195.607777777775</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46195.607777777775</v>
+        <v>46207.615613425929</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>28</v>
@@ -1429,7 +1339,7 @@
         <v>29</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>30</v>
@@ -1447,191 +1357,187 @@
         <v>34</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A31" si="0">A6+1</f>
+        <f t="shared" ref="A7:A29" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46207.615613425929</v>
+        <v>46207.576469907406</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46207.576469907406</v>
+        <v>46205.453009259261</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="L8" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46205.453009259261</v>
+        <v>46205.494942129626</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="I9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="J9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46205.494942129626</v>
+        <v>46210.652129629627</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="11" t="s">
+      <c r="I10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="J10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="L10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="M10" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46201.595092592594</v>
+        <v>46210.569652777776</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="11" t="s">
         <v>64</v>
       </c>
@@ -1639,7 +1545,7 @@
         <v>65</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>66</v>
@@ -1657,118 +1563,120 @@
         <v>70</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46209.552187499998</v>
+        <v>46201.595092592594</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="E12" s="11" t="s">
         <v>72</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46209.612268518518</v>
+        <v>46210.622071759259</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46209.599178240744</v>
+        <v>46210.649409722224</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>90</v>
@@ -1777,16 +1685,16 @@
         <v>91</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46209.478703703702</v>
+        <v>46210.429166666669</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>92</v>
@@ -1799,668 +1707,545 @@
         <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46209.516458333332</v>
+        <v>46210.694456018522</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46207.570416666669</v>
+        <v>46209.478831018518</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="5">
-        <v>46209.676226851851</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="B18" s="18">
+        <v>46210.588252314818</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="G18" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="H18" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="23">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="5">
-        <v>46209.671689814815</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="B19" s="24">
+        <v>46210.651701388888</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="5">
-        <v>46209.4294212963</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="B20" s="24">
+        <v>46210.360254629632</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="23">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="5">
-        <v>46209.586909722224</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="B21" s="24">
+        <v>46210.629467592589</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="23">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="5">
-        <v>46209.478831018518</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="B22" s="27"/>
+      <c r="C22" s="28">
+        <v>313909</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="23">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="5">
-        <v>46209.644907407404</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="B23" s="27"/>
+      <c r="C23" s="28">
+        <v>313910</v>
+      </c>
+      <c r="D23" s="27"/>
+      <c r="E23" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="23">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="5">
-        <v>46209.557511574072</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="11" t="s">
+      <c r="B24" s="27"/>
+      <c r="C24" s="28">
+        <v>313911</v>
+      </c>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    </row>
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="5">
-        <v>46209.558888888889</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="28">
+        <v>313912</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="M25" s="11" t="s">
+      <c r="F25" s="28" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+      <c r="G25" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="23">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" s="23">
-        <v>46209.682905092595</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="24" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="28">
+        <v>313913</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="I26" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="K26" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="L26" s="27" t="s">
+      <c r="I26" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="M26" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="J26" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="23">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="I27" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J27" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="K27" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="M27" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="22">
+      <c r="B27" s="27"/>
+      <c r="C27" s="28">
+        <v>313914</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="23">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="I28" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J28" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K28" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="M28" s="31" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="28">
+        <v>313915</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="F28" s="28" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="G28" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="23">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J29" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="K29" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="L29" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="M29" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="22">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="K30" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="L30" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="M30" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="I31" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="J31" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="K31" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="L31" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="M31" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="29"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="28">
+        <v>314003</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="29" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="187">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -157,355 +157,355 @@
     <t>9425801350</t>
   </si>
   <si>
-    <t>MR2607/0015</t>
-  </si>
-  <si>
-    <t>220KV_220kv ashta</t>
-  </si>
-  <si>
-    <t>for safe working of Crane</t>
-  </si>
-  <si>
-    <t>04-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0131</t>
-  </si>
-  <si>
-    <t>220KV_160MVA X-MER (BBL)</t>
-  </si>
-  <si>
-    <t>220KV_BARWAHA</t>
-  </si>
-  <si>
-    <t>Bus Bar protection Work</t>
-  </si>
-  <si>
-    <t>10-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Er. Imran Beg</t>
-  </si>
-  <si>
-    <t>9425805200</t>
-  </si>
-  <si>
-    <t>MR2607/0120</t>
-  </si>
-  <si>
-    <t>40MVA_132/33KV_BBL_X'mer_2</t>
-  </si>
-  <si>
-    <t>132KV_BIJAWAR</t>
-  </si>
-  <si>
-    <t>33kv side y phase ct clamp hot point attending wor</t>
-  </si>
-  <si>
-    <t>10-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 13:30:00</t>
-  </si>
-  <si>
-    <t>Brajendra Kumar Soni</t>
+    <t>MR2607/0134</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina-Rajghat Ckt</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>f/o disc insulator replacement work</t>
+  </si>
+  <si>
+    <t>11-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Satish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>9425806916</t>
+  </si>
+  <si>
+    <t>MR2607/0137</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina- Mungaoli RTS Ckt-1&amp;132 KV Mungaoli RTS Ckt-1</t>
+  </si>
+  <si>
+    <t>one side hanger open on tower at loc 13 T phase</t>
+  </si>
+  <si>
+    <t>11-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Dilip Singh Walkey</t>
+  </si>
+  <si>
+    <t>9425804578</t>
+  </si>
+  <si>
+    <t>MR2607/0133</t>
+  </si>
+  <si>
+    <t>132KV_132kV Dindori Gorakhpur Line</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>Jumper Cone Tightening &amp; Other Maint. Work</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2607/0139</t>
+  </si>
+  <si>
+    <t>220KV_160 mva x-mer - iiird (BHEL)</t>
+  </si>
+  <si>
+    <t>220KV_GUNA</t>
+  </si>
+  <si>
+    <t>OIL TOPPING WORK</t>
+  </si>
+  <si>
+    <t>Sagar Shingh Dhakad</t>
+  </si>
+  <si>
+    <t>9589205697</t>
+  </si>
+  <si>
+    <t>MR2607/0142</t>
+  </si>
+  <si>
+    <t>132KV_132kv half main bus</t>
+  </si>
+  <si>
+    <t>132KV_KYMORE</t>
+  </si>
+  <si>
+    <t>For stringing high bus gantry to gantry over main</t>
+  </si>
+  <si>
+    <t>11-07-2026 06:00:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>S.K. chaturvedi</t>
+  </si>
+  <si>
+    <t>9425806938</t>
+  </si>
+  <si>
+    <t>MR2607/0136</t>
+  </si>
+  <si>
+    <t>132KV_50 MVA TRANSFORMER ATLANTA</t>
+  </si>
+  <si>
+    <t>132KV_NOWGAON</t>
+  </si>
+  <si>
+    <t>for providing additional support to WTI&amp; OTI Meter</t>
+  </si>
+  <si>
+    <t>Brajendra Soni</t>
   </si>
   <si>
     <t>9131327770</t>
   </si>
   <si>
-    <t>MR2607/0121</t>
-  </si>
-  <si>
-    <t>50MVA_132/33KV_BBL_Xmer</t>
-  </si>
-  <si>
-    <t>provide extra additional support to WTI &amp; OTI mete</t>
-  </si>
-  <si>
-    <t>10-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 16:30:00</t>
-  </si>
-  <si>
-    <t>MR2607/0123</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Tikamgarh-Budhera Ckt. II line</t>
-  </si>
-  <si>
-    <t>132KV_BUDHERA</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>DFO replacement &amp; other line maintenance</t>
-  </si>
-  <si>
-    <t>10-07-2026 18:00:00</t>
+    <t>MR2607/0138</t>
+  </si>
+  <si>
+    <t>132KV_50 MVA BBL</t>
+  </si>
+  <si>
+    <t>for additional support provide toWTI &amp; OTI Meters</t>
+  </si>
+  <si>
+    <t>11-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0068</t>
+  </si>
+  <si>
+    <t>220KV_220KV PITHAMPUR IC CKT-1 LINE</t>
+  </si>
+  <si>
+    <t>400KV_PITHAMPUR4</t>
+  </si>
+  <si>
+    <t>replacement single insulator fitting with Doubl</t>
+  </si>
+  <si>
+    <t>07-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>11-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>RAJENDRA KANOJE</t>
+  </si>
+  <si>
+    <t>9425801348</t>
+  </si>
+  <si>
+    <t>MR2607/0124</t>
+  </si>
+  <si>
+    <t>220KV_220KV PITHAMPUR IC CKT-2</t>
+  </si>
+  <si>
+    <t>replacement of single insulator fitting with Doubl</t>
+  </si>
+  <si>
+    <t>10-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>14-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0140</t>
+  </si>
+  <si>
+    <t>132KV_132 KV SLEEMNABAD - MANSAKRA LINE</t>
+  </si>
+  <si>
+    <t>132KV_SALEEMNABAD</t>
+  </si>
+  <si>
+    <t>F/o Disc Replacement and Other Line Maintenance</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2607/0135</t>
+  </si>
+  <si>
+    <t>132KV_Sarni Khapaswami</t>
+  </si>
+  <si>
+    <t>220KV_SARNI</t>
+  </si>
+  <si>
+    <t>F/O disc replacement &amp; other line maint. work</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>MR2607/0141</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Satna  â¿¿  Nagod ckt â¿¿Ist line.</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>maintenance work of 132 kv Satna - Nagod ckt â¿¿Ist</t>
+  </si>
+  <si>
+    <t>R.K. Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2607/0127</t>
+  </si>
+  <si>
+    <t>132KV_132kV Seoni Lalbarra Line</t>
+  </si>
+  <si>
+    <t>132KV_SEONI1</t>
+  </si>
+  <si>
+    <t>Re-sagging of section Loc no. 141 to 158</t>
+  </si>
+  <si>
+    <t>10-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2607/0098</t>
+  </si>
+  <si>
+    <t>220KV_220 KV ATPS-Shahdol Line</t>
+  </si>
+  <si>
+    <t>220KV_SHAHDOL</t>
+  </si>
+  <si>
+    <t>Tower Erection,Stringing &amp; De-stringing work</t>
+  </si>
+  <si>
+    <t>09-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>15-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Dharmendra Dwivedi</t>
+  </si>
+  <si>
+    <t>9425805311</t>
+  </si>
+  <si>
+    <t>MR2607/0099</t>
+  </si>
+  <si>
+    <t>220KV_220 KV ATPS -Sidhi Line</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Tower Erection, Stringing &amp; De-Stringing work</t>
+  </si>
+  <si>
+    <t>MR2607/0132</t>
+  </si>
+  <si>
+    <t>132KV_132KV MAIN BUS</t>
+  </si>
+  <si>
+    <t>132KV_SIRONJ</t>
+  </si>
+  <si>
+    <t>Jumpering work from Main Bus to Isolator New bay</t>
+  </si>
+  <si>
+    <t>11-07-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>Mahendra Raj Sahu</t>
+  </si>
+  <si>
+    <t>9425804982</t>
+  </si>
+  <si>
+    <t>MR2607/0143</t>
+  </si>
+  <si>
+    <t>220KV_220kV Tikamgarh-Damoh (PGCIL) Line</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>DFO replacement work</t>
+  </si>
+  <si>
+    <t>pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2607/0101</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Tikamgrah Chhatarpur ckt-1</t>
+  </si>
+  <si>
+    <t>For modification &amp; shifting work</t>
+  </si>
+  <si>
+    <t>09-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>17-07-2026 18:00:00</t>
   </si>
   <si>
     <t>Pankaj Yadav</t>
   </si>
   <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2607/0116</t>
-  </si>
-  <si>
-    <t>132KV_132KV BWFPL RE FEEDER</t>
-  </si>
-  <si>
-    <t>132KV_GUDGAON</t>
-  </si>
-  <si>
-    <t>C&amp;R PANEL REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>09-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>10-07-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>ER M.K. SHARMA</t>
-  </si>
-  <si>
-    <t>9425805883</t>
-  </si>
-  <si>
-    <t>MR2607/0125</t>
-  </si>
-  <si>
-    <t>132KV_132kv Kotma-Arya Energy ckt</t>
-  </si>
-  <si>
-    <t>132KV_KOTMA</t>
-  </si>
-  <si>
-    <t>F/o disc stringing replacement &amp; other line maint.</t>
-  </si>
-  <si>
-    <t>MR2607/0119</t>
-  </si>
-  <si>
-    <t>220KV_Chhindwara Pandhurna</t>
-  </si>
-  <si>
-    <t>220KV_PANDHURNA</t>
-  </si>
-  <si>
-    <t>F/O disc replacement &amp; other line maint. work</t>
-  </si>
-  <si>
-    <t>10-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>SHIV KUMAR</t>
-  </si>
-  <si>
-    <t>9425806917</t>
-  </si>
-  <si>
-    <t>MR2607/0068</t>
-  </si>
-  <si>
-    <t>220KV_220KV PITHAMPUR IC CKT-1 LINE</t>
-  </si>
-  <si>
-    <t>400KV_PITHAMPUR4</t>
-  </si>
-  <si>
-    <t>replacement single insulator fitting with Doubl</t>
-  </si>
-  <si>
-    <t>07-07-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>11-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>RAJENDRA KANOJE</t>
-  </si>
-  <si>
-    <t>9425801348</t>
-  </si>
-  <si>
-    <t>MR2607/0124</t>
-  </si>
-  <si>
-    <t>220KV_220KV PITHAMPUR IC CKT-2</t>
-  </si>
-  <si>
-    <t>replacement of single insulator fitting with Doubl</t>
-  </si>
-  <si>
-    <t>10-07-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>14-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0130</t>
-  </si>
-  <si>
-    <t>220KV_50 MVA BBL XMER</t>
-  </si>
-  <si>
-    <t>400KV_SAGAR</t>
-  </si>
-  <si>
-    <t>DIFFERENTIAL RELAY CHANGE</t>
-  </si>
-  <si>
-    <t>SRAJAN SISODIYA</t>
-  </si>
-  <si>
-    <t>7879960164</t>
-  </si>
-  <si>
-    <t>MR2607/0122</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna  â¿¿  Nagod ckt â¿¿Ist line.</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>r line maintenance work of 132 kv Satna - Nagod ck</t>
-  </si>
-  <si>
-    <t>R.K. Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2607/0126</t>
-  </si>
-  <si>
-    <t>400KV_400 kV Seoni-Sarni line</t>
-  </si>
-  <si>
-    <t>765KV_SEONI-PG</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Spacer provide work</t>
-  </si>
-  <si>
-    <t>A.M.Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2607/0127</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Lalbarra Line</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>Re-sagging of section Loc no. 141 to 158</t>
-  </si>
-  <si>
-    <t>10-07-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>13-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>MR2607/0098</t>
-  </si>
-  <si>
-    <t>220KV_220 KV ATPS-Shahdol Line</t>
-  </si>
-  <si>
-    <t>220KV_SHAHDOL</t>
-  </si>
-  <si>
-    <t>Tower Erection,Stringing &amp; De-stringing work</t>
-  </si>
-  <si>
-    <t>09-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>15-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Dharmendra Dwivedi</t>
-  </si>
-  <si>
-    <t>9425805311</t>
-  </si>
-  <si>
-    <t>MR2607/0099</t>
-  </si>
-  <si>
-    <t>220KV_220 KV ATPS -Sidhi Line</t>
-  </si>
-  <si>
-    <t>220KV_SIDHI</t>
-  </si>
-  <si>
-    <t>Tower Erection, Stringing &amp; De-Stringing work</t>
-  </si>
-  <si>
-    <t>MR2607/0128</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Sirmaur-Atraila ckt.-2 line</t>
-  </si>
-  <si>
-    <t>220KV_SIRMOUR</t>
-  </si>
-  <si>
-    <t>various line maintenance work</t>
-  </si>
-  <si>
-    <t>Mr. Ajay Kumar Chaurasia</t>
-  </si>
-  <si>
-    <t>9425805081</t>
-  </si>
-  <si>
-    <t>MR2607/0101</t>
-  </si>
-  <si>
-    <t>220KV_220 kv Tikamgrah Chhatarpur ckt-1</t>
-  </si>
-  <si>
-    <t>220KV_TIKAMGARH</t>
-  </si>
-  <si>
-    <t>For modification &amp; shifting work</t>
-  </si>
-  <si>
-    <t>09-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>17-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>not in WR list</t>
+    <t>ok</t>
   </si>
   <si>
     <t>ok, line to be in service</t>
@@ -514,73 +514,67 @@
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok, o&amp;m shall be informed</t>
+    <t>deferred</t>
+  </si>
+  <si>
+    <t>real time</t>
   </si>
   <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok, 220kv Pandhurna-Kalmeshwar ckt to be in service</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>deferred by site</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>GWALIOR - 400KV - BUS 1</t>
-  </si>
-  <si>
-    <t>400KV-SEONI-PG-SATPURA-1</t>
-  </si>
-  <si>
-    <t>220KV-MALANPUR-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-SATNA-MP-SATNA-3</t>
-  </si>
-  <si>
-    <t>220KV-SATNA-MAIHAR-1</t>
-  </si>
-  <si>
-    <t>AMP works</t>
+    <t>deferred due to s/d on 220 kv Tikamgrah Chhatarpur ckt-1</t>
+  </si>
+  <si>
+    <t>approved for ckt 2, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>ok, ACC to be informed, any new charging to be done after FTC formalitites</t>
+  </si>
+  <si>
+    <t>220KV-MEHGAON-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-AJAYGARH-SATNA-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHEGAON-1</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
+  </si>
+  <si>
+    <t>11-Jul-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
   </si>
   <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
-  </si>
-  <si>
-    <t>FOR STRINGING AND JUMPERING  WORK FOR CHARGING OF NEWLY CONSTRUCTED 220 KV SATNA (PG)-SATNA (IC-4) AND 220 KV SATNA (PG) - MAIHAR-II LINE DUE TO MULTI CKT TOWER</t>
-  </si>
-  <si>
-    <t>FOR STRINGING AND JUMPERING  WORK FOR CHARGING OF NEWLY CONSTRUCTED 220 KV SATNA (PG)-SATNA (IC-4) AND 220 KV SATNA (PG) - MAIHAR-II LINE, DUE TO MULTI CKT TOWER. ALSO MAIN BUS JUMPERING WORK AT MAIHAR END</t>
-  </si>
-  <si>
-    <t>10-Jul-2026</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>08-Jul-2026</t>
-  </si>
-  <si>
-    <t>08:00</t>
+    <t xml:space="preserve">	FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
   </si>
   <si>
     <t>OCCM-WR</t>
@@ -589,7 +583,7 @@
     <t>S/I ,SLDC MPPTCL JABALPUR</t>
   </si>
   <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.10.07.2026</t>
+    <t>APPROVED OUTAGE LIST FOR DTD.11.07.2026</t>
   </si>
 </sst>
 </file>
@@ -600,7 +594,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -635,14 +629,7 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -662,7 +649,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -768,28 +755,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -797,9 +775,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1164,20 +1139,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="55.140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="62.85546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="50.140625" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="50" customWidth="1"/>
+    <col min="13" max="13" width="52.140625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
@@ -1201,21 +1176,21 @@
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24">
-        <v>46213</v>
+      <c r="B2" s="18">
+        <v>46214</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
+      <c r="E2" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1272,15 +1247,15 @@
       <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="23"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1317,11 +1292,11 @@
       <c r="L5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="9" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>2</v>
@@ -1359,13 +1334,13 @@
       <c r="L6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f t="shared" ref="A7:A31" si="0">A6+1</f>
+        <f t="shared" ref="A7:A29" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="3">
@@ -1401,121 +1376,119 @@
       <c r="L7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>46205.494942129626</v>
+        <v>46213.547685185185</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="9" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>46212.653611111113</v>
+        <v>46213.573819444442</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>46212.523761574077</v>
+        <v>46213.462951388887</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>63</v>
@@ -1523,17 +1496,17 @@
       <c r="L10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>46212.526030092595</v>
+        <v>46213.594293981485</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>65</v>
@@ -1543,181 +1516,181 @@
         <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="J11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="L11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <v>46212.546041666668</v>
+        <v>46213.616608796299</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>46211.678298611114</v>
+        <v>46213.571157407408</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="L13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>46212.621296296296</v>
+        <v>46213.575370370374</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>46212.506504629629</v>
+        <v>46209.478831018518</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>95</v>
@@ -1725,17 +1698,17 @@
       <c r="L15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>46209.478831018518</v>
+        <v>46212.574641203704</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>97</v>
@@ -1747,241 +1720,241 @@
         <v>98</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="K16" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>46212.574641203704</v>
+        <v>46213.604710648149</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>46212.640532407408</v>
+        <v>46213.561307870368</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>46212.53707175926</v>
+        <v>46213.607789351852</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>46212.622499999998</v>
+        <v>46212.624918981484</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="9" t="s">
+      <c r="G20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="I20" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="J20" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="K20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" s="5" t="s">
+      <c r="L20" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L20" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="3">
-        <v>46212.624918981484</v>
+        <v>46210.751759259256</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="J21" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="K21" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="L21" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="3">
-        <v>46210.751759259256</v>
+        <v>46210.755798611113</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>136</v>
@@ -2002,92 +1975,90 @@
         <v>139</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="3">
-        <v>46210.755798611113</v>
+        <v>46212.758298611108</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="3">
-        <v>46212.637777777774</v>
+        <v>46213.6565162037</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>151</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>152</v>
@@ -2095,11 +2066,11 @@
       <c r="L24" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2117,31 +2088,31 @@
         <v>155</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="J25" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="K25" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="L25" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2149,35 +2120,35 @@
       <c r="B26" s="3">
         <v>46211.51048611111</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9" t="s">
-        <v>186</v>
+        <v>170</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="H26" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="I26" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L26" s="17" t="s">
-        <v>181</v>
+      <c r="J26" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2185,35 +2156,35 @@
       <c r="B27" s="3">
         <v>46211.51048611111</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9" t="s">
-        <v>186</v>
+        <v>171</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L27" s="17" t="s">
         <v>181</v>
       </c>
+      <c r="I27" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>178</v>
+      </c>
       <c r="M27" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2221,35 +2192,35 @@
       <c r="B28" s="3">
         <v>46211.51048611111</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9" t="s">
-        <v>186</v>
+        <v>172</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I28" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J28" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L28" s="17" t="s">
-        <v>182</v>
-      </c>
       <c r="M28" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2257,122 +2228,170 @@
       <c r="B29" s="3">
         <v>46211.51048611111</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
       <c r="E29" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>186</v>
+        <v>173</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I29" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="J29" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>182</v>
-      </c>
       <c r="M29" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="3">
-        <v>46211.51048611111</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="J30" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="K30" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="3">
-        <v>46211.51048611111</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="18" t="s">
-        <v>187</v>
-      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$13</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$23</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="172">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -141,6 +141,153 @@
     <t>9425805295</t>
   </si>
   <si>
+    <t>MR2607/0166</t>
+  </si>
+  <si>
+    <t>220KV_220kv Barwaha-Indore-l</t>
+  </si>
+  <si>
+    <t>220KV_BARWAHA</t>
+  </si>
+  <si>
+    <t>Bus bar protection wiring</t>
+  </si>
+  <si>
+    <t>13-07-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>er. imran beg</t>
+  </si>
+  <si>
+    <t>9425805200</t>
+  </si>
+  <si>
+    <t>MR2607/0161</t>
+  </si>
+  <si>
+    <t>132KV_Betul Amla</t>
+  </si>
+  <si>
+    <t>220KV_BETUL</t>
+  </si>
+  <si>
+    <t>F/O disc replacement &amp; other line maint. work</t>
+  </si>
+  <si>
+    <t>13-07-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>MR2607/0160</t>
+  </si>
+  <si>
+    <t>132KV_Betul Multai</t>
+  </si>
+  <si>
+    <t>13-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0158</t>
+  </si>
+  <si>
+    <t>220KV_220KV Dhar-Pithampur ckt</t>
+  </si>
+  <si>
+    <t>220KV_DHAR</t>
+  </si>
+  <si>
+    <t>Bay Mainten.&amp; Adii.Relay  (DPR-2) Installation wor</t>
+  </si>
+  <si>
+    <t>13-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Er. Nirmal Patel</t>
+  </si>
+  <si>
+    <t>9826854560</t>
+  </si>
+  <si>
+    <t>MR2607/0159</t>
+  </si>
+  <si>
+    <t>220KV_220kv 160MVA Xmer-ll CGL</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>oil topping work</t>
+  </si>
+  <si>
+    <t>13-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>VIKRAM AHIRWAR</t>
+  </si>
+  <si>
+    <t>9425805415</t>
+  </si>
+  <si>
+    <t>MR2607/0163</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR - MANSAKRA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>F/o Disc Replacement and Other Line Maintenance</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2607/0152</t>
+  </si>
+  <si>
+    <t>220KV_220 KV ITARSI-PIPARIYA I</t>
+  </si>
+  <si>
+    <t>220KV_PIPARIYA</t>
+  </si>
+  <si>
+    <t>Replacement of Single to Double Disc Insulator</t>
+  </si>
+  <si>
+    <t>17-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>ASHUTOSH RAI</t>
+  </si>
+  <si>
+    <t>9425806902</t>
+  </si>
+  <si>
     <t>MR2607/0124</t>
   </si>
   <si>
@@ -165,22 +312,82 @@
     <t>9425801348</t>
   </si>
   <si>
-    <t>MR2607/0149</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna-Manjhgawan Line</t>
+    <t>MR2607/0154</t>
+  </si>
+  <si>
+    <t>132KV_132kv Sabalgarh Jora Ckt</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2607/0164</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Satna  â¿¿  Nagod ckt â¿¿Ist line</t>
   </si>
   <si>
     <t>220KV_SATNA</t>
   </si>
   <si>
-    <t>Stringing work Kotar Manjhgawan Line</t>
-  </si>
-  <si>
-    <t>12-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>12-07-2026 16:00:00</t>
+    <t>line maintenance work of 132 kv Satna  â¿¿  Nagod ck</t>
+  </si>
+  <si>
+    <t>R.K.Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2607/0127</t>
+  </si>
+  <si>
+    <t>132KV_132kV Seoni Lalbarra Line</t>
+  </si>
+  <si>
+    <t>132KV_SEONI1</t>
+  </si>
+  <si>
+    <t>Re-sagging of section Loc no. 141 to 158</t>
+  </si>
+  <si>
+    <t>10-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2607/0098</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220 KV ATPS-Shahdol Line</t>
+  </si>
+  <si>
+    <t>220KV_SHAHDOL</t>
+  </si>
+  <si>
+    <t>Tower Erection,Stringing &amp; De-stringing work</t>
+  </si>
+  <si>
+    <t>09-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>15-07-2026 18:00:00</t>
   </si>
   <si>
     <t>Dharmendra Dwivedi</t>
@@ -189,75 +396,6 @@
     <t>9425805311</t>
   </si>
   <si>
-    <t>MR2607/0156</t>
-  </si>
-  <si>
-    <t>132KV_33 kv main bus shutdown</t>
-  </si>
-  <si>
-    <t>132KV_SATNA1</t>
-  </si>
-  <si>
-    <t>33 kv main bus maintenanace</t>
-  </si>
-  <si>
-    <t>12-07-2026 07:30:00</t>
-  </si>
-  <si>
-    <t>12-07-2026 10:30:00</t>
-  </si>
-  <si>
-    <t>SHRI ARUN KUMAR KOL</t>
-  </si>
-  <si>
-    <t>8319677721</t>
-  </si>
-  <si>
-    <t>MR2607/0127</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Lalbarra Line</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>Re-sagging of section Loc no. 141 to 158</t>
-  </si>
-  <si>
-    <t>10-07-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>13-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2607/0098</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220 KV ATPS-Shahdol Line</t>
-  </si>
-  <si>
-    <t>220KV_SHAHDOL</t>
-  </si>
-  <si>
-    <t>Tower Erection,Stringing &amp; De-stringing work</t>
-  </si>
-  <si>
-    <t>09-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>15-07-2026 18:00:00</t>
-  </si>
-  <si>
     <t>MR2607/0099</t>
   </si>
   <si>
@@ -270,28 +408,70 @@
     <t>Tower Erection, Stringing &amp; De-Stringing work</t>
   </si>
   <si>
+    <t>MR2607/0165</t>
+  </si>
+  <si>
+    <t>132KV_132kv Tikamgarh-Digoda 1st line</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>Y-phase Pole of CB replacement work</t>
+  </si>
+  <si>
+    <t>Pushpendra kumar soni</t>
+  </si>
+  <si>
+    <t>9425806398</t>
+  </si>
+  <si>
+    <t>MR2607/0167</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Tikamgrah digoda 1</t>
+  </si>
+  <si>
+    <t>For maintenance in opportunity SD</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
     <t>MR2607/0101</t>
   </si>
   <si>
     <t>220KV_220 kv Tikamgrah Chhatarpur ckt-1</t>
   </si>
   <si>
-    <t>220KV_TIKAMGARH</t>
-  </si>
-  <si>
     <t>For modification &amp; shifting work</t>
   </si>
   <si>
     <t>09-07-2026 18:00:00</t>
   </si>
   <si>
-    <t>17-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
+    <t>MR2607/0147</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Ujjain-PGCIL-I (Hathunia)</t>
+  </si>
+  <si>
+    <t>220KV_UJJAIN</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Premonsoon Maintanance work</t>
+  </si>
+  <si>
+    <t>B.C JOSHI</t>
+  </si>
+  <si>
+    <t>7587951137</t>
   </si>
   <si>
     <t>ok</t>
@@ -300,19 +480,46 @@
     <t>ok, line to be in service</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>real time</t>
   </si>
   <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 12.07.26</t>
-  </si>
-  <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
-  </si>
-  <si>
-    <t>12-Jul-2026</t>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>deferred, not in WR list</t>
+  </si>
+  <si>
+    <t>deferred, due to s/d on 220KV PITHAMPUR IC CKT-2</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 13.07.2026</t>
+  </si>
+  <si>
+    <t>400KV/132KV VINDHYACHAL-ICT-3</t>
+  </si>
+  <si>
+    <t>13-Jul-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18-Jul-2026</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Annual Bay Maintenance and Testing / CRP Replacement</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
   </si>
   <si>
     <t>09:00</t>
@@ -321,28 +528,16 @@
     <t>17:00</t>
   </si>
   <si>
-    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
-  </si>
-  <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>220KV-AJAYGARH-SATNA-1</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-2</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF EXISTING CONDUCTOR WITH HTLS TYPE CONDUCTOR</t>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-GWALIOR-II-1</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>220KV-ITARSI-MP-ITARSI-1</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
@@ -400,7 +595,7 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -434,7 +629,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -617,14 +812,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="15" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -992,23 +1185,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="57.5703125" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="50.140625" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="56.85546875" customWidth="1"/>
+    <col min="13" max="13" width="44.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -1025,28 +1217,28 @@
       <c r="L1" s="10"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="13" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="1"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="15"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1069,7 +1261,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1108,7 +1300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1146,10 +1338,10 @@
         <v>26</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1188,23 +1380,21 @@
         <v>34</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A17" si="0">A6+1</f>
+        <f t="shared" ref="A7:A28" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46212.574641203704</v>
+        <v>46215.701689814814</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
         <v>36</v>
       </c>
@@ -1230,16 +1420,16 @@
         <v>42</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46213.769976851851</v>
+        <v>46215.515451388892</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>43</v>
@@ -1270,16 +1460,16 @@
         <v>50</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46214.610347222224</v>
+        <v>46215.513877314814</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>51</v>
@@ -1289,368 +1479,799 @@
         <v>52</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="K9" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46212.624918981484</v>
+        <v>46215.421944444446</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="M10" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46210.751759259256</v>
+        <v>46215.458402777775</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46210.755798611113</v>
+        <v>46215.515902777777</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="17">
-        <v>46211.51048611111</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="5">
+        <v>46214.488229166665</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="G13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="16" t="s">
+      <c r="I13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="K13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="L13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K13" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="L13" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="M13" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22" t="s">
+      <c r="B14" s="5">
+        <v>46212.574641203704</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="N14" s="24"/>
-    </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
+      <c r="M14" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22" t="s">
+      <c r="B15" s="5">
+        <v>46214.53800925926</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="N15" s="24"/>
-    </row>
-    <row r="16" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="M15" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22" t="s">
+      <c r="B16" s="5">
+        <v>46215.545312499999</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="22" t="s">
+      <c r="I16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="N16" s="24"/>
-    </row>
-    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+      <c r="L16" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="22" t="s">
+      <c r="B17" s="5">
+        <v>46212.624918981484</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="24"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="26" t="s">
+      <c r="F17" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="N18" s="24"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46210.751759259256</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46210.755798611113</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46215.553425925929</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46215.763043981482</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46211.51048611111</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="17">
+        <v>46213.761307870373</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="24" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$10</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -87,6 +87,33 @@
     <t>REMARK</t>
   </si>
   <si>
+    <t>MR2607/0272</t>
+  </si>
+  <si>
+    <t>132KV_132KV Alot-Jharla Ckt-II Line</t>
+  </si>
+  <si>
+    <t>132KV_ALOT</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>OPGW Stringing work between Loc.No.1 to Gantry</t>
+  </si>
+  <si>
+    <t>20-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>20-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Naresh pandre</t>
+  </si>
+  <si>
+    <t>9425806905</t>
+  </si>
+  <si>
     <t>MR2606/0252</t>
   </si>
   <si>
@@ -99,9 +126,6 @@
     <t>220KV_ANUPPUR</t>
   </si>
   <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
     <t>For work of conductor re sagging in various loc.</t>
   </si>
   <si>
@@ -117,6 +141,27 @@
     <t>9424445533</t>
   </si>
   <si>
+    <t>MR2607/0280</t>
+  </si>
+  <si>
+    <t>220KV_220KV Barwaha -Indore -I</t>
+  </si>
+  <si>
+    <t>220KV_BARWAHA</t>
+  </si>
+  <si>
+    <t>for Bus Bar Protection Wiring</t>
+  </si>
+  <si>
+    <t>20-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er.Imran Beg</t>
+  </si>
+  <si>
+    <t>9425805200</t>
+  </si>
+  <si>
     <t>MR2607/0264</t>
   </si>
   <si>
@@ -153,6 +198,90 @@
     <t>Shutdown required for 220KV line Modification work</t>
   </si>
   <si>
+    <t>MR2607/0277</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA ECE X-mer-I</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
+  </si>
+  <si>
+    <t>LV side RVB CT replacement work</t>
+  </si>
+  <si>
+    <t>20-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Er Ganesh Mansare</t>
+  </si>
+  <si>
+    <t>9425802441</t>
+  </si>
+  <si>
+    <t>MR2607/0282</t>
+  </si>
+  <si>
+    <t>132KV_132kv Shahdol-Dindori ckt-II</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>For flash over disc Replacement &amp; other line work</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Ashati</t>
+  </si>
+  <si>
+    <t>MR2607/0281</t>
+  </si>
+  <si>
+    <t>132KV_132KV Handia -Harda -2 Feeder</t>
+  </si>
+  <si>
+    <t>220KV_HANDIYA</t>
+  </si>
+  <si>
+    <t>For R Phase CT Hot Point Attending Work</t>
+  </si>
+  <si>
+    <t>20-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>20-07-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>K.R.Dongre</t>
+  </si>
+  <si>
+    <t>9424430754</t>
+  </si>
+  <si>
+    <t>MR2607/0278</t>
+  </si>
+  <si>
+    <t>220KV_220KV Nagra Sailana ckt-1&amp;2</t>
+  </si>
+  <si>
+    <t>220KV_NAGRA</t>
+  </si>
+  <si>
+    <t>replacement of OPGW hotline permit</t>
+  </si>
+  <si>
+    <t>20-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>21-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>P.S.Solanki</t>
+  </si>
+  <si>
+    <t>9425820041</t>
+  </si>
+  <si>
     <t>220KV_Bus Coupler and Bus A</t>
   </si>
   <si>
@@ -165,9 +294,6 @@
     <t>15-07-2026 10:00:00</t>
   </si>
   <si>
-    <t>20-07-2026 18:00:00</t>
-  </si>
-  <si>
     <t>Chandan Dalai</t>
   </si>
   <si>
@@ -177,79 +303,107 @@
     <t>MR2607/0227</t>
   </si>
   <si>
-    <t>MR2607/0273</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Satna Nagod Ckt-1st Line</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>Stringing work of 2nd Ckt of 132 KV Nagod Powai Li</t>
-  </si>
-  <si>
-    <t>19-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>19-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Dharmendra Dwivedi</t>
-  </si>
-  <si>
-    <t>9425805311</t>
-  </si>
-  <si>
-    <t>MR2607/0203</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Katangi Line</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>Work for Re-sagging of Section Loc 141 to 158</t>
-  </si>
-  <si>
-    <t>15-07-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>ok, through sub ld, charging permission of electrical Inspector will be required during charging the line</t>
-  </si>
-  <si>
-    <t>deferred, not in WR list</t>
+    <t>MR2607/0279</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 40 MVA TELK X-MER</t>
+  </si>
+  <si>
+    <t>132KV_SIDHI1</t>
+  </si>
+  <si>
+    <t>33KV INCOMER RYB PHASE CT REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>SHRI VISHAL BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425804690</t>
+  </si>
+  <si>
+    <t>sub ld</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>telemetry availability to be ensured, line to be in service</t>
+  </si>
+  <si>
+    <t>400KV-SAGAR-BINA-1</t>
+  </si>
+  <si>
+    <t>400KV-INDORE-MP-ASOJ-2</t>
+  </si>
+  <si>
     <t>220KV-MEHGAON-AURIYA-1</t>
   </si>
   <si>
+    <t>220KV-GWALIOR-MAHALGAON-3</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
+  </si>
+  <si>
+    <t>220KV-REWA-SINDHI-MP-1</t>
+  </si>
+  <si>
+    <t>220KV-SEONI-PG-CHINDWARA-1</t>
+  </si>
+  <si>
+    <t>1.For Autoreclose relay retroffiting  (Main &amp; Tie Bay) with Dia Open
+2. For Line terminal AMP work</t>
+  </si>
+  <si>
+    <t>CRP retrofitting work in new SPR at Asoj (Under O&amp;M Add cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>20-Jul-2026</t>
+  </si>
+  <si>
     <t>09:00</t>
   </si>
   <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>31-Jul-2026</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
-  </si>
-  <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>OCCM -WR</t>
-  </si>
-  <si>
-    <t>MP SLDC</t>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>WR-OCCM</t>
+  </si>
+  <si>
+    <t>S/I ,SLDC MPTCL JABALPUR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.20.07.2026</t>
   </si>
 </sst>
 </file>
@@ -260,7 +414,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -299,6 +453,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -314,12 +480,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -368,6 +534,19 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -381,78 +560,67 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -817,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -826,395 +994,851 @@
     <col min="5" max="5" width="39.140625" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="47.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="46.85546875" customWidth="1"/>
+    <col min="9" max="10" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="20.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="44.140625" customWidth="1"/>
+    <col min="13" max="13" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>46222</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="17">
+        <v>46223</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="7" t="s">
+      <c r="L4" s="16"/>
+      <c r="M4" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="3">
+        <v>46221.533449074072</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <f>A5+1</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
         <v>46184.683831018519</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <f t="shared" ref="A7:A22" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46222.615682870368</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46220.601724537039</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46220.603622685187</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46222.484502314815</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46222.700613425928</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46222.619490740741</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46222.489837962959</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46218.568136574075</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="B21" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46220.601724537039</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46220.603622685187</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46218.568136574075</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11">
-        <v>46221.589583333334</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11">
-        <v>46217.559537037036</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>7</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15">
-        <v>313959</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="17" t="s">
-        <v>69</v>
-      </c>
+      <c r="B22" s="3">
+        <v>46222.536111111112</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E2:L2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,31 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$15</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="129">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -87,45 +76,21 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2607/0272</t>
-  </si>
-  <si>
-    <t>132KV_132KV Alot-Jharla Ckt-II Line</t>
-  </si>
-  <si>
-    <t>132KV_ALOT</t>
+    <t>MR2606/0252</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Anuppur-Kotmikala Circuit I</t>
+  </si>
+  <si>
+    <t>220KV_ANUPPUR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>OPGW Stringing work between Loc.No.1 to Gantry</t>
-  </si>
-  <si>
-    <t>20-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>20-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Naresh pandre</t>
-  </si>
-  <si>
-    <t>9425806905</t>
-  </si>
-  <si>
-    <t>MR2606/0252</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Anuppur-Kotmikala Circuit I</t>
-  </si>
-  <si>
-    <t>220KV_ANUPPUR</t>
-  </si>
-  <si>
     <t>For work of conductor re sagging in various loc.</t>
   </si>
   <si>
@@ -141,27 +106,63 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2607/0280</t>
-  </si>
-  <si>
-    <t>220KV_220KV Barwaha -Indore -I</t>
+    <t>MR2607/0293</t>
+  </si>
+  <si>
+    <t>220KV_220 KV BAIRAGARH ASHTA LINE</t>
+  </si>
+  <si>
+    <t>400KV_ASHTA4</t>
+  </si>
+  <si>
+    <t>LINE MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>21-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>21-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>NITIN RESHWAL</t>
+  </si>
+  <si>
+    <t>9425804890</t>
+  </si>
+  <si>
+    <t>MR2607/0290</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 160MVA X-MRE (BBL)</t>
   </si>
   <si>
     <t>220KV_BARWAHA</t>
   </si>
   <si>
-    <t>for Bus Bar Protection Wiring</t>
-  </si>
-  <si>
-    <t>20-07-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Er.Imran Beg</t>
+    <t>Trip transfer scheme work</t>
+  </si>
+  <si>
+    <t>21-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>21-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er. Imran Beg</t>
   </si>
   <si>
     <t>9425805200</t>
   </si>
   <si>
+    <t>MR2607/0291</t>
+  </si>
+  <si>
+    <t>220KV_220KV Barwaha - Itarsi Feeder</t>
+  </si>
+  <si>
+    <t>Bus Bar protection wiring work</t>
+  </si>
+  <si>
     <t>MR2607/0264</t>
   </si>
   <si>
@@ -198,64 +199,106 @@
     <t>Shutdown required for 220KV line Modification work</t>
   </si>
   <si>
-    <t>MR2607/0277</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA ECE X-mer-I</t>
-  </si>
-  <si>
-    <t>400KV_CHHEGAON4</t>
-  </si>
-  <si>
-    <t>LV side RVB CT replacement work</t>
-  </si>
-  <si>
-    <t>20-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Er Ganesh Mansare</t>
-  </si>
-  <si>
-    <t>9425802441</t>
-  </si>
-  <si>
-    <t>MR2607/0282</t>
-  </si>
-  <si>
-    <t>132KV_132kv Shahdol-Dindori ckt-II</t>
-  </si>
-  <si>
-    <t>132KV_DINDORI</t>
-  </si>
-  <si>
-    <t>For flash over disc Replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>Jagdish Prasad Ashati</t>
-  </si>
-  <si>
-    <t>MR2607/0281</t>
-  </si>
-  <si>
-    <t>132KV_132KV Handia -Harda -2 Feeder</t>
-  </si>
-  <si>
-    <t>220KV_HANDIYA</t>
-  </si>
-  <si>
-    <t>For R Phase CT Hot Point Attending Work</t>
-  </si>
-  <si>
-    <t>20-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>20-07-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>K.R.Dongre</t>
-  </si>
-  <si>
-    <t>9424430754</t>
+    <t>MR2607/0285</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bina Pichhore line</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>Flash over disc replacement work and other line ma</t>
+  </si>
+  <si>
+    <t>21-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Satish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>9425806916</t>
+  </si>
+  <si>
+    <t>MR2607/0289</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Chhatarpur â¿¿ Nowgaon Ckt. 2nd Line</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>F/o disc replacement</t>
+  </si>
+  <si>
+    <t>Pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2607/0294</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Bus Tie</t>
+  </si>
+  <si>
+    <t>220KV_GUNA</t>
+  </si>
+  <si>
+    <t>R phase Isolater Clamp Hot Point Attend Work</t>
+  </si>
+  <si>
+    <t>21-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>21-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Sagar shingh Dhakad</t>
+  </si>
+  <si>
+    <t>9589205697</t>
+  </si>
+  <si>
+    <t>MR2607/0295</t>
+  </si>
+  <si>
+    <t>220KV_220KV ITARSI-BARWAHA LINE</t>
+  </si>
+  <si>
+    <t>220KV_ITARSI</t>
+  </si>
+  <si>
+    <t>FLASH OVER DISC REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>R.N. PARTE</t>
+  </si>
+  <si>
+    <t>9425804701</t>
+  </si>
+  <si>
+    <t>MR2607/0292</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Jabalpur-Narsinghpur Line Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>Installation of Bird excreta preventer work at Loc</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
   </si>
   <si>
     <t>MR2607/0278</t>
@@ -273,55 +316,34 @@
     <t>20-07-2026 08:00:00</t>
   </si>
   <si>
-    <t>21-07-2026 17:00:00</t>
-  </si>
-  <si>
     <t>P.S.Solanki</t>
   </si>
   <si>
     <t>9425820041</t>
   </si>
   <si>
-    <t>220KV_Bus Coupler and Bus A</t>
-  </si>
-  <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
-    <t>Annual Maintenance</t>
-  </si>
-  <si>
-    <t>15-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Chandan Dalai</t>
-  </si>
-  <si>
-    <t>8085450465</t>
-  </si>
-  <si>
-    <t>MR2607/0227</t>
-  </si>
-  <si>
-    <t>MR2607/0279</t>
-  </si>
-  <si>
-    <t>132KV_132/33 KV 40 MVA TELK X-MER</t>
-  </si>
-  <si>
-    <t>132KV_SIDHI1</t>
-  </si>
-  <si>
-    <t>33KV INCOMER RYB PHASE CT REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>SHRI VISHAL BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425804690</t>
-  </si>
-  <si>
-    <t>sub ld</t>
+    <t>MR2607/0299</t>
+  </si>
+  <si>
+    <t>33KV_33 KV MAIN BUS</t>
+  </si>
+  <si>
+    <t>132KV_REWA-II (SAGRA)</t>
+  </si>
+  <si>
+    <t>33 KV MAIN BUS MAINTINENCE WORK</t>
+  </si>
+  <si>
+    <t>21-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>21-07-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>ER. KANISHK SINGH</t>
+  </si>
+  <si>
+    <t>9425804656</t>
   </si>
   <si>
     <t>ok</t>
@@ -330,80 +352,64 @@
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>telemetry availability to be ensured, line to be in service</t>
-  </si>
-  <si>
-    <t>400KV-SAGAR-BINA-1</t>
-  </si>
-  <si>
-    <t>400KV-INDORE-MP-ASOJ-2</t>
-  </si>
-  <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-MAHALGAON-3</t>
+    <t>ok, as opportunity s/d</t>
+  </si>
+  <si>
+    <t>ok, for x-mer</t>
+  </si>
+  <si>
+    <t>availability of telemetry to be confirmed SLDC SCADA, line to be in service</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
-    <t>220KV-REWA-SINDHI-MP-1</t>
-  </si>
-  <si>
-    <t>220KV-SEONI-PG-CHINDWARA-1</t>
-  </si>
-  <si>
-    <t>1.For Autoreclose relay retroffiting  (Main &amp; Tie Bay) with Dia Open
-2. For Line terminal AMP work</t>
-  </si>
-  <si>
-    <t>CRP retrofitting work in new SPR at Asoj (Under O&amp;M Add cap)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
-  </si>
-  <si>
-    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-2</t>
+  </si>
+  <si>
+    <t>220KV-INDORE-UJJAIN-2</t>
   </si>
   <si>
     <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+  </si>
+  <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
     <t>real time</t>
   </si>
   <si>
-    <t>20-Jul-2026</t>
+    <t>21-Jul-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>31-Jul-2026</t>
-  </si>
-  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>WR-OCCM</t>
-  </si>
-  <si>
-    <t>S/I ,SLDC MPTCL JABALPUR</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.20.07.2026</t>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>S/I, SLDC MPPTCL JBP</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD. 21.07.2026</t>
   </si>
 </sst>
 </file>
@@ -411,10 +417,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -427,18 +433,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -448,20 +457,21 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="18"/>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -480,12 +490,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -545,81 +555,69 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -985,183 +983,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="39.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="46.85546875" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="13" max="13" width="43.5703125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
-    </row>
-    <row r="2" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17">
-        <v>46223</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="B2" s="21">
+        <v>46224</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+    </row>
+    <row r="3" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="14" t="s">
+      <c r="L4" s="20"/>
+      <c r="M4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>46221.533449074072</v>
+        <v>46184.683831018519</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>46184.683831018519</v>
+        <v>46223.628009259257</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>30</v>
@@ -1178,636 +1176,621 @@
       <c r="L6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f t="shared" ref="A7:A22" si="0">A6+1</f>
+        <f t="shared" ref="A7:A21" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>46222.615682870368</v>
+        <v>46223.58016203704</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>46220.601724537039</v>
+        <v>46223.581828703704</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>46220.603622685187</v>
+        <v>46220.601724537039</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="J9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="K9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="L9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>46222.484502314815</v>
+        <v>46220.603622685187</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="D10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>46222.700613425928</v>
+        <v>46223.425497685188</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="I11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="J11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="L11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <v>46222.619490740741</v>
+        <v>46223.572812500002</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="I12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="L12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>46222.489837962959</v>
+        <v>46223.629444444443</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="I13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="J13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="L13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>46218.568136574075</v>
+        <v>46223.63045138889</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="L14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>46222.536111111112</v>
+        <v>46223.612372685187</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2" t="s">
+      <c r="I15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="L15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M15" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>46222.536111111112</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>46222.489837962959</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>107</v>
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>46222.536111111112</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>46223.671805555554</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>108</v>
+        <v>21</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>46222.536111111112</v>
+        <v>46223.671805555554</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="7" t="s">
-        <v>102</v>
+      <c r="E18" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="J18" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>46222.536111111112</v>
+        <v>46223.671805555554</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="7" t="s">
-        <v>103</v>
+      <c r="E19" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="J19" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>46222.536111111112</v>
+        <v>46223.671805555554</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="7" t="s">
-        <v>104</v>
+      <c r="E20" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="J20" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="3">
-        <v>46222.536111111112</v>
+        <v>46223.671805555554</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="7" t="s">
-        <v>105</v>
+      <c r="E21" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="J21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="K21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46222.536111111112</v>
-      </c>
+    </row>
+    <row r="22" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="7" t="s">
-        <v>106</v>
-      </c>
+      <c r="E22" s="9"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="E23" s="9"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1815,33 +1798,16 @@
       <c r="J23" s="4"/>
       <c r="K23" s="5"/>
       <c r="L23" s="6"/>
-      <c r="M23" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="2"/>
+      <c r="M23" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$24</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="200">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,10 +76,10 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2607/0310</t>
-  </si>
-  <si>
-    <t>220KV_Amk-Birsingpur No.2</t>
+    <t>MR2607/0312</t>
+  </si>
+  <si>
+    <t>220KV_Amk-Gorabazar</t>
   </si>
   <si>
     <t>220KV_AMARKANTAK</t>
@@ -91,10 +91,10 @@
     <t>CPRI Protection audit work</t>
   </si>
   <si>
-    <t>22-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22-07-2026 18:00:00</t>
+    <t>23-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23-07-2026 18:00:00</t>
   </si>
   <si>
     <t>Vijay Kothari</t>
@@ -103,24 +103,42 @@
     <t>9425808910</t>
   </si>
   <si>
-    <t>MR2607/0309</t>
-  </si>
-  <si>
-    <t>220KV_Amk-Panagar</t>
+    <t>MR2607/0317</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_220KV TRANSFER BUS</t>
+  </si>
+  <si>
+    <t>Jumper work to newly constructed Bay 22-23</t>
   </si>
   <si>
     <t>22-07-2026 09:00:00</t>
   </si>
   <si>
-    <t>22-07-2026 13:00:00</t>
+    <t>AJAY PARTETI</t>
+  </si>
+  <si>
+    <t>9425808877</t>
+  </si>
+  <si>
+    <t>MR2607/0311</t>
+  </si>
+  <si>
+    <t>220KV_Amk-Jabalpur</t>
+  </si>
+  <si>
+    <t>23-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>23-07-2026 13:00:00</t>
   </si>
   <si>
     <t>MR2606/0252</t>
   </si>
   <si>
-    <t>Daily</t>
-  </si>
-  <si>
     <t>220KV_220 kV Anuppur-Kotmikala Circuit I</t>
   </si>
   <si>
@@ -136,43 +154,259 @@
     <t>09-07-2026 08:00:00</t>
   </si>
   <si>
-    <t>23-07-2026 18:00:00</t>
-  </si>
-  <si>
     <t>Jagdish Prasad Asati</t>
   </si>
   <si>
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2607/0304</t>
-  </si>
-  <si>
-    <t>220KV_220 kv jabalpur birsinghpur circuit 1</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>Disc F/o change at loc. 88 , 215</t>
-  </si>
-  <si>
-    <t>jitendra tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2607/0305</t>
-  </si>
-  <si>
-    <t>132KV_132 KV KATNI - PANAGAR LINE</t>
-  </si>
-  <si>
-    <t>132KV_KATNI</t>
-  </si>
-  <si>
-    <t>F/o Disc Replacement and Other Line Maintenance</t>
+    <t>220KV_220 KV Chichli- narsinghpur Load transfer in buscoupler</t>
+  </si>
+  <si>
+    <t>220KV_CHICHLI</t>
+  </si>
+  <si>
+    <t>9425805203</t>
+  </si>
+  <si>
+    <t>MR2607/0325</t>
+  </si>
+  <si>
+    <t>Load shift 0n buscoupler, Relay testing work</t>
+  </si>
+  <si>
+    <t>23-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>23-07-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>shri R. Chaturvedi</t>
+  </si>
+  <si>
+    <t>MR2607/0301</t>
+  </si>
+  <si>
+    <t>132KV_132KV DAMOH - PATERA LINE IST&amp;IIND CKT</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>23-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>29-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2607/0340</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>132KV_I/C no.2nd (160MVA EMCo)</t>
+  </si>
+  <si>
+    <t>220KV_DEWAS</t>
+  </si>
+  <si>
+    <t>C.B. Gas Leakage Attanding work</t>
+  </si>
+  <si>
+    <t>23-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>A.K. Joshi</t>
+  </si>
+  <si>
+    <t>9425801305</t>
+  </si>
+  <si>
+    <t>MR2607/0324</t>
+  </si>
+  <si>
+    <t>220KV_Dhar-Kanwan ckt-2</t>
+  </si>
+  <si>
+    <t>220KV_DHAR</t>
+  </si>
+  <si>
+    <t>For line maintenance work</t>
+  </si>
+  <si>
+    <t>22-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>24-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>V.R. Panadia</t>
+  </si>
+  <si>
+    <t>9425802330</t>
+  </si>
+  <si>
+    <t>MR2607/0337</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Tikamgarh - Jatara Line</t>
+  </si>
+  <si>
+    <t>132KV_JATARA</t>
+  </si>
+  <si>
+    <t>F/o disc replacement</t>
+  </si>
+  <si>
+    <t>23-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2607/0257</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Modifiction work</t>
+  </si>
+  <si>
+    <t>22-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>05-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2607/0336</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 50MVA TAL X-MER</t>
+  </si>
+  <si>
+    <t>220KV_MAIHAR</t>
+  </si>
+  <si>
+    <t>installation of a CT shifting arrangement on LV Si</t>
+  </si>
+  <si>
+    <t>23-07-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>23-07-2026 13:30:00</t>
+  </si>
+  <si>
+    <t>ARUN KUMAR KOL</t>
+  </si>
+  <si>
+    <t>7000923305</t>
+  </si>
+  <si>
+    <t>MR2607/0343</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Nagra - Sailana Ckt-1st&amp;2nd</t>
+  </si>
+  <si>
+    <t>220KV_NAGRA</t>
+  </si>
+  <si>
+    <t>For OPGW replacement work</t>
+  </si>
+  <si>
+    <t>24-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Pappu Singh Solanki</t>
+  </si>
+  <si>
+    <t>9425820041</t>
+  </si>
+  <si>
+    <t>MR2607/0328</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>For Line Maintenance Work</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2607/0342</t>
+  </si>
+  <si>
+    <t>220KV_OPGW of 220 KV Mandsaur Nipaniya line</t>
+  </si>
+  <si>
+    <t>220KV_NIPANIYA</t>
+  </si>
+  <si>
+    <t>OPGW Work</t>
+  </si>
+  <si>
+    <t>23-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0339</t>
+  </si>
+  <si>
+    <t>220KV_220KV Mandsaur Nipaniya Circuit Ist</t>
+  </si>
+  <si>
+    <t>Hotline shutdown</t>
+  </si>
+  <si>
+    <t>MR2607/0341</t>
+  </si>
+  <si>
+    <t>220KV_220KV Mandsaur Nipaniya Circuit IInd</t>
+  </si>
+  <si>
+    <t>MR2607/0331</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR - MANSAKRA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>F/o Disc Replacement and other line maintenance</t>
   </si>
   <si>
     <t>MANOJ KUMAR TIWARI</t>
@@ -181,67 +415,46 @@
     <t>9425804993</t>
   </si>
   <si>
-    <t>MR2607/0306</t>
-  </si>
-  <si>
-    <t>132KV_132 KV KATNI - KYMORE LINE CKT - 2ND</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>MR2607/0257</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Modifiction work</t>
-  </si>
-  <si>
-    <t>22-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>05-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2607/0308</t>
-  </si>
-  <si>
-    <t>220KV_160MVA Xmer-I (Areva)</t>
-  </si>
-  <si>
-    <t>220KV_SABALGARH</t>
-  </si>
-  <si>
-    <t>HV Side LA(RYB Ph) Replacement work</t>
-  </si>
-  <si>
-    <t>22-07-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Sh. Deendayal Mahour</t>
-  </si>
-  <si>
-    <t>9425805742</t>
-  </si>
-  <si>
-    <t>MR2607/0307</t>
-  </si>
-  <si>
-    <t>132KV_132KV 40MVA XMER ABB</t>
+    <t>MR2607/0335</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Prithvipur-PIML Ckt. 1st Line</t>
+  </si>
+  <si>
+    <t>132KV_PRITHVIPUR</t>
+  </si>
+  <si>
+    <t>Necessary maintenance work of line.</t>
+  </si>
+  <si>
+    <t>23-07-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0327</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA X-MAR EMCO</t>
+  </si>
+  <si>
+    <t>132KV_SAGAR1</t>
+  </si>
+  <si>
+    <t>R PHAES LV BUSSING HOT POINT ATTAND WORK</t>
+  </si>
+  <si>
+    <t>23-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>SK HAJARI</t>
+  </si>
+  <si>
+    <t>9425620010</t>
+  </si>
+  <si>
+    <t>MR2607/0333</t>
+  </si>
+  <si>
+    <t>132KV_132kv 40mva xmer abb</t>
   </si>
   <si>
     <t>220KV_SATNA</t>
@@ -250,150 +463,156 @@
     <t>OCCM-MP</t>
   </si>
   <si>
-    <t>For  lv ct rybph repacement work</t>
-  </si>
-  <si>
-    <t>22-07-2026 09:28:00</t>
-  </si>
-  <si>
-    <t>poshkar kushwaha</t>
+    <t>For replace Lv CT RYBph replacement work</t>
+  </si>
+  <si>
+    <t>23-07-2026 09:27:00</t>
+  </si>
+  <si>
+    <t>23-07-2026 17:37:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
   </si>
   <si>
     <t>9425813990</t>
   </si>
   <si>
-    <t>MR2607/0302</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Ujjain Interconnector - 3</t>
-  </si>
-  <si>
-    <t>220KV_UJJAIN</t>
-  </si>
-  <si>
-    <t>Bay maintenance work</t>
-  </si>
-  <si>
-    <t>B C Joshi</t>
-  </si>
-  <si>
-    <t>7587951137</t>
-  </si>
-  <si>
-    <t>deferred, not in WRPC approval list</t>
+    <t>MR2607/0330</t>
+  </si>
+  <si>
+    <t>132KV_132KV SATNA-NAGOD CKT1 LINE</t>
+  </si>
+  <si>
+    <t>STRINGING WORK FROM LOC 56R TO 65</t>
+  </si>
+  <si>
+    <t>DHARMENDRA DWIVEDI</t>
+  </si>
+  <si>
+    <t>9425805311</t>
+  </si>
+  <si>
+    <t>MR2607/0332</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Udaipura-Tendukheda line Ckt-II</t>
+  </si>
+  <si>
+    <t>132KV_TENDUKHEDA</t>
+  </si>
+  <si>
+    <t>Flashover disc replacement work at loc.No. 70/Y-01</t>
+  </si>
+  <si>
+    <t>Ashish Kumar</t>
+  </si>
+  <si>
+    <t>9425805935</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220KV BARWAHA- NIMRANI TAP OSP CIRCUIT </t>
-  </si>
-  <si>
-    <t>220KV_BARWAHA</t>
-  </si>
-  <si>
-    <t>FOR BUS BAR PROTECTION WIRING WORK</t>
-  </si>
-  <si>
-    <t>AE S/S BARWAHA</t>
-  </si>
-  <si>
-    <t>220KV DHAR - KANWAN CIRCUIT -2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR LINE MAINTENANCE </t>
-  </si>
-  <si>
-    <t>AE TLM SUB DN. RAJGARH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63 MVA BBL X-MER </t>
-  </si>
-  <si>
-    <t>FOR DIFF RELAY R/P &amp; TESTING WORK</t>
-  </si>
-  <si>
-    <t>AE TLM RAJGARH</t>
-  </si>
-  <si>
-    <t>132KV_BARMAN</t>
-  </si>
-  <si>
-    <t>AE S/S BARMAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220KV CHAPDA- DEWAS CIRCUIT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">220KV_CHAPDA </t>
-  </si>
-  <si>
-    <t>FOR DRP-2 COMM. &amp; TEST</t>
-  </si>
-  <si>
-    <t>AE S/S CHAPDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220KV TRANSFER BUS </t>
-  </si>
-  <si>
-    <t>220KV _ATPS</t>
-  </si>
-  <si>
-    <t>FOR TRANFER BUS JUMPER WORK FROM EXISTING 220KV BUS TO NEWLY CONSTRUCTED 220KV BUS OF BAY NO. 22&amp;23</t>
-  </si>
-  <si>
-    <t>400 KV EMD-III,ATPS CHACHAI</t>
-  </si>
-  <si>
-    <t>ok,</t>
-  </si>
-  <si>
-    <t>220KV-MALANPUR-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-DAMOH-SAGAR-2</t>
-  </si>
-  <si>
-    <t>220KV-REWA-SINDHI-MP-2</t>
+    <t>ok, line to be in service through TBC</t>
+  </si>
+  <si>
+    <t>deferred, not in WR list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">telemtry to be confirmed, line to be in service </t>
+  </si>
+  <si>
+    <t>ok, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>ok, line to be in service, through sub ld</t>
+  </si>
+  <si>
+    <t>ok, line to be in service</t>
+  </si>
+  <si>
+    <t>ok, as opportunity s/d</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>400KV-KORADI-SATPURA-1</t>
+  </si>
+  <si>
+    <t>220KV-MEHGAON-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-1</t>
+  </si>
+  <si>
+    <t>220KV-SHUJALPUR-RAJGARH-MP-1</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+    <t>132 KV TIKAMGARH - JATARA CIRCUIT</t>
+  </si>
+  <si>
+    <t>400 KV, EHT-C Dn SAGAR</t>
+  </si>
+  <si>
+    <t>ok, charging permission for EI will be required for charging on new tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220KV_ MORENA </t>
+  </si>
+  <si>
+    <t>FOR PMM</t>
+  </si>
+  <si>
+    <t>For stringing between Loc no 15 to 14 and for tower errection of loc no 14R on line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 kv Bus coupler </t>
+  </si>
+  <si>
+    <t>AE S/S MORENA</t>
+  </si>
+  <si>
+    <t>Overhauling work of CB (External Agency involved)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
   </si>
   <si>
     <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
+    <t xml:space="preserve">	FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>08:00</t>
   </si>
   <si>
+    <t>18:00</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
-    <t>18:00</t>
+    <t>POWERGRID_WR2</t>
   </si>
   <si>
     <t>MP_SLDC</t>
   </si>
   <si>
+    <t>POWERGRID-WR1 (PGCIL)</t>
+  </si>
+  <si>
     <t>NLDC,MADHYA PRADESH</t>
   </si>
   <si>
@@ -401,9 +620,6 @@
   </si>
   <si>
     <t>MADHYA PRADESH,CHATTISGARH</t>
-  </si>
-  <si>
-    <t>real time</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
@@ -417,7 +633,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010409]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010409]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -430,26 +646,18 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -460,6 +668,27 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -484,7 +713,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -574,32 +803,60 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -633,13 +890,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -653,45 +910,65 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1056,20 +1333,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="52.85546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="56.85546875" style="12" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="46.28515625" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="51.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
+    <col min="13" max="13" width="38.85546875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,11 +1371,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="9"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1106,7 +1383,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1121,7 +1398,7 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1129,7 +1406,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1144,7 +1421,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1166,16 +1443,16 @@
         <v>15</v>
       </c>
       <c r="L4" s="15"/>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46224.708506944444</v>
+        <v>46224.719710648147</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1190,7 +1467,7 @@
       <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -1205,24 +1482,26 @@
       <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46224.702986111108</v>
+        <v>46224.737905092596</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E6" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>19</v>
@@ -1230,652 +1509,1087 @@
       <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <f t="shared" ref="A7:A25" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46224.712627314817</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="I7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <f t="shared" ref="A7:A12" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46184.683831018519</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46224.485185185185</v>
+        <v>46184.683831018519</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="11" t="s">
+      <c r="H8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46224.69326388889</v>
+        <v>46225.513703703706</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="6">
-        <v>46225.375</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46224.695162037038</v>
+        <v>46223.674907407411</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E10" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46219.722129629627</v>
+        <v>46225.675775462965</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46224.700648148151</v>
+        <v>46224.76457175926</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" s="11" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>40</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46224.697731481479</v>
+        <v>46225.668032407404</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="11" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>75</v>
+        <v>20</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="M13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46219.722129629627</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46223.73841435185</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
+      <c r="B15" s="5">
+        <v>46225.666608796295</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="6">
-        <v>46225.416666666664</v>
-      </c>
-      <c r="J15" s="6">
-        <v>46225.708333333336</v>
+        <v>95</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="B16" s="5">
+        <v>46225.684259259258</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I16" s="6">
-        <v>46225.416666666664</v>
-      </c>
-      <c r="J16" s="6">
-        <v>46225.75</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
+      <c r="B17" s="5">
+        <v>46225.56763888889</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="6">
-        <v>46225.416666666664</v>
-      </c>
-      <c r="J17" s="6">
-        <v>46225.75</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I18" s="6">
-        <v>46225.458333333336</v>
-      </c>
-      <c r="J18" s="6">
-        <v>46225.708333333336</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>46225.682719907411</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="I19" s="6">
-        <v>46225.458333333336</v>
-      </c>
-      <c r="J19" s="6">
-        <v>46226.75</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>46225.675347222219</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="24" t="s">
+      <c r="B20" s="5">
+        <v>46225.67664351852</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="F21" s="24" t="s">
+      <c r="B21" s="5">
+        <v>46225.611377314817</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="L21" s="25"/>
-      <c r="M21" s="26" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>46225.659722222219</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="K23" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="L23" s="25"/>
-      <c r="M23" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="29"/>
+      <c r="B23" s="5">
+        <v>46225.551585648151</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46225.636840277781</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46225.581203703703</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46225.634050925924</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" s="6">
+        <v>46226.375</v>
+      </c>
+      <c r="J27" s="6">
+        <v>46231.791666666664</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="L27" s="8">
+        <v>9406713326</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" s="6">
+        <v>46226.458333333336</v>
+      </c>
+      <c r="J28" s="6">
+        <v>46226.583333333336</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="L28" s="8">
+        <v>8370093158</v>
+      </c>
+      <c r="M28" s="34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>25</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G29" s="18"/>
+      <c r="H29" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="L29" s="21"/>
+      <c r="M29" s="35" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18">
+        <v>26</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="18"/>
+      <c r="H30" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="L30" s="21"/>
+      <c r="M30" s="35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>27</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="18"/>
+      <c r="H31" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="L31" s="21"/>
+      <c r="M31" s="35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18">
+        <v>28</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="L32" s="21"/>
+      <c r="M32" s="35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="27">
+        <v>29</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="27"/>
+      <c r="H33" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="L33" s="23"/>
+      <c r="M33" s="36" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.11811023622047245" footer="0.11811023622047245"/>
+  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,20 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$15</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,10 +87,10 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2607/0322</t>
-  </si>
-  <si>
-    <t>220KV_Amk-Anuppur No.2</t>
+    <t>MR2607/0323</t>
+  </si>
+  <si>
+    <t>220KV_Amk-Traction No.2</t>
   </si>
   <si>
     <t>220KV_AMARKANTAK</t>
@@ -91,10 +102,10 @@
     <t>CPRI Protection audit work</t>
   </si>
   <si>
-    <t>25-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>25-07-2026 18:00:00</t>
+    <t>26-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>26-07-2026 13:00:00</t>
   </si>
   <si>
     <t>Vijay Kothari</t>
@@ -103,18 +114,6 @@
     <t>9425808910</t>
   </si>
   <si>
-    <t>220KV_Amk-Anuppur No.1</t>
-  </si>
-  <si>
-    <t>25-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>25-07-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0319</t>
-  </si>
-  <si>
     <t>MR2606/0253</t>
   </si>
   <si>
@@ -145,136 +144,172 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2607/0366</t>
-  </si>
-  <si>
-    <t>132KV_BADNAGAR-INGORIA_Ckt</t>
-  </si>
-  <si>
-    <t>220KV_BADNAGAR</t>
-  </si>
-  <si>
-    <t>Stringing work of 132 KV Badnagar-Bercha Line.</t>
+    <t>MR2607/0301</t>
+  </si>
+  <si>
+    <t>132KV_132KV DAMOH - PATERA LINE IST&amp;IIND CKT</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>23-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>29-07-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2607/0340</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>132KV_I/C no.2nd (160MVA EMCo)</t>
+  </si>
+  <si>
+    <t>220KV_DEWAS</t>
+  </si>
+  <si>
+    <t>C.B. Gas Leakage Attanding work</t>
+  </si>
+  <si>
+    <t>23-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>A.K. Joshi</t>
+  </si>
+  <si>
+    <t>9425801305</t>
+  </si>
+  <si>
+    <t>220KV_GANJBASODA</t>
+  </si>
+  <si>
+    <t>26-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>26-07-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>MR2607/0373</t>
+  </si>
+  <si>
+    <t>132KV_132KV Main Bus</t>
+  </si>
+  <si>
+    <t>Main  Bus Jumpering work</t>
+  </si>
+  <si>
+    <t>T K Mishra</t>
+  </si>
+  <si>
+    <t>9425805312</t>
+  </si>
+  <si>
+    <t>MR2607/0257</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Modifiction work</t>
+  </si>
+  <si>
+    <t>22-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>05-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2607/0378</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Prithvipur-PIML Ckt. 1st Line</t>
+  </si>
+  <si>
+    <t>132KV_PRITHVIPUR</t>
+  </si>
+  <si>
+    <t>Necessary maintenance work of line</t>
+  </si>
+  <si>
+    <t>26-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>26-07-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>132KV_SAHARWASA</t>
+  </si>
+  <si>
+    <t>MR2607/0374</t>
+  </si>
+  <si>
+    <t>main Bus jumpering work</t>
+  </si>
+  <si>
+    <t>MR2607/0363</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Satna  â¿¿  Rampur Baghelan line</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>Conductor Re-sagging work at loc. no. 87-100 of 13</t>
   </si>
   <si>
     <t>25-07-2026 08:00:00</t>
   </si>
   <si>
-    <t>25-07-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>J.P. Parmar</t>
-  </si>
-  <si>
-    <t>9425806919</t>
-  </si>
-  <si>
-    <t>400KV_400KV Bina-JP Ckt.</t>
-  </si>
-  <si>
-    <t>400KV_BINA4</t>
-  </si>
-  <si>
-    <t>Relay Testing work at 400KV S/S Bina</t>
-  </si>
-  <si>
-    <t>25-07-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mr.P.N. Namdeo</t>
-  </si>
-  <si>
-    <t>7587951092</t>
-  </si>
-  <si>
-    <t>MR2607/0361</t>
-  </si>
-  <si>
-    <t>MR2607/0301</t>
-  </si>
-  <si>
-    <t>132KV_132KV DAMOH - PATERA LINE IST&amp;IIND CKT</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
-  </si>
-  <si>
-    <t>23-07-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>29-07-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>M.M. BAIG</t>
-  </si>
-  <si>
-    <t>9425805067</t>
-  </si>
-  <si>
-    <t>MR2607/0340</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>132KV_I/C no.2nd (160MVA EMCo)</t>
-  </si>
-  <si>
-    <t>220KV_DEWAS</t>
-  </si>
-  <si>
-    <t>C.B. Gas Leakage Attanding work</t>
-  </si>
-  <si>
-    <t>23-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>27-07-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>A.K. Joshi</t>
-  </si>
-  <si>
-    <t>9425801305</t>
-  </si>
-  <si>
-    <t>MR2607/0351</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Tikamgarh - Jatara Line</t>
-  </si>
-  <si>
-    <t>132KV_JATARA</t>
-  </si>
-  <si>
-    <t>F/o disc replacement and other maintenance work</t>
-  </si>
-  <si>
-    <t>24-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2607/0368</t>
-  </si>
-  <si>
-    <t>132KV_132kV Kotar Majhgawan DCDS line</t>
-  </si>
-  <si>
-    <t>220KV_KOTAR</t>
-  </si>
-  <si>
-    <t>Stringing and jumpering work</t>
-  </si>
-  <si>
-    <t>25-07-2026 08:30:00</t>
+    <t>27-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>R.K. Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2607/0377</t>
+  </si>
+  <si>
+    <t>132KV_132KV Satna-Nagod Ckt-1 line</t>
+  </si>
+  <si>
+    <t>Stringing work at 132kv Satna Nagod ckt-1 line</t>
+  </si>
+  <si>
+    <t>26-07-2026 18:00:00</t>
   </si>
   <si>
     <t>Dharmendra Dwivedi</t>
@@ -283,124 +318,37 @@
     <t>9425805311</t>
   </si>
   <si>
-    <t>MR2607/0257</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Modifiction work</t>
-  </si>
-  <si>
-    <t>22-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>05-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2607/0363</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna  â¿¿  Rampur Baghelan line</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>Conductor Re-sagging work at loc. no. 87-100 of 13</t>
-  </si>
-  <si>
-    <t>27-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>R.K. Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2607/0365</t>
-  </si>
-  <si>
-    <t>132KV_132KV Anuppur-Shahdol ckt</t>
-  </si>
-  <si>
-    <t>220KV_SHAHDOL</t>
-  </si>
-  <si>
-    <t>for Flash over disc Replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>25-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Jagdish prasad ashati</t>
-  </si>
-  <si>
-    <t>942445533</t>
-  </si>
-  <si>
-    <t>MR2607/0364</t>
-  </si>
-  <si>
-    <t>132KV_132KV INTCC SIDHI CKT-I</t>
-  </si>
-  <si>
-    <t>220KV_SIDHI</t>
-  </si>
-  <si>
-    <t>C&amp;R PANEL REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>SHRI VISHAL BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425804690</t>
+    <t>MR2607/0367</t>
+  </si>
+  <si>
+    <t>132KV_132 kV SATNA- MAJHGAWAN LINE</t>
+  </si>
+  <si>
+    <t>Stringing work at 132 kv Satna Majhgawan line</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>ok, line to be in service</t>
   </si>
   <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>deferred, not in WR list</t>
-  </si>
-  <si>
-    <t>deferred, due to s/d on 220kv ckts adjoining anuppur</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>consent from WRLDC IS awaited for ckt 1</t>
-  </si>
-  <si>
-    <t>BHOPAL-MP - 400KV - BUS 2</t>
-  </si>
-  <si>
-    <t>400KV-BHOPAL-MP-DAMOH-1</t>
-  </si>
-  <si>
-    <t>400KV-SAGAR-SATNA-1</t>
-  </si>
-  <si>
-    <t>400KV-ITARSI-INDORE-MP-1</t>
-  </si>
-  <si>
-    <t>220KV-MORENA-MEHGAON-1</t>
+    <t>deferred</t>
+  </si>
+  <si>
+    <t>PIML consent required</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>400KV-BINA-MP-BINA-1</t>
   </si>
   <si>
     <t>220KV-MALANPUR-AURIYA-1</t>
@@ -412,20 +360,32 @@
     <t>400KV-INDORE-MP-ASOJ-2</t>
   </si>
   <si>
-    <t>for alignment of Bus-2 PG Isolator, simultaneously 400KV-BHOPAL-MP-DAMOH-1 Outage required</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Line Isolator alignment &amp; AMP works, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retrofitting of Reactor Differential Old Static Relay with Numerical Relay, Dia to be kept open at both ends.
-</t>
-  </si>
-  <si>
-    <t>For Line Terminal and Line Reactor AMP Works &amp; Oil Leakage Attending works, Dia to be kept open at both ends.</t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>26-Jul-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20-Jul-2026</t>
+  </si>
+  <si>
+    <t>31-Jul-2026</t>
+  </si>
+  <si>
+    <t>1.For Autoreclose relay retroffiting  (Main &amp; Tie Bay) with Dia Open
+2. For Line terminal AMP work</t>
   </si>
   <si>
     <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
@@ -437,40 +397,13 @@
     <t>CRP retrofitting work in new SPR at Asoj (Under O&amp;M Add cap)</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>25-Jul-2026</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>20-Jul-2026</t>
-  </si>
-  <si>
-    <t>31-Jul-2026</t>
-  </si>
-  <si>
-    <t>OCCMWR</t>
-  </si>
-  <si>
-    <t>S/I ,SLDC MPPTCL JBP</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.25.07.26</t>
+    <t>occm-wr</t>
+  </si>
+  <si>
+    <t>S/I, SLDC MPPTCL JBP</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.26.07.26</t>
   </si>
 </sst>
 </file>
@@ -494,28 +427,23 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -529,7 +457,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,12 +472,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -638,37 +560,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -676,6 +594,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1040,134 +961,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="62.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="62.42578125" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="48.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="39.140625" customWidth="1"/>
+    <col min="13" max="13" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16">
-        <v>46228</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="20">
+        <v>46229</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="21"/>
-      <c r="M4" s="8" t="s">
+      <c r="L4" s="19"/>
+      <c r="M4" s="17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>46224.756122685183</v>
+        <v>46224.760752314818</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1192,365 +1113,365 @@
         <v>25</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>46224.753599537034</v>
+        <v>46184.684016203704</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <f t="shared" ref="A7:A19" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46223.674907407411</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <f t="shared" ref="A7:A17" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46184.684016203704</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>46227.690717592595</v>
+        <v>46225.675775462965</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>46227.531145833331</v>
+        <v>46228.416990740741</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="J9" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>46223.674907407411</v>
+        <v>46219.722129629627</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>56</v>
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>46225.675775462965</v>
+        <v>46228.661435185182</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <v>46226.582199074073</v>
+        <v>46228.419386574074</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>46227.704421296294</v>
+        <v>46227.543402777781</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="F13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>46219.722129629627</v>
+        <v>46228.661145833335</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>91</v>
@@ -1562,401 +1483,208 @@
         <v>93</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>46227.543402777781</v>
+        <v>46227.700497685182</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>46227.631018518521</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>46227.700497685182</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="E16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>104</v>
+        <v>120</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C17" s="2" t="s">
+        <v>46227.700497685182</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="18" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
       <c r="B18" s="3">
-        <v>46227.626770833333</v>
+        <v>46227.700497685182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="9" t="s">
-        <v>121</v>
+      <c r="E18" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
       <c r="B19" s="3">
-        <v>46227.626770833333</v>
+        <v>46227.700497685182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="9" t="s">
-        <v>122</v>
+      <c r="E19" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>130</v>
+        <v>120</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="3">
-        <v>46227.626770833333</v>
-      </c>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="9" t="s">
-        <v>123</v>
-      </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="B21" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="3">
-        <v>46227.626770833333</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="15" t="s">
-        <v>147</v>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1966,7 +1694,7 @@
     <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,33 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="32760" yWindow="32760" windowWidth="20490" windowHeight="7305"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$15</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="123">
-  <si>
-    <t>STATE LOAD DESPATCH CENTRE 
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="156">
+  <si>
+    <t>STATE LOAD DESPATCH CENTRE _x000D_
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
   </si>
   <si>
@@ -87,33 +76,6 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2607/0323</t>
-  </si>
-  <si>
-    <t>220KV_Amk-Traction No.2</t>
-  </si>
-  <si>
-    <t>220KV_AMARKANTAK</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>CPRI Protection audit work</t>
-  </si>
-  <si>
-    <t>26-07-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>26-07-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>Vijay Kothari</t>
-  </si>
-  <si>
-    <t>9425808910</t>
-  </si>
-  <si>
     <t>MR2606/0253</t>
   </si>
   <si>
@@ -144,6 +106,75 @@
     <t>9424445533</t>
   </si>
   <si>
+    <t>MR2607/0383</t>
+  </si>
+  <si>
+    <t>132KV_40MVA ECE Transformer</t>
+  </si>
+  <si>
+    <t>132KV_BEOHARI</t>
+  </si>
+  <si>
+    <t>SFRA testing work</t>
+  </si>
+  <si>
+    <t>27-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Vijay Kumar Sahu</t>
+  </si>
+  <si>
+    <t>9425814035</t>
+  </si>
+  <si>
+    <t>MR2607/0385</t>
+  </si>
+  <si>
+    <t>132KV_132 kv Budera-Tikamgarh 1st Line</t>
+  </si>
+  <si>
+    <t>132KV_BUDHERA</t>
+  </si>
+  <si>
+    <t>For B phase CT oil leakage attending work</t>
+  </si>
+  <si>
+    <t>27-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>27-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Neeraj Kumar Patel</t>
+  </si>
+  <si>
+    <t>7000698221</t>
+  </si>
+  <si>
+    <t>MR2607/0379</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Chhegaon - Bhikangaon DP Line</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
+  </si>
+  <si>
+    <t>For Broken &amp; Poor insulator , Disc Replacement and</t>
+  </si>
+  <si>
+    <t>27-07-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>M.K.More</t>
+  </si>
+  <si>
+    <t>9425805258</t>
+  </si>
+  <si>
     <t>MR2607/0301</t>
   </si>
   <si>
@@ -168,6 +199,27 @@
     <t>9425805067</t>
   </si>
   <si>
+    <t>MR2607/0386</t>
+  </si>
+  <si>
+    <t>220KV_220KV depalur Pithampur line only depalpur end MT</t>
+  </si>
+  <si>
+    <t>220KV_DEPALPUR</t>
+  </si>
+  <si>
+    <t>additional DPR connection work</t>
+  </si>
+  <si>
+    <t>27-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Rambabu Nagar</t>
+  </si>
+  <si>
+    <t>9425802879</t>
+  </si>
+  <si>
     <t>MR2607/0340</t>
   </si>
   <si>
@@ -195,28 +247,46 @@
     <t>9425801305</t>
   </si>
   <si>
-    <t>220KV_GANJBASODA</t>
-  </si>
-  <si>
-    <t>26-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>26-07-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>MR2607/0373</t>
-  </si>
-  <si>
-    <t>132KV_132KV Main Bus</t>
-  </si>
-  <si>
-    <t>Main  Bus Jumpering work</t>
-  </si>
-  <si>
-    <t>T K Mishra</t>
-  </si>
-  <si>
-    <t>9425805312</t>
+    <t>MR2607/0369</t>
+  </si>
+  <si>
+    <t>400KV_315MVA ICT-2</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>For defective Conservator tank Replacement work</t>
+  </si>
+  <si>
+    <t>29-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>ATUL PARADKAR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2607/0380</t>
+  </si>
+  <si>
+    <t>400KV_100MVA X-mer-1 Make BHEL</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>For Pre Monsoon Maintainance</t>
+  </si>
+  <si>
+    <t>27-07-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Sandeep Damahe</t>
+  </si>
+  <si>
+    <t>9425805009</t>
   </si>
   <si>
     <t>MR2607/0257</t>
@@ -243,37 +313,40 @@
     <t>9425805317</t>
   </si>
   <si>
-    <t>MR2607/0378</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Prithvipur-PIML Ckt. 1st Line</t>
-  </si>
-  <si>
-    <t>132KV_PRITHVIPUR</t>
-  </si>
-  <si>
-    <t>Necessary maintenance work of line</t>
-  </si>
-  <si>
-    <t>26-07-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>26-07-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>132KV_SAHARWASA</t>
-  </si>
-  <si>
-    <t>MR2607/0374</t>
-  </si>
-  <si>
-    <t>main Bus jumpering work</t>
+    <t>MR2607/0375</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Panagar- Amarkantak</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>Disc Change at loc. 222 Top Ph, A/H 290,292,294</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2607/0382</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA X-MER BHEL-IInd</t>
+  </si>
+  <si>
+    <t>220KV_SARNI</t>
+  </si>
+  <si>
+    <t>132KV C.T. Replacement Work</t>
+  </si>
+  <si>
+    <t>ER. ANUP KUMAR DANGE</t>
+  </si>
+  <si>
+    <t>9425814073</t>
   </si>
   <si>
     <t>MR2607/0363</t>
@@ -291,104 +364,98 @@
     <t>25-07-2026 08:00:00</t>
   </si>
   <si>
-    <t>27-07-2026 18:00:00</t>
-  </si>
-  <si>
     <t>R.K. Prajapati</t>
   </si>
   <si>
     <t>9407070182</t>
   </si>
   <si>
-    <t>MR2607/0377</t>
-  </si>
-  <si>
-    <t>132KV_132KV Satna-Nagod Ckt-1 line</t>
-  </si>
-  <si>
-    <t>Stringing work at 132kv Satna Nagod ckt-1 line</t>
-  </si>
-  <si>
-    <t>26-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Dharmendra Dwivedi</t>
-  </si>
-  <si>
-    <t>9425805311</t>
-  </si>
-  <si>
-    <t>MR2607/0367</t>
-  </si>
-  <si>
-    <t>132KV_132 kV SATNA- MAJHGAWAN LINE</t>
-  </si>
-  <si>
-    <t>Stringing work at 132 kv Satna Majhgawan line</t>
+    <t>MR2607/0384</t>
+  </si>
+  <si>
+    <t>132KV_Sonkatchh-Jawarjod line</t>
+  </si>
+  <si>
+    <t>132KV_SONKATCH</t>
+  </si>
+  <si>
+    <t>Jumper cone tighting work</t>
+  </si>
+  <si>
+    <t>Ravindra Patil</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2607/0381</t>
+  </si>
+  <si>
+    <t>220KV_220kv 160MVA xmer BHEL</t>
+  </si>
+  <si>
+    <t>220KV_UDAIPURA</t>
+  </si>
+  <si>
+    <t>132kv Y ph CT hot point attend work</t>
+  </si>
+  <si>
+    <t>27-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj kumar hariyale</t>
+  </si>
+  <si>
+    <t>9827202680</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>RTS consent required</t>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>ok, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>sub ld</t>
   </si>
   <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>sub ld</t>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>real time</t>
   </si>
   <si>
     <t>deferred</t>
   </si>
   <si>
-    <t>PIML consent required</t>
-  </si>
-  <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>400KV-BINA-MP-BINA-1</t>
-  </si>
-  <si>
-    <t>220KV-MALANPUR-AURIYA-1</t>
+    <t>400KV-BINA-MP-BINA-2</t>
+  </si>
+  <si>
+    <t>220KV-MEHGAON-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-SEONI-PG-CHINDWARA-2</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-2</t>
   </si>
   <si>
     <t>400KV-INDORE-MP-ASOJ-2</t>
-  </si>
-  <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>26-Jul-2026</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>20-Jul-2026</t>
-  </si>
-  <si>
-    <t>31-Jul-2026</t>
   </si>
   <si>
     <t>1.For Autoreclose relay retroffiting  (Main &amp; Tie Bay) with Dia Open
 2. For Line terminal AMP work</t>
   </si>
   <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
     <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
@@ -397,13 +464,34 @@
     <t>CRP retrofitting work in new SPR at Asoj (Under O&amp;M Add cap)</t>
   </si>
   <si>
-    <t>occm-wr</t>
-  </si>
-  <si>
-    <t>S/I, SLDC MPPTCL JBP</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.26.07.26</t>
+    <t>27-Jul-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20-Jul-2026</t>
+  </si>
+  <si>
+    <t>31-Jul-2026</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>S/I ,SLDC MPPTCL JBP</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.27.07.26</t>
   </si>
 </sst>
 </file>
@@ -411,49 +499,56 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
-    <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
+    <numFmt numFmtId="172" formatCode="[$-1010809]dd\-mm\-yyyy"/>
+    <numFmt numFmtId="173" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FF000000"/>
+      <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -466,12 +561,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,16 +582,42 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,36 +625,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -540,47 +636,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -592,10 +694,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -625,38 +733,62 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>605333</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3335</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>547688</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1026" name="Picture 1"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:ext cx="609600" cy="552450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="9"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -951,185 +1083,179 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="62.42578125" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="48.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="27.85546875" customWidth="1"/>
+    <col min="13" max="13" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="75.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="9"/>
-    </row>
-    <row r="2" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20">
-        <v>46229</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="B2" s="17">
+        <v>46230</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" spans="1:13" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" s="16" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+    </row>
+    <row r="4" spans="1:13" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="19"/>
-      <c r="M4" s="17" t="s">
+      <c r="L4" s="21"/>
+      <c r="M4" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>46224.760752314818</v>
+        <v>46184.684016203704</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>46184.684016203704</v>
+        <v>46229.526435185187</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>28</v>
       </c>
@@ -1137,134 +1263,129 @@
         <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="L6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46229.668240740742</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <f t="shared" ref="A7:A19" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46228.682916666665</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
         <v>46223.674907407411</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46225.675775462965</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="F9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46228.416990740741</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>54</v>
@@ -1273,168 +1394,164 @@
         <v>55</v>
       </c>
       <c r="K9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46229.68855324074</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="F10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="3">
-        <v>46219.722129629627</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="K10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="L10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="M10" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46225.675775462965</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46228.661435185182</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="G11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="I11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="J11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="K11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="L11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="M11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46227.717256944445</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="D12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46228.419386574074</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="K12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="L12" s="6" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>46227.543402777781</v>
+        <v>46229.463784722226</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>86</v>
@@ -1443,248 +1560,437 @@
         <v>87</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>46228.661145833335</v>
+        <v>46219.722129629627</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>46227.700497685182</v>
+        <v>46228.482824074075</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>46227.700497685182</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>46229.474074074074</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>116</v>
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="I16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46227.543402777781</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="6" t="s">
+      <c r="G17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46227.700497685182</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>117</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>46227.700497685182</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>46229.605532407404</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="G18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="M18" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>46227.700497685182</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>119</v>
+        <v>21</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="36" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="11" t="s">
-        <v>121</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46229.464861111112</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="12" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1694,7 +2000,8 @@
     <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$36</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="181">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -133,6 +133,30 @@
     <t>9425805312</t>
   </si>
   <si>
+    <t>MR2607/0416</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Badnagar Indore</t>
+  </si>
+  <si>
+    <t>220KV_BADNAGAR</t>
+  </si>
+  <si>
+    <t>For attending hot point in R phase jaw of aux isol</t>
+  </si>
+  <si>
+    <t>29-07-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>29-07-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Ravi Pandey</t>
+  </si>
+  <si>
+    <t>9425805296</t>
+  </si>
+  <si>
     <t>MR2607/0395</t>
   </si>
   <si>
@@ -169,195 +193,138 @@
     <t>9425805067</t>
   </si>
   <si>
-    <t>MR2607/0391</t>
-  </si>
-  <si>
-    <t>220KV_220 KV PGCIL(GWL)</t>
-  </si>
-  <si>
-    <t>220KV_DATIA</t>
+    <t>MR2607/0421</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Ganjbasoda- Bareth RTS Ckt-2.</t>
+  </si>
+  <si>
+    <t>220KV_GANJBASODA</t>
   </si>
   <si>
     <t>NON-OCCM-WR</t>
   </si>
   <si>
-    <t>Y Phase LA Replacement work</t>
+    <t>disc insulater replacement at loc no 25T,31T</t>
+  </si>
+  <si>
+    <t>29-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Dilip Singh Walkey</t>
+  </si>
+  <si>
+    <t>9425804578</t>
+  </si>
+  <si>
+    <t>MR2607/0404</t>
+  </si>
+  <si>
+    <t>400KV_315 MVA , 400/220/33 KV ICT-II</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>For defective Conservator tank Replacement work by</t>
+  </si>
+  <si>
+    <t>29-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>31-07-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er.Atul paradkar</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2607/0417</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL NO-4 X-MER</t>
+  </si>
+  <si>
+    <t>132KV_KATNI</t>
+  </si>
+  <si>
+    <t>Attending of hot point R-ph LV CB To CT Jumfer hot</t>
+  </si>
+  <si>
+    <t>29-07-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>RAJENDRA RAWAT</t>
+  </si>
+  <si>
+    <t>7974696966</t>
+  </si>
+  <si>
+    <t>MR2607/0257</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Modifiction work</t>
+  </si>
+  <si>
+    <t>22-07-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>05-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2607/0400</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Malharagarh Line</t>
+  </si>
+  <si>
+    <t>132KV_MALHARGARH</t>
+  </si>
+  <si>
+    <t>Hotline shutdown</t>
+  </si>
+  <si>
+    <t>28-07-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>10-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2607/0412</t>
+  </si>
+  <si>
+    <t>132KV_132KV Nagda-RTS  Ckt-1&amp; 2 Line</t>
+  </si>
+  <si>
+    <t>220KV_NAGDA</t>
+  </si>
+  <si>
+    <t>Jumper cone tighting work</t>
   </si>
   <si>
     <t>28-07-2026 10:00:00</t>
   </si>
   <si>
-    <t>28-07-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Mukesh Verma</t>
-  </si>
-  <si>
-    <t>7587951058</t>
-  </si>
-  <si>
-    <t>MR2607/0407</t>
-  </si>
-  <si>
-    <t>220KV_220KV DEPALPUR-PITHAMPUR LINE</t>
-  </si>
-  <si>
-    <t>220KV_DEPALPUR</t>
-  </si>
-  <si>
-    <t>Additional DPR connection work</t>
-  </si>
-  <si>
-    <t>28-07-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>RAM BABU NAGAR</t>
-  </si>
-  <si>
-    <t>9425802879</t>
-  </si>
-  <si>
-    <t>MR2607/0406</t>
-  </si>
-  <si>
-    <t>220KV_Dhar to Kanwan ckt-2</t>
-  </si>
-  <si>
-    <t>220KV_DHAR</t>
-  </si>
-  <si>
-    <t>For line maintenance work</t>
-  </si>
-  <si>
-    <t>V.R. Panadia</t>
-  </si>
-  <si>
-    <t>9425802330</t>
-  </si>
-  <si>
-    <t>MR2607/0411</t>
-  </si>
-  <si>
-    <t>132KV_132KV Garhakota Damoh Line</t>
-  </si>
-  <si>
-    <t>132KV_GARHAKOTA</t>
-  </si>
-  <si>
-    <t>132 kv CT Replacement work</t>
-  </si>
-  <si>
-    <t>28-07-2026 10:30:00</t>
-  </si>
-  <si>
-    <t>SK Hajari</t>
-  </si>
-  <si>
-    <t>9425620010</t>
-  </si>
-  <si>
-    <t>MR2607/0390</t>
-  </si>
-  <si>
-    <t>132KV_132 Harda Khirkiya Traction no.I</t>
-  </si>
-  <si>
-    <t>132KV_HARDA</t>
-  </si>
-  <si>
-    <t>B Ph LA errection &amp; Comm.work</t>
-  </si>
-  <si>
-    <t>28-07-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Sh.J.0. Khoria</t>
-  </si>
-  <si>
-    <t>9425804975</t>
-  </si>
-  <si>
-    <t>MR2607/0405</t>
-  </si>
-  <si>
-    <t>220KV_220 KV KATNI - MAIHAR LINE</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>T-CLAMP REMOVAL AND OTHER MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2607/0257</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt-III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Modifiction work</t>
-  </si>
-  <si>
-    <t>22-07-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>05-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2607/0400</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Malharagarh Line</t>
-  </si>
-  <si>
-    <t>132KV_MALHARGARH</t>
-  </si>
-  <si>
-    <t>Hotline shutdown</t>
-  </si>
-  <si>
-    <t>28-07-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>10-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2607/0412</t>
-  </si>
-  <si>
-    <t>132KV_132KV Nagda-RTS  Ckt-1&amp; 2 Line</t>
-  </si>
-  <si>
-    <t>220KV_NAGDA</t>
-  </si>
-  <si>
-    <t>Jumper cone tighting work</t>
-  </si>
-  <si>
-    <t>29-07-2026 17:00:00</t>
-  </si>
-  <si>
     <t>Er.Naresh pandre</t>
   </si>
   <si>
@@ -388,100 +355,97 @@
     <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
   </si>
   <si>
-    <t>132KV_50 MVA ATLANTA XMER</t>
-  </si>
-  <si>
-    <t>132KV_NOWGAON</t>
-  </si>
-  <si>
-    <t>LV CB HOT POINT ATTENDING WORK</t>
-  </si>
-  <si>
-    <t>28-07-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>BRAJENDRA KUMAR SONI</t>
-  </si>
-  <si>
-    <t>9131327770</t>
-  </si>
-  <si>
-    <t>MR2607/0393</t>
-  </si>
-  <si>
-    <t>MR2607/0403</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Pandhurna-Kalmeshwar</t>
-  </si>
-  <si>
-    <t>220KV_PANDHURNA</t>
+    <t>MR2607/0420</t>
+  </si>
+  <si>
+    <t>220KV_220 KV 160 MVA -Ist (areva)</t>
+  </si>
+  <si>
+    <t>220KV_RAJGARH (BIAORA)</t>
+  </si>
+  <si>
+    <t>132 kv INC Isolator Hot point attend work</t>
+  </si>
+  <si>
+    <t>29-07-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>29-07-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>NEELESH BASTRI</t>
+  </si>
+  <si>
+    <t>9425804342</t>
+  </si>
+  <si>
+    <t>MR2607/0415</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ratangarh - Neemuch-I</t>
+  </si>
+  <si>
+    <t>220KV_RATANGARH</t>
+  </si>
+  <si>
+    <t>Maintenance and Testing work</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
+  </si>
+  <si>
+    <t>MR2607/0422</t>
+  </si>
+  <si>
+    <t>132KV_132KV Main Bus</t>
+  </si>
+  <si>
+    <t>400KV_SAGAR</t>
+  </si>
+  <si>
+    <t>for Jumpering of main Bus</t>
+  </si>
+  <si>
+    <t>29-07-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>Anil Mahor</t>
+  </si>
+  <si>
+    <t>9425805149</t>
+  </si>
+  <si>
+    <t>MR2607/0376</t>
+  </si>
+  <si>
+    <t>220KV_220kv Main Bus -1</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
   </si>
   <si>
     <t>OCCM-MP</t>
   </si>
   <si>
-    <t>Double fitting work</t>
-  </si>
-  <si>
-    <t>A.M.Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2607/0409</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Rampur baghelan- Rewa (Tap Bela Cement) Line</t>
-  </si>
-  <si>
-    <t>132KV_RAMPUR BAGHELAN</t>
-  </si>
-  <si>
-    <t>For jumper opening work at loc. no. 18</t>
-  </si>
-  <si>
-    <t>28-07-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>Mr. Ramkirti Prajapati</t>
-  </si>
-  <si>
-    <t>9407070182</t>
-  </si>
-  <si>
-    <t>MR2607/0401</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Satna â¿¿ Rampur Baghelan line</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>Conductor Re-sagging work at loc. no. 87-100</t>
-  </si>
-  <si>
-    <t>R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>MR2607/0398</t>
-  </si>
-  <si>
-    <t>132KV_132kV Seoni Nainpur SC Old Line</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>Work for replacement of f/o disc &amp; other work</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>MR2607/0402</t>
+    <t>For repair Main Bus conductor &amp;220kv ajaygarh,pgci</t>
+  </si>
+  <si>
+    <t>29-07-2026 09:28:00</t>
+  </si>
+  <si>
+    <t>29-07-2026 17:33:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2607/0418</t>
   </si>
   <si>
     <t>220KV_220kv Birshinghpur-TPH-Shahdol ckt</t>
@@ -490,10 +454,13 @@
     <t>400KV_SGTPS</t>
   </si>
   <si>
-    <t>For flash over disc replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>Jagdish Prasad Asathi</t>
+    <t>flash over disc Replacement &amp; other line work</t>
+  </si>
+  <si>
+    <t>29-07-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Ashati</t>
   </si>
   <si>
     <t>MR2607/0410</t>
@@ -514,112 +481,91 @@
     <t>sub ld</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>deferred, not in WR list</t>
-  </si>
-  <si>
-    <t>deferred, due to s/d on 132 kv Satna - Rampur Baghelan line</t>
-  </si>
-  <si>
-    <t>deferred due to s/d on AMK bus</t>
+    <t>deferred</t>
+  </si>
+  <si>
+    <t>ok, wrldc approval for emergency will be required for 220kv Satna PG-Satna ckt 1</t>
+  </si>
+  <si>
+    <t>o&amp;m consnet required</t>
+  </si>
+  <si>
+    <t>real time</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-2</t>
   </si>
   <si>
-    <t>220KV-MEHGAON-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-DAMOH-TIKAMGAD-1</t>
-  </si>
-  <si>
-    <t>220KV-PANDURNA-KALMESHWAR-1</t>
-  </si>
-  <si>
-    <t>220KV-SHUJALPUR-RAJGARH-MP-2</t>
-  </si>
-  <si>
-    <t>132KV-SHEOPUR-KHANDAR-1</t>
+    <t>29-Jul-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
   </si>
   <si>
     <t>400KV-INDORE-MP-ASOJ-2</t>
   </si>
   <si>
-    <t>MADHYA PRADESH,CHATTISGARH</t>
-  </si>
-  <si>
-    <t>NLDC,MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,MAHARASHTRA</t>
-  </si>
-  <si>
-    <t>POWERGRID-NR,MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR2 (PGCIL)</t>
-  </si>
-  <si>
-    <t>FOR CONDUCTOR RE-SAGGING WORK AT VARIOUS SECTION OF LINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For replacement of defective dics insulator string at various locations </t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK i.e. CLEANING OF DISC INSULATORS DURING LINE PATROLLING , REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+    <t>20-Jul-2026</t>
+  </si>
+  <si>
+    <t>31-Jul-2026</t>
   </si>
   <si>
     <t>CRP retrofitting work in new SPR at Asoj (Under O&amp;M Add cap)</t>
   </si>
   <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>220KV MAIN BUS-1</t>
-  </si>
-  <si>
-    <t>220KV SIDHI FEEDER ( BAY NO.21)</t>
-  </si>
-  <si>
-    <t>ATPS CHACHAI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUMPER WORK </t>
-  </si>
-  <si>
-    <t>MP_SLDC</t>
-  </si>
-  <si>
-    <t>POWERGRID_WR2</t>
-  </si>
-  <si>
-    <t>AJAY PARTETI</t>
-  </si>
-  <si>
-    <t>S/I, SLDC, JABALPUR</t>
+    <t>50 MVA X-MER NO. 1</t>
+  </si>
+  <si>
+    <t>132 KV GOPALGANJ</t>
+  </si>
+  <si>
+    <t>OK, O&amp;M SHALL BE INFORMED</t>
+  </si>
+  <si>
+    <t>50 MVA X-MER NO. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 MVA X-MER </t>
+  </si>
+  <si>
+    <t>220 KV NIMRANI</t>
+  </si>
+  <si>
+    <t>RYB CT REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>29.7.26</t>
+  </si>
+  <si>
+    <t>OK, THROUGH SUB LD</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 29.07.2026</t>
   </si>
 </sst>
 </file>
@@ -630,7 +576,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -664,28 +610,20 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,12 +637,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -794,19 +738,8 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -815,47 +748,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -887,8 +794,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -898,58 +811,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1315,53 +1217,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="62.140625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" style="12" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="54.28515625" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="37.42578125" style="11" customWidth="1"/>
+    <col min="13" max="13" width="37.28515625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="E2" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1421,15 +1325,15 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="16"/>
       <c r="M4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1442,7 +1346,7 @@
       <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1466,11 +1370,11 @@
       <c r="L5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1484,7 +1388,7 @@
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1508,25 +1412,23 @@
       <c r="L6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A26" si="0">A6+1</f>
+        <f t="shared" ref="A7:A30" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46230.522118055553</v>
+        <v>46231.520833333336</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="11" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1539,129 +1441,131 @@
         <v>39</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46223.674907407411</v>
+        <v>46230.522118055553</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>41</v>
+        <v>28</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46230.447465277779</v>
+        <v>46223.674907407411</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="I9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46230.635520833333</v>
+        <v>46231.628333333334</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>60</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>61</v>
@@ -1672,23 +1576,25 @@
       <c r="L10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46230.61346064815</v>
+        <v>46230.595821759256</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>65</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1701,232 +1607,236 @@
         <v>67</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46230.667175925926</v>
+        <v>46231.521006944444</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="10" t="s">
-        <v>71</v>
+      <c r="E12" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46230.426365740743</v>
+        <v>46219.722129629627</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46230.606666666667</v>
+        <v>46230.548402777778</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="10" t="s">
-        <v>85</v>
+        <v>87</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46219.722129629627</v>
+        <v>46230.6953587963</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>91</v>
+        <v>18</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46230.548402777778</v>
+        <v>46230.543634259258</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>99</v>
+      <c r="E16" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46230.6953587963</v>
+        <v>46230.546249999999</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>106</v>
@@ -1934,768 +1844,542 @@
       <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46230.543634259258</v>
+        <v>46230.541574074072</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>114</v>
+      <c r="E18" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46230.546249999999</v>
+        <v>46231.605497685188</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>118</v>
+        <v>110</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="L19" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46230.541574074072</v>
+        <v>46231.49486111111</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="F20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46230.492789351854</v>
+        <v>46231.719108796293</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D21" s="4"/>
-      <c r="E21" s="10" t="s">
-        <v>121</v>
+      <c r="E21" s="13" t="s">
+        <v>125</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46230.568240740744</v>
+        <v>46228.573750000003</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="10" t="s">
-        <v>129</v>
+      <c r="E22" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46230.64634259259</v>
+        <v>46231.525208333333</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D23" s="4"/>
-      <c r="E23" s="10" t="s">
-        <v>136</v>
+      <c r="E23" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+        <v>26</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="21">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="5">
-        <v>46230.551365740743</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="B24" s="22">
+        <v>46230.654166666667</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H24" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="5">
-        <v>46230.544560185182</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="M25" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    </row>
+    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="21">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" s="5">
-        <v>46230.564201388886</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="M26" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="L26" s="8" t="s">
+    </row>
+    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="L27" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="M27" s="30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="21">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="32">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K28" s="30"/>
+      <c r="L28" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M28" s="31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K29" s="30"/>
+      <c r="L29" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="M29" s="31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="21">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="M26" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>24</v>
-      </c>
-      <c r="B28" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="L28" s="8">
-        <v>9425808877</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="L29" s="8">
-        <v>9425808877</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>26</v>
-      </c>
-      <c r="B30" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="F30" s="18" t="s">
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="K30" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L30" s="20"/>
-      <c r="M30" s="32" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>27</v>
-      </c>
-      <c r="B31" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="F31" s="18" t="s">
+      <c r="G30" s="30"/>
+      <c r="H30" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="H31" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="J31" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="K31" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L31" s="20"/>
-      <c r="M31" s="32" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>28</v>
-      </c>
-      <c r="B32" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="F32" s="18" t="s">
+      <c r="I30" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="19"/>
-      <c r="H32" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="J32" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="K32" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L32" s="20"/>
-      <c r="M32" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>29</v>
-      </c>
-      <c r="B33" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" s="18" t="s">
+      <c r="J30" s="32">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="K30" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="M30" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="K33" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L33" s="20"/>
-      <c r="M33" s="32" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>30</v>
-      </c>
-      <c r="B34" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="G34" s="19"/>
-      <c r="H34" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L34" s="20"/>
-      <c r="M34" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
-        <v>31</v>
-      </c>
-      <c r="B35" s="5">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="G35" s="19"/>
-      <c r="H35" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="K35" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="L35" s="20"/>
-      <c r="M35" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
-        <v>32</v>
-      </c>
-      <c r="B36" s="17">
-        <v>46230.654166666667</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="K36" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="L36" s="23"/>
-      <c r="M36" s="33" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="26"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="I37:M37"/>
+    <mergeCell ref="E2:I2"/>
   </mergeCells>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="45" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$25</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$23</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="168">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,45 +76,21 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0121</t>
-  </si>
-  <si>
-    <t>220KV_220KV BADNAWAR RATLAM CKT -2</t>
-  </si>
-  <si>
-    <t>400KV_BADNAWAR</t>
+    <t>MR2608/0099</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Bargi Lakhnadaun</t>
+  </si>
+  <si>
+    <t>132KV_BARGI</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>DOUBLE DPR INSTALLATION &amp; TESTING WORK</t>
-  </si>
-  <si>
-    <t>12-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>12-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SUNIL BAMNIYA</t>
-  </si>
-  <si>
-    <t>8349013626</t>
-  </si>
-  <si>
-    <t>MR2608/0099</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Bargi Lakhnadaun</t>
-  </si>
-  <si>
-    <t>132KV_BARGI</t>
-  </si>
-  <si>
     <t>More than 35 year string replaced through contract</t>
   </si>
   <si>
@@ -130,27 +106,27 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>MR2608/0104</t>
+    <t>MR2608/0134</t>
   </si>
   <si>
     <t>Continuous</t>
   </si>
   <si>
-    <t>132KV_132 kV Bhopal- Bagroda line</t>
+    <t>132KV_132 kV Bhopal-Bagroda line</t>
   </si>
   <si>
     <t>220KV_BHOPAL</t>
   </si>
   <si>
-    <t>Modification work</t>
-  </si>
-  <si>
-    <t>10-08-2026 17:00:00</t>
+    <t>Modification/Shifting work</t>
   </si>
   <si>
     <t>12-08-2026 17:00:00</t>
   </si>
   <si>
+    <t>14-08-2026 17:00:00</t>
+  </si>
+  <si>
     <t>Ankit Mehroliya</t>
   </si>
   <si>
@@ -178,190 +154,133 @@
     <t>15-08-2026 18:00:00</t>
   </si>
   <si>
-    <t>MR2608/0116</t>
-  </si>
-  <si>
-    <t>220KV_220KV CHHEGAON - NEPANAGAR Ckt.</t>
-  </si>
-  <si>
-    <t>400KV_CHHEGAON4</t>
+    <t>MR2608/0108</t>
+  </si>
+  <si>
+    <t>132KV_132KV DAMOH - PATERA IST&amp;IIND LINE</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>11-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>17-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2608/0114</t>
+  </si>
+  <si>
+    <t>132KV_132kV Kirnapur Dongargarh Line</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>PID Defective Disc Replacement &amp; Other Line Mainte</t>
+  </si>
+  <si>
+    <t>13-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>13-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2608/0063</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Erection/Dismentalling of tower &amp; making cut point</t>
+  </si>
+  <si>
+    <t>06-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>26-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2608/0135</t>
+  </si>
+  <si>
+    <t>132KV_132 kV MACT-Mandideep line</t>
+  </si>
+  <si>
+    <t>220KV_MANDIDEEP</t>
+  </si>
+  <si>
+    <t>MR2608/0095</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Budha Line</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>For Crossing Work</t>
+  </si>
+  <si>
+    <t>11-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2608/0127</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch - Mandsaur-II</t>
   </si>
   <si>
     <t>NON-OCCM-WR</t>
   </si>
   <si>
-    <t>Main 2 DPR Relay testing work</t>
-  </si>
-  <si>
-    <t>12-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>Ganesh Manshare</t>
-  </si>
-  <si>
-    <t>9425802441</t>
-  </si>
-  <si>
-    <t>MR2608/0113</t>
-  </si>
-  <si>
-    <t>132KV_132KV Chourai-Chhindwara Feeder</t>
-  </si>
-  <si>
-    <t>132KV_CHOURAI</t>
-  </si>
-  <si>
-    <t>Structure Painting Work.</t>
-  </si>
-  <si>
-    <t>12-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>S.K.Okte</t>
-  </si>
-  <si>
-    <t>7587951132</t>
-  </si>
-  <si>
-    <t>MR2608/0108</t>
-  </si>
-  <si>
-    <t>132KV_132KV DAMOH - PATERA IST&amp;IIND LINE</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
-  </si>
-  <si>
-    <t>11-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>M.M. BAIG</t>
-  </si>
-  <si>
-    <t>9425805067</t>
-  </si>
-  <si>
-    <t>MR2608/0118</t>
-  </si>
-  <si>
-    <t>132KV_132 KV JABALPUR-SHAHPURA LINE</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>REMOVAL OF TIE JUMPER FROM 132 KV JABALPUR-SHAHPUR</t>
-  </si>
-  <si>
-    <t>12-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>RAJESH TIWARI</t>
-  </si>
-  <si>
-    <t>7898239595</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0105</t>
-  </si>
-  <si>
-    <t>132KV_132 kV MACT- Mandideep line</t>
-  </si>
-  <si>
-    <t>220KV_MANDIDEEP</t>
-  </si>
-  <si>
-    <t>MR2608/0112</t>
-  </si>
-  <si>
-    <t>132KV_132kV Mandla Dindori Line</t>
-  </si>
-  <si>
-    <t>132KV_MANDLA</t>
-  </si>
-  <si>
-    <t>Bird Guard Installation Work &amp; Emergency Side TC W</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2608/0111</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA BBL-1  X MER</t>
-  </si>
-  <si>
-    <t>132KV_MANGAWAN</t>
-  </si>
-  <si>
-    <t>40MVA BBL-1 X-MER 33KV Y PHASE CT CLAMP RED HOT</t>
-  </si>
-  <si>
-    <t>12-08-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>ER. KANISHK SINGH</t>
-  </si>
-  <si>
-    <t>9425804656</t>
-  </si>
-  <si>
-    <t>MR2608/0095</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Budha Line</t>
-  </si>
-  <si>
-    <t>220KV_NEEMUCH</t>
-  </si>
-  <si>
-    <t>For Crossing Work</t>
-  </si>
-  <si>
-    <t>11-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
+    <t>DPR relay replacement work</t>
+  </si>
+  <si>
+    <t>13-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>13-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
   </si>
   <si>
     <t>MR2608/0093</t>
@@ -388,6 +307,30 @@
     <t>Hotline Shutdown for crossing work</t>
   </si>
   <si>
+    <t>132KV_132kv Prithvipur -orchha 2nd line</t>
+  </si>
+  <si>
+    <t>132KV_ORCHHA</t>
+  </si>
+  <si>
+    <t>Tan-delta measurement of CT</t>
+  </si>
+  <si>
+    <t>13-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>13-08-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Santosh lodhi</t>
+  </si>
+  <si>
+    <t>6260498028</t>
+  </si>
+  <si>
+    <t>MR2608/0129</t>
+  </si>
+  <si>
     <t>MR2608/0100</t>
   </si>
   <si>
@@ -412,22 +355,43 @@
     <t>9425804993</t>
   </si>
   <si>
-    <t>MR2608/0119</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Rajmilan â¿¿Bargawan (TBCB) circuit</t>
-  </si>
-  <si>
-    <t>132KV_RAJMILAN</t>
-  </si>
-  <si>
-    <t>Disc F/o Change</t>
-  </si>
-  <si>
-    <t>G.L Sahu</t>
-  </si>
-  <si>
-    <t>9425805102</t>
+    <t>132KV_132 kv prithvipur orchha 2</t>
+  </si>
+  <si>
+    <t>132KV_PRITHVIPUR</t>
+  </si>
+  <si>
+    <t>For changing flash over insulator</t>
+  </si>
+  <si>
+    <t>Pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2608/0132</t>
+  </si>
+  <si>
+    <t>132KV_132kv Main Bus -2</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For Main Bus YBPH Loop conductor jumper repair wor</t>
+  </si>
+  <si>
+    <t>13-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2608/0139</t>
   </si>
   <si>
     <t>MR2608/0085</t>
@@ -454,10 +418,10 @@
     <t>9425611049</t>
   </si>
   <si>
-    <t>MR2608/0115</t>
-  </si>
-  <si>
-    <t>132KV_132 KV SHAHDOL - BIRSINGHPUR CKT II</t>
+    <t>MR2608/0136</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Shahdol-Dindori Circuit II</t>
   </si>
   <si>
     <t>132KV_SHAHDOL</t>
@@ -472,91 +436,70 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>220KV_220 KV MAIN BUS</t>
-  </si>
-  <si>
-    <t>220KV_UJJAIN</t>
-  </si>
-  <si>
-    <t>220 KV Main Bus</t>
-  </si>
-  <si>
-    <t>12-08-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>B.C JOSHI</t>
-  </si>
-  <si>
-    <t>7587951137</t>
-  </si>
-  <si>
-    <t>MR2607/0427</t>
+    <t>MR2608/0137</t>
+  </si>
+  <si>
+    <t>132KV_132kv Shivpuri Bairad Ckt -2</t>
+  </si>
+  <si>
+    <t>220KV_SHIVPURI</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>ok, line to be in service</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>sub ld</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>ok, line to be in service, o&amp;m to be informed</t>
-  </si>
-  <si>
-    <t>real time, as per load management conditions</t>
-  </si>
-  <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>ok, sub ld to monitor/manage the loading in132kv network</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m to be informed</t>
-  </si>
-  <si>
-    <t>220KV-SATNA-MAIHAR-1</t>
-  </si>
-  <si>
-    <t>220KV-INDORE-UJJAIN-1</t>
-  </si>
-  <si>
-    <t>220KV-INDORE-UJJAIN-2</t>
-  </si>
-  <si>
-    <t>400KV-SEONI-PG-SATPURA-1</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-GWALIOR-II-1</t>
+    <t>ok, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>ok, line to be in service,  through sub ld</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.13.08.26</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-GWALIOR-II-2</t>
   </si>
   <si>
     <t>220KV-AJAYGARH-SATNA-1</t>
   </si>
   <si>
-    <t>220KV-ITARSI-MP-ITARSI-2</t>
+    <t>132KV-KIRNAPUR-DONGARGARH-1</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
-    <t>220KV-PITHAMPUR-RAJGARH-1</t>
-  </si>
-  <si>
-    <t>220KV-RAJGARH-DHAR-1</t>
-  </si>
-  <si>
     <t>real time</t>
   </si>
   <si>
-    <t>S/I, SLDC MPPTCL JBP.</t>
-  </si>
-  <si>
-    <t>12-Aug-2026</t>
+    <t>13-Aug-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
   </si>
   <si>
     <t>08:00</t>
@@ -565,52 +508,25 @@
     <t>19:00</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
     <t>18:00</t>
   </si>
   <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>11-Aug-2026</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>26-Aug-2026</t>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
   </si>
   <si>
     <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t>due to s/d on 220kv Main Bus at 220kv ss Ujjain for maintenance work</t>
-  </si>
-  <si>
-    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF SINGLE FITTING HARDWARE INTO DOUBLE FITTING HARDWARE AT VARIOUS ROAD CROSSING LOCATIONS </t>
-  </si>
-  <si>
     <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
   </si>
   <si>
-    <t xml:space="preserve">FOR MOD. SHIFTING WORK OF LINE DUE TO CONSTRUTION OF NEW RAILWAY LINE BETWEEN TIRLA- AMJHERA-SARDARPUR SECTION BY WR RATLAM </t>
-  </si>
-  <si>
-    <t>deferred by site</t>
-  </si>
-  <si>
     <t>OCCM-WR</t>
   </si>
   <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.12.08.2026</t>
+    <t>S/I,SLDC MPPTCL JBP</t>
   </si>
 </sst>
 </file>
@@ -621,7 +537,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -632,13 +548,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -655,10 +564,11 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -668,12 +578,25 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -687,19 +610,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -783,24 +700,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -809,46 +726,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -879,8 +790,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>605333</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>551023</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>3335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1213,24 +1124,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="63.85546875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="56.140625" style="10" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="61.28515625" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" customWidth="1"/>
     <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="44.7109375" style="10" customWidth="1"/>
+    <col min="13" max="13" width="53.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="17" t="s">
         <v>0</v>
@@ -1251,20 +1162,20 @@
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23">
-        <v>46246</v>
+      <c r="B2" s="13">
+        <v>46247</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="22"/>
+      <c r="E2" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
@@ -1322,108 +1233,110 @@
       <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="12"/>
       <c r="M4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>46245.705520833333</v>
+        <v>46243.521261574075</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>46243.521261574075</v>
+        <v>46246.600949074076</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <f t="shared" ref="A7:A27" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46234.633958333332</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <f t="shared" ref="A7:A35" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46244.536550925928</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -1432,76 +1345,76 @@
         <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>46234.633958333332</v>
+        <v>46244.646956018521</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="L8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>46245.577685185184</v>
+        <v>46245.556388888886</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>51</v>
@@ -1514,16 +1427,16 @@
         <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>57</v>
@@ -1531,22 +1444,24 @@
       <c r="L9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="9" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>46245.530902777777</v>
+        <v>46239.682071759256</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E10" s="9" t="s">
         <v>60</v>
       </c>
@@ -1554,7 +1469,7 @@
         <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>62</v>
@@ -1563,545 +1478,541 @@
         <v>63</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>46244.646956018521</v>
+        <v>46246.602222222224</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <v>46245.598009259258</v>
+        <v>46242.584861111114</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="11" t="s">
+      <c r="J12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="K12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="L12" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>46239.682071759256</v>
+        <v>46246.552546296298</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="I13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="J13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="K13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="L13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>46244.538530092592</v>
+        <v>46242.578993055555</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>46245.509733796294</v>
+        <v>46242.58148148148</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E15" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="3">
-        <v>46245.422164351854</v>
+        <v>46242.586817129632</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="E16" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="3">
-        <v>46242.584861111114</v>
+        <v>46246.585555555554</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="9" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="3">
-        <v>46242.578993055555</v>
+        <v>46243.548333333332</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="K18" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="3">
-        <v>46242.58148148148</v>
+        <v>46246.586585648147</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>46242.586817129632</v>
+        <v>46246.665046296293</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="I20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="K20" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="L20" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="3">
-        <v>46243.548333333332</v>
+        <v>46241.879166666666</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="3">
-        <v>46245.633055555554</v>
+        <v>46246.617835648147</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="3">
-        <v>46241.879166666666</v>
+        <v>46246.636030092595</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>141</v>
@@ -2109,124 +2020,116 @@
       <c r="L23" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M23" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="3">
-        <v>46245.566747685189</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>46246.636030092595</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="E24" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>162</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="M24" s="9" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="3">
-        <v>46232.560081018521</v>
-      </c>
-      <c r="C25" s="2" t="s">
+        <v>46246.636030092595</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="3">
-        <v>46232.560081018521</v>
+        <v>46246.636030092595</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="14" t="s">
-        <v>165</v>
+      <c r="E26" s="20" t="s">
+        <v>153</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>175</v>
+        <v>161</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
@@ -2235,340 +2138,112 @@
         <v>23</v>
       </c>
       <c r="B27" s="3">
-        <v>46232.560081018521</v>
+        <v>46246.636030092595</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="14" t="s">
-        <v>166</v>
+      <c r="E27" s="20" t="s">
+        <v>154</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" s="3">
-        <v>46232.560081018521</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="9"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="51" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" s="3">
-        <v>46232.560081018521</v>
-      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="14" t="s">
-        <v>168</v>
-      </c>
+      <c r="E29" s="9"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="3">
-        <v>46232.560081018521</v>
-      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="14" t="s">
-        <v>169</v>
-      </c>
+      <c r="E30" s="9"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="3">
-        <v>46232.560081018521</v>
-      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="14" t="s">
-        <v>170</v>
-      </c>
+      <c r="E31" s="9"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" s="3">
-        <v>46232.560081018521</v>
-      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="14" t="s">
-        <v>171</v>
-      </c>
+      <c r="E32" s="9"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" s="3">
-        <v>46232.560081018521</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" s="3">
-        <v>46232.560081018521</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" s="3">
-        <v>46232.560081018521</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="12" t="s">
-        <v>176</v>
-      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,23 @@
   <definedNames>
     <definedName name="__bookmark_1">Sheet0!$A$1:$M$15</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="106">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,34 +87,52 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2607/0452</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>400KV_400 kV Bhopal-Itarsi Ckt I &amp; II</t>
-  </si>
-  <si>
-    <t>400KV_BHOPAL4</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>modification of line between loc.No. 77 to 79 due</t>
-  </si>
-  <si>
-    <t>01-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>15-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Ankit Mehroliya</t>
-  </si>
-  <si>
-    <t>9425804506</t>
+    <t>MR2608/0159</t>
+  </si>
+  <si>
+    <t>132KV_132KV MAIN BUS</t>
+  </si>
+  <si>
+    <t>220KV_ASHOKNAGAR</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>New Additional 50MVA X-mer 132 Side High Bus strin</t>
+  </si>
+  <si>
+    <t>16-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>16-08-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>RAKESH SUMAN</t>
+  </si>
+  <si>
+    <t>7587951093</t>
+  </si>
+  <si>
+    <t>MR2608/0157</t>
+  </si>
+  <si>
+    <t>132KV_132 KV MAIN BUS</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>FOR NEW BUS COPLER JUMPERING WORK</t>
+  </si>
+  <si>
+    <t>16-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>BRAJENDRA SONI</t>
+  </si>
+  <si>
+    <t>9131327770</t>
   </si>
   <si>
     <t>MR2608/0108</t>
@@ -118,9 +147,6 @@
     <t>220KV_DAMOH</t>
   </si>
   <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
     <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
   </si>
   <si>
@@ -160,6 +186,27 @@
     <t>9425805317</t>
   </si>
   <si>
+    <t>MR2608/0158</t>
+  </si>
+  <si>
+    <t>132KV_132 kv half main bus section - II</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>R-phase Twin zebra span damaged conductor</t>
+  </si>
+  <si>
+    <t>16-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>VIKRAM AHIRWAR</t>
+  </si>
+  <si>
+    <t>9425805415</t>
+  </si>
+  <si>
     <t>MR2608/0095</t>
   </si>
   <si>
@@ -208,22 +255,19 @@
     <t>Hotline Shutdown for crossing work</t>
   </si>
   <si>
-    <t>MR2608/0100</t>
-  </si>
-  <si>
-    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
+    <t>MR2608/0151</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR DHEEMARKHEDA LINE</t>
   </si>
   <si>
     <t>220KV_PANAGAR</t>
   </si>
   <si>
-    <t>OPGW Live Line Installation</t>
-  </si>
-  <si>
-    <t>10-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>15-08-2026 19:00:00</t>
+    <t>OPGW Live Line Installation at 132kV Panagar  - Dh</t>
+  </si>
+  <si>
+    <t>16-08-2026 07:00:00</t>
   </si>
   <si>
     <t>MANOJ KUMAR TIWARI</t>
@@ -232,58 +276,82 @@
     <t>9425804993</t>
   </si>
   <si>
-    <t>MR2608/0152</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA X-MER 1st EMCO</t>
-  </si>
-  <si>
-    <t>220KV_SHIVPURI</t>
-  </si>
-  <si>
-    <t>for 220KV SIDE NEW FOUNDATION work</t>
-  </si>
-  <si>
-    <t>15-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>15-08-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>DHIRENDRA CHAURASIYA</t>
-  </si>
-  <si>
-    <t>7000491070</t>
-  </si>
-  <si>
-    <t>work completed</t>
+    <t>MR2608/0123</t>
+  </si>
+  <si>
+    <t>132KV_shutdown - On 132kv Main bus</t>
+  </si>
+  <si>
+    <t>132KV_SHEOPUR KALAN</t>
+  </si>
+  <si>
+    <t>shutdown- To 132 kV Interconnector-I ckt 132 kV Ma</t>
+  </si>
+  <si>
+    <t>16-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>16-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>Dharmendra Uikey JE</t>
+  </si>
+  <si>
+    <t>8236941498</t>
   </si>
   <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
+    <t>continous</t>
+  </si>
+  <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
-  </si>
-  <si>
-    <t>ok, line to be in service, o&amp;m to be informed</t>
+    <t>sub ld, send emergency proposal of 132kv Sheopur-Sabalgarh tap khandar to WRLDC for approval</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
+    <t>220KV-PITHAMPUR-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>220KV-RAJGARH-DHAR-1</t>
+  </si>
+  <si>
+    <t>16-Aug-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>31-Aug-2026</t>
+  </si>
+  <si>
+    <t>Continous</t>
+  </si>
+  <si>
     <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR MOD. SHIFTING WORK OF LINE DUE TO CONSTRUTION OF NEW RAILWAY LINE BETWEEN TIRLA- AMJHERA-SARDARPUR SECTION BY WR RATLAM </t>
+  </si>
+  <si>
     <t>MADHYA PRADESH,CHATTISGARH</t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>S/I ,SLDC, JABALPUR</t>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>real time</t>
   </si>
 </sst>
 </file>
@@ -294,7 +362,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -329,6 +397,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -344,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,20 +518,24 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -449,76 +543,95 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +663,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>605333</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3335</xdr:rowOff>
+      <xdr:rowOff>12860</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -883,549 +996,690 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr defaultRowHeight="42.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="54" style="12" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="26.28515625" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="57.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="11.140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="6"/>
+    <col min="5" max="5" width="47.85546875" style="25" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" style="25" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="6" customWidth="1"/>
+    <col min="8" max="8" width="48.7109375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="40.140625" style="25" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>46249</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="7">
+        <v>46250</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="21"/>
+    </row>
+    <row r="3" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="21"/>
+    </row>
+    <row r="4" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="5"/>
+      <c r="M4" s="22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A5" s="4">
+    <row r="5" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
-        <v>46234.633958333332</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="11">
+        <v>46249.55741898148</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="J5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="M5" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11">
+        <v>46249.396967592591</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A7" s="10">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46244.646956018521</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46239.682071759256</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46249.510636574072</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A10" s="10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46242.584861111114</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A11" s="10">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46242.578993055555</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46242.58148148148</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46242.586817129632</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A14" s="10">
+        <v>10</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46248.519097222219</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A6" s="4">
-        <f>A5+1</f>
-        <v>2</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46244.646956018521</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="6" t="s">
+      <c r="J14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="42.75" customHeight="1">
+      <c r="A15" s="10">
+        <v>11</v>
+      </c>
+      <c r="B15" s="15">
+        <v>46246.522372685184</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="82.5" customHeight="1">
+      <c r="A16" s="10">
+        <v>12</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="1">
+        <v>316092</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A7" s="4">
-        <f t="shared" ref="A7:A12" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46239.682071759256</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46242.584861111114</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46242.578993055555</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46242.58148148148</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46242.586817129632</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46243.548333333332</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A13" s="4">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46248.575104166666</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14" s="6">
-        <v>46249.333333333336</v>
-      </c>
-      <c r="J14" s="6">
-        <v>46249.75</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="4" t="s">
-        <v>86</v>
+      <c r="E16" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="24">
+        <v>220</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="82.5" customHeight="1">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="1">
+        <v>315982</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="24">
+        <v>220</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M17" s="26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="82.5" customHeight="1">
+      <c r="A18" s="10">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="1">
+        <v>315983</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="24">
+        <v>220</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M18" s="26" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A15:L15"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -662,8 +662,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>605333</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12860</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>555785</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -996,8 +996,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="42.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="57" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6"/>
     <col min="2" max="2" width="11.140625" style="6" customWidth="1"/>
@@ -1015,7 +1018,7 @@
     <col min="14" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="42.75" customHeight="1">
+    <row r="1" spans="1:13" ht="57" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1032,7 +1035,7 @@
       <c r="L1" s="4"/>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" spans="1:13" ht="42.75" customHeight="1">
+    <row r="2" spans="1:13" ht="57" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1051,7 +1054,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="21"/>
     </row>
-    <row r="3" spans="1:13" ht="42.75" customHeight="1">
+    <row r="3" spans="1:13" ht="57" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
@@ -1074,7 +1077,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="21"/>
     </row>
-    <row r="4" spans="1:13" ht="42.75" customHeight="1">
+    <row r="4" spans="1:13" ht="57" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -1113,7 +1116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="42.75" customHeight="1">
+    <row r="5" spans="1:13" ht="57" customHeight="1">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="42.75" customHeight="1">
+    <row r="6" spans="1:13" ht="57" customHeight="1">
       <c r="A6" s="10">
         <v>2</v>
       </c>
@@ -1191,7 +1194,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="42.75" customHeight="1">
+    <row r="7" spans="1:13" ht="57" customHeight="1">
       <c r="A7" s="10">
         <v>3</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="42.75" customHeight="1">
+    <row r="8" spans="1:13" ht="57" customHeight="1">
       <c r="A8" s="10">
         <v>4</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="42.75" customHeight="1">
+    <row r="9" spans="1:13" ht="57" customHeight="1">
       <c r="A9" s="10">
         <v>5</v>
       </c>
@@ -1312,7 +1315,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="42.75" customHeight="1">
+    <row r="10" spans="1:13" ht="57" customHeight="1">
       <c r="A10" s="10">
         <v>6</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="42.75" customHeight="1">
+    <row r="11" spans="1:13" ht="57" customHeight="1">
       <c r="A11" s="10">
         <v>7</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="42.75" customHeight="1">
+    <row r="12" spans="1:13" ht="57" customHeight="1">
       <c r="A12" s="10">
         <v>8</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="42.75" customHeight="1">
+    <row r="13" spans="1:13" ht="57" customHeight="1">
       <c r="A13" s="10">
         <v>9</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="42.75" customHeight="1">
+    <row r="14" spans="1:13" ht="57" customHeight="1">
       <c r="A14" s="10">
         <v>10</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="42.75" customHeight="1">
+    <row r="15" spans="1:13" ht="57" customHeight="1">
       <c r="A15" s="10">
         <v>11</v>
       </c>
@@ -1556,7 +1559,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="82.5" customHeight="1">
+    <row r="16" spans="1:13" ht="57" customHeight="1">
       <c r="A16" s="10">
         <v>12</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="82.5" customHeight="1">
+    <row r="17" spans="1:13" ht="57" customHeight="1">
       <c r="A17" s="10">
         <v>13</v>
       </c>
@@ -1634,7 +1637,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="82.5" customHeight="1">
+    <row r="18" spans="1:13" ht="57" customHeight="1">
       <c r="A18" s="10">
         <v>14</v>
       </c>
@@ -1678,8 +1681,8 @@
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -9,20 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$20</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="123">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,76 +76,52 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0168</t>
-  </si>
-  <si>
-    <t>132KV_132KV AMARPATAN-BANSAGAR(JHINNA) FEEDER</t>
-  </si>
-  <si>
-    <t>132KV_AMARPATAN</t>
+    <t>MR2608/0181</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Chhegaon Nepanagar ckt</t>
+  </si>
+  <si>
+    <t>400KV_CHHEGAON4</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>Atending red hot point (Y&amp;B)PH Line Isolater clamp</t>
-  </si>
-  <si>
-    <t>17-08-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>J K SINGH</t>
-  </si>
-  <si>
-    <t>8359015288</t>
-  </si>
-  <si>
-    <t>MR2608/0165</t>
-  </si>
-  <si>
-    <t>220KV_220KV Chhegaon- Nepanagar ckt.</t>
-  </si>
-  <si>
-    <t>400KV_CHHEGAON4</t>
-  </si>
-  <si>
-    <t>Main 2 Relay Autoreclose Testing work</t>
-  </si>
-  <si>
-    <t>17-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Shri Ganesh Mansare</t>
+    <t>Main-2 DPR autorecloser testing work</t>
+  </si>
+  <si>
+    <t>18-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>18-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er Ganesh Mansare</t>
   </si>
   <si>
     <t>9425802441</t>
   </si>
   <si>
-    <t>MR2608/0108</t>
+    <t>MR2608/0180</t>
   </si>
   <si>
     <t>Daily</t>
   </si>
   <si>
-    <t>132KV_132KV DAMOH - PATERA IST&amp;IIND LINE</t>
+    <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
   </si>
   <si>
     <t>220KV_DAMOH</t>
   </si>
   <si>
-    <t>PTW FOR OPGW LIVE LINE INSTALLATION WORK</t>
-  </si>
-  <si>
-    <t>11-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 19:00:00</t>
+    <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
+  </si>
+  <si>
+    <t>18-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 19:00:00</t>
   </si>
   <si>
     <t>M.M. BAIG</t>
@@ -154,51 +130,6 @@
     <t>9425805067</t>
   </si>
   <si>
-    <t>MR2608/0169</t>
-  </si>
-  <si>
-    <t>132KV_132kv Shahdol-Dindori ckt-I</t>
-  </si>
-  <si>
-    <t>132KV_DINDORI</t>
-  </si>
-  <si>
-    <t>For Flash over disc Replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>17-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>JAGDISH PRASAD ASHATI</t>
-  </si>
-  <si>
-    <t>9424445533</t>
-  </si>
-  <si>
-    <t>MR2608/0179</t>
-  </si>
-  <si>
-    <t>132KV_132KV Katangi- Waraseoni Bay CB</t>
-  </si>
-  <si>
-    <t>132KV_KATANGI</t>
-  </si>
-  <si>
-    <t>For SF6 gas leakage attending work</t>
-  </si>
-  <si>
-    <t>17-08-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Seema Dongre</t>
-  </si>
-  <si>
-    <t>9425807247</t>
-  </si>
-  <si>
     <t>MR2608/0063</t>
   </si>
   <si>
@@ -223,6 +154,48 @@
     <t>9425805317</t>
   </si>
   <si>
+    <t>MR2608/0193</t>
+  </si>
+  <si>
+    <t>132KV_132kv RTS ckt</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Bay Maintenance both end</t>
+  </si>
+  <si>
+    <t>18-08-2026 14:30:00</t>
+  </si>
+  <si>
+    <t>18-08-2026 16:30:00</t>
+  </si>
+  <si>
+    <t>VIKRAM AHIRWAR</t>
+  </si>
+  <si>
+    <t>9425805415</t>
+  </si>
+  <si>
+    <t>MR2608/0194</t>
+  </si>
+  <si>
+    <t>132KV_Opportunity Shutdown on 132KV RTS Malanpur</t>
+  </si>
+  <si>
+    <t>Opportunity Shutdown for Line Maintenanace work</t>
+  </si>
+  <si>
+    <t>Baidyanath Kumar</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
     <t>MR2608/0095</t>
   </si>
   <si>
@@ -247,6 +220,27 @@
     <t>9425805120</t>
   </si>
   <si>
+    <t>MR2608/0185</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch- Mandsaur-II</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>IInd New DPR relay replacement work</t>
+  </si>
+  <si>
+    <t>18-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
+  </si>
+  <si>
     <t>MR2608/0093</t>
   </si>
   <si>
@@ -271,193 +265,133 @@
     <t>Hotline Shutdown for crossing work</t>
   </si>
   <si>
-    <t>MR2608/0151</t>
-  </si>
-  <si>
-    <t>132KV_132 KV PANAGAR DHEEMARKHEDA LINE</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>OPGW Live Line Installation at 132kV Panagar  - Dh</t>
-  </si>
-  <si>
-    <t>16-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2608/0172</t>
-  </si>
-  <si>
-    <t>132KV_132/3340mva ABB &amp; 40mva BBLxmer</t>
-  </si>
-  <si>
-    <t>132KV_RAMPUR BAGHELAN</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>New erected 50mva Tal xmer 33 kv jumpher work</t>
-  </si>
-  <si>
-    <t>17-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>17-08-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>KANISHK SINGH</t>
-  </si>
-  <si>
-    <t>9425804656</t>
+    <t>MR2608/0184</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Pandhurna-Betul PGCIL</t>
+  </si>
+  <si>
+    <t>220KV_PANDHURNA</t>
+  </si>
+  <si>
+    <t>Suspension clamp, A/h, V/d tightening</t>
+  </si>
+  <si>
+    <t>18-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
   </si>
   <si>
     <t>220KV_220 KV BUS TIE</t>
   </si>
   <si>
-    <t>220KV_SEONI</t>
-  </si>
-  <si>
-    <t>220 KV PGCL - I Feeder Main Bus I Isolator alignme</t>
-  </si>
-  <si>
-    <t>Arshad Quershi</t>
-  </si>
-  <si>
-    <t>7000771014</t>
-  </si>
-  <si>
-    <t>MR2608/0164</t>
-  </si>
-  <si>
-    <t>MR2608/0170</t>
-  </si>
-  <si>
-    <t>220KV_220k Seoni Interconnector Ckt 1st</t>
-  </si>
-  <si>
-    <t>Jumper cone/Arcin Horn Nut bolt tightning</t>
-  </si>
-  <si>
-    <t>17-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>8319697216</t>
-  </si>
-  <si>
-    <t>MR2608/0154</t>
-  </si>
-  <si>
-    <t>220KV_220KV ATPS -SHAHDOL LINE</t>
-  </si>
-  <si>
-    <t>220KV_SHAHDOL</t>
-  </si>
-  <si>
-    <t>OPGW STRINGING AND JOINT SPLICING WORK</t>
-  </si>
-  <si>
-    <t>DHARMENDRA DWIVEDI</t>
-  </si>
-  <si>
-    <t>9425805311</t>
-  </si>
-  <si>
-    <t>MR2608/0153</t>
-  </si>
-  <si>
-    <t>220KV_220KV ATPS-SIDHI LINE</t>
-  </si>
-  <si>
     <t>220KV_SIDHI</t>
   </si>
   <si>
+    <t>R PHASE CT CLAMP ISOLATOR SIDE HOT POINT ATTENDING</t>
+  </si>
+  <si>
+    <t>18-08-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>18-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>VISHAL BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425613436</t>
+  </si>
+  <si>
+    <t>MR2608/0188</t>
+  </si>
+  <si>
+    <t>132KV_132kV Sidhi - Mauganj Ckt - I</t>
+  </si>
+  <si>
+    <t>Disc Replacement And Bird Excreta Provided work.</t>
+  </si>
+  <si>
+    <t>18-08-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>G.L Sahu</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2608/0187</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>ok, line to be in service</t>
+  </si>
+  <si>
+    <t>continous</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>ok, through sub ld, AR off also approved</t>
+  </si>
+  <si>
+    <t>ok, line to be in service, Outage also approved</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
-    <t>real timer, through sub ld</t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>ok, line to be in service through TBC</t>
-  </si>
-  <si>
-    <t>continous</t>
-  </si>
-  <si>
-    <t>sub ld</t>
-  </si>
-  <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>deferred by site</t>
-  </si>
-  <si>
-    <t>220KV-SEONI-MP-SEONI-PG-1</t>
-  </si>
-  <si>
-    <t>220KV-MALANPUR-AURIYA-1</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-MAHALGAON-3</t>
-  </si>
-  <si>
-    <t>220KV-SHUJALPUR-SHUJALPUR-MP-1</t>
+    <t>ok, 220kv Pandhurna-Kalmeshwar ckt to be in service</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
-    <t>17-Aug-2026</t>
+    <t>220KV-INDORE-UJJAIN-1</t>
+  </si>
+  <si>
+    <t>220KV-DAMOH-SAGAR-2</t>
+  </si>
+  <si>
+    <t>220KV-BETUL-PANDURNA-1</t>
+  </si>
+  <si>
+    <t>18-Aug-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>06:00</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
+    <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
   </si>
   <si>
     <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
-  </si>
-  <si>
-    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
-  </si>
-  <si>
-    <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
-  </si>
-  <si>
     <t>OCCM-WR</t>
   </si>
   <si>
-    <t>S/I ,SLDC MPPTCL JBP</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.17.08.26</t>
+    <t>S/I ,SLDC MPPTCL JABALPUR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.18.08.26</t>
   </si>
 </sst>
 </file>
@@ -468,7 +402,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -481,15 +415,25 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -500,7 +444,7 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="22"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -594,7 +538,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -614,43 +558,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,8 +634,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>605333</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3335</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>551023</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1015,134 +968,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="63" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="48.42578125" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="59.7109375" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" customWidth="1"/>
     <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="48.42578125" customWidth="1"/>
+    <col min="13" max="13" width="40" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1">
+    <row r="1" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
-    </row>
-    <row r="2" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="17"/>
+    </row>
+    <row r="2" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13">
-        <v>46251</v>
-      </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="B2" s="20">
+        <v>46252</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="11"/>
+    </row>
+    <row r="3" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" s="10" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>15</v>
       </c>
       <c r="L4" s="19"/>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1">
+    <row r="5" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>46250.543981481482</v>
+        <v>46251.489537037036</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1166,63 +1119,67 @@
       <c r="L5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="30" customHeight="1">
+      <c r="M5" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
+        <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>46250.37164351852</v>
+        <v>46251.488530092596</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="E6" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="30" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
+        <f t="shared" ref="A7:A21" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>46244.646956018521</v>
+        <v>46239.682071759256</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -1246,65 +1203,67 @@
       <c r="L7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="30" customHeight="1">
+      <c r="M7" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>46250.565983796296</v>
+        <v>46251.667187500003</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="9" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30" customHeight="1">
+        <v>51</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>46250.715567129628</v>
+        <v>46251.710162037038</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
+      <c r="E9" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1313,653 +1272,554 @@
         <v>54</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46242.584861111114</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="30" customHeight="1">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3">
-        <v>46239.682071759256</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="M10" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46251.587048611109</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="30" customHeight="1">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46242.584861111114</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="L11" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="30" customHeight="1">
+      <c r="M11" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="3">
         <v>46242.578993055555</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>75</v>
+        <v>27</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="30" customHeight="1">
+        <v>64</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="3">
         <v>46242.58148148148</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>78</v>
+        <v>27</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="30" customHeight="1">
+        <v>64</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="3">
         <v>46242.586817129632</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>27</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46251.579317129632</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="30" customHeight="1">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46248.519097222219</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="I15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="K15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46251.618657407409</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K15" s="5" t="s">
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46251.614895833336</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="F17" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30" customHeight="1">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46250.63077546296</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="30" customHeight="1">
-      <c r="A17" s="2">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46249.897141203706</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46251.614895833336</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="51" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46251.614895833336</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46250.583645833336</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1">
-      <c r="A19" s="2">
-        <v>15</v>
-      </c>
-      <c r="B19" s="3">
-        <v>46248.599560185183</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="J19" s="4" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="N19" s="7"/>
-    </row>
-    <row r="20" spans="1:14" ht="39" customHeight="1">
+      <c r="M19" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="3">
-        <v>46248.596817129626</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>116</v>
-      </c>
+        <v>46251.614895833336</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="2" t="s">
+      <c r="K20" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="63.75">
+      <c r="M20" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="3">
-        <v>46248.596817129626</v>
+        <v>46251.614895833336</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
-        <v>128</v>
+      <c r="E21" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>138</v>
+        <v>120</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="25.5">
-      <c r="A22" s="2">
-        <v>18</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46248.596817129626</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="36" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="E22" s="9"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="38.25">
-      <c r="A23" s="2">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3">
-        <v>46248.596817129626</v>
-      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="E23" s="9"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="63.75">
-      <c r="A24" s="2">
-        <v>20</v>
-      </c>
-      <c r="B24" s="3">
-        <v>46248.596817129626</v>
-      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="25.5">
-      <c r="A25" s="2">
-        <v>21</v>
-      </c>
-      <c r="B25" s="3">
-        <v>46248.596817129626</v>
-      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="E25" s="9"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="23.25">
-      <c r="B26" s="3"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="20" t="s">
-        <v>143</v>
-      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1968,7 +1828,7 @@
     <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$32</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$36</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="203">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,418 +76,496 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0196</t>
-  </si>
-  <si>
-    <t>220KV_160MVA XMER_I AREVA</t>
-  </si>
-  <si>
-    <t>220KV_BADOD</t>
+    <t>MR2608/0214</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Anuppur-Janakpur cicuit</t>
+  </si>
+  <si>
+    <t>220KV_ANUPPUR</t>
+  </si>
+  <si>
+    <t>NON-OCCM-MP</t>
+  </si>
+  <si>
+    <t>F/o disc stringing replacement &amp; other line maint.</t>
+  </si>
+  <si>
+    <t>20-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>20-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Asati</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2608/0200</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Bairagarh-Kurawar line</t>
+  </si>
+  <si>
+    <t>220KV_BAIRAGARH</t>
+  </si>
+  <si>
+    <t>Stringing work</t>
+  </si>
+  <si>
+    <t>19-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Ankit Mehroliya</t>
+  </si>
+  <si>
+    <t>9425804506</t>
+  </si>
+  <si>
+    <t>MR2608/0215</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Bargi- Lakhnadaun</t>
+  </si>
+  <si>
+    <t>132KV_BARGI</t>
+  </si>
+  <si>
+    <t>More than 35 year string replaced through contract</t>
+  </si>
+  <si>
+    <t>20-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>30-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2608/0216</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina -Borl Ckt 1</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>f/o disc insulater replacement at loc15T tension</t>
+  </si>
+  <si>
+    <t>20-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Dilip Singh Walkey</t>
+  </si>
+  <si>
+    <t>9425804578</t>
+  </si>
+  <si>
+    <t>132KV_220 KV Chhatarpur-Tikamgarh line</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>installation of ERS</t>
+  </si>
+  <si>
+    <t>pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2608/0227</t>
+  </si>
+  <si>
+    <t>MR2608/0212</t>
+  </si>
+  <si>
+    <t>50MVA_132/33KV_BHEL_X'mer_2</t>
+  </si>
+  <si>
+    <t>132KV_CHOURAI</t>
+  </si>
+  <si>
+    <t>Structure painting work.</t>
+  </si>
+  <si>
+    <t>20-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>S.K.Okte</t>
+  </si>
+  <si>
+    <t>7587951132</t>
+  </si>
+  <si>
+    <t>MR2608/0180</t>
+  </si>
+  <si>
+    <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
+  </si>
+  <si>
+    <t>18-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2608/0217</t>
+  </si>
+  <si>
+    <t>132KV_132kV Guna Aron Line</t>
+  </si>
+  <si>
+    <t>220KV_GUNA</t>
+  </si>
+  <si>
+    <t>For DF/o replacement work</t>
+  </si>
+  <si>
+    <t>Akhilesh Singh</t>
+  </si>
+  <si>
+    <t>8586865656</t>
+  </si>
+  <si>
+    <t>MR2608/0192</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220KV MAIN BUS-I</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF SUPPORT INSULATOR /PI OF EACH U</t>
+  </si>
+  <si>
+    <t>19-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>21-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>ATUL PARADKAR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2608/0211</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA ECE XMER</t>
+  </si>
+  <si>
+    <t>132KV_KHAJURAHO</t>
+  </si>
+  <si>
+    <t>OIL TOPPING WORK</t>
+  </si>
+  <si>
+    <t>20-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>20-08-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>BRAJENDRA SONI</t>
+  </si>
+  <si>
+    <t>9131327770</t>
+  </si>
+  <si>
+    <t>MR2608/0197</t>
+  </si>
+  <si>
+    <t>400KV_400kV Kirnapur Bhilai Line</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Suspension Clamp Tightening Work &amp; Other Line Main</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2608/0063</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Erection/Dismentalling of tower &amp; making cut point</t>
+  </si>
+  <si>
+    <t>06-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>26-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2608/0219</t>
+  </si>
+  <si>
+    <t>132KV_SHUTDOWN ON 132 KV Mansakra-Panager Feeder AT 132KV S/S Mansakra.</t>
+  </si>
+  <si>
+    <t>132KV_MANSAKRA</t>
+  </si>
+  <si>
+    <t>to attend hot point in Y ph CT stud clamp</t>
+  </si>
+  <si>
+    <t>20-08-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>R P Rawat</t>
+  </si>
+  <si>
+    <t>9907030507</t>
+  </si>
+  <si>
+    <t>MR2608/0220</t>
+  </si>
+  <si>
+    <t>132KV_SHUTDOWN ON 132 KV Mansakra-Sleemnabad Feeder AT 132KV S/S Mansakra.</t>
+  </si>
+  <si>
+    <t>to attend hot point in R ph CT stud Clamp</t>
+  </si>
+  <si>
+    <t>MR2608/0095</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Budha Line</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>For Crossing Work</t>
+  </si>
+  <si>
+    <t>11-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2608/0093</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
+  </si>
+  <si>
+    <t>For Crossing Wrok</t>
+  </si>
+  <si>
+    <t>MR2608/0094</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
+  </si>
+  <si>
+    <t>MR2608/0096</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Malharagarh Line</t>
+  </si>
+  <si>
+    <t>Hotline Shutdown for crossing work</t>
+  </si>
+  <si>
+    <t>MR2608/0210</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>19-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>25-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2608/0223</t>
+  </si>
+  <si>
+    <t>132KV_132kV Rajmilan - Janakpur Ckt</t>
+  </si>
+  <si>
+    <t>132KV_RAJMILAN</t>
+  </si>
+  <si>
+    <t>Disc Replacement work.</t>
+  </si>
+  <si>
+    <t>20-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>G.L Sahu</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2608/0221</t>
+  </si>
+  <si>
+    <t>132KV_132kv 63mva xmer bbl</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For B-ph damage conductor replacement and ryb ph c</t>
+  </si>
+  <si>
+    <t>20-08-2026 10:24:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2608/0213</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA X-Mer BBL -  I</t>
+  </si>
+  <si>
+    <t>132KV_SEONI1</t>
+  </si>
+  <si>
+    <t>33 KV Half Main Bus S/D For Iso. Repl. Work</t>
+  </si>
+  <si>
+    <t>20-08-2026 11:30:00</t>
+  </si>
+  <si>
+    <t>Arshad Qureshi</t>
+  </si>
+  <si>
+    <t>7648817144</t>
+  </si>
+  <si>
+    <t>MR2608/0222</t>
+  </si>
+  <si>
+    <t>132KV_132kV Sidhi - Mauganj Ckt - I</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Disc Replacement And Bird Excreta Provided work.</t>
+  </si>
+  <si>
+    <t>MR2608/0218</t>
+  </si>
+  <si>
+    <t>132KV_132 KV SIDHI - IC CKT - IInd  (SIDHI)FDR</t>
   </si>
   <si>
     <t>NON-OCCM-WR</t>
   </si>
   <si>
-    <t>R&amp;Y Phase CT replacement work 220kv class CT</t>
-  </si>
-  <si>
-    <t>19-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>19-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>ER Y K RATHORE</t>
-  </si>
-  <si>
-    <t>9425804968</t>
-  </si>
-  <si>
-    <t>MR2608/0200</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Bairagarh-Kurawar line</t>
-  </si>
-  <si>
-    <t>220KV_BAIRAGARH</t>
-  </si>
-  <si>
-    <t>NON-OCCM-MP</t>
-  </si>
-  <si>
-    <t>Stringing work</t>
-  </si>
-  <si>
-    <t>19-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>20-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Ankit Mehroliya</t>
-  </si>
-  <si>
-    <t>9425804506</t>
-  </si>
-  <si>
-    <t>MR2608/0177</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Ajaygarh-Chhatarpur (TBCB) 1</t>
-  </si>
-  <si>
-    <t>220KV_CHATARPUR</t>
-  </si>
-  <si>
-    <t>For ERS installation in modification work</t>
-  </si>
-  <si>
-    <t>19-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>pankaj yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2608/0180</t>
-  </si>
-  <si>
-    <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
-  </si>
-  <si>
-    <t>18-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>M.M. BAIG</t>
-  </si>
-  <si>
-    <t>9425805067</t>
-  </si>
-  <si>
-    <t>MR2608/0192</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220KV MAIN BUS-I</t>
-  </si>
-  <si>
-    <t>400KV_INDORE4</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF SUPPORT INSULATOR /PI OF EACH U</t>
-  </si>
-  <si>
-    <t>19-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>ATUL PARADKAR</t>
-  </si>
-  <si>
-    <t>9425804929</t>
-  </si>
-  <si>
-    <t>MR2608/0205</t>
-  </si>
-  <si>
-    <t>220KV_220 KV KATNI - SATNA LINE</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>F/o Disc Replacement  and Other Line Maintenance</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0095</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Budha Line</t>
-  </si>
-  <si>
-    <t>220KV_NEEMUCH</t>
-  </si>
-  <si>
-    <t>For Crossing Work</t>
-  </si>
-  <si>
-    <t>11-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2608/0093</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
-  </si>
-  <si>
-    <t>For Crossing Wrok</t>
-  </si>
-  <si>
-    <t>MR2608/0094</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
-  </si>
-  <si>
-    <t>MR2608/0096</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Malharagarh Line</t>
-  </si>
-  <si>
-    <t>Hotline Shutdown for crossing work</t>
-  </si>
-  <si>
-    <t>MR2608/0204</t>
-  </si>
-  <si>
-    <t>132KV_132kv Sabalgarh Jora Ckt</t>
-  </si>
-  <si>
-    <t>220KV_SABALGARH</t>
-  </si>
-  <si>
-    <t>Line Maintenance work</t>
-  </si>
-  <si>
-    <t>Suraj Pawar</t>
-  </si>
-  <si>
-    <t>9425814079</t>
-  </si>
-  <si>
-    <t>MR2608/0195</t>
-  </si>
-  <si>
-    <t>220KV_160 mva - II</t>
-  </si>
-  <si>
-    <t>220KV_SAILANA2</t>
-  </si>
-  <si>
-    <t>220 kv side Breaker control cable Repairing work.</t>
-  </si>
-  <si>
-    <t>19-08-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Rakesh Badgotya</t>
-  </si>
-  <si>
-    <t>8305447051</t>
-  </si>
-  <si>
-    <t>MR2608/0198</t>
-  </si>
-  <si>
-    <t>132KV_Sarni Umreth</t>
-  </si>
-  <si>
-    <t>220KV_SARNI</t>
-  </si>
-  <si>
-    <t>Broken disc replacement &amp; other line maint. work</t>
-  </si>
-  <si>
-    <t>19-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>SHIV KUMAR</t>
-  </si>
-  <si>
-    <t>9425806917</t>
-  </si>
-  <si>
-    <t>MR2608/0199</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Seoni-Seoni ICT-II</t>
-  </si>
-  <si>
-    <t>220KV_SEONI</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Jumper cone, Suspension Clamp, A/h, V/d Tightening</t>
-  </si>
-  <si>
-    <t>A.M.Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2608/0206</t>
-  </si>
-  <si>
-    <t>220KV_220KV S/S BUS Tie</t>
-  </si>
-  <si>
-    <t>220KV PGCIL-2 main bus -ll isolator alignment work</t>
-  </si>
-  <si>
-    <t>Arshad Qureshi</t>
-  </si>
-  <si>
-    <t>9425618267</t>
-  </si>
-  <si>
-    <t>MR2608/0191</t>
-  </si>
-  <si>
-    <t>220KV_220KV ATPS -Shahdol Line</t>
-  </si>
-  <si>
-    <t>220KV_SHAHDOL</t>
-  </si>
-  <si>
-    <t>OPGW stringing and joint splicing work</t>
-  </si>
-  <si>
-    <t>Dharmendra Dwivedi</t>
-  </si>
-  <si>
-    <t>9425805311</t>
-  </si>
-  <si>
-    <t>MR2608/0201</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA X-MER 1st EMCO</t>
-  </si>
-  <si>
-    <t>220KV_SHIVPURI</t>
-  </si>
-  <si>
-    <t>for 220KV SIDE NEW FOUNDATION work</t>
-  </si>
-  <si>
-    <t>19-08-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>DHIRENDRA CHAURSIYA</t>
-  </si>
-  <si>
-    <t>7000491070</t>
-  </si>
-  <si>
-    <t>MR2608/0190</t>
-  </si>
-  <si>
-    <t>220KV_220KV ATPS - Sidhi Line</t>
-  </si>
-  <si>
-    <t>220KV_SIDHI</t>
-  </si>
-  <si>
-    <t>MR2608/0208</t>
-  </si>
-  <si>
-    <t>132KV_132KV Sidhi-Mauganj Circuit -I</t>
-  </si>
-  <si>
-    <t>Flash over Disc replacement</t>
-  </si>
-  <si>
-    <t>G.L sahu</t>
-  </si>
-  <si>
-    <t>9425805102</t>
-  </si>
-  <si>
-    <t>MR2608/0209</t>
-  </si>
-  <si>
-    <t>132KV_63 mva xmer</t>
-  </si>
-  <si>
-    <t>132KV_SIMROL</t>
-  </si>
-  <si>
-    <t>Transformer oil leakage attending work.</t>
-  </si>
-  <si>
-    <t>19-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>Ajay Singh Bisen</t>
-  </si>
-  <si>
-    <t>9425804927</t>
-  </si>
-  <si>
-    <t>MR2608/0202</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Umreth-Sarni line</t>
-  </si>
-  <si>
-    <t>132KV_UMRETH</t>
-  </si>
-  <si>
-    <t>Jumper cone, A/h, V/d tightening work</t>
-  </si>
-  <si>
-    <t>ok, through sub ld</t>
+    <t>CONTROL &amp; RELAY PANAL REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>VISHAL BALADHARE</t>
+  </si>
+  <si>
+    <t>9425804690</t>
+  </si>
+  <si>
+    <t>MR2608/0225</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA bbl-make Transformer</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>Oil topping</t>
+  </si>
+  <si>
+    <t>20-08-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>Pushpendra Kumar soni</t>
+  </si>
+  <si>
+    <t>9425806398</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
   <si>
     <t>sub ld</t>
@@ -496,82 +574,64 @@
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>deferred, not in WR list</t>
-  </si>
-  <si>
-    <t>under review</t>
-  </si>
-  <si>
-    <t>SEONI-PG - 220KV - BUS 2</t>
-  </si>
-  <si>
-    <t>220KV-REWA-REWA-MP-1</t>
+    <t>ok, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 132 kV Anuppur-Janakpur cicuit</t>
+  </si>
+  <si>
+    <t>o&amp;m consent to be taken</t>
+  </si>
+  <si>
+    <t>400KV-KIRNAPUR-BHILAI-1</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-MALANPUR-2</t>
+  </si>
+  <si>
+    <t>220KV-MORENA-MALANPUR-1</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-2</t>
+  </si>
+  <si>
+    <t>220KV-REWA-REWA-MP-2</t>
   </si>
   <si>
     <t>220KV-ANNUPUR-KOTMIKALA-1</t>
   </si>
   <si>
-    <t>400KV/220KV INDORE-ICT-3</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR1 (PGCIL)</t>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>MP_SLDC</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH,CHATTISGARH</t>
   </si>
   <si>
     <t>MADHYA PRADESH</t>
   </si>
   <si>
-    <t>MADHYA PRADESH,CHATTISGARH</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR2 (PGCIL)</t>
-  </si>
-  <si>
-    <t>For AMP work @ Seoni SS. Elements shall remian in service through Bus-1 and TBC bay if shifted.</t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
-  </si>
-  <si>
-    <t>ICT AMP WORK</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>POWERGRID_WR1</t>
-  </si>
-  <si>
-    <t>MP_SLDC</t>
-  </si>
-  <si>
-    <t>POWERGRID_WR2</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.19.08.26</t>
-  </si>
-  <si>
     <t>S/I , SLDC, JABALPUR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.20.08.26</t>
   </si>
 </sst>
 </file>
@@ -582,7 +642,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -595,30 +655,40 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="&quot;Open Sans&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,8 +706,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF9F9F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -730,37 +806,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -792,7 +837,18 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -801,7 +857,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -809,7 +867,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -855,59 +913,63 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,21 +1334,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="57.140625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="63" style="11" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="60.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="9" max="10" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="43.140625" customWidth="1"/>
+    <col min="13" max="13" width="51.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1">
@@ -1311,20 +1372,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19"/>
+      <c r="E2" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1">
@@ -1340,14 +1401,14 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="22"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1">
@@ -1389,12 +1450,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="33.75" customHeight="1">
+    <row r="5" spans="1:13" ht="28.5" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46252.478263888886</v>
+        <v>46253.523831018516</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1425,10 +1486,10 @@
         <v>25</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5" customHeight="1">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
@@ -1449,1005 +1510,1174 @@
         <v>29</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="J6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="L6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="M6" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5" customHeight="1">
+      <c r="A7" s="4">
+        <f t="shared" ref="A7:A28" si="0">A6+1</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
+        <v>46253.530636574076</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A7" s="4">
-        <f t="shared" ref="A7:A25" si="0">A6+1</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46250.643136574072</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="I7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="J7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" customHeight="1">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46251.488530092596</v>
+        <v>46253.568344907406</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="L8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="M8" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.5" customHeight="1">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46251.642638888887</v>
+        <v>46253.69804398148</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="I9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="L9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="M9" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.5" customHeight="1">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46252.592905092592</v>
+        <v>46253.47724537037</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="33.75" customHeight="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="28.5" customHeight="1">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46239.682071759256</v>
+        <v>46251.488530092596</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="K11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="L11" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="M11" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.5" customHeight="1">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46242.584861111114</v>
+        <v>46253.58871527778</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="L12" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="M12" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="33.75" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="28.5" customHeight="1">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46242.578993055555</v>
+        <v>46251.642638888887</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="K13" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="L13" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>81</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="33.75" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28.5" customHeight="1">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46242.58148148148</v>
+        <v>46253.466724537036</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5" customHeight="1">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46242.586817129632</v>
+        <v>46252.487083333333</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="33.75" customHeight="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="28.5" customHeight="1">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46252.592546296299</v>
+        <v>46239.682071759256</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E16" s="10" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="33.75" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" customHeight="1">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46252.453298611108</v>
+        <v>46253.604664351849</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="33.75" customHeight="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="28.5" customHeight="1">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46252.52306712963</v>
+        <v>46253.606261574074</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="10" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="33.75" customHeight="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.5" customHeight="1">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46252.527233796296</v>
+        <v>46242.584861111114</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="4"/>
+        <v>118</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E19" s="10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="33.75" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.5" customHeight="1">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46252.605000000003</v>
+        <v>46242.578993055555</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="4"/>
+        <v>126</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E20" s="10" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="28.5" customHeight="1">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46251.628761574073</v>
+        <v>46242.58148148148</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="10" t="s">
+      <c r="J21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="K21" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="L21" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="M21" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="28.5" customHeight="1">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46252.545497685183</v>
+        <v>46242.586817129632</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>131</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E22" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="33.75" customHeight="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="28.5" customHeight="1">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46251.626481481479</v>
+        <v>46253.337245370371</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="I23" s="6" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="33.75" customHeight="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="28.5" customHeight="1">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46252.632557870369</v>
+        <v>46253.637916666667</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="33.75" customHeight="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.5" customHeight="1">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46252.670914351853</v>
+        <v>46253.617534722223</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="10" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="33.75" customHeight="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.5" customHeight="1">
       <c r="A26" s="4">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46252.553773148145</v>
+        <v>46253.513298611113</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="28.5" customHeight="1">
+      <c r="A27" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46253.633958333332</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="28.5" customHeight="1">
+      <c r="A28" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46253.595081018517</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="28.5" customHeight="1">
+      <c r="A29" s="4">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46253.692974537036</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="24" customFormat="1" ht="48.75" customHeight="1">
+      <c r="A30" s="17">
+        <v>26</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="17"/>
+      <c r="H30" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K30" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L30" s="23"/>
+      <c r="M30" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="24" customFormat="1" ht="44.25" customHeight="1">
+      <c r="A31" s="17">
+        <v>27</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31" s="17"/>
+      <c r="H31" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="M31" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="24" customFormat="1" ht="71.25" customHeight="1">
+      <c r="A32" s="17">
+        <v>28</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="17"/>
+      <c r="H32" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L32" s="23"/>
+      <c r="M32" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="24" customFormat="1" ht="64.5" customHeight="1">
+      <c r="A33" s="17">
+        <v>29</v>
+      </c>
+      <c r="B33" s="18"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G33" s="17"/>
+      <c r="H33" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L33" s="23"/>
+      <c r="M33" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="24" customFormat="1" ht="57.75" customHeight="1">
+      <c r="A34" s="17">
         <v>30</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="55.5" customHeight="1">
-      <c r="A27" s="23">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="K27" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="L27" s="27"/>
-      <c r="M27" s="28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="66" customHeight="1">
-      <c r="A28" s="23">
-        <v>24</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="J28" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="K28" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="L28" s="27"/>
-      <c r="M28" s="28" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="53.25" customHeight="1">
-      <c r="A29" s="23">
-        <v>25</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="J29" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="K29" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="L29" s="27"/>
-      <c r="M29" s="28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A30" s="23">
-        <v>26</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="K30" s="25" t="s">
+      <c r="B34" s="18"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="G34" s="17"/>
+      <c r="H34" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K34" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L34" s="23"/>
+      <c r="M34" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="24" customFormat="1" ht="48.75" customHeight="1">
+      <c r="A35" s="17">
+        <v>31</v>
+      </c>
+      <c r="B35" s="18"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" s="17"/>
+      <c r="H35" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K35" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L35" s="23"/>
+      <c r="M35" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="L30" s="27"/>
-      <c r="M30" s="28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A31" s="29"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="L31" s="30"/>
-      <c r="M31" s="31"/>
-    </row>
-    <row r="32" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A32" s="32"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="34"/>
+    </row>
+    <row r="36" spans="1:13" s="24" customFormat="1" ht="28.5" customHeight="1">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="L36" s="29"/>
+      <c r="M36" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:L3"/>
-    <mergeCell ref="A31:J32"/>
-    <mergeCell ref="K31:M32"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="E2:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$36</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$28</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="199">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,60 +76,39 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0214</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Anuppur-Janakpur cicuit</t>
-  </si>
-  <si>
-    <t>220KV_ANUPPUR</t>
+    <t>MR2608/0237</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Badnawar - Wonder Cement</t>
+  </si>
+  <si>
+    <t>400KV_BADNAWAR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>F/o disc stringing replacement &amp; other line maint.</t>
-  </si>
-  <si>
-    <t>20-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>20-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Jagdish Prasad Asati</t>
-  </si>
-  <si>
-    <t>9424445533</t>
-  </si>
-  <si>
-    <t>MR2608/0200</t>
+    <t>Work at wonder cement end</t>
+  </si>
+  <si>
+    <t>21-08-2026 06:30:00</t>
+  </si>
+  <si>
+    <t>21-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Pappu Singh Solanki</t>
+  </si>
+  <si>
+    <t>9425820041</t>
+  </si>
+  <si>
+    <t>MR2608/0215</t>
   </si>
   <si>
     <t>Daily</t>
   </si>
   <si>
-    <t>132KV_132 kV Bairagarh-Kurawar line</t>
-  </si>
-  <si>
-    <t>220KV_BAIRAGARH</t>
-  </si>
-  <si>
-    <t>Stringing work</t>
-  </si>
-  <si>
-    <t>19-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Ankit Mehroliya</t>
-  </si>
-  <si>
-    <t>9425804506</t>
-  </si>
-  <si>
-    <t>MR2608/0215</t>
-  </si>
-  <si>
     <t>132KV_132 kV Bargi- Lakhnadaun</t>
   </si>
   <si>
@@ -151,19 +130,22 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>MR2608/0216</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Bina -Borl Ckt 1</t>
+    <t>MR2608/0240</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina -Khurai 1</t>
   </si>
   <si>
     <t>220KV_BINA</t>
   </si>
   <si>
-    <t>f/o disc insulater replacement at loc15T tension</t>
-  </si>
-  <si>
-    <t>20-08-2026 09:00:00</t>
+    <t>f/o disc insulater replacement at loc no18T</t>
+  </si>
+  <si>
+    <t>21-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>21-08-2026 18:00:00</t>
   </si>
   <si>
     <t>Dilip Singh Walkey</t>
@@ -172,37 +154,61 @@
     <t>9425804578</t>
   </si>
   <si>
-    <t>132KV_220 KV Chhatarpur-Tikamgarh line</t>
-  </si>
-  <si>
-    <t>220KV_CHATARPUR</t>
-  </si>
-  <si>
-    <t>installation of ERS</t>
-  </si>
-  <si>
-    <t>pankaj yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2608/0227</t>
-  </si>
-  <si>
-    <t>MR2608/0212</t>
-  </si>
-  <si>
-    <t>50MVA_132/33KV_BHEL_X'mer_2</t>
+    <t>MR2608/0235</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Seoni-Chhindwara Ckt-I</t>
+  </si>
+  <si>
+    <t>220KV_CHHINDWARA</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Jumper cone, Suspension Clamp,A/h,V/d tightening</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2608/0236</t>
+  </si>
+  <si>
+    <t>132KV_40MVA_132/33KV_ABB_X-mer_1</t>
+  </si>
+  <si>
+    <t>132KV_CHICHOLI</t>
+  </si>
+  <si>
+    <t>Replacement of 33 KV B-Phase CT</t>
+  </si>
+  <si>
+    <t>Er. Vishal Kumar Malviya</t>
+  </si>
+  <si>
+    <t>9425804955</t>
+  </si>
+  <si>
+    <t>MR2608/0239</t>
+  </si>
+  <si>
+    <t>50MVA_132/33KV_BHEL_Xmer_1</t>
   </si>
   <si>
     <t>132KV_CHOURAI</t>
   </si>
   <si>
-    <t>Structure painting work.</t>
-  </si>
-  <si>
-    <t>20-08-2026 16:00:00</t>
+    <t>Structure Painting work.</t>
+  </si>
+  <si>
+    <t>21-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>21-08-2026 16:00:00</t>
   </si>
   <si>
     <t>S.K.Okte</t>
@@ -211,15 +217,36 @@
     <t>7587951132</t>
   </si>
   <si>
+    <t>MR2608/0242</t>
+  </si>
+  <si>
+    <t>220KV_160MVA 220/132KV BHEL X-MER-1</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>OLTC Conservator oil filling work</t>
+  </si>
+  <si>
+    <t>21-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>21-08-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>M.K.Choubey</t>
+  </si>
+  <si>
+    <t>9425801424</t>
+  </si>
+  <si>
     <t>MR2608/0180</t>
   </si>
   <si>
     <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
   </si>
   <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
     <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
   </si>
   <si>
@@ -235,13 +262,220 @@
     <t>9425805067</t>
   </si>
   <si>
-    <t>MR2608/0217</t>
-  </si>
-  <si>
-    <t>132KV_132kV Guna Aron Line</t>
-  </si>
-  <si>
-    <t>220KV_GUNA</t>
+    <t>MR2608/0234</t>
+  </si>
+  <si>
+    <t>220KV_220/132kV 200 MVA BBL X-Mer</t>
+  </si>
+  <si>
+    <t>220KV_HANDIYA</t>
+  </si>
+  <si>
+    <t>FOR OLTC OIL SAMPLE COLLECTING PERPOSE</t>
+  </si>
+  <si>
+    <t>21-08-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>K.R. DONGRE</t>
+  </si>
+  <si>
+    <t>9424430754</t>
+  </si>
+  <si>
+    <t>MR2608/0192</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220KV MAIN BUS-I</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF SUPPORT INSULATOR /PI OF EACH U</t>
+  </si>
+  <si>
+    <t>19-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>ATUL PARADKAR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2608/0063</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Erection/Dismentalling of tower &amp; making cut point</t>
+  </si>
+  <si>
+    <t>06-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>26-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2608/0245</t>
+  </si>
+  <si>
+    <t>220KV_220KV Malanpur Auraiya line</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>Insulator Replacement work &amp; Other maint. work</t>
+  </si>
+  <si>
+    <t>Baidyanath Kumar</t>
+  </si>
+  <si>
+    <t>6265588473</t>
+  </si>
+  <si>
+    <t>MR2608/0244</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Malharagarh Single circuit</t>
+  </si>
+  <si>
+    <t>132KV_MALHARGARH</t>
+  </si>
+  <si>
+    <t>For line maintenance work</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2608/0224</t>
+  </si>
+  <si>
+    <t>220KV_220KV MAIN BUS Ist.</t>
+  </si>
+  <si>
+    <t>220KV_MORENA</t>
+  </si>
+  <si>
+    <t>Jumper work of 220KV Main bus Ist.</t>
+  </si>
+  <si>
+    <t>Amit kumar Dhaneliya</t>
+  </si>
+  <si>
+    <t>9425802242</t>
+  </si>
+  <si>
+    <t>MR2608/0229</t>
+  </si>
+  <si>
+    <t>132KV_132 KV MORWA RTS SINGRAULI LINE</t>
+  </si>
+  <si>
+    <t>132KV_MORWA</t>
+  </si>
+  <si>
+    <t>ERECTION OF CT&amp; CB</t>
+  </si>
+  <si>
+    <t>JAGAT NARAYAN SINGH</t>
+  </si>
+  <si>
+    <t>9425802388</t>
+  </si>
+  <si>
+    <t>MR2608/0095</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Budha Line</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>For Crossing Work</t>
+  </si>
+  <si>
+    <t>11-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>MR2608/0093</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
+  </si>
+  <si>
+    <t>For Crossing Wrok</t>
+  </si>
+  <si>
+    <t>MR2608/0094</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
+  </si>
+  <si>
+    <t>MR2608/0096</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Malharagarh Line</t>
+  </si>
+  <si>
+    <t>Hotline Shutdown for crossing work</t>
+  </si>
+  <si>
+    <t>MR2608/0210</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>19-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>25-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2608/0241</t>
+  </si>
+  <si>
+    <t>132KV_132kV Raghogarh Rajgarh line</t>
+  </si>
+  <si>
+    <t>132KV_RAGHOGARH</t>
   </si>
   <si>
     <t>For DF/o replacement work</t>
@@ -253,385 +487,139 @@
     <t>8586865656</t>
   </si>
   <si>
-    <t>MR2608/0192</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220KV MAIN BUS-I</t>
-  </si>
-  <si>
-    <t>400KV_INDORE4</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF SUPPORT INSULATOR /PI OF EACH U</t>
-  </si>
-  <si>
-    <t>19-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>ATUL PARADKAR</t>
-  </si>
-  <si>
-    <t>9425804929</t>
-  </si>
-  <si>
-    <t>MR2608/0211</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA ECE XMER</t>
-  </si>
-  <si>
-    <t>132KV_KHAJURAHO</t>
-  </si>
-  <si>
-    <t>OIL TOPPING WORK</t>
-  </si>
-  <si>
-    <t>20-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>20-08-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>BRAJENDRA SONI</t>
-  </si>
-  <si>
-    <t>9131327770</t>
-  </si>
-  <si>
-    <t>MR2608/0197</t>
-  </si>
-  <si>
-    <t>400KV_400kV Kirnapur Bhilai Line</t>
-  </si>
-  <si>
-    <t>400KV_KIRNAPUR</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Suspension Clamp Tightening Work &amp; Other Line Main</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0219</t>
-  </si>
-  <si>
-    <t>132KV_SHUTDOWN ON 132 KV Mansakra-Panager Feeder AT 132KV S/S Mansakra.</t>
-  </si>
-  <si>
-    <t>132KV_MANSAKRA</t>
-  </si>
-  <si>
-    <t>to attend hot point in Y ph CT stud clamp</t>
-  </si>
-  <si>
-    <t>20-08-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>R P Rawat</t>
-  </si>
-  <si>
-    <t>9907030507</t>
-  </si>
-  <si>
-    <t>MR2608/0220</t>
-  </si>
-  <si>
-    <t>132KV_SHUTDOWN ON 132 KV Mansakra-Sleemnabad Feeder AT 132KV S/S Mansakra.</t>
-  </si>
-  <si>
-    <t>to attend hot point in R ph CT stud Clamp</t>
-  </si>
-  <si>
-    <t>MR2608/0095</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Budha Line</t>
-  </si>
-  <si>
-    <t>220KV_NEEMUCH</t>
-  </si>
-  <si>
-    <t>For Crossing Work</t>
-  </si>
-  <si>
-    <t>11-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2608/0093</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
-  </si>
-  <si>
-    <t>For Crossing Wrok</t>
-  </si>
-  <si>
-    <t>MR2608/0094</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
-  </si>
-  <si>
-    <t>MR2608/0096</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Malharagarh Line</t>
-  </si>
-  <si>
-    <t>Hotline Shutdown for crossing work</t>
-  </si>
-  <si>
-    <t>MR2608/0210</t>
-  </si>
-  <si>
-    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>OPGW LIVE LINE INSTALLATION WORK</t>
-  </si>
-  <si>
-    <t>19-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>25-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2608/0223</t>
-  </si>
-  <si>
-    <t>132KV_132kV Rajmilan - Janakpur Ckt</t>
-  </si>
-  <si>
-    <t>132KV_RAJMILAN</t>
-  </si>
-  <si>
-    <t>Disc Replacement work.</t>
-  </si>
-  <si>
-    <t>20-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>G.L Sahu</t>
-  </si>
-  <si>
-    <t>9425805102</t>
-  </si>
-  <si>
-    <t>MR2608/0221</t>
-  </si>
-  <si>
-    <t>132KV_132kv 63mva xmer bbl</t>
+    <t>MR2608/0230</t>
+  </si>
+  <si>
+    <t>220KV_Sarni-Betul PGCIL</t>
+  </si>
+  <si>
+    <t>220KV_SARNI</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>SHIV KUMAR</t>
+  </si>
+  <si>
+    <t>9425806917</t>
+  </si>
+  <si>
+    <t>MR2608/0243</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Satna - Manpur (TBCB) line</t>
   </si>
   <si>
     <t>220KV_SATNA</t>
   </si>
   <si>
-    <t>For B-ph damage conductor replacement and ryb ph c</t>
-  </si>
-  <si>
-    <t>20-08-2026 10:24:00</t>
-  </si>
-  <si>
-    <t>Poshkar kushwaha</t>
-  </si>
-  <si>
-    <t>9425813990</t>
-  </si>
-  <si>
-    <t>MR2608/0213</t>
-  </si>
-  <si>
-    <t>132KV_63 MVA X-Mer BBL -  I</t>
-  </si>
-  <si>
-    <t>132KV_SEONI1</t>
-  </si>
-  <si>
-    <t>33 KV Half Main Bus S/D For Iso. Repl. Work</t>
-  </si>
-  <si>
-    <t>20-08-2026 11:30:00</t>
-  </si>
-  <si>
-    <t>Arshad Qureshi</t>
-  </si>
-  <si>
-    <t>7648817144</t>
-  </si>
-  <si>
-    <t>MR2608/0222</t>
-  </si>
-  <si>
-    <t>132KV_132kV Sidhi - Mauganj Ckt - I</t>
-  </si>
-  <si>
-    <t>220KV_SIDHI</t>
-  </si>
-  <si>
-    <t>Disc Replacement And Bird Excreta Provided work.</t>
-  </si>
-  <si>
-    <t>MR2608/0218</t>
-  </si>
-  <si>
-    <t>132KV_132 KV SIDHI - IC CKT - IInd  (SIDHI)FDR</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>CONTROL &amp; RELAY PANAL REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>VISHAL BALADHARE</t>
-  </si>
-  <si>
-    <t>9425804690</t>
-  </si>
-  <si>
-    <t>MR2608/0225</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA bbl-make Transformer</t>
-  </si>
-  <si>
-    <t>220KV_TIKAMGARH</t>
-  </si>
-  <si>
-    <t>Oil topping</t>
-  </si>
-  <si>
-    <t>20-08-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>Pushpendra Kumar soni</t>
-  </si>
-  <si>
-    <t>9425806398</t>
+    <t>Replacement of flash over disc insulator string</t>
+  </si>
+  <si>
+    <t>Mr. Ajay kumar Chaurasia</t>
+  </si>
+  <si>
+    <t>9425805081</t>
+  </si>
+  <si>
+    <t>MR2608/0238</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA X-Mer no.2 make Telk</t>
+  </si>
+  <si>
+    <t>132KV_SULTANPUR</t>
+  </si>
+  <si>
+    <t>for collecting of oil sample of OLTC Tank</t>
+  </si>
+  <si>
+    <t>B.L.Lakhore</t>
+  </si>
+  <si>
+    <t>6261378828</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>ok, line to be in service</t>
+  </si>
+  <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>deferred</t>
+  </si>
+  <si>
     <t>sub ld</t>
   </si>
   <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>deferred due to s/d on 132 kV Anuppur-Janakpur cicuit</t>
-  </si>
-  <si>
-    <t>o&amp;m consent to be taken</t>
-  </si>
-  <si>
-    <t>400KV-KIRNAPUR-BHILAI-1</t>
-  </si>
-  <si>
-    <t>220KV-GWALIOR-MALANPUR-2</t>
-  </si>
-  <si>
-    <t>220KV-MORENA-MALANPUR-1</t>
-  </si>
-  <si>
-    <t>220KV-KHANDWA-CHHANERA-2</t>
-  </si>
-  <si>
-    <t>220KV-REWA-REWA-MP-2</t>
-  </si>
-  <si>
-    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
+    <t>ok, through sub ld, 220kv Pandhurna-Kalmeshwar ckt to be in service if required</t>
+  </si>
+  <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>wonder cement consent required</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 21.08.2026</t>
+  </si>
+  <si>
+    <t>220KV-INDORE-UJJAIN-2</t>
+  </si>
+  <si>
+    <t>21-Aug-2026</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
   </si>
   <si>
     <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
-    <t>FOR CONDUCTOR RE-SAGGING WORK IN LOCATION NO.379-388,388-397,397-406 &amp;406-418</t>
-  </si>
-  <si>
     <t>real time</t>
   </si>
   <si>
-    <t>07:00</t>
+    <t>220KV-DAMOH-TIKAMGAD-1</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>MP_SLDC</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,CHATTISGARH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>S/I , SLDC, JABALPUR</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD.20.08.26</t>
+    <t>220KV-SEONI-PG-CHINDWARA-1</t>
+  </si>
+  <si>
+    <t>220KV-BETUL-SARNI-1</t>
+  </si>
+  <si>
+    <t>220KV-REWA-SINDHI-MP-1</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>400KV/220KV SATNA-ICT-3</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AMP Work.Dia to be kept open at both sides</t>
+  </si>
+  <si>
+    <t>S/I SLDC JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -642,7 +630,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -676,13 +664,22 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="&quot;Open Sans&quot;"/>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -702,18 +699,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFF9F9F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -806,46 +803,6 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -863,11 +820,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,6 +862,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -910,66 +883,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1335,60 +1298,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="63" style="11" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="63" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="60.5703125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="51.42578125" customWidth="1"/>
+    <col min="13" max="13" width="56" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="14"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1">
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="1"/>
+      <c r="E2" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="19"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1">
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1401,17 +1364,17 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="36"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1">
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1424,7 +1387,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1442,26 +1405,26 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="15"/>
+      <c r="M4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="28.5" customHeight="1">
+    <row r="5" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46253.523831018516</v>
+        <v>46254.551226851851</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1485,17 +1448,17 @@
       <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="28.5" customHeight="1">
+    <row r="6" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46252.530185185184</v>
+        <v>46253.530636574076</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
@@ -1503,7 +1466,7 @@
       <c r="D6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1519,415 +1482,413 @@
         <v>31</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.5" customHeight="1">
+        <v>34</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A28" si="0">A6+1</f>
+        <f t="shared" ref="A7:A34" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46253.530636574076</v>
+        <v>46254.578402777777</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="10" t="s">
         <v>35</v>
       </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.5" customHeight="1">
+        <v>42</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46253.568344907406</v>
+        <v>46254.516134259262</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="10" t="s">
-        <v>43</v>
+      <c r="E8" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.5" customHeight="1">
+        <v>49</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46253.69804398148</v>
+        <v>46254.52039351852</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="10" t="s">
-        <v>49</v>
+      <c r="E9" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28.5" customHeight="1">
+        <v>55</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46253.47724537037</v>
+        <v>46254.572048611109</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="10" t="s">
-        <v>56</v>
+      <c r="E10" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.5" customHeight="1">
+        <v>63</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46251.488530092596</v>
+        <v>46254.641446759262</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="28.5" customHeight="1">
+        <v>71</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46253.58871527778</v>
+        <v>46251.488530092596</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.5" customHeight="1">
+        <v>78</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46251.642638888887</v>
+        <v>46254.511562500003</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.5" customHeight="1">
+        <v>85</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46253.466724537036</v>
+        <v>46251.642638888887</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="10" t="s">
         <v>86</v>
       </c>
+      <c r="D14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="F14" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28.5" customHeight="1">
+        <v>93</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46252.487083333333</v>
+        <v>46239.682071759256</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="10" t="s">
         <v>94</v>
       </c>
+      <c r="D15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="F15" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>97</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28.5" customHeight="1">
+        <v>101</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46239.682071759256</v>
+        <v>46254.720682870371</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>106</v>
@@ -1935,23 +1896,23 @@
       <c r="L16" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M16" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46253.604664351849</v>
+        <v>46254.661851851852</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>108</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="4" t="s">
         <v>109</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -1964,38 +1925,38 @@
         <v>111</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="J17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="L17" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M17" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46253.606261574074</v>
+        <v>46253.661574074074</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="10" t="s">
+      <c r="F18" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
@@ -2004,52 +1965,50 @@
         <v>117</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="28.5" customHeight="1">
+        <v>119</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46242.584861111114</v>
+        <v>46253.733761574076</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>124</v>
@@ -2057,17 +2016,17 @@
       <c r="L19" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M19" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46242.578993055555</v>
+        <v>46242.584861111114</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>126</v>
@@ -2075,587 +2034,573 @@
       <c r="D20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="4" t="s">
         <v>127</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="28.5" customHeight="1">
+        <v>113</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46242.58148148148</v>
+        <v>46242.578993055555</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>130</v>
+      <c r="E21" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="28.5" customHeight="1">
+        <v>113</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46242.586817129632</v>
+        <v>46242.58148148148</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>132</v>
+      <c r="E22" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="28.5" customHeight="1">
+        <v>113</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46253.337245370371</v>
+        <v>46242.586817129632</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>135</v>
+      <c r="E23" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="28.5" customHeight="1">
+        <v>113</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46253.637916666667</v>
+        <v>46253.337245370371</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="6" t="s">
+      <c r="K24" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="L24" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="L24" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M24" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46253.617534722223</v>
+        <v>46254.620740740742</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="10" t="s">
+      <c r="F25" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="4" t="s">
+      <c r="I25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="L25" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M25" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46253.513298611113</v>
+        <v>46254.460092592592</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="10" t="s">
+      <c r="G26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="I26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="4" t="s">
+      <c r="L26" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="28.5" customHeight="1">
+      <c r="M26" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="5">
-        <v>46253.633958333332</v>
+        <v>46254.642881944441</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D27" s="4"/>
-      <c r="E27" s="10" t="s">
-        <v>164</v>
+      <c r="E27" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A28" s="4">
+        <v>165</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" s="5">
-        <v>46253.595081018517</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="B28" s="21">
+        <v>46254.557349537034</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="10" t="s">
+      <c r="F28" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="7" t="s">
+      <c r="L28" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="L28" s="8" t="s">
+      <c r="M28" s="25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L29" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="M29" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="20">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="M30" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="K31" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L31" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="M31" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="M28" s="4" t="s">
+    </row>
+    <row r="32" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="20">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="I32" s="29" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A29" s="4">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5">
-        <v>46253.692974537036</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J29" s="6" t="s">
+      <c r="J32" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="K32" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L32" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="M32" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" s="24" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A30" s="17">
-        <v>26</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="19" t="s">
+    </row>
+    <row r="33" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I30" s="21" t="s">
+      <c r="I33" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="L33" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="M33" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="K30" s="22" t="s">
+      <c r="I34" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="J34" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="K34" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="M34" s="34" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="L30" s="23"/>
-      <c r="M30" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="24" customFormat="1" ht="44.25" customHeight="1">
-      <c r="A31" s="17">
-        <v>27</v>
-      </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G31" s="17"/>
-      <c r="H31" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I31" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K31" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L31" s="23"/>
-      <c r="M31" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" s="24" customFormat="1" ht="71.25" customHeight="1">
-      <c r="A32" s="17">
-        <v>28</v>
-      </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G32" s="17"/>
-      <c r="H32" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="J32" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L32" s="23"/>
-      <c r="M32" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" s="24" customFormat="1" ht="64.5" customHeight="1">
-      <c r="A33" s="17">
-        <v>29</v>
-      </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G33" s="17"/>
-      <c r="H33" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="J33" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K33" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L33" s="23"/>
-      <c r="M33" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="24" customFormat="1" ht="57.75" customHeight="1">
-      <c r="A34" s="17">
-        <v>30</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="G34" s="17"/>
-      <c r="H34" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="J34" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K34" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L34" s="23"/>
-      <c r="M34" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="24" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A35" s="17">
-        <v>31</v>
-      </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="G35" s="17"/>
-      <c r="H35" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="J35" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="K35" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="L35" s="23"/>
-      <c r="M35" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="24" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A36" s="25"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="26"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -2664,20 +2609,16 @@
       <c r="G36" s="26"/>
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="L36" s="29"/>
-      <c r="M36" s="30"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="E2:I2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$28</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="151">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,31 +76,31 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0237</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Badnawar - Wonder Cement</t>
-  </si>
-  <si>
-    <t>400KV_BADNAWAR</t>
+    <t>MR2608/0250</t>
+  </si>
+  <si>
+    <t>132KV_132kv Anuppur-Janakpur ckt</t>
+  </si>
+  <si>
+    <t>220KV_ANUPPUR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>Work at wonder cement end</t>
-  </si>
-  <si>
-    <t>21-08-2026 06:30:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Pappu Singh Solanki</t>
-  </si>
-  <si>
-    <t>9425820041</t>
+    <t>for Flash over disc replacement &amp; other line work</t>
+  </si>
+  <si>
+    <t>22-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Ashati</t>
+  </si>
+  <si>
+    <t>9424445533</t>
   </si>
   <si>
     <t>MR2608/0215</t>
@@ -130,454 +130,340 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>MR2608/0240</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Bina -Khurai 1</t>
-  </si>
-  <si>
-    <t>220KV_BINA</t>
-  </si>
-  <si>
-    <t>f/o disc insulater replacement at loc no18T</t>
-  </si>
-  <si>
-    <t>21-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Dilip Singh Walkey</t>
-  </si>
-  <si>
-    <t>9425804578</t>
-  </si>
-  <si>
-    <t>MR2608/0235</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Seoni-Chhindwara Ckt-I</t>
-  </si>
-  <si>
-    <t>220KV_CHHINDWARA</t>
+    <t>MR2608/0249</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Bina Pichhore</t>
+  </si>
+  <si>
+    <t>400KV_BINA4</t>
+  </si>
+  <si>
+    <t>Flash over disc replacement work.</t>
+  </si>
+  <si>
+    <t>22-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Satish Kumar Bhagat</t>
+  </si>
+  <si>
+    <t>9425806916</t>
+  </si>
+  <si>
+    <t>MR2608/0251</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Ajaygarh-Chhatarpur (TBCB) 1</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>Tower erection work</t>
+  </si>
+  <si>
+    <t>22-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>23-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2608/0180</t>
+  </si>
+  <si>
+    <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
+  </si>
+  <si>
+    <t>18-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>M.M. BAIG</t>
+  </si>
+  <si>
+    <t>9425805067</t>
+  </si>
+  <si>
+    <t>MR2608/0254</t>
+  </si>
+  <si>
+    <t>132KV_132kv Gwalior(2) - Dabra Line</t>
+  </si>
+  <si>
+    <t>220KV_GWALIOR-II</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2608/0063</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Erection/Dismentalling of tower &amp; making cut point</t>
+  </si>
+  <si>
+    <t>06-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>26-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>MR2608/0207</t>
+  </si>
+  <si>
+    <t>132KV_132kV Mandla-Bichhiya Line</t>
+  </si>
+  <si>
+    <t>132KV_MANDLA</t>
+  </si>
+  <si>
+    <t>OPGW Stringing On Hot Line Work &amp; Other Line Maint</t>
+  </si>
+  <si>
+    <t>31-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2608/0095</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Budha Line</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>For Crossing Work</t>
+  </si>
+  <si>
+    <t>11-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2608/0093</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
+  </si>
+  <si>
+    <t>For Crossing Wrok</t>
+  </si>
+  <si>
+    <t>MR2608/0094</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
+  </si>
+  <si>
+    <t>MR2608/0096</t>
+  </si>
+  <si>
+    <t>132KV_132KV Neemuch Malharagarh Line</t>
+  </si>
+  <si>
+    <t>Hotline Shutdown for crossing work</t>
+  </si>
+  <si>
+    <t>MR2608/0210</t>
+  </si>
+  <si>
+    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>OPGW LIVE LINE INSTALLATION WORK</t>
+  </si>
+  <si>
+    <t>19-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>25-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2608/0203</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Prithvipur-Jatara DCSS Line</t>
+  </si>
+  <si>
+    <t>132KV_PRITHVIPUR</t>
+  </si>
+  <si>
+    <t>22-08-2026 08:30:00</t>
+  </si>
+  <si>
+    <t>MR2608/0253</t>
+  </si>
+  <si>
+    <t>132KV_132kv Main Bus</t>
+  </si>
+  <si>
+    <t>132KV_SAGAR1</t>
+  </si>
+  <si>
+    <t>132kv main bus hot point attending work</t>
+  </si>
+  <si>
+    <t>22-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>SK HAJARI</t>
+  </si>
+  <si>
+    <t>9425620010</t>
+  </si>
+  <si>
+    <t>MR2608/0252</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA X-MER BHEL IInd</t>
+  </si>
+  <si>
+    <t>220KV_SARNI</t>
+  </si>
+  <si>
+    <t>For oil Leakage attending work</t>
+  </si>
+  <si>
+    <t>22-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Anup kumar Dange</t>
+  </si>
+  <si>
+    <t>9425814073</t>
+  </si>
+  <si>
+    <t>MR2608/0255</t>
+  </si>
+  <si>
+    <t>132KV_132kv 63mva xmer make BBL</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
   </si>
   <si>
     <t>OCCM-MP</t>
   </si>
   <si>
-    <t>Jumper cone, Suspension Clamp,A/h,V/d tightening</t>
-  </si>
-  <si>
-    <t>A.M.Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2608/0236</t>
-  </si>
-  <si>
-    <t>132KV_40MVA_132/33KV_ABB_X-mer_1</t>
-  </si>
-  <si>
-    <t>132KV_CHICHOLI</t>
-  </si>
-  <si>
-    <t>Replacement of 33 KV B-Phase CT</t>
-  </si>
-  <si>
-    <t>Er. Vishal Kumar Malviya</t>
-  </si>
-  <si>
-    <t>9425804955</t>
-  </si>
-  <si>
-    <t>MR2608/0239</t>
-  </si>
-  <si>
-    <t>50MVA_132/33KV_BHEL_Xmer_1</t>
-  </si>
-  <si>
-    <t>132KV_CHOURAI</t>
-  </si>
-  <si>
-    <t>Structure Painting work.</t>
-  </si>
-  <si>
-    <t>21-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>S.K.Okte</t>
-  </si>
-  <si>
-    <t>7587951132</t>
-  </si>
-  <si>
-    <t>MR2608/0242</t>
-  </si>
-  <si>
-    <t>220KV_160MVA 220/132KV BHEL X-MER-1</t>
-  </si>
-  <si>
-    <t>220KV_DAMOH</t>
-  </si>
-  <si>
-    <t>OLTC Conservator oil filling work</t>
-  </si>
-  <si>
-    <t>21-08-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>21-08-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>M.K.Choubey</t>
-  </si>
-  <si>
-    <t>9425801424</t>
-  </si>
-  <si>
-    <t>MR2608/0180</t>
-  </si>
-  <si>
-    <t>132KV_132KV DAMOH-PATERA LINE IST&amp;IIND CKT</t>
-  </si>
-  <si>
-    <t>PTW FOR LIVE LINE OPGW INSTALLATION</t>
-  </si>
-  <si>
-    <t>18-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>M.M. BAIG</t>
-  </si>
-  <si>
-    <t>9425805067</t>
-  </si>
-  <si>
-    <t>MR2608/0234</t>
-  </si>
-  <si>
-    <t>220KV_220/132kV 200 MVA BBL X-Mer</t>
-  </si>
-  <si>
-    <t>220KV_HANDIYA</t>
-  </si>
-  <si>
-    <t>FOR OLTC OIL SAMPLE COLLECTING PERPOSE</t>
-  </si>
-  <si>
-    <t>21-08-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>K.R. DONGRE</t>
-  </si>
-  <si>
-    <t>9424430754</t>
-  </si>
-  <si>
-    <t>MR2608/0192</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220KV MAIN BUS-I</t>
-  </si>
-  <si>
-    <t>400KV_INDORE4</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF SUPPORT INSULATOR /PI OF EACH U</t>
-  </si>
-  <si>
-    <t>19-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>ATUL PARADKAR</t>
-  </si>
-  <si>
-    <t>9425804929</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0245</t>
-  </si>
-  <si>
-    <t>220KV_220KV Malanpur Auraiya line</t>
-  </si>
-  <si>
-    <t>220KV_MALANPUR</t>
-  </si>
-  <si>
-    <t>Insulator Replacement work &amp; Other maint. work</t>
-  </si>
-  <si>
-    <t>Baidyanath Kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
-  </si>
-  <si>
-    <t>MR2608/0244</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Malharagarh Single circuit</t>
-  </si>
-  <si>
-    <t>132KV_MALHARGARH</t>
-  </si>
-  <si>
-    <t>For line maintenance work</t>
-  </si>
-  <si>
-    <t>Gaurav Goyal</t>
-  </si>
-  <si>
-    <t>9425805120</t>
-  </si>
-  <si>
-    <t>MR2608/0224</t>
-  </si>
-  <si>
-    <t>220KV_220KV MAIN BUS Ist.</t>
-  </si>
-  <si>
-    <t>220KV_MORENA</t>
-  </si>
-  <si>
-    <t>Jumper work of 220KV Main bus Ist.</t>
-  </si>
-  <si>
-    <t>Amit kumar Dhaneliya</t>
-  </si>
-  <si>
-    <t>9425802242</t>
-  </si>
-  <si>
-    <t>MR2608/0229</t>
-  </si>
-  <si>
-    <t>132KV_132 KV MORWA RTS SINGRAULI LINE</t>
-  </si>
-  <si>
-    <t>132KV_MORWA</t>
-  </si>
-  <si>
-    <t>ERECTION OF CT&amp; CB</t>
-  </si>
-  <si>
-    <t>JAGAT NARAYAN SINGH</t>
-  </si>
-  <si>
-    <t>9425802388</t>
-  </si>
-  <si>
-    <t>MR2608/0095</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Budha Line</t>
-  </si>
-  <si>
-    <t>220KV_NEEMUCH</t>
-  </si>
-  <si>
-    <t>For Crossing Work</t>
-  </si>
-  <si>
-    <t>11-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>22-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>MR2608/0093</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
-  </si>
-  <si>
-    <t>For Crossing Wrok</t>
-  </si>
-  <si>
-    <t>MR2608/0094</t>
-  </si>
-  <si>
-    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
-  </si>
-  <si>
-    <t>MR2608/0096</t>
-  </si>
-  <si>
-    <t>132KV_132KV Neemuch Malharagarh Line</t>
-  </si>
-  <si>
-    <t>Hotline Shutdown for crossing work</t>
-  </si>
-  <si>
-    <t>MR2608/0210</t>
-  </si>
-  <si>
-    <t>132KV_132 KV PANAGAR - DHEEMARKHEDA LINE</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>OPGW LIVE LINE INSTALLATION WORK</t>
-  </si>
-  <si>
-    <t>19-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>25-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>MANOJ KUMAR TIWARI</t>
-  </si>
-  <si>
-    <t>9425804993</t>
-  </si>
-  <si>
-    <t>MR2608/0241</t>
-  </si>
-  <si>
-    <t>132KV_132kV Raghogarh Rajgarh line</t>
-  </si>
-  <si>
-    <t>132KV_RAGHOGARH</t>
-  </si>
-  <si>
-    <t>For DF/o replacement work</t>
-  </si>
-  <si>
-    <t>Akhilesh Singh</t>
-  </si>
-  <si>
-    <t>8586865656</t>
-  </si>
-  <si>
-    <t>MR2608/0230</t>
-  </si>
-  <si>
-    <t>220KV_Sarni-Betul PGCIL</t>
-  </si>
-  <si>
-    <t>220KV_SARNI</t>
-  </si>
-  <si>
-    <t>Line Maintenance work</t>
-  </si>
-  <si>
-    <t>SHIV KUMAR</t>
-  </si>
-  <si>
-    <t>9425806917</t>
-  </si>
-  <si>
-    <t>MR2608/0243</t>
-  </si>
-  <si>
-    <t>220KV_220 kv Satna - Manpur (TBCB) line</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>Replacement of flash over disc insulator string</t>
-  </si>
-  <si>
-    <t>Mr. Ajay kumar Chaurasia</t>
-  </si>
-  <si>
-    <t>9425805081</t>
-  </si>
-  <si>
-    <t>MR2608/0238</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA X-Mer no.2 make Telk</t>
-  </si>
-  <si>
-    <t>132KV_SULTANPUR</t>
-  </si>
-  <si>
-    <t>for collecting of oil sample of OLTC Tank</t>
-  </si>
-  <si>
-    <t>B.L.Lakhore</t>
-  </si>
-  <si>
-    <t>6261378828</t>
+    <t>For B-ph CB top jumper clamp towards Main Bus isol</t>
+  </si>
+  <si>
+    <t>22-08-2026 10:28:00</t>
+  </si>
+  <si>
+    <t>22-08-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2608/0178</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Chhatarpur-Tikamgarh</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>ERS installation work for modification</t>
+  </si>
+  <si>
+    <t>24-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>pankaj Yadav</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>ok, through sub ld</t>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
   </si>
   <si>
     <t>deferred</t>
   </si>
   <si>
-    <t>sub ld</t>
-  </si>
-  <si>
-    <t>ok, through sub ld, 220kv Pandhurna-Kalmeshwar ckt to be in service if required</t>
-  </si>
-  <si>
-    <t>RTS consent required</t>
-  </si>
-  <si>
-    <t>o&amp;m consent required</t>
-  </si>
-  <si>
-    <t>wonder cement consent required</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 21.08.2026</t>
-  </si>
-  <si>
-    <t>220KV-INDORE-UJJAIN-2</t>
-  </si>
-  <si>
-    <t>21-Aug-2026</t>
-  </si>
-  <si>
-    <t>06:00</t>
+    <t>ok, line to be in service, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>ok, is modification to be done in MPPTCL, Pl clarify?</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 22.08.2026</t>
+  </si>
+  <si>
+    <t>220KV-KHANDWA-CHHANERA-1</t>
+  </si>
+  <si>
+    <t>22-Aug-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
   </si>
   <si>
     <t>18:00</t>
@@ -587,36 +473,6 @@
   </si>
   <si>
     <t>real time</t>
-  </si>
-  <si>
-    <t>220KV-DAMOH-TIKAMGAD-1</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>220KV-SEONI-PG-CHINDWARA-1</t>
-  </si>
-  <si>
-    <t>220KV-BETUL-SARNI-1</t>
-  </si>
-  <si>
-    <t>220KV-REWA-SINDHI-MP-1</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>400KV/220KV SATNA-ICT-3</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>AMP Work.Dia to be kept open at both sides</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
@@ -665,7 +521,7 @@
     </font>
     <font>
       <b/>
-      <sz val="36"/>
+      <sz val="26"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -699,7 +555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,7 +566,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -820,24 +676,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -863,17 +706,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -907,32 +741,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1297,59 +1117,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="63" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="60.5703125" customWidth="1"/>
+    <col min="8" max="8" width="49.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="56" style="12" customWidth="1"/>
+    <col min="13" max="13" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="15"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="1"/>
+      <c r="E2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="9"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1372,7 +1191,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="9"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1405,11 +1224,11 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="15"/>
-      <c r="M4" s="10" t="s">
+      <c r="L4" s="12"/>
+      <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1418,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46254.551226851851</v>
+        <v>46255.549120370371</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1448,8 +1267,8 @@
       <c r="L5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>180</v>
+      <c r="M5" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1490,17 +1309,17 @@
       <c r="L6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="11" t="s">
-        <v>172</v>
+      <c r="M6" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A34" si="0">A6+1</f>
+        <f t="shared" ref="A7:A22" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46254.578402777777</v>
+        <v>46255.487557870372</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
@@ -1519,19 +1338,19 @@
         <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>172</v>
+      <c r="M7" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1540,29 +1359,31 @@
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46254.516134259262</v>
+        <v>46255.556446759256</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>48</v>
@@ -1570,8 +1391,8 @@
       <c r="L8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>172</v>
+      <c r="M8" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1580,12 +1401,14 @@
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46254.52039351852</v>
+        <v>46251.488530092596</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E9" s="4" t="s">
         <v>51</v>
       </c>
@@ -1599,19 +1422,19 @@
         <v>53</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>176</v>
+        <v>57</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1620,29 +1443,29 @@
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46254.572048611109</v>
+        <v>46255.650347222225</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>62</v>
@@ -1650,8 +1473,8 @@
       <c r="L10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>179</v>
+      <c r="M10" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1660,12 +1483,14 @@
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46254.641446759262</v>
+        <v>46239.682071759256</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>65</v>
       </c>
@@ -1685,13 +1510,13 @@
         <v>69</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>172</v>
+        <v>63</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1700,40 +1525,40 @@
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46251.488530092596</v>
+        <v>46252.611527777779</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="K12" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="L12" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>173</v>
+      <c r="M12" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1742,38 +1567,40 @@
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46254.511562500003</v>
+        <v>46242.584861111114</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="L13" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>174</v>
+      <c r="M13" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1782,40 +1609,40 @@
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46251.642638888887</v>
+        <v>46242.578993055555</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1824,40 +1651,40 @@
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46239.682071759256</v>
+        <v>46242.58148148148</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1866,38 +1693,40 @@
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46254.720682870371</v>
+        <v>46242.586817129632</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>89</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E16" s="4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>175</v>
+        <v>83</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1906,38 +1735,40 @@
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46254.661851851852</v>
+        <v>46253.337245370371</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>92</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>176</v>
+        <v>99</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1946,38 +1777,40 @@
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46253.661574074074</v>
+        <v>46252.556817129633</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M18" s="11" t="s">
-        <v>174</v>
+        <v>49</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,38 +1819,38 @@
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46253.733761574076</v>
+        <v>46255.625347222223</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>121</v>
+      <c r="E19" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>178</v>
+        <v>112</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -2026,40 +1859,38 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46242.584861111114</v>
+        <v>46255.600983796299</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>176</v>
+        <v>119</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -2068,557 +1899,135 @@
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46242.578993055555</v>
+        <v>46255.663252314815</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>27</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>173</v>
+      <c r="M21" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="5">
-        <v>46242.58148148148</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="B22" s="18">
+        <v>46250.648402777777</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M22" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <f t="shared" si="0"/>
+      <c r="H22" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="26">
         <v>19</v>
       </c>
-      <c r="B23" s="5">
-        <v>46242.586817129632</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46253.337245370371</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="6" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I23" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="J23" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="K23" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="M24" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46254.620740740742</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="M23" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="4" t="s">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46254.460092592592</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46254.642881944441</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" s="21">
-        <v>46254.557349537034</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="L28" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="M28" s="25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I29" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="K29" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L29" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="M29" s="30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I30" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="J30" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="M30" s="30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="J31" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="K31" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L31" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="M31" s="30" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="J32" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="M32" s="31" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="K33" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="L33" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="M33" s="30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="J34" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="L34" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="M34" s="34" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="35" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$13</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="129">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -106,66 +106,135 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>MR2608/0251</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Ajaygarh-Chhatarpur (TBCB) 1</t>
+    <t>MR2608/0267</t>
+  </si>
+  <si>
+    <t>220KV_220 Kv Chhatarpur ajaygarh 1</t>
   </si>
   <si>
     <t>220KV_CHATARPUR</t>
   </si>
   <si>
-    <t>Tower erection work</t>
+    <t>For ERS INSTALLATION IN MODIFICATION AND SHIFTING</t>
+  </si>
+  <si>
+    <t>24-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>24-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2608/0257</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Seoni-Chhindwara Ckt-II</t>
+  </si>
+  <si>
+    <t>220KV_CHHINDWARA</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Jumper cone, Suspension Clamp,A/h,V/d Tightening</t>
+  </si>
+  <si>
+    <t>24-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>A.M.Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2608/0256</t>
+  </si>
+  <si>
+    <t>220KV_JAITPURA ASHTA CKT-1</t>
+  </si>
+  <si>
+    <t>220KV_INDORE-II (JETPURA)</t>
+  </si>
+  <si>
+    <t>JUMPER CONE TIGHTING OTHER MAINTENANCE WORK.</t>
+  </si>
+  <si>
+    <t>24-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2608/0268</t>
+  </si>
+  <si>
+    <t>400KV_100 MVA 400/132 BHEL XMER 1</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>PRE MANSOON MAINTENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>24-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>SANDEEP DAMAHE</t>
+  </si>
+  <si>
+    <t>9425805009</t>
+  </si>
+  <si>
+    <t>MR2608/0063</t>
+  </si>
+  <si>
+    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
+  </si>
+  <si>
+    <t>220KV_MAHALGAON</t>
+  </si>
+  <si>
+    <t>Erection/Dismentalling of tower &amp; making cut point</t>
+  </si>
+  <si>
+    <t>06-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>26-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar</t>
+  </si>
+  <si>
+    <t>9425805317</t>
+  </si>
+  <si>
+    <t>MR2608/0207</t>
+  </si>
+  <si>
+    <t>132KV_132kV Mandla-Bichhiya Line</t>
+  </si>
+  <si>
+    <t>132KV_MANDLA</t>
+  </si>
+  <si>
+    <t>OPGW Stringing On Hot Line Work &amp; Other Line Maint</t>
   </si>
   <si>
     <t>22-08-2026 07:00:00</t>
   </si>
   <si>
-    <t>23-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Yadav</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0207</t>
-  </si>
-  <si>
-    <t>132KV_132kV Mandla-Bichhiya Line</t>
-  </si>
-  <si>
-    <t>132KV_MANDLA</t>
-  </si>
-  <si>
-    <t>OPGW Stringing On Hot Line Work &amp; Other Line Maint</t>
-  </si>
-  <si>
     <t>31-08-2026 19:00:00</t>
   </si>
   <si>
@@ -175,28 +244,28 @@
     <t>9425807264</t>
   </si>
   <si>
-    <t>MR2608/0259</t>
-  </si>
-  <si>
-    <t>132KV_132kv sidhi- Mauganj circuit -1</t>
-  </si>
-  <si>
-    <t>132KV_MAUGANJ</t>
-  </si>
-  <si>
-    <t>maintance work</t>
-  </si>
-  <si>
-    <t>23-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>23-08-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>G.L. SAHU</t>
-  </si>
-  <si>
-    <t>9425805102</t>
+    <t>MR2608/0264</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Nagra-Nagda  -I</t>
+  </si>
+  <si>
+    <t>220KV_NAGRA</t>
+  </si>
+  <si>
+    <t>TCS Relay Chang</t>
+  </si>
+  <si>
+    <t>24-08-2026 12:30:00</t>
+  </si>
+  <si>
+    <t>24-08-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Shailendra Borasi</t>
+  </si>
+  <si>
+    <t>9907246485</t>
   </si>
   <si>
     <t>MR2608/0210</t>
@@ -223,45 +292,48 @@
     <t>9425804993</t>
   </si>
   <si>
-    <t>MR2608/0203</t>
+    <t>MR2608/0269</t>
+  </si>
+  <si>
+    <t>132KV_132 kv sabalgarh vijaypur ckt 2</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>for line maintananace work.</t>
+  </si>
+  <si>
+    <t>Er. Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2608/0266</t>
+  </si>
+  <si>
+    <t>220KV_220kv Satna -Ajaygarh line</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For B-ph CB bottom jumpher clamp attending Red hot</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2608/0178</t>
   </si>
   <si>
     <t>Continuous</t>
   </si>
   <si>
-    <t>132KV_132 kV Prithvipur-Jatara DCSS Line</t>
-  </si>
-  <si>
-    <t>132KV_PRITHVIPUR</t>
-  </si>
-  <si>
-    <t>22-08-2026 08:30:00</t>
-  </si>
-  <si>
-    <t>MR2608/0258</t>
-  </si>
-  <si>
-    <t>132KV_132 KV MAIN BUS</t>
-  </si>
-  <si>
-    <t>132KV_RAHATGARH</t>
-  </si>
-  <si>
-    <t>NEW TRANSFORMER HIGH BUS STRINGING WORK</t>
-  </si>
-  <si>
-    <t>23-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>BHUPENDRA KHAWSE</t>
-  </si>
-  <si>
-    <t>9074588975</t>
-  </si>
-  <si>
-    <t>MR2608/0178</t>
-  </si>
-  <si>
     <t>220KV_220 KV Chhatarpur-Tikamgarh</t>
   </si>
   <si>
@@ -271,22 +343,73 @@
     <t>ERS installation work for modification</t>
   </si>
   <si>
-    <t>24-08-2026 18:00:00</t>
-  </si>
-  <si>
     <t>pankaj Yadav</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>ok, through sub ld</t>
+  </si>
+  <si>
+    <t>real time as per load management</t>
+  </si>
+  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>deferred</t>
   </si>
   <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 23.08.2026</t>
+    <t>deferred due to s/d on 220kv Satna -Ajaygarh line</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-SEONI-PG-CHINDWARA-2</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-1</t>
+  </si>
+  <si>
+    <t>220KV-REWA-SINDHI-MP-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>24-Aug-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>S/I ,SLDC MPPTCL JBP</t>
+  </si>
+  <si>
+    <t>OCCM-WR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.24.08.26</t>
   </si>
 </sst>
 </file>
@@ -297,7 +420,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -312,12 +435,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -328,9 +445,27 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -348,7 +483,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,48 +552,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,492 +988,777 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="63" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.140625" customWidth="1"/>
+    <col min="8" max="8" width="55.5703125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="40.85546875" customWidth="1"/>
+    <col min="13" max="13" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="17"/>
+    </row>
+    <row r="2" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>46257</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="13" t="s">
+      <c r="B2" s="22">
+        <v>46258</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+    </row>
+    <row r="3" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+    </row>
+    <row r="4" spans="1:13" s="7" customFormat="1" ht="42" customHeight="1">
+      <c r="A4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="21"/>
+      <c r="M4" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46253.530636574076</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46257.521423611113</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46256.563090277778</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46256.487476851849</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46257.523831018516</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46239.682071759256</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46252.611527777779</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46257.418564814812</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46253.337245370371</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="L13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="B14" s="3">
+        <v>46257.630115740743</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A15" s="2">
         <v>11</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="B15" s="3">
+        <v>46257.495104166665</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30.75" customHeight="1">
+      <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="B16" s="3">
+        <v>46250.648402777777</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="25.5">
+      <c r="A17" s="2">
         <v>13</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="B17" s="3">
+        <v>46257.495104166665</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="51">
+      <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="B18" s="3">
+        <v>46257.495104166665</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="51">
+      <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="3" t="s">
+      <c r="B19" s="3">
+        <v>46257.495104166665</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="51">
+      <c r="A20" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="24" customHeight="1">
-      <c r="A5" s="4">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46253.530636574076</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="24" customHeight="1">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46255.556446759256</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1">
-      <c r="A7" s="4">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46239.682071759256</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1">
-      <c r="A8" s="4">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46252.611527777779</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="24" customHeight="1">
-      <c r="A9" s="4">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46256.686678240738</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24" customHeight="1">
-      <c r="A10" s="4">
-        <v>1</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46253.337245370371</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46252.556817129633</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="24" customHeight="1">
-      <c r="A12" s="4">
-        <v>7</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46256.63857638889</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="24" customHeight="1">
-      <c r="A13" s="4">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46250.648402777777</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="B20" s="3">
+        <v>46257.495104166665</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,20 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$14</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="142">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,43 +87,301 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0292</t>
-  </si>
-  <si>
-    <t>132KV_132 KV ASHTA ARNIYAKALA CKT-2</t>
-  </si>
-  <si>
-    <t>400KV_ASHTA4</t>
+    <t>MR2608/0310</t>
+  </si>
+  <si>
+    <t>220KV_220kv Amarkantak-Sidhi ckt</t>
+  </si>
+  <si>
+    <t>220KV_AMARKANTAK</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>LINE MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>26-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>NITIN RESHWAL</t>
-  </si>
-  <si>
-    <t>9425804890</t>
-  </si>
-  <si>
-    <t>MR2608/0291</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Chichli Barman Line</t>
-  </si>
-  <si>
-    <t>132KV_BARMAN</t>
-  </si>
-  <si>
-    <t>Flashover Disc replacement work at Loc.No.63/R Ph</t>
+    <t>for flash over disc replacement &amp; other line work</t>
+  </si>
+  <si>
+    <t>27-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-08-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Ashathi</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2608/0311</t>
+  </si>
+  <si>
+    <t>220KV_220kV Amarkantak-Shahdol ckt</t>
+  </si>
+  <si>
+    <t>27-08-2026 14:30:00</t>
+  </si>
+  <si>
+    <t>27-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Asati</t>
+  </si>
+  <si>
+    <t>MR2608/0287</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Bhopal-Shujalpur Ckt I &amp; II</t>
+  </si>
+  <si>
+    <t>400KV_BHOPAL4</t>
+  </si>
+  <si>
+    <t>Stringing work</t>
+  </si>
+  <si>
+    <t>26-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>28-08-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Ankit Mehroliya</t>
+  </si>
+  <si>
+    <t>9425804506</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Tikamgarh-Chhatarpur line</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>installation of ERS and tower errection below line</t>
+  </si>
+  <si>
+    <t>02-09-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>PANKAJ YADAV</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2608/0315</t>
+  </si>
+  <si>
+    <t>MR2608/0294</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Ajaygarh-Chhatarpur (TBCB) 2 line</t>
+  </si>
+  <si>
+    <t>Tower erection work</t>
+  </si>
+  <si>
+    <t>26-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>MR2608/0295</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Tikamgrah Chhatarpur line</t>
+  </si>
+  <si>
+    <t>pANKAJ YADAV</t>
+  </si>
+  <si>
+    <t>MR2608/0318</t>
+  </si>
+  <si>
+    <t>220KV_220KV Daloda Mandsaur Circuit Ist</t>
+  </si>
+  <si>
+    <t>220KV_DALODA</t>
+  </si>
+  <si>
+    <t>Hotline shutdown for crossing work</t>
+  </si>
+  <si>
+    <t>27-08-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>05-09-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Gaurav Goyal</t>
+  </si>
+  <si>
+    <t>9425805120</t>
+  </si>
+  <si>
+    <t>MR2608/0319</t>
+  </si>
+  <si>
+    <t>220KV_220KV Daloda Mandsaur Circuit IInd</t>
+  </si>
+  <si>
+    <t>MR2608/0312</t>
+  </si>
+  <si>
+    <t>220KV_220KV ITARSI-BARWAHA LINE</t>
+  </si>
+  <si>
+    <t>220KV_ITARSI</t>
+  </si>
+  <si>
+    <t>FLASHOVER DISC REPLACEMENT</t>
+  </si>
+  <si>
+    <t>27-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>R.N. PARTE</t>
+  </si>
+  <si>
+    <t>9425804701</t>
+  </si>
+  <si>
+    <t>MR2608/0288</t>
+  </si>
+  <si>
+    <t>400KV_400kV Kirnapur Seoni Line</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Work for tightening of S/C, A/H, C/R &amp; other work</t>
+  </si>
+  <si>
+    <t>27-08-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2608/0321</t>
+  </si>
+  <si>
+    <t>220KV_220KV KUKSHI-JULWANIYA-II LINE</t>
+  </si>
+  <si>
+    <t>220KV_KUKSHI</t>
+  </si>
+  <si>
+    <t>RELAY TESTING WORK</t>
+  </si>
+  <si>
+    <t>27-08-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>MANOJ RANDHA</t>
+  </si>
+  <si>
+    <t>9425820034</t>
+  </si>
+  <si>
+    <t>MR2608/0207</t>
+  </si>
+  <si>
+    <t>132KV_132kV Mandla-Bichhiya Line</t>
+  </si>
+  <si>
+    <t>132KV_MANDLA</t>
+  </si>
+  <si>
+    <t>OPGW Stringing On Hot Line Work &amp; Other Line Maint</t>
+  </si>
+  <si>
+    <t>22-08-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>31-08-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2608/0308</t>
+  </si>
+  <si>
+    <t>220KV_220 KV NAGRA AMBA I</t>
+  </si>
+  <si>
+    <t>220KV_NAGRA</t>
+  </si>
+  <si>
+    <t>TCs Relay Replace</t>
+  </si>
+  <si>
+    <t>27-08-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>27-08-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Sailendra Borasi</t>
+  </si>
+  <si>
+    <t>9907246485</t>
+  </si>
+  <si>
+    <t>MR2608/0309</t>
+  </si>
+  <si>
+    <t>220KV_220 KV NAGRA AMBA II</t>
+  </si>
+  <si>
+    <t>27-08-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>220KV_220 KV NAGRA NAGDA II</t>
+  </si>
+  <si>
+    <t>27-08-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>MR2608/0303</t>
+  </si>
+  <si>
+    <t>MR2608/0320</t>
+  </si>
+  <si>
+    <t>132KV_132kV Sidhi - Sagra (Rewa - 2) Circuit</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Line Maintenance Work</t>
+  </si>
+  <si>
+    <t>G.L Sahu</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>132KV_TENDUKHEDA</t>
   </si>
   <si>
     <t>Ashish Kumar</t>
@@ -121,221 +390,76 @@
     <t>9425805935</t>
   </si>
   <si>
-    <t>MR2608/0287</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Bhopal-Shujalpur Ckt I &amp; II</t>
-  </si>
-  <si>
-    <t>400KV_BHOPAL4</t>
-  </si>
-  <si>
-    <t>Stringing work</t>
-  </si>
-  <si>
-    <t>26-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>28-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Ankit Mehroliya</t>
-  </si>
-  <si>
-    <t>9425804506</t>
-  </si>
-  <si>
-    <t>MR2608/0290</t>
-  </si>
-  <si>
-    <t>132KV_132KV BINA -MEHLUWA CHOURAHA [TBCB]</t>
-  </si>
-  <si>
-    <t>220KV_BINA</t>
-  </si>
-  <si>
-    <t>f/o disc insulater replacement at loc no37M</t>
-  </si>
-  <si>
-    <t>26-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Dilip Singh Walkey</t>
-  </si>
-  <si>
-    <t>9425804578</t>
-  </si>
-  <si>
-    <t>MR2608/0294</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Ajaygarh-Chhatarpur (TBCB) 2 line</t>
-  </si>
-  <si>
-    <t>220KV_CHATARPUR</t>
-  </si>
-  <si>
-    <t>Tower erection work</t>
-  </si>
-  <si>
-    <t>26-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>27-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>PANKAJ YADAV</t>
-  </si>
-  <si>
-    <t>9406713326</t>
-  </si>
-  <si>
-    <t>MR2608/0295</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Tikamgrah Chhatarpur line</t>
-  </si>
-  <si>
-    <t>pANKAJ YADAV</t>
-  </si>
-  <si>
-    <t>MR2608/0063</t>
-  </si>
-  <si>
-    <t>220KV_220kV Mahalgaon - Datia &amp; 220kV Mahalgaon - PGCIL ckt -III</t>
-  </si>
-  <si>
-    <t>220KV_MAHALGAON</t>
-  </si>
-  <si>
-    <t>Erection/Dismentalling of tower &amp; making cut point</t>
-  </si>
-  <si>
-    <t>06-08-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj Kumar</t>
-  </si>
-  <si>
-    <t>9425805317</t>
-  </si>
-  <si>
-    <t>MR2608/0289</t>
-  </si>
-  <si>
-    <t>220KV_220kv Malanpur-Auraiya</t>
-  </si>
-  <si>
-    <t>220KV_MALANPUR</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Line Maintenance work</t>
-  </si>
-  <si>
-    <t>Baidyanath Kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
-  </si>
-  <si>
-    <t>MR2608/0207</t>
-  </si>
-  <si>
-    <t>132KV_132kV Mandla-Bichhiya Line</t>
-  </si>
-  <si>
-    <t>132KV_MANDLA</t>
-  </si>
-  <si>
-    <t>OPGW Stringing On Hot Line Work &amp; Other Line Maint</t>
-  </si>
-  <si>
-    <t>22-08-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>31-08-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2608/0293</t>
-  </si>
-  <si>
-    <t>220KV_160 Mva X-mer-II BHEL</t>
-  </si>
-  <si>
-    <t>220KV_NIMRANI</t>
-  </si>
-  <si>
-    <t>For Oil Leakage attendig work of 132 Kv Y Phase CT</t>
-  </si>
-  <si>
-    <t>26-08-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Er Pradip Patidar</t>
-  </si>
-  <si>
-    <t>9425801217</t>
-  </si>
-  <si>
-    <t>sub ld</t>
+    <t>MR2608/0317</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Udaypura- Tendukheda line ckt-II</t>
+  </si>
+  <si>
+    <t>F/o Polymer String replacement work at Loc.No.116</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>under review</t>
+  </si>
+  <si>
+    <t>ok, line to be in service</t>
+  </si>
+  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>220KV_Mehgaon-Auraiya ckt s/d is approved</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 26.08.2026</t>
-  </si>
-  <si>
-    <t>400KV-BINA-MP-BINA-1</t>
-  </si>
-  <si>
-    <t>26-Aug-2026</t>
-  </si>
-  <si>
-    <t>1.For Autoreclose relay retroffiting  (Main &amp; Tie Bay) with Dia Open
-2. For Line terminal AMP work</t>
+    <t>khema power consent required, through sub ld</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 27.08.2026</t>
+  </si>
+  <si>
+    <t>400KV-SEONI-KIRNAPUR-1</t>
+  </si>
+  <si>
+    <t>27-Aug-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-DATIA-1</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>deferred</t>
   </si>
   <si>
     <t>220KV-MEHGAON-AURIYA-1</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+    <t>220KV-ANNUPUR-KOTMIKALA-2</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-2</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>132KV-SHEOPUR-KHANDAR-1</t>
+  </si>
+  <si>
+    <t>WR</t>
   </si>
   <si>
     <t>S/I SLDC JABALPUR</t>
-  </si>
-  <si>
-    <t>WR</t>
   </si>
 </sst>
 </file>
@@ -346,7 +470,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -359,29 +483,25 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="26"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -415,7 +535,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -540,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,21 +686,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,17 +703,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,11 +722,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -995,61 +1094,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="54.140625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="51.5703125" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="49.42578125" customWidth="1"/>
+    <col min="8" max="8" width="44.7109375" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="44.140625" customWidth="1"/>
+    <col min="13" max="13" width="37.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="1"/>
+      <c r="E2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1062,7 +1161,7 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1072,7 +1171,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="42" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1085,7 +1184,7 @@
       <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1103,26 +1202,26 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="K4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="16"/>
+      <c r="L4" s="11"/>
       <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="26.25" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46259.624502314815</v>
+        <v>46260.548402777778</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1147,132 +1246,134 @@
         <v>25</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="26.25" customHeight="1">
       <c r="A6" s="4">
         <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46259.618055555555</v>
+        <v>46260.550937499997</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="26.25" customHeight="1">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A16" si="0">A6+1</f>
+        <f t="shared" ref="A7:A27" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>46259.443715277775</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="26.25" customHeight="1">
       <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46259.612523148149</v>
+        <v>46260.596296296295</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="L8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="M8" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="26.25" customHeight="1">
       <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1281,40 +1382,40 @@
         <v>46259.688067129631</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="26.25" customHeight="1">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1323,311 +1424,717 @@
         <v>46259.690046296295</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>58</v>
+        <v>32</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="L10" s="8" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="26.25" customHeight="1">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46239.682071759256</v>
+        <v>46260.635046296295</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>61</v>
+        <v>48</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="26.25" customHeight="1">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46259.612037037034</v>
+        <v>46260.636493055557</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="11" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="26.25" customHeight="1">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46252.611527777779</v>
+        <v>46260.552442129629</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>75</v>
+        <v>65</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="23">
-        <v>46259.651493055557</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>46259.517685185187</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="26.25" customHeight="1">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="J15" s="30">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="30">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="B15" s="5">
+        <v>46260.688460648147</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29" t="s">
+      <c r="B16" s="5">
+        <v>46252.611527777779</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A17" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46260.491307870368</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="I17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A18" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46260.492847222224</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="28"/>
-      <c r="H16" s="21" t="s">
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" s="29" t="s">
+      <c r="L18" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A19" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46260.48709490741</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K16" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M16" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="32" t="s">
+      <c r="K19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
+      <c r="M19" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A20" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46260.639166666668</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A21" s="16">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="17">
+        <v>46260.602777777778</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L22" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="16">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="16">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="16">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,20 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$10</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$9</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,42 +87,21 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2608/0287</t>
+    <t>MR2608/0313</t>
   </si>
   <si>
     <t>Continuous</t>
   </si>
   <si>
-    <t>220KV_220 kV Bhopal-Shujalpur Ckt I &amp; II</t>
-  </si>
-  <si>
-    <t>400KV_BHOPAL4</t>
+    <t>220KV_220 kv Tikamgarh-Chhatarpur line</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>Stringing work</t>
-  </si>
-  <si>
-    <t>26-08-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>28-08-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Ankit Mehroliya</t>
-  </si>
-  <si>
-    <t>9425804506</t>
-  </si>
-  <si>
-    <t>220KV_220 kv Tikamgarh-Chhatarpur line</t>
-  </si>
-  <si>
-    <t>220KV_CHATARPUR</t>
-  </si>
-  <si>
     <t>installation of ERS and tower errection below line</t>
   </si>
   <si>
@@ -127,9 +117,6 @@
     <t>9406713326</t>
   </si>
   <si>
-    <t>MR2608/0315</t>
-  </si>
-  <si>
     <t>MR2608/0318</t>
   </si>
   <si>
@@ -187,79 +174,73 @@
     <t>9425807264</t>
   </si>
   <si>
-    <t>MR2608/0322</t>
-  </si>
-  <si>
-    <t>220KV_220KV Mehgaon Aurraiya line</t>
-  </si>
-  <si>
-    <t>220KV_MEHGAON</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Insulator replace &amp; Other Maintenanace work</t>
-  </si>
-  <si>
-    <t>28-08-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Baidyanath Kumar</t>
-  </si>
-  <si>
-    <t>6265588473</t>
+    <t>MR2608/0327</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Mungaliya Chhap - Sehore line</t>
+  </si>
+  <si>
+    <t>220KV_MUGALIYACHAAP</t>
+  </si>
+  <si>
+    <t>construction activities</t>
+  </si>
+  <si>
+    <t>29-08-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>29-08-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>S S thakur</t>
+  </si>
+  <si>
+    <t>9425804603</t>
   </si>
   <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>220KV Malanpur Aurraiya s/d is approved</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 28.08.2026</t>
-  </si>
-  <si>
-    <t>400KV/220KV INDORE-ICT-2</t>
-  </si>
-  <si>
-    <t>28-Aug-2026</t>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>BHOPAL-BDTCL - 400KV - BUS 1</t>
+  </si>
+  <si>
+    <t>220KV-MALANPUR-AURIYA-1</t>
+  </si>
+  <si>
+    <t>29-Aug-2026</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>ICT AMP WORK</t>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> for carrying out AMP and isolator clamp-connector tightness work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>220KV-PANDURNA-KALMESHWAR-1</t>
-  </si>
-  <si>
-    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
-  </si>
-  <si>
-    <t>real time</t>
-  </si>
-  <si>
-    <t>220KV-MALANPUR-AURIYA-1</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
-  </si>
-  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>S/I SLDC JABALPUR</t>
+    <t>IndiGrid</t>
+  </si>
+  <si>
+    <t>MP_SLDC</t>
   </si>
 </sst>
 </file>
@@ -304,13 +285,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -318,14 +292,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,12 +321,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,73 +439,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,8 +548,8 @@
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>605333</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3335</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>555785</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -895,504 +882,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="51.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="40.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="49.42578125" customWidth="1"/>
-    <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="40.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="7"/>
+    <col min="2" max="2" width="11.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="11" style="7" customWidth="1"/>
+    <col min="5" max="5" width="42.42578125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="49.42578125" style="25" customWidth="1"/>
+    <col min="9" max="10" width="11.42578125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="41" style="25" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+    <row r="1" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>46262</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="13" t="s">
+      <c r="B2" s="8">
+        <v>46263</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="9" t="